--- a/Realistic_ER_Estimate/ER_Summary.xlsx
+++ b/Realistic_ER_Estimate/ER_Summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mihirbendre/Documents/Gazelle/Gazelle_2026/Kenya_Project/Agricentric_SOC_Modeling/Realistic_ER_Estimate/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C0943E-5CC2-AC45-9703-A7DD89D39690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{079945BD-A94D-0E46-9BFA-DF8D58CB2920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" activeTab="2" xr2:uid="{72AD1D35-862B-EB40-AF7A-21135E5EFD45}"/>
   </bookViews>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="52">
   <si>
     <t>Nth</t>
   </si>
@@ -220,6 +220,9 @@
   <si>
     <t>Napier - ERs (tCO2e/ha)</t>
   </si>
+  <si>
+    <t>Conservative Buffer (20% buffer + 20% model uncertainty-deduction + 10% other updates):</t>
+  </si>
 </sst>
 </file>
 
@@ -333,7 +336,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -350,6 +353,8 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -580,124 +585,124 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="40"/>
                 <c:pt idx="0">
-                  <c:v>1703061.8842301555</c:v>
+                  <c:v>821584.90334901295</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>909379.45805196755</c:v>
+                  <c:v>439102.27272334381</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>581358.85233733943</c:v>
+                  <c:v>281025.89568057278</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>405124.11958168616</c:v>
+                  <c:v>196094.14731331487</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>307572.59402394621</c:v>
+                  <c:v>149079.05322744849</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>251329.57856731428</c:v>
+                  <c:v>121969.80607606156</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>217014.63355997927</c:v>
+                  <c:v>105426.99848537613</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>194490.71406657202</c:v>
+                  <c:v>94565.621342954968</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>178424.54884188162</c:v>
+                  <c:v>86815.617806178256</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>165996.40351509218</c:v>
+                  <c:v>80818.214935822019</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>155707.12209237207</c:v>
+                  <c:v>75851.031860754927</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>146753.25838435226</c:v>
+                  <c:v>71526.95140630292</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>138698.71362276727</c:v>
+                  <c:v>67635.879475738519</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>131301.84780213729</c:v>
+                  <c:v>64061.428399597622</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>124424.33016052275</c:v>
+                  <c:v>60736.991188713255</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>117983.03021858906</c:v>
+                  <c:v>57622.557538888817</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>111924.59419714739</c:v>
+                  <c:v>54692.462213103536</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>106211.9863813343</c:v>
+                  <c:v>51928.89948980209</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>100817.34491334268</c:v>
+                  <c:v>49318.480611395004</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>95718.172215576895</c:v>
+                  <c:v>46850.398221670672</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>90895.288042336702</c:v>
+                  <c:v>44515.440218805874</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>86331.715552191046</c:v>
+                  <c:v>42305.453222623684</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>82012.062408180369</c:v>
+                  <c:v>40213.044580948837</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>77922.165541748182</c:v>
+                  <c:v>38231.411418136682</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>74048.877265620715</c:v>
+                  <c:v>36354.237781756718</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>70379.927987972085</c:v>
+                  <c:v>34575.628686041055</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>66903.831180462774</c:v>
+                  <c:v>32890.064501069988</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>63609.812314750452</c:v>
+                  <c:v>31292.366877145072</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>60487.751975332554</c:v>
+                  <c:v>29777.671486732157</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>57528.137853182983</c:v>
+                  <c:v>28341.405033236544</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>54722.02271054357</c:v>
+                  <c:v>26979.265125554244</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>52060.986677162618</c:v>
+                  <c:v>25687.202229242059</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>49537.102918374585</c:v>
+                  <c:v>24461.403232800763</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>47142.906083183727</c:v>
+                  <c:v>23298.276344703554</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>44871.363141826369</c:v>
+                  <c:v>22194.437133741587</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>42715.846336037146</c:v>
+                  <c:v>21146.695579998177</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>40670.10803099574</c:v>
+                  <c:v>20152.044035386793</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>38728.257298469791</c:v>
+                  <c:v>19207.646012163597</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>36884.738087138234</c:v>
+                  <c:v>18310.825730527624</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>35134.308854222501</c:v>
+                  <c:v>17459.058365121538</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2279,124 +2284,124 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="40"/>
                 <c:pt idx="0">
-                  <c:v>445879.02935889084</c:v>
+                  <c:v>385462.42088076117</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>233944.23285077335</c:v>
+                  <c:v>202244.78929949357</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>146358.61197190915</c:v>
+                  <c:v>126527.02004971547</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>99338.419933995916</c:v>
+                  <c:v>85878.064032939481</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>73350.690147965259</c:v>
+                  <c:v>63411.671632915975</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>58409.57462133708</c:v>
+                  <c:v>50495.07726014591</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>49337.029780273231</c:v>
+                  <c:v>42651.862245046214</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>43424.371414480527</c:v>
+                  <c:v>37540.369087818421</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>39246.082476200289</c:v>
+                  <c:v>33928.238300675148</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>36048.004350171024</c:v>
+                  <c:v>31163.499760722858</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>33428.703445477724</c:v>
+                  <c:v>28899.114128615496</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>31172.594226910951</c:v>
+                  <c:v>26948.707709164519</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>29162.255478156829</c:v>
+                  <c:v>25210.769860866581</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>27332.265305845256</c:v>
+                  <c:v>23628.743356903222</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>25644.861469344843</c:v>
+                  <c:v>22169.982740248615</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>24077.092891597324</c:v>
+                  <c:v>20814.646804785887</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>22614.027431293842</c:v>
+                  <c:v>19549.826714353527</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>21245.153857786834</c:v>
+                  <c:v>18366.435510056719</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>19962.46964245506</c:v>
+                  <c:v>17257.555005902399</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>18759.459175170097</c:v>
+                  <c:v>16217.552456934549</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>17630.542809778308</c:v>
+                  <c:v>15241.604259053349</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>16570.775298477311</c:v>
+                  <c:v>14325.435245533636</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>15575.676695813205</c:v>
+                  <c:v>13465.172503530517</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>14641.133959223729</c:v>
+                  <c:v>12657.260307748915</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>13763.340576437413</c:v>
+                  <c:v>11898.407928330145</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>12938.756914317193</c:v>
+                  <c:v>11185.555352427215</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>12164.082098323282</c:v>
+                  <c:v>10515.848974000479</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>11436.232520002264</c:v>
+                  <c:v>9886.6230135419592</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>10752.324338510973</c:v>
+                  <c:v>9295.3843906427355</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>10109.658543984497</c:v>
+                  <c:v>8739.7998112745972</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>9505.7077891888257</c:v>
+                  <c:v>8217.6843837537417</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>8938.1045363726644</c:v>
+                  <c:v>7726.9913716941683</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>8404.6302492476661</c:v>
+                  <c:v>7265.802850474608</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>7903.2054596060716</c:v>
+                  <c:v>6832.3211198294493</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>7431.880592938749</c:v>
+                  <c:v>6424.860772595549</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>6988.8274689356977</c:v>
+                  <c:v>6041.8413468949102</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>6572.3314112335784</c:v>
+                  <c:v>5681.7805050114284</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>6180.7839124915054</c:v>
+                  <c:v>5343.2876923489066</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>5812.6758087305207</c:v>
+                  <c:v>5025.0582366475355</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>5466.5909223573517</c:v>
+                  <c:v>4725.8678523779299</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2827,124 +2832,124 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="40"/>
                 <c:pt idx="0">
-                  <c:v>1702619.4492301554</c:v>
+                  <c:v>821101.42037601292</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>908937.0230519675</c:v>
+                  <c:v>438618.78975034383</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>580916.41733733937</c:v>
+                  <c:v>280542.4127075728</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>404681.68458168616</c:v>
+                  <c:v>195610.66434031486</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>307130.15902394621</c:v>
+                  <c:v>148595.57025444848</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>250887.14356731428</c:v>
+                  <c:v>121486.32310306156</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>216572.19855997927</c:v>
+                  <c:v>104943.51551237612</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>194048.27906657202</c:v>
+                  <c:v>94082.138369954962</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>177982.11384188163</c:v>
+                  <c:v>86332.13483317825</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>165553.96851509219</c:v>
+                  <c:v>80334.731962822014</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>155264.68709237207</c:v>
+                  <c:v>75367.548887754921</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>146310.82338435226</c:v>
+                  <c:v>71043.468433302914</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>138256.27862276728</c:v>
+                  <c:v>67152.396502738513</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>130859.41280213727</c:v>
+                  <c:v>63577.945426597624</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>123981.89516052275</c:v>
+                  <c:v>60253.508215713257</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>117540.59521858906</c:v>
+                  <c:v>57139.074565888819</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>111482.1591971474</c:v>
+                  <c:v>54208.979240103537</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>105769.5513813343</c:v>
+                  <c:v>51445.416516802092</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>100374.90991334268</c:v>
+                  <c:v>48834.997638395005</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>95275.737215576897</c:v>
+                  <c:v>46366.915248670673</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>90452.853042336705</c:v>
+                  <c:v>44031.957245805876</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>85889.280552191049</c:v>
+                  <c:v>41821.970249623686</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>81569.627408180371</c:v>
+                  <c:v>39729.561607948839</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>77479.730541748184</c:v>
+                  <c:v>37747.928445136684</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>73606.442265620717</c:v>
+                  <c:v>35870.754808756719</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>69937.492987972088</c:v>
+                  <c:v>34092.145713041056</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>66461.396180462776</c:v>
+                  <c:v>32406.58152806999</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>63167.377314750454</c:v>
+                  <c:v>30808.883904145074</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>60045.316975332556</c:v>
+                  <c:v>29294.188513732159</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>57085.702853182986</c:v>
+                  <c:v>27857.922060236546</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>54279.587710543572</c:v>
+                  <c:v>26495.782152554246</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>51618.551677162621</c:v>
+                  <c:v>25203.719256242061</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>49094.667918374587</c:v>
+                  <c:v>23977.920259800765</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>46700.471083183729</c:v>
+                  <c:v>22814.793371703556</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>44428.928141826371</c:v>
+                  <c:v>21710.954160741589</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>42273.411336037148</c:v>
+                  <c:v>20663.212606998179</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>40227.673030995742</c:v>
+                  <c:v>19668.561062386794</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>38285.822298469793</c:v>
+                  <c:v>18724.163039163599</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>36442.303087138236</c:v>
+                  <c:v>17827.342757527626</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>34691.873854222504</c:v>
+                  <c:v>16975.57539212154</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3360,124 +3365,124 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="40"/>
                 <c:pt idx="0">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>442.435</c:v>
+                  <c:v>483.48297300000007</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3882,124 +3887,124 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="40"/>
                 <c:pt idx="0">
-                  <c:v>1702619.4492301554</c:v>
+                  <c:v>821101.42037601292</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2611556.4722821228</c:v>
+                  <c:v>1259720.2101263567</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3192472.8896194622</c:v>
+                  <c:v>1540262.6228339295</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3597154.5742011485</c:v>
+                  <c:v>1735873.2871742444</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3904284.7332250946</c:v>
+                  <c:v>1884468.8574286927</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4155171.876792409</c:v>
+                  <c:v>2005955.1805317546</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4371744.0753523875</c:v>
+                  <c:v>2110898.6960441307</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4565792.3544189595</c:v>
+                  <c:v>2204980.8344140854</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4743774.4682608414</c:v>
+                  <c:v>2291312.9692472639</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>4909328.436775934</c:v>
+                  <c:v>2371647.7012100858</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3361973.6746381507</c:v>
+                  <c:v>1625913.8297218278</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2599347.4749705354</c:v>
+                  <c:v>1258338.5084047869</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2156687.3362559634</c:v>
+                  <c:v>1044948.4921999525</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1882865.0644764144</c:v>
+                  <c:v>912915.77328623529</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1699716.800612991</c:v>
+                  <c:v>824573.71124750015</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1566370.2522642657</c:v>
+                  <c:v>760226.46271032747</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1461280.2129014339</c:v>
+                  <c:v>709491.92643805488</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1373001.4852161962</c:v>
+                  <c:v>666855.20458490192</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1295394.2812876573</c:v>
+                  <c:v>629358.06739011873</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1225116.049988142</c:v>
+                  <c:v>595390.25067596731</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1160304.2159381066</c:v>
+                  <c:v>564054.65903401829</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1099882.6731059453</c:v>
+                  <c:v>534833.1608503391</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1043196.0218913585</c:v>
+                  <c:v>507410.32595554943</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>989816.33963096945</c:v>
+                  <c:v>481580.30897408846</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>939440.88673606736</c:v>
+                  <c:v>457197.55556713196</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>891837.78450545028</c:v>
+                  <c:v>434150.62671428418</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>846817.02148876584</c:v>
+                  <c:v>412348.22900225065</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>804214.84742218186</c:v>
+                  <c:v>391711.69638959365</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>763885.25448417175</c:v>
+                  <c:v>372170.88726493082</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>725695.22012177785</c:v>
+                  <c:v>353661.89407649665</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>689521.95478998474</c:v>
+                  <c:v>336125.71898324502</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>655251.22591495642</c:v>
+                  <c:v>319507.46798986342</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>622776.26642515056</c:v>
+                  <c:v>303755.82664171531</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>591997.00696658611</c:v>
+                  <c:v>288822.69156828214</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>562819.49284279172</c:v>
+                  <c:v>274662.89092026703</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>535155.41119085671</c:v>
+                  <c:v>261233.95781422418</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>508921.6880413898</c:v>
+                  <c:v>248495.93734854099</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>484040.13302510913</c:v>
+                  <c:v>236411.21648355952</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>460437.11913691479</c:v>
+                  <c:v>224944.37072735498</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>438043.29013795435</c:v>
+                  <c:v>214062.02405923998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4162,124 +4167,124 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="40"/>
                 <c:pt idx="0">
-                  <c:v>1702619.4492301554</c:v>
+                  <c:v>821101.42037601292</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2611556.4722821228</c:v>
+                  <c:v>1259720.2101263567</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3192472.8896194622</c:v>
+                  <c:v>1540262.6228339295</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3597154.5742011485</c:v>
+                  <c:v>1735873.2871742444</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3904284.7332250946</c:v>
+                  <c:v>1884468.8574286927</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4155171.876792409</c:v>
+                  <c:v>2005955.1805317546</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4371744.0753523875</c:v>
+                  <c:v>2110898.6960441307</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4565792.3544189595</c:v>
+                  <c:v>2204980.8344140854</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4743774.4682608414</c:v>
+                  <c:v>2291312.9692472639</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>4909328.436775934</c:v>
+                  <c:v>2371647.7012100858</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3361973.6746381507</c:v>
+                  <c:v>1625913.8297218278</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2599347.4749705354</c:v>
+                  <c:v>1258338.5084047869</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2156687.3362559634</c:v>
+                  <c:v>1044948.4921999525</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1882865.0644764144</c:v>
+                  <c:v>912915.77328623529</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1699716.800612991</c:v>
+                  <c:v>824573.71124750015</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1566370.2522642657</c:v>
+                  <c:v>760226.46271032747</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1461280.2129014339</c:v>
+                  <c:v>709491.92643805488</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1373001.4852161962</c:v>
+                  <c:v>666855.20458490192</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1295394.2812876573</c:v>
+                  <c:v>629358.06739011873</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1225116.049988142</c:v>
+                  <c:v>595390.25067596731</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1160304.2159381066</c:v>
+                  <c:v>564054.65903401829</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1099882.6731059453</c:v>
+                  <c:v>534833.1608503391</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1043196.0218913585</c:v>
+                  <c:v>507410.32595554943</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>989816.33963096945</c:v>
+                  <c:v>481580.30897408846</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>939440.88673606736</c:v>
+                  <c:v>457197.55556713196</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>891837.78450545028</c:v>
+                  <c:v>434150.62671428418</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>846817.02148876584</c:v>
+                  <c:v>412348.22900225065</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>804214.84742218186</c:v>
+                  <c:v>391711.69638959365</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>763885.25448417175</c:v>
+                  <c:v>372170.88726493082</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>725695.22012177785</c:v>
+                  <c:v>353661.89407649665</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>689521.95478998474</c:v>
+                  <c:v>336125.71898324502</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>655251.22591495642</c:v>
+                  <c:v>319507.46798986342</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>622776.26642515056</c:v>
+                  <c:v>303755.82664171531</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>591997.00696658611</c:v>
+                  <c:v>288822.69156828214</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>562819.49284279172</c:v>
+                  <c:v>274662.89092026703</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>535155.41119085671</c:v>
+                  <c:v>261233.95781422418</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>508921.6880413898</c:v>
+                  <c:v>248495.93734854099</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>484040.13302510913</c:v>
+                  <c:v>236411.21648355952</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>460437.11913691479</c:v>
+                  <c:v>224944.37072735498</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>438043.29013795435</c:v>
+                  <c:v>214062.02405923998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4433,124 +4438,124 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="40"/>
                 <c:pt idx="0">
-                  <c:v>1702619.4492301554</c:v>
+                  <c:v>821101.42037601292</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2611556.4722821228</c:v>
+                  <c:v>1259720.2101263567</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3192472.8896194622</c:v>
+                  <c:v>1540262.6228339295</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3597154.5742011485</c:v>
+                  <c:v>1735873.2871742444</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3904284.7332250946</c:v>
+                  <c:v>1884468.8574286927</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4155171.876792409</c:v>
+                  <c:v>2005955.1805317546</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4371744.0753523875</c:v>
+                  <c:v>2110898.6960441307</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4565792.3544189595</c:v>
+                  <c:v>2204980.8344140854</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4743774.4682608414</c:v>
+                  <c:v>2291312.9692472639</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>4909328.436775934</c:v>
+                  <c:v>2371647.7012100858</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3361973.6746381507</c:v>
+                  <c:v>1625913.8297218278</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2599347.4749705354</c:v>
+                  <c:v>1258338.5084047869</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2156687.3362559634</c:v>
+                  <c:v>1044948.4921999525</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1882865.0644764144</c:v>
+                  <c:v>912915.77328623529</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1699716.800612991</c:v>
+                  <c:v>824573.71124750015</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1566370.2522642657</c:v>
+                  <c:v>760226.46271032747</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1461280.2129014339</c:v>
+                  <c:v>709491.92643805488</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1373001.4852161962</c:v>
+                  <c:v>666855.20458490192</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1295394.2812876573</c:v>
+                  <c:v>629358.06739011873</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1225116.049988142</c:v>
+                  <c:v>595390.25067596731</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1160304.2159381066</c:v>
+                  <c:v>564054.65903401829</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1099882.6731059453</c:v>
+                  <c:v>534833.1608503391</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1043196.0218913585</c:v>
+                  <c:v>507410.32595554943</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>989816.33963096945</c:v>
+                  <c:v>481580.30897408846</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>939440.88673606736</c:v>
+                  <c:v>457197.55556713196</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>891837.78450545028</c:v>
+                  <c:v>434150.62671428418</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>846817.02148876584</c:v>
+                  <c:v>412348.22900225065</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>804214.84742218186</c:v>
+                  <c:v>391711.69638959365</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>763885.25448417175</c:v>
+                  <c:v>372170.88726493082</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>725695.22012177785</c:v>
+                  <c:v>353661.89407649665</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>689521.95478998474</c:v>
+                  <c:v>336125.71898324502</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>655251.22591495642</c:v>
+                  <c:v>319507.46798986342</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>622776.26642515056</c:v>
+                  <c:v>303755.82664171531</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>591997.00696658611</c:v>
+                  <c:v>288822.69156828214</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>562819.49284279172</c:v>
+                  <c:v>274662.89092026703</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>535155.41119085671</c:v>
+                  <c:v>261233.95781422418</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>508921.6880413898</c:v>
+                  <c:v>248495.93734854099</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>484040.13302510913</c:v>
+                  <c:v>236411.21648355952</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>460437.11913691479</c:v>
+                  <c:v>224944.37072735498</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>438043.29013795435</c:v>
+                  <c:v>214062.02405923998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4713,124 +4718,124 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="40"/>
                 <c:pt idx="0">
-                  <c:v>1702619.4492301554</c:v>
+                  <c:v>821101.42037601292</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2611556.4722821228</c:v>
+                  <c:v>1259720.2101263567</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3192472.8896194622</c:v>
+                  <c:v>1540262.6228339295</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3597154.5742011485</c:v>
+                  <c:v>1735873.2871742444</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3904284.7332250946</c:v>
+                  <c:v>1884468.8574286927</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4155171.876792409</c:v>
+                  <c:v>2005955.1805317546</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4371744.0753523875</c:v>
+                  <c:v>2110898.6960441307</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4565792.3544189595</c:v>
+                  <c:v>2204980.8344140854</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4743774.4682608414</c:v>
+                  <c:v>2291312.9692472639</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>4909328.436775934</c:v>
+                  <c:v>2371647.7012100858</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3361973.6746381507</c:v>
+                  <c:v>1625913.8297218278</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2599347.4749705354</c:v>
+                  <c:v>1258338.5084047869</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2156687.3362559634</c:v>
+                  <c:v>1044948.4921999525</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1882865.0644764144</c:v>
+                  <c:v>912915.77328623529</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1699716.800612991</c:v>
+                  <c:v>824573.71124750015</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1566370.2522642657</c:v>
+                  <c:v>760226.46271032747</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1461280.2129014339</c:v>
+                  <c:v>709491.92643805488</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1373001.4852161962</c:v>
+                  <c:v>666855.20458490192</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1295394.2812876573</c:v>
+                  <c:v>629358.06739011873</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1225116.049988142</c:v>
+                  <c:v>595390.25067596731</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1160304.2159381066</c:v>
+                  <c:v>564054.65903401829</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1099882.6731059453</c:v>
+                  <c:v>534833.1608503391</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1043196.0218913585</c:v>
+                  <c:v>507410.32595554943</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>989816.33963096945</c:v>
+                  <c:v>481580.30897408846</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>939440.88673606736</c:v>
+                  <c:v>457197.55556713196</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>891837.78450545028</c:v>
+                  <c:v>434150.62671428418</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>846817.02148876584</c:v>
+                  <c:v>412348.22900225065</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>804214.84742218186</c:v>
+                  <c:v>391711.69638959365</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>763885.25448417175</c:v>
+                  <c:v>372170.88726493082</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>725695.22012177785</c:v>
+                  <c:v>353661.89407649665</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>689521.95478998474</c:v>
+                  <c:v>336125.71898324502</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>655251.22591495642</c:v>
+                  <c:v>319507.46798986342</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>622776.26642515056</c:v>
+                  <c:v>303755.82664171531</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>591997.00696658611</c:v>
+                  <c:v>288822.69156828214</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>562819.49284279172</c:v>
+                  <c:v>274662.89092026703</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>535155.41119085671</c:v>
+                  <c:v>261233.95781422418</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>508921.6880413898</c:v>
+                  <c:v>248495.93734854099</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>484040.13302510913</c:v>
+                  <c:v>236411.21648355952</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>460437.11913691479</c:v>
+                  <c:v>224944.37072735498</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>438043.29013795435</c:v>
+                  <c:v>214062.02405923998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7789,15 +7794,15 @@
       </c>
       <c r="B3" s="1" cm="1">
         <f t="array" ref="B3:B42">Summary_Removals!H6:H45</f>
-        <v>1702619.4492301554</v>
+        <v>821101.42037601292</v>
       </c>
       <c r="C3">
         <f>Summary_Reductions!H8</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E3" s="5">
         <f>SUM(B3:C3)</f>
-        <v>1703061.8842301555</v>
+        <v>821584.90334901295</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -7805,15 +7810,15 @@
         <v>2027</v>
       </c>
       <c r="B4" s="1">
-        <v>908937.0230519675</v>
+        <v>438618.78975034383</v>
       </c>
       <c r="C4">
         <f>Summary_Reductions!H9</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E4" s="5">
         <f t="shared" ref="E4:E42" si="0">SUM(B4:C4)</f>
-        <v>909379.45805196755</v>
+        <v>439102.27272334381</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -7821,15 +7826,15 @@
         <v>2028</v>
       </c>
       <c r="B5" s="1">
-        <v>580916.41733733937</v>
+        <v>280542.4127075728</v>
       </c>
       <c r="C5">
         <f>Summary_Reductions!H10</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E5" s="5">
         <f t="shared" si="0"/>
-        <v>581358.85233733943</v>
+        <v>281025.89568057278</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -7837,15 +7842,15 @@
         <v>2029</v>
       </c>
       <c r="B6" s="1">
-        <v>404681.68458168616</v>
+        <v>195610.66434031486</v>
       </c>
       <c r="C6">
         <f>Summary_Reductions!H11</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E6" s="5">
         <f t="shared" si="0"/>
-        <v>405124.11958168616</v>
+        <v>196094.14731331487</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -7853,15 +7858,15 @@
         <v>2030</v>
       </c>
       <c r="B7" s="1">
-        <v>307130.15902394621</v>
+        <v>148595.57025444848</v>
       </c>
       <c r="C7">
         <f>Summary_Reductions!H12</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E7" s="5">
         <f t="shared" si="0"/>
-        <v>307572.59402394621</v>
+        <v>149079.05322744849</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -7869,15 +7874,15 @@
         <v>2031</v>
       </c>
       <c r="B8" s="1">
-        <v>250887.14356731428</v>
+        <v>121486.32310306156</v>
       </c>
       <c r="C8">
         <f>Summary_Reductions!H13</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E8" s="5">
         <f t="shared" si="0"/>
-        <v>251329.57856731428</v>
+        <v>121969.80607606156</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -7885,15 +7890,15 @@
         <v>2032</v>
       </c>
       <c r="B9" s="1">
-        <v>216572.19855997927</v>
+        <v>104943.51551237612</v>
       </c>
       <c r="C9">
         <f>Summary_Reductions!H14</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E9" s="5">
         <f t="shared" si="0"/>
-        <v>217014.63355997927</v>
+        <v>105426.99848537613</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -7901,15 +7906,15 @@
         <v>2033</v>
       </c>
       <c r="B10" s="1">
-        <v>194048.27906657202</v>
+        <v>94082.138369954962</v>
       </c>
       <c r="C10">
         <f>Summary_Reductions!H15</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E10" s="5">
         <f t="shared" si="0"/>
-        <v>194490.71406657202</v>
+        <v>94565.621342954968</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -7917,15 +7922,15 @@
         <v>2034</v>
       </c>
       <c r="B11" s="1">
-        <v>177982.11384188163</v>
+        <v>86332.13483317825</v>
       </c>
       <c r="C11">
         <f>Summary_Reductions!H16</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E11" s="5">
         <f t="shared" si="0"/>
-        <v>178424.54884188162</v>
+        <v>86815.617806178256</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -7933,15 +7938,15 @@
         <v>2035</v>
       </c>
       <c r="B12" s="1">
-        <v>165553.96851509219</v>
+        <v>80334.731962822014</v>
       </c>
       <c r="C12">
         <f>Summary_Reductions!H17</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E12" s="5">
         <f t="shared" si="0"/>
-        <v>165996.40351509218</v>
+        <v>80818.214935822019</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -7949,15 +7954,15 @@
         <v>2036</v>
       </c>
       <c r="B13" s="1">
-        <v>155264.68709237207</v>
+        <v>75367.548887754921</v>
       </c>
       <c r="C13">
         <f>Summary_Reductions!H18</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E13" s="5">
         <f t="shared" si="0"/>
-        <v>155707.12209237207</v>
+        <v>75851.031860754927</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -7965,15 +7970,15 @@
         <v>2037</v>
       </c>
       <c r="B14" s="1">
-        <v>146310.82338435226</v>
+        <v>71043.468433302914</v>
       </c>
       <c r="C14">
         <f>Summary_Reductions!H19</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E14" s="5">
         <f>SUM(B14:C14)</f>
-        <v>146753.25838435226</v>
+        <v>71526.95140630292</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -7981,15 +7986,15 @@
         <v>2038</v>
       </c>
       <c r="B15" s="1">
-        <v>138256.27862276728</v>
+        <v>67152.396502738513</v>
       </c>
       <c r="C15">
         <f>Summary_Reductions!H20</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E15" s="5">
         <f t="shared" si="0"/>
-        <v>138698.71362276727</v>
+        <v>67635.879475738519</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -7997,15 +8002,15 @@
         <v>2039</v>
       </c>
       <c r="B16" s="1">
-        <v>130859.41280213727</v>
+        <v>63577.945426597624</v>
       </c>
       <c r="C16">
         <f>Summary_Reductions!H21</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E16" s="5">
         <f t="shared" si="0"/>
-        <v>131301.84780213729</v>
+        <v>64061.428399597622</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -8013,15 +8018,15 @@
         <v>2040</v>
       </c>
       <c r="B17" s="1">
-        <v>123981.89516052275</v>
+        <v>60253.508215713257</v>
       </c>
       <c r="C17">
         <f>Summary_Reductions!H22</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E17" s="5">
         <f t="shared" si="0"/>
-        <v>124424.33016052275</v>
+        <v>60736.991188713255</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -8029,15 +8034,15 @@
         <v>2041</v>
       </c>
       <c r="B18" s="1">
-        <v>117540.59521858906</v>
+        <v>57139.074565888819</v>
       </c>
       <c r="C18">
         <f>Summary_Reductions!H23</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E18" s="5">
         <f t="shared" si="0"/>
-        <v>117983.03021858906</v>
+        <v>57622.557538888817</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -8045,15 +8050,15 @@
         <v>2042</v>
       </c>
       <c r="B19" s="1">
-        <v>111482.1591971474</v>
+        <v>54208.979240103537</v>
       </c>
       <c r="C19">
         <f>Summary_Reductions!H24</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E19" s="5">
         <f t="shared" si="0"/>
-        <v>111924.59419714739</v>
+        <v>54692.462213103536</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -8061,15 +8066,15 @@
         <v>2043</v>
       </c>
       <c r="B20" s="1">
-        <v>105769.5513813343</v>
+        <v>51445.416516802092</v>
       </c>
       <c r="C20">
         <f>Summary_Reductions!H25</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E20" s="5">
         <f t="shared" si="0"/>
-        <v>106211.9863813343</v>
+        <v>51928.89948980209</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -8077,15 +8082,15 @@
         <v>2044</v>
       </c>
       <c r="B21" s="1">
-        <v>100374.90991334268</v>
+        <v>48834.997638395005</v>
       </c>
       <c r="C21">
         <f>Summary_Reductions!H26</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E21" s="5">
         <f t="shared" si="0"/>
-        <v>100817.34491334268</v>
+        <v>49318.480611395004</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -8093,15 +8098,15 @@
         <v>2045</v>
       </c>
       <c r="B22" s="1">
-        <v>95275.737215576897</v>
+        <v>46366.915248670673</v>
       </c>
       <c r="C22">
         <f>Summary_Reductions!H27</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E22" s="5">
         <f t="shared" si="0"/>
-        <v>95718.172215576895</v>
+        <v>46850.398221670672</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -8109,15 +8114,15 @@
         <v>2046</v>
       </c>
       <c r="B23" s="1">
-        <v>90452.853042336705</v>
+        <v>44031.957245805876</v>
       </c>
       <c r="C23">
         <f>Summary_Reductions!H28</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E23" s="5">
         <f t="shared" si="0"/>
-        <v>90895.288042336702</v>
+        <v>44515.440218805874</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -8125,15 +8130,15 @@
         <v>2047</v>
       </c>
       <c r="B24" s="1">
-        <v>85889.280552191049</v>
+        <v>41821.970249623686</v>
       </c>
       <c r="C24">
         <f>Summary_Reductions!H29</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E24" s="5">
         <f t="shared" si="0"/>
-        <v>86331.715552191046</v>
+        <v>42305.453222623684</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -8141,15 +8146,15 @@
         <v>2048</v>
       </c>
       <c r="B25" s="1">
-        <v>81569.627408180371</v>
+        <v>39729.561607948839</v>
       </c>
       <c r="C25">
         <f>Summary_Reductions!H30</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E25" s="5">
         <f t="shared" si="0"/>
-        <v>82012.062408180369</v>
+        <v>40213.044580948837</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -8157,15 +8162,15 @@
         <v>2049</v>
       </c>
       <c r="B26" s="1">
-        <v>77479.730541748184</v>
+        <v>37747.928445136684</v>
       </c>
       <c r="C26">
         <f>Summary_Reductions!H31</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E26" s="5">
         <f t="shared" si="0"/>
-        <v>77922.165541748182</v>
+        <v>38231.411418136682</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -8173,15 +8178,15 @@
         <v>2050</v>
       </c>
       <c r="B27" s="1">
-        <v>73606.442265620717</v>
+        <v>35870.754808756719</v>
       </c>
       <c r="C27">
         <f>Summary_Reductions!H32</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E27" s="5">
         <f t="shared" si="0"/>
-        <v>74048.877265620715</v>
+        <v>36354.237781756718</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -8189,15 +8194,15 @@
         <v>2051</v>
       </c>
       <c r="B28" s="1">
-        <v>69937.492987972088</v>
+        <v>34092.145713041056</v>
       </c>
       <c r="C28">
         <f>Summary_Reductions!H33</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E28" s="5">
         <f t="shared" si="0"/>
-        <v>70379.927987972085</v>
+        <v>34575.628686041055</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -8205,15 +8210,15 @@
         <v>2052</v>
       </c>
       <c r="B29" s="1">
-        <v>66461.396180462776</v>
+        <v>32406.58152806999</v>
       </c>
       <c r="C29">
         <f>Summary_Reductions!H34</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E29" s="5">
         <f t="shared" si="0"/>
-        <v>66903.831180462774</v>
+        <v>32890.064501069988</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -8221,15 +8226,15 @@
         <v>2053</v>
       </c>
       <c r="B30" s="1">
-        <v>63167.377314750454</v>
+        <v>30808.883904145074</v>
       </c>
       <c r="C30">
         <f>Summary_Reductions!H35</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E30" s="5">
         <f t="shared" si="0"/>
-        <v>63609.812314750452</v>
+        <v>31292.366877145072</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -8237,15 +8242,15 @@
         <v>2054</v>
       </c>
       <c r="B31" s="1">
-        <v>60045.316975332556</v>
+        <v>29294.188513732159</v>
       </c>
       <c r="C31">
         <f>Summary_Reductions!H36</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E31" s="5">
         <f t="shared" si="0"/>
-        <v>60487.751975332554</v>
+        <v>29777.671486732157</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -8253,15 +8258,15 @@
         <v>2055</v>
       </c>
       <c r="B32" s="1">
-        <v>57085.702853182986</v>
+        <v>27857.922060236546</v>
       </c>
       <c r="C32">
         <f>Summary_Reductions!H37</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E32" s="5">
         <f t="shared" si="0"/>
-        <v>57528.137853182983</v>
+        <v>28341.405033236544</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -8269,15 +8274,15 @@
         <v>2056</v>
       </c>
       <c r="B33" s="1">
-        <v>54279.587710543572</v>
+        <v>26495.782152554246</v>
       </c>
       <c r="C33">
         <f>Summary_Reductions!H38</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E33" s="5">
         <f t="shared" si="0"/>
-        <v>54722.02271054357</v>
+        <v>26979.265125554244</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -8285,15 +8290,15 @@
         <v>2057</v>
       </c>
       <c r="B34" s="1">
-        <v>51618.551677162621</v>
+        <v>25203.719256242061</v>
       </c>
       <c r="C34">
         <f>Summary_Reductions!H39</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E34" s="5">
         <f t="shared" si="0"/>
-        <v>52060.986677162618</v>
+        <v>25687.202229242059</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -8301,15 +8306,15 @@
         <v>2058</v>
       </c>
       <c r="B35" s="1">
-        <v>49094.667918374587</v>
+        <v>23977.920259800765</v>
       </c>
       <c r="C35">
         <f>Summary_Reductions!H40</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E35" s="5">
         <f t="shared" si="0"/>
-        <v>49537.102918374585</v>
+        <v>24461.403232800763</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -8317,15 +8322,15 @@
         <v>2059</v>
       </c>
       <c r="B36" s="1">
-        <v>46700.471083183729</v>
+        <v>22814.793371703556</v>
       </c>
       <c r="C36">
         <f>Summary_Reductions!H41</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E36" s="5">
         <f t="shared" si="0"/>
-        <v>47142.906083183727</v>
+        <v>23298.276344703554</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -8333,15 +8338,15 @@
         <v>2060</v>
       </c>
       <c r="B37" s="1">
-        <v>44428.928141826371</v>
+        <v>21710.954160741589</v>
       </c>
       <c r="C37">
         <f>Summary_Reductions!H42</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E37" s="5">
         <f t="shared" si="0"/>
-        <v>44871.363141826369</v>
+        <v>22194.437133741587</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -8349,15 +8354,15 @@
         <v>2061</v>
       </c>
       <c r="B38" s="1">
-        <v>42273.411336037148</v>
+        <v>20663.212606998179</v>
       </c>
       <c r="C38">
         <f>Summary_Reductions!H43</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E38" s="5">
         <f t="shared" si="0"/>
-        <v>42715.846336037146</v>
+        <v>21146.695579998177</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -8365,15 +8370,15 @@
         <v>2062</v>
       </c>
       <c r="B39" s="1">
-        <v>40227.673030995742</v>
+        <v>19668.561062386794</v>
       </c>
       <c r="C39">
         <f>Summary_Reductions!H44</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E39" s="5">
         <f t="shared" si="0"/>
-        <v>40670.10803099574</v>
+        <v>20152.044035386793</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -8381,15 +8386,15 @@
         <v>2063</v>
       </c>
       <c r="B40" s="1">
-        <v>38285.822298469793</v>
+        <v>18724.163039163599</v>
       </c>
       <c r="C40">
         <f>Summary_Reductions!H45</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E40" s="5">
         <f t="shared" si="0"/>
-        <v>38728.257298469791</v>
+        <v>19207.646012163597</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -8397,15 +8402,15 @@
         <v>2064</v>
       </c>
       <c r="B41" s="1">
-        <v>36442.303087138236</v>
+        <v>17827.342757527626</v>
       </c>
       <c r="C41">
         <f>Summary_Reductions!H46</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E41" s="5">
         <f t="shared" si="0"/>
-        <v>36884.738087138234</v>
+        <v>18310.825730527624</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -8413,21 +8418,21 @@
         <v>2065</v>
       </c>
       <c r="B42" s="1">
-        <v>34691.873854222504</v>
+        <v>16975.57539212154</v>
       </c>
       <c r="C42">
         <f>Summary_Reductions!H47</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
       <c r="E42" s="5">
         <f t="shared" si="0"/>
-        <v>35134.308854222501</v>
+        <v>17459.058365121538</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="E44" s="5">
         <f>SUM(E3:E42)</f>
-        <v>7315880.3970238063</v>
+        <v>3554101.1889417893</v>
       </c>
     </row>
   </sheetData>
@@ -8455,7 +8460,10 @@
   <sheetData>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>51</v>
+      </c>
+      <c r="G3" s="12">
+        <v>0.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -8503,11 +8511,11 @@
       </c>
       <c r="F6" s="1">
         <f>Kipsigis!E3</f>
-        <v>445879.02935889084</v>
+        <v>385462.42088076117</v>
       </c>
       <c r="H6" s="1">
-        <f>SUM(B6:F6)</f>
-        <v>1702619.4492301554</v>
+        <f>SUM(B6:F6)*$G$3</f>
+        <v>821101.42037601292</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -8532,11 +8540,11 @@
       </c>
       <c r="F7" s="1">
         <f>Kipsigis!E4</f>
-        <v>233944.23285077335</v>
+        <v>202244.78929949357</v>
       </c>
       <c r="H7" s="1">
-        <f t="shared" ref="H7:H45" si="0">SUM(B7:F7)</f>
-        <v>908937.0230519675</v>
+        <f t="shared" ref="H7:H45" si="0">SUM(B7:F7)*$G$3</f>
+        <v>438618.78975034383</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -8561,11 +8569,11 @@
       </c>
       <c r="F8" s="1">
         <f>Kipsigis!E5</f>
-        <v>146358.61197190915</v>
+        <v>126527.02004971547</v>
       </c>
       <c r="H8" s="1">
         <f t="shared" si="0"/>
-        <v>580916.41733733937</v>
+        <v>280542.4127075728</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -8590,11 +8598,11 @@
       </c>
       <c r="F9" s="1">
         <f>Kipsigis!E6</f>
-        <v>99338.419933995916</v>
+        <v>85878.064032939481</v>
       </c>
       <c r="H9" s="1">
         <f t="shared" si="0"/>
-        <v>404681.68458168616</v>
+        <v>195610.66434031486</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -8619,11 +8627,11 @@
       </c>
       <c r="F10" s="1">
         <f>Kipsigis!E7</f>
-        <v>73350.690147965259</v>
+        <v>63411.671632915975</v>
       </c>
       <c r="H10" s="1">
         <f t="shared" si="0"/>
-        <v>307130.15902394621</v>
+        <v>148595.57025444848</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -8648,11 +8656,11 @@
       </c>
       <c r="F11" s="1">
         <f>Kipsigis!E8</f>
-        <v>58409.57462133708</v>
+        <v>50495.07726014591</v>
       </c>
       <c r="H11" s="1">
         <f t="shared" si="0"/>
-        <v>250887.14356731428</v>
+        <v>121486.32310306156</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -8677,11 +8685,11 @@
       </c>
       <c r="F12" s="1">
         <f>Kipsigis!E9</f>
-        <v>49337.029780273231</v>
+        <v>42651.862245046214</v>
       </c>
       <c r="H12" s="1">
         <f t="shared" si="0"/>
-        <v>216572.19855997927</v>
+        <v>104943.51551237612</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -8706,11 +8714,11 @@
       </c>
       <c r="F13" s="1">
         <f>Kipsigis!E10</f>
-        <v>43424.371414480527</v>
+        <v>37540.369087818421</v>
       </c>
       <c r="H13" s="1">
         <f t="shared" si="0"/>
-        <v>194048.27906657202</v>
+        <v>94082.138369954962</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -8735,11 +8743,11 @@
       </c>
       <c r="F14" s="1">
         <f>Kipsigis!E11</f>
-        <v>39246.082476200289</v>
+        <v>33928.238300675148</v>
       </c>
       <c r="H14" s="1">
         <f t="shared" si="0"/>
-        <v>177982.11384188163</v>
+        <v>86332.13483317825</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -8764,11 +8772,11 @@
       </c>
       <c r="F15" s="1">
         <f>Kipsigis!E12</f>
-        <v>36048.004350171024</v>
+        <v>31163.499760722858</v>
       </c>
       <c r="H15" s="1">
         <f t="shared" si="0"/>
-        <v>165553.96851509219</v>
+        <v>80334.731962822014</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -8793,11 +8801,11 @@
       </c>
       <c r="F16" s="1">
         <f>Kipsigis!E13</f>
-        <v>33428.703445477724</v>
+        <v>28899.114128615496</v>
       </c>
       <c r="H16" s="1">
         <f t="shared" si="0"/>
-        <v>155264.68709237207</v>
+        <v>75367.548887754921</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -8822,11 +8830,11 @@
       </c>
       <c r="F17" s="1">
         <f>Kipsigis!E14</f>
-        <v>31172.594226910951</v>
+        <v>26948.707709164519</v>
       </c>
       <c r="H17" s="1">
         <f t="shared" si="0"/>
-        <v>146310.82338435226</v>
+        <v>71043.468433302914</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -8851,11 +8859,11 @@
       </c>
       <c r="F18" s="1">
         <f>Kipsigis!E15</f>
-        <v>29162.255478156829</v>
+        <v>25210.769860866581</v>
       </c>
       <c r="H18" s="1">
         <f t="shared" si="0"/>
-        <v>138256.27862276728</v>
+        <v>67152.396502738513</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -8880,11 +8888,11 @@
       </c>
       <c r="F19" s="1">
         <f>Kipsigis!E16</f>
-        <v>27332.265305845256</v>
+        <v>23628.743356903222</v>
       </c>
       <c r="H19" s="1">
         <f t="shared" si="0"/>
-        <v>130859.41280213727</v>
+        <v>63577.945426597624</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -8909,11 +8917,11 @@
       </c>
       <c r="F20" s="1">
         <f>Kipsigis!E17</f>
-        <v>25644.861469344843</v>
+        <v>22169.982740248615</v>
       </c>
       <c r="H20" s="1">
         <f t="shared" si="0"/>
-        <v>123981.89516052275</v>
+        <v>60253.508215713257</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -8938,11 +8946,11 @@
       </c>
       <c r="F21" s="1">
         <f>Kipsigis!E18</f>
-        <v>24077.092891597324</v>
+        <v>20814.646804785887</v>
       </c>
       <c r="H21" s="1">
         <f t="shared" si="0"/>
-        <v>117540.59521858906</v>
+        <v>57139.074565888819</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -8967,11 +8975,11 @@
       </c>
       <c r="F22" s="1">
         <f>Kipsigis!E19</f>
-        <v>22614.027431293842</v>
+        <v>19549.826714353527</v>
       </c>
       <c r="H22" s="1">
         <f t="shared" si="0"/>
-        <v>111482.1591971474</v>
+        <v>54208.979240103537</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -8996,11 +9004,11 @@
       </c>
       <c r="F23" s="1">
         <f>Kipsigis!E20</f>
-        <v>21245.153857786834</v>
+        <v>18366.435510056719</v>
       </c>
       <c r="H23" s="1">
         <f t="shared" si="0"/>
-        <v>105769.5513813343</v>
+        <v>51445.416516802092</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -9025,11 +9033,11 @@
       </c>
       <c r="F24" s="1">
         <f>Kipsigis!E21</f>
-        <v>19962.46964245506</v>
+        <v>17257.555005902399</v>
       </c>
       <c r="H24" s="1">
         <f t="shared" si="0"/>
-        <v>100374.90991334268</v>
+        <v>48834.997638395005</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -9054,11 +9062,11 @@
       </c>
       <c r="F25" s="1">
         <f>Kipsigis!E22</f>
-        <v>18759.459175170097</v>
+        <v>16217.552456934549</v>
       </c>
       <c r="H25" s="1">
         <f t="shared" si="0"/>
-        <v>95275.737215576897</v>
+        <v>46366.915248670673</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -9083,11 +9091,11 @@
       </c>
       <c r="F26" s="1">
         <f>Kipsigis!E23</f>
-        <v>17630.542809778308</v>
+        <v>15241.604259053349</v>
       </c>
       <c r="H26" s="1">
         <f t="shared" si="0"/>
-        <v>90452.853042336705</v>
+        <v>44031.957245805876</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -9112,11 +9120,11 @@
       </c>
       <c r="F27" s="1">
         <f>Kipsigis!E24</f>
-        <v>16570.775298477311</v>
+        <v>14325.435245533636</v>
       </c>
       <c r="H27" s="1">
         <f t="shared" si="0"/>
-        <v>85889.280552191049</v>
+        <v>41821.970249623686</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -9141,11 +9149,11 @@
       </c>
       <c r="F28" s="1">
         <f>Kipsigis!E25</f>
-        <v>15575.676695813205</v>
+        <v>13465.172503530517</v>
       </c>
       <c r="H28" s="1">
         <f t="shared" si="0"/>
-        <v>81569.627408180371</v>
+        <v>39729.561607948839</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -9170,11 +9178,11 @@
       </c>
       <c r="F29" s="1">
         <f>Kipsigis!E26</f>
-        <v>14641.133959223729</v>
+        <v>12657.260307748915</v>
       </c>
       <c r="H29" s="1">
         <f t="shared" si="0"/>
-        <v>77479.730541748184</v>
+        <v>37747.928445136684</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -9199,11 +9207,11 @@
       </c>
       <c r="F30" s="1">
         <f>Kipsigis!E27</f>
-        <v>13763.340576437413</v>
+        <v>11898.407928330145</v>
       </c>
       <c r="H30" s="1">
         <f t="shared" si="0"/>
-        <v>73606.442265620717</v>
+        <v>35870.754808756719</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -9228,11 +9236,11 @@
       </c>
       <c r="F31" s="1">
         <f>Kipsigis!E28</f>
-        <v>12938.756914317193</v>
+        <v>11185.555352427215</v>
       </c>
       <c r="H31" s="1">
         <f t="shared" si="0"/>
-        <v>69937.492987972088</v>
+        <v>34092.145713041056</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -9257,11 +9265,11 @@
       </c>
       <c r="F32" s="1">
         <f>Kipsigis!E29</f>
-        <v>12164.082098323282</v>
+        <v>10515.848974000479</v>
       </c>
       <c r="H32" s="1">
         <f t="shared" si="0"/>
-        <v>66461.396180462776</v>
+        <v>32406.58152806999</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -9286,11 +9294,11 @@
       </c>
       <c r="F33" s="1">
         <f>Kipsigis!E30</f>
-        <v>11436.232520002264</v>
+        <v>9886.6230135419592</v>
       </c>
       <c r="H33" s="1">
         <f t="shared" si="0"/>
-        <v>63167.377314750454</v>
+        <v>30808.883904145074</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -9315,11 +9323,11 @@
       </c>
       <c r="F34" s="1">
         <f>Kipsigis!E31</f>
-        <v>10752.324338510973</v>
+        <v>9295.3843906427355</v>
       </c>
       <c r="H34" s="1">
         <f t="shared" si="0"/>
-        <v>60045.316975332556</v>
+        <v>29294.188513732159</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -9344,11 +9352,11 @@
       </c>
       <c r="F35" s="1">
         <f>Kipsigis!E32</f>
-        <v>10109.658543984497</v>
+        <v>8739.7998112745972</v>
       </c>
       <c r="H35" s="1">
         <f t="shared" si="0"/>
-        <v>57085.702853182986</v>
+        <v>27857.922060236546</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -9373,11 +9381,11 @@
       </c>
       <c r="F36" s="1">
         <f>Kipsigis!E33</f>
-        <v>9505.7077891888257</v>
+        <v>8217.6843837537417</v>
       </c>
       <c r="H36" s="1">
         <f t="shared" si="0"/>
-        <v>54279.587710543572</v>
+        <v>26495.782152554246</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -9402,11 +9410,11 @@
       </c>
       <c r="F37" s="1">
         <f>Kipsigis!E34</f>
-        <v>8938.1045363726644</v>
+        <v>7726.9913716941683</v>
       </c>
       <c r="H37" s="1">
         <f t="shared" si="0"/>
-        <v>51618.551677162621</v>
+        <v>25203.719256242061</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -9431,11 +9439,11 @@
       </c>
       <c r="F38" s="1">
         <f>Kipsigis!E35</f>
-        <v>8404.6302492476661</v>
+        <v>7265.802850474608</v>
       </c>
       <c r="H38" s="1">
         <f t="shared" si="0"/>
-        <v>49094.667918374587</v>
+        <v>23977.920259800765</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -9460,11 +9468,11 @@
       </c>
       <c r="F39" s="1">
         <f>Kipsigis!E36</f>
-        <v>7903.2054596060716</v>
+        <v>6832.3211198294493</v>
       </c>
       <c r="H39" s="1">
         <f t="shared" si="0"/>
-        <v>46700.471083183729</v>
+        <v>22814.793371703556</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -9489,11 +9497,11 @@
       </c>
       <c r="F40" s="1">
         <f>Kipsigis!E37</f>
-        <v>7431.880592938749</v>
+        <v>6424.860772595549</v>
       </c>
       <c r="H40" s="1">
         <f t="shared" si="0"/>
-        <v>44428.928141826371</v>
+        <v>21710.954160741589</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -9518,11 +9526,11 @@
       </c>
       <c r="F41" s="1">
         <f>Kipsigis!E38</f>
-        <v>6988.8274689356977</v>
+        <v>6041.8413468949102</v>
       </c>
       <c r="H41" s="1">
         <f t="shared" si="0"/>
-        <v>42273.411336037148</v>
+        <v>20663.212606998179</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -9547,11 +9555,11 @@
       </c>
       <c r="F42" s="1">
         <f>Kipsigis!E39</f>
-        <v>6572.3314112335784</v>
+        <v>5681.7805050114284</v>
       </c>
       <c r="H42" s="1">
         <f t="shared" si="0"/>
-        <v>40227.673030995742</v>
+        <v>19668.561062386794</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -9576,11 +9584,11 @@
       </c>
       <c r="F43" s="1">
         <f>Kipsigis!E40</f>
-        <v>6180.7839124915054</v>
+        <v>5343.2876923489066</v>
       </c>
       <c r="H43" s="1">
         <f t="shared" si="0"/>
-        <v>38285.822298469793</v>
+        <v>18724.163039163599</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -9605,11 +9613,11 @@
       </c>
       <c r="F44" s="1">
         <f>Kipsigis!E41</f>
-        <v>5812.6758087305207</v>
+        <v>5025.0582366475355</v>
       </c>
       <c r="H44" s="1">
         <f t="shared" si="0"/>
-        <v>36442.303087138236</v>
+        <v>17827.342757527626</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -9634,11 +9642,11 @@
       </c>
       <c r="F45" s="1">
         <f>Kipsigis!E42</f>
-        <v>5466.5909223573517</v>
+        <v>4725.8678523779299</v>
       </c>
       <c r="H45" s="1">
         <f t="shared" si="0"/>
-        <v>34691.873854222504</v>
+        <v>16975.57539212154</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -9647,7 +9655,7 @@
       </c>
       <c r="H47" s="1">
         <f>SUM(H6:H45)</f>
-        <v>7298182.9970238097</v>
+        <v>3534761.8700217889</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -9656,13 +9664,13 @@
       </c>
       <c r="H48" s="1">
         <f>H47/40</f>
-        <v>182454.57492559525</v>
+        <v>88369.046750544716</v>
       </c>
     </row>
     <row r="49" spans="7:8">
       <c r="H49" s="1">
         <f>H48/35000</f>
-        <v>5.2129878550170075</v>
+        <v>2.5248299071584204</v>
       </c>
     </row>
     <row r="50" spans="7:8">
@@ -9671,7 +9679,7 @@
       </c>
       <c r="H50" s="1">
         <f>AVERAGE(H6:H15)</f>
-        <v>490932.84367759351</v>
+        <v>237164.77012100857</v>
       </c>
     </row>
   </sheetData>
@@ -9682,13 +9690,30 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8796C41C-1BC9-EA45-B875-C5F0B93D7AE5}">
-  <dimension ref="A2:H47"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:8">
+      <c r="B1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>2</v>
@@ -9700,7 +9725,7 @@
         <v>4636</v>
       </c>
       <c r="D2">
-        <v>1310</v>
+        <v>5120</v>
       </c>
       <c r="E2">
         <v>15358</v>
@@ -9714,19 +9739,19 @@
         <v>22</v>
       </c>
       <c r="B3">
-        <v>0.03</v>
+        <v>3.2894E-2</v>
       </c>
       <c r="C3">
-        <v>0.1</v>
+        <v>9.6970000000000001E-2</v>
       </c>
       <c r="D3">
-        <v>0.03</v>
+        <v>2.5499999999999998E-2</v>
       </c>
       <c r="E3">
-        <v>0.01</v>
+        <v>9.3810000000000004E-3</v>
       </c>
       <c r="F3">
-        <v>0.01</v>
+        <v>1.0175E-2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -9764,27 +9789,27 @@
       </c>
       <c r="B8">
         <f>B$3*B$2</f>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C8">
-        <f t="shared" ref="C8:F23" si="0">C$3*C$2</f>
-        <v>463.6</v>
+        <f t="shared" ref="C8:F27" si="0">C$3*C$2</f>
+        <v>449.55292000000003</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F8">
         <f>F$3*F$2</f>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H8">
         <f>SUM(B8:F8) * 0.5</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -9792,28 +9817,28 @@
         <v>2027</v>
       </c>
       <c r="B9">
-        <f t="shared" ref="B9:F24" si="1">B$3*B$2</f>
-        <v>131.60999999999999</v>
+        <f t="shared" ref="B9:F28" si="1">B$3*B$2</f>
+        <v>144.30597800000001</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F9">
         <f t="shared" si="0"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H9">
         <f t="shared" ref="H9:H47" si="2">SUM(B9:F9) * 0.5</f>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -9822,27 +9847,27 @@
       </c>
       <c r="B10">
         <f t="shared" si="1"/>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F10">
         <f t="shared" si="0"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H10">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -9851,27 +9876,27 @@
       </c>
       <c r="B11">
         <f t="shared" si="1"/>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E11">
         <f t="shared" si="0"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F11">
         <f t="shared" si="0"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H11">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -9880,27 +9905,27 @@
       </c>
       <c r="B12">
         <f t="shared" si="1"/>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E12">
         <f t="shared" si="0"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F12">
         <f t="shared" si="0"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H12">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -9909,27 +9934,27 @@
       </c>
       <c r="B13">
         <f t="shared" si="1"/>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F13">
         <f t="shared" si="0"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H13">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -9938,27 +9963,27 @@
       </c>
       <c r="B14">
         <f t="shared" si="1"/>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F14">
         <f t="shared" si="0"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H14">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -9967,27 +9992,27 @@
       </c>
       <c r="B15">
         <f t="shared" si="1"/>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D15">
         <f t="shared" si="0"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E15">
         <f t="shared" si="0"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F15">
         <f t="shared" si="0"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H15">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -9996,27 +10021,27 @@
       </c>
       <c r="B16">
         <f t="shared" si="1"/>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D16">
         <f t="shared" si="0"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E16">
         <f t="shared" si="0"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F16">
         <f t="shared" si="0"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H16">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -10025,27 +10050,27 @@
       </c>
       <c r="B17">
         <f t="shared" si="1"/>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D17">
         <f t="shared" si="0"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E17">
         <f t="shared" si="0"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F17">
         <f t="shared" si="0"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H17">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -10054,27 +10079,27 @@
       </c>
       <c r="B18">
         <f t="shared" si="1"/>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C18">
         <f t="shared" si="0"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D18">
         <f t="shared" si="0"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E18">
         <f t="shared" si="0"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F18">
         <f t="shared" si="0"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H18">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -10083,27 +10108,27 @@
       </c>
       <c r="B19">
         <f t="shared" si="1"/>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C19">
         <f t="shared" si="0"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D19">
         <f t="shared" si="0"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E19">
         <f t="shared" si="0"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F19">
         <f t="shared" si="0"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H19">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -10112,27 +10137,27 @@
       </c>
       <c r="B20">
         <f t="shared" si="1"/>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C20">
         <f t="shared" si="0"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D20">
         <f t="shared" si="0"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E20">
         <f t="shared" si="0"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F20">
         <f t="shared" si="0"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H20">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -10141,27 +10166,27 @@
       </c>
       <c r="B21">
         <f t="shared" si="1"/>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C21">
         <f t="shared" si="0"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D21">
         <f t="shared" si="0"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E21">
         <f t="shared" si="0"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F21">
         <f t="shared" si="0"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H21">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -10170,27 +10195,27 @@
       </c>
       <c r="B22">
         <f t="shared" si="1"/>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C22">
         <f t="shared" si="0"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D22">
         <f t="shared" si="0"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E22">
         <f t="shared" si="0"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F22">
         <f t="shared" si="0"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H22">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -10199,27 +10224,27 @@
       </c>
       <c r="B23">
         <f t="shared" si="1"/>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C23">
         <f t="shared" si="0"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D23">
         <f t="shared" si="0"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E23">
         <f t="shared" si="0"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F23">
         <f t="shared" si="0"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H23">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -10228,27 +10253,27 @@
       </c>
       <c r="B24">
         <f t="shared" si="1"/>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C24">
         <f t="shared" si="1"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D24">
         <f t="shared" si="1"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E24">
         <f t="shared" si="1"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F24">
         <f t="shared" si="1"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H24">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -10256,28 +10281,28 @@
         <v>2043</v>
       </c>
       <c r="B25">
-        <f t="shared" ref="B25:F47" si="3">B$3*B$2</f>
-        <v>131.60999999999999</v>
+        <f t="shared" ref="B25:F51" si="3">B$3*B$2</f>
+        <v>144.30597800000001</v>
       </c>
       <c r="C25">
         <f t="shared" si="3"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D25">
         <f t="shared" si="3"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E25">
         <f t="shared" si="3"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F25">
         <f t="shared" si="3"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H25">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -10286,27 +10311,27 @@
       </c>
       <c r="B26">
         <f t="shared" si="3"/>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C26">
         <f t="shared" si="3"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D26">
         <f t="shared" si="3"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E26">
         <f t="shared" si="3"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F26">
         <f t="shared" si="3"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H26">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -10315,27 +10340,27 @@
       </c>
       <c r="B27">
         <f t="shared" si="3"/>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C27">
         <f t="shared" si="3"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D27">
         <f t="shared" si="3"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E27">
         <f t="shared" si="3"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F27">
         <f t="shared" si="3"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H27">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -10344,27 +10369,27 @@
       </c>
       <c r="B28">
         <f t="shared" si="3"/>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C28">
         <f t="shared" si="3"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D28">
         <f t="shared" si="3"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E28">
         <f t="shared" si="3"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F28">
         <f t="shared" si="3"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H28">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -10373,27 +10398,27 @@
       </c>
       <c r="B29">
         <f t="shared" si="3"/>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C29">
         <f t="shared" si="3"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D29">
         <f t="shared" si="3"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E29">
         <f t="shared" si="3"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F29">
         <f t="shared" si="3"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H29">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -10402,27 +10427,27 @@
       </c>
       <c r="B30">
         <f t="shared" si="3"/>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C30">
         <f t="shared" si="3"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D30">
         <f t="shared" si="3"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E30">
         <f t="shared" si="3"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F30">
         <f t="shared" si="3"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H30">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -10431,27 +10456,27 @@
       </c>
       <c r="B31">
         <f t="shared" si="3"/>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C31">
         <f t="shared" si="3"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D31">
         <f t="shared" si="3"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E31">
         <f t="shared" si="3"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F31">
         <f t="shared" si="3"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H31">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -10460,27 +10485,27 @@
       </c>
       <c r="B32">
         <f t="shared" si="3"/>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C32">
         <f t="shared" si="3"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D32">
         <f t="shared" si="3"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E32">
         <f t="shared" si="3"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F32">
         <f t="shared" si="3"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H32">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -10489,27 +10514,27 @@
       </c>
       <c r="B33">
         <f t="shared" si="3"/>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C33">
         <f t="shared" si="3"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D33">
         <f t="shared" si="3"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E33">
         <f t="shared" si="3"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F33">
         <f t="shared" si="3"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H33">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -10518,27 +10543,27 @@
       </c>
       <c r="B34">
         <f t="shared" si="3"/>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C34">
         <f t="shared" si="3"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D34">
         <f t="shared" si="3"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E34">
         <f t="shared" si="3"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F34">
         <f t="shared" si="3"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H34">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -10547,27 +10572,27 @@
       </c>
       <c r="B35">
         <f t="shared" si="3"/>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C35">
         <f t="shared" si="3"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D35">
         <f t="shared" si="3"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E35">
         <f t="shared" si="3"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F35">
         <f t="shared" si="3"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H35">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -10576,27 +10601,27 @@
       </c>
       <c r="B36">
         <f t="shared" si="3"/>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C36">
         <f t="shared" si="3"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D36">
         <f t="shared" si="3"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E36">
         <f t="shared" si="3"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F36">
         <f t="shared" si="3"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H36">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -10605,27 +10630,27 @@
       </c>
       <c r="B37">
         <f t="shared" si="3"/>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C37">
         <f t="shared" si="3"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D37">
         <f t="shared" si="3"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E37">
         <f t="shared" si="3"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F37">
         <f t="shared" si="3"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H37">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -10634,27 +10659,27 @@
       </c>
       <c r="B38">
         <f t="shared" si="3"/>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C38">
         <f t="shared" si="3"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D38">
         <f t="shared" si="3"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E38">
         <f t="shared" si="3"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F38">
         <f t="shared" si="3"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H38">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -10663,27 +10688,27 @@
       </c>
       <c r="B39">
         <f t="shared" si="3"/>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C39">
         <f t="shared" si="3"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D39">
         <f t="shared" si="3"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E39">
         <f t="shared" si="3"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F39">
         <f t="shared" si="3"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H39">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -10692,27 +10717,27 @@
       </c>
       <c r="B40">
         <f t="shared" si="3"/>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C40">
         <f t="shared" si="3"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D40">
         <f t="shared" si="3"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E40">
         <f t="shared" si="3"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F40">
         <f t="shared" si="3"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H40">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -10721,27 +10746,27 @@
       </c>
       <c r="B41">
         <f t="shared" si="3"/>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C41">
         <f t="shared" si="3"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D41">
         <f t="shared" si="3"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E41">
         <f t="shared" si="3"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F41">
         <f t="shared" si="3"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H41">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -10750,27 +10775,27 @@
       </c>
       <c r="B42">
         <f t="shared" si="3"/>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C42">
         <f t="shared" si="3"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D42">
         <f t="shared" si="3"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E42">
         <f t="shared" si="3"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F42">
         <f t="shared" si="3"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H42">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -10779,27 +10804,27 @@
       </c>
       <c r="B43">
         <f t="shared" si="3"/>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C43">
         <f t="shared" si="3"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D43">
         <f t="shared" si="3"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E43">
         <f t="shared" si="3"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F43">
         <f t="shared" si="3"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H43">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -10808,27 +10833,27 @@
       </c>
       <c r="B44">
         <f t="shared" si="3"/>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C44">
         <f t="shared" si="3"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D44">
         <f t="shared" si="3"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E44">
         <f t="shared" si="3"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F44">
         <f t="shared" si="3"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H44">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -10837,27 +10862,27 @@
       </c>
       <c r="B45">
         <f t="shared" si="3"/>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C45">
         <f t="shared" si="3"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D45">
         <f t="shared" si="3"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E45">
         <f t="shared" si="3"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F45">
         <f t="shared" si="3"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H45">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -10866,27 +10891,27 @@
       </c>
       <c r="B46">
         <f t="shared" si="3"/>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C46">
         <f t="shared" si="3"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D46">
         <f t="shared" si="3"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E46">
         <f t="shared" si="3"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F46">
         <f t="shared" si="3"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H46">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -10895,27 +10920,27 @@
       </c>
       <c r="B47">
         <f t="shared" si="3"/>
-        <v>131.60999999999999</v>
+        <v>144.30597800000001</v>
       </c>
       <c r="C47">
         <f t="shared" si="3"/>
-        <v>463.6</v>
+        <v>449.55292000000003</v>
       </c>
       <c r="D47">
         <f t="shared" si="3"/>
-        <v>39.299999999999997</v>
+        <v>130.56</v>
       </c>
       <c r="E47">
         <f t="shared" si="3"/>
-        <v>153.58000000000001</v>
+        <v>144.073398</v>
       </c>
       <c r="F47">
         <f t="shared" si="3"/>
-        <v>96.78</v>
+        <v>98.473650000000006</v>
       </c>
       <c r="H47">
         <f t="shared" si="2"/>
-        <v>442.435</v>
+        <v>483.48297300000007</v>
       </c>
     </row>
   </sheetData>
@@ -10981,11 +11006,11 @@
       </c>
       <c r="B3" s="1">
         <f>Summary_Removals!$H6</f>
-        <v>1702619.4492301554</v>
+        <v>821101.42037601292</v>
       </c>
       <c r="L3" s="5">
         <f>SUM(B3:K3)</f>
-        <v>1702619.4492301554</v>
+        <v>821101.42037601292</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -10994,15 +11019,15 @@
       </c>
       <c r="B4" s="1">
         <f>Summary_Removals!$H7</f>
-        <v>908937.0230519675</v>
+        <v>438618.78975034383</v>
       </c>
       <c r="C4" s="1">
         <f>Summary_Removals!$H6</f>
-        <v>1702619.4492301554</v>
+        <v>821101.42037601292</v>
       </c>
       <c r="L4" s="5">
         <f t="shared" ref="L4:L42" si="0">SUM(B4:K4)</f>
-        <v>2611556.4722821228</v>
+        <v>1259720.2101263567</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -11011,19 +11036,19 @@
       </c>
       <c r="B5" s="1">
         <f>Summary_Removals!$H8</f>
-        <v>580916.41733733937</v>
+        <v>280542.4127075728</v>
       </c>
       <c r="C5" s="1">
         <f>Summary_Removals!$H7</f>
-        <v>908937.0230519675</v>
+        <v>438618.78975034383</v>
       </c>
       <c r="D5" s="6">
         <f>Summary_Removals!$H6</f>
-        <v>1702619.4492301554</v>
+        <v>821101.42037601292</v>
       </c>
       <c r="L5" s="5">
         <f t="shared" si="0"/>
-        <v>3192472.8896194622</v>
+        <v>1540262.6228339295</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -11032,23 +11057,23 @@
       </c>
       <c r="B6" s="1">
         <f>Summary_Removals!$H9</f>
-        <v>404681.68458168616</v>
+        <v>195610.66434031486</v>
       </c>
       <c r="C6" s="1">
         <f>Summary_Removals!$H8</f>
-        <v>580916.41733733937</v>
+        <v>280542.4127075728</v>
       </c>
       <c r="D6" s="6">
         <f>Summary_Removals!$H7</f>
-        <v>908937.0230519675</v>
+        <v>438618.78975034383</v>
       </c>
       <c r="E6" s="6">
         <f>Summary_Removals!$H6</f>
-        <v>1702619.4492301554</v>
+        <v>821101.42037601292</v>
       </c>
       <c r="L6" s="5">
         <f t="shared" si="0"/>
-        <v>3597154.5742011485</v>
+        <v>1735873.2871742444</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -11057,27 +11082,27 @@
       </c>
       <c r="B7" s="1">
         <f>Summary_Removals!$H10</f>
-        <v>307130.15902394621</v>
+        <v>148595.57025444848</v>
       </c>
       <c r="C7" s="1">
         <f>Summary_Removals!$H9</f>
-        <v>404681.68458168616</v>
+        <v>195610.66434031486</v>
       </c>
       <c r="D7" s="6">
         <f>Summary_Removals!$H8</f>
-        <v>580916.41733733937</v>
+        <v>280542.4127075728</v>
       </c>
       <c r="E7" s="6">
         <f>Summary_Removals!$H7</f>
-        <v>908937.0230519675</v>
+        <v>438618.78975034383</v>
       </c>
       <c r="F7" s="6">
         <f>Summary_Removals!$H6</f>
-        <v>1702619.4492301554</v>
+        <v>821101.42037601292</v>
       </c>
       <c r="L7" s="5">
         <f t="shared" si="0"/>
-        <v>3904284.7332250946</v>
+        <v>1884468.8574286927</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -11086,31 +11111,31 @@
       </c>
       <c r="B8" s="1">
         <f>Summary_Removals!$H11</f>
-        <v>250887.14356731428</v>
+        <v>121486.32310306156</v>
       </c>
       <c r="C8" s="1">
         <f>Summary_Removals!$H10</f>
-        <v>307130.15902394621</v>
+        <v>148595.57025444848</v>
       </c>
       <c r="D8" s="6">
         <f>Summary_Removals!$H9</f>
-        <v>404681.68458168616</v>
+        <v>195610.66434031486</v>
       </c>
       <c r="E8" s="6">
         <f>Summary_Removals!$H8</f>
-        <v>580916.41733733937</v>
+        <v>280542.4127075728</v>
       </c>
       <c r="F8" s="6">
         <f>Summary_Removals!$H7</f>
-        <v>908937.0230519675</v>
+        <v>438618.78975034383</v>
       </c>
       <c r="G8" s="6">
         <f>Summary_Removals!$H6</f>
-        <v>1702619.4492301554</v>
+        <v>821101.42037601292</v>
       </c>
       <c r="L8" s="5">
         <f t="shared" si="0"/>
-        <v>4155171.876792409</v>
+        <v>2005955.1805317546</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -11119,35 +11144,35 @@
       </c>
       <c r="B9" s="1">
         <f>Summary_Removals!$H12</f>
-        <v>216572.19855997927</v>
+        <v>104943.51551237612</v>
       </c>
       <c r="C9" s="1">
         <f>Summary_Removals!$H11</f>
-        <v>250887.14356731428</v>
+        <v>121486.32310306156</v>
       </c>
       <c r="D9" s="6">
         <f>Summary_Removals!$H10</f>
-        <v>307130.15902394621</v>
+        <v>148595.57025444848</v>
       </c>
       <c r="E9" s="6">
         <f>Summary_Removals!$H9</f>
-        <v>404681.68458168616</v>
+        <v>195610.66434031486</v>
       </c>
       <c r="F9" s="6">
         <f>Summary_Removals!$H8</f>
-        <v>580916.41733733937</v>
+        <v>280542.4127075728</v>
       </c>
       <c r="G9" s="6">
         <f>Summary_Removals!$H7</f>
-        <v>908937.0230519675</v>
+        <v>438618.78975034383</v>
       </c>
       <c r="H9" s="6">
         <f>Summary_Removals!$H6</f>
-        <v>1702619.4492301554</v>
+        <v>821101.42037601292</v>
       </c>
       <c r="L9" s="5">
         <f t="shared" si="0"/>
-        <v>4371744.0753523875</v>
+        <v>2110898.6960441307</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -11156,39 +11181,39 @@
       </c>
       <c r="B10" s="1">
         <f>Summary_Removals!$H13</f>
-        <v>194048.27906657202</v>
+        <v>94082.138369954962</v>
       </c>
       <c r="C10" s="1">
         <f>Summary_Removals!$H12</f>
-        <v>216572.19855997927</v>
+        <v>104943.51551237612</v>
       </c>
       <c r="D10" s="6">
         <f>Summary_Removals!$H11</f>
-        <v>250887.14356731428</v>
+        <v>121486.32310306156</v>
       </c>
       <c r="E10" s="6">
         <f>Summary_Removals!$H10</f>
-        <v>307130.15902394621</v>
+        <v>148595.57025444848</v>
       </c>
       <c r="F10" s="6">
         <f>Summary_Removals!$H9</f>
-        <v>404681.68458168616</v>
+        <v>195610.66434031486</v>
       </c>
       <c r="G10" s="6">
         <f>Summary_Removals!$H8</f>
-        <v>580916.41733733937</v>
+        <v>280542.4127075728</v>
       </c>
       <c r="H10" s="6">
         <f>Summary_Removals!$H7</f>
-        <v>908937.0230519675</v>
+        <v>438618.78975034383</v>
       </c>
       <c r="I10" s="6">
         <f>Summary_Removals!$H6</f>
-        <v>1702619.4492301554</v>
+        <v>821101.42037601292</v>
       </c>
       <c r="L10" s="5">
         <f t="shared" si="0"/>
-        <v>4565792.3544189595</v>
+        <v>2204980.8344140854</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -11197,43 +11222,43 @@
       </c>
       <c r="B11" s="1">
         <f>Summary_Removals!$H14</f>
-        <v>177982.11384188163</v>
+        <v>86332.13483317825</v>
       </c>
       <c r="C11" s="1">
         <f>Summary_Removals!$H13</f>
-        <v>194048.27906657202</v>
+        <v>94082.138369954962</v>
       </c>
       <c r="D11" s="6">
         <f>Summary_Removals!$H12</f>
-        <v>216572.19855997927</v>
+        <v>104943.51551237612</v>
       </c>
       <c r="E11" s="6">
         <f>Summary_Removals!$H11</f>
-        <v>250887.14356731428</v>
+        <v>121486.32310306156</v>
       </c>
       <c r="F11" s="6">
         <f>Summary_Removals!$H10</f>
-        <v>307130.15902394621</v>
+        <v>148595.57025444848</v>
       </c>
       <c r="G11" s="6">
         <f>Summary_Removals!$H9</f>
-        <v>404681.68458168616</v>
+        <v>195610.66434031486</v>
       </c>
       <c r="H11" s="6">
         <f>Summary_Removals!$H8</f>
-        <v>580916.41733733937</v>
+        <v>280542.4127075728</v>
       </c>
       <c r="I11" s="6">
         <f>Summary_Removals!$H7</f>
-        <v>908937.0230519675</v>
+        <v>438618.78975034383</v>
       </c>
       <c r="J11" s="6">
         <f>Summary_Removals!$H6</f>
-        <v>1702619.4492301554</v>
+        <v>821101.42037601292</v>
       </c>
       <c r="L11" s="5">
         <f t="shared" si="0"/>
-        <v>4743774.4682608414</v>
+        <v>2291312.9692472639</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -11242,47 +11267,47 @@
       </c>
       <c r="B12" s="1">
         <f>Summary_Removals!$H15</f>
-        <v>165553.96851509219</v>
+        <v>80334.731962822014</v>
       </c>
       <c r="C12" s="1">
         <f>Summary_Removals!$H14</f>
-        <v>177982.11384188163</v>
+        <v>86332.13483317825</v>
       </c>
       <c r="D12" s="6">
         <f>Summary_Removals!$H13</f>
-        <v>194048.27906657202</v>
+        <v>94082.138369954962</v>
       </c>
       <c r="E12" s="6">
         <f>Summary_Removals!$H12</f>
-        <v>216572.19855997927</v>
+        <v>104943.51551237612</v>
       </c>
       <c r="F12" s="6">
         <f>Summary_Removals!$H11</f>
-        <v>250887.14356731428</v>
+        <v>121486.32310306156</v>
       </c>
       <c r="G12" s="6">
         <f>Summary_Removals!$H10</f>
-        <v>307130.15902394621</v>
+        <v>148595.57025444848</v>
       </c>
       <c r="H12" s="6">
         <f>Summary_Removals!$H9</f>
-        <v>404681.68458168616</v>
+        <v>195610.66434031486</v>
       </c>
       <c r="I12" s="6">
         <f>Summary_Removals!$H8</f>
-        <v>580916.41733733937</v>
+        <v>280542.4127075728</v>
       </c>
       <c r="J12" s="6">
         <f>Summary_Removals!$H7</f>
-        <v>908937.0230519675</v>
+        <v>438618.78975034383</v>
       </c>
       <c r="K12" s="6">
         <f>Summary_Removals!$H6</f>
-        <v>1702619.4492301554</v>
+        <v>821101.42037601292</v>
       </c>
       <c r="L12" s="5">
         <f t="shared" si="0"/>
-        <v>4909328.436775934</v>
+        <v>2371647.7012100858</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -11291,47 +11316,47 @@
       </c>
       <c r="B13" s="1">
         <f>Summary_Removals!$H16</f>
-        <v>155264.68709237207</v>
+        <v>75367.548887754921</v>
       </c>
       <c r="C13" s="1">
         <f>Summary_Removals!$H15</f>
-        <v>165553.96851509219</v>
+        <v>80334.731962822014</v>
       </c>
       <c r="D13" s="6">
         <f>Summary_Removals!$H14</f>
-        <v>177982.11384188163</v>
+        <v>86332.13483317825</v>
       </c>
       <c r="E13" s="6">
         <f>Summary_Removals!$H13</f>
-        <v>194048.27906657202</v>
+        <v>94082.138369954962</v>
       </c>
       <c r="F13" s="6">
         <f>Summary_Removals!$H12</f>
-        <v>216572.19855997927</v>
+        <v>104943.51551237612</v>
       </c>
       <c r="G13" s="6">
         <f>Summary_Removals!$H11</f>
-        <v>250887.14356731428</v>
+        <v>121486.32310306156</v>
       </c>
       <c r="H13" s="6">
         <f>Summary_Removals!$H10</f>
-        <v>307130.15902394621</v>
+        <v>148595.57025444848</v>
       </c>
       <c r="I13" s="6">
         <f>Summary_Removals!$H9</f>
-        <v>404681.68458168616</v>
+        <v>195610.66434031486</v>
       </c>
       <c r="J13" s="6">
         <f>Summary_Removals!$H8</f>
-        <v>580916.41733733937</v>
+        <v>280542.4127075728</v>
       </c>
       <c r="K13" s="6">
         <f>Summary_Removals!$H7</f>
-        <v>908937.0230519675</v>
+        <v>438618.78975034383</v>
       </c>
       <c r="L13" s="5">
         <f>SUM(B13:K13)</f>
-        <v>3361973.6746381507</v>
+        <v>1625913.8297218278</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -11340,47 +11365,47 @@
       </c>
       <c r="B14" s="1">
         <f>Summary_Removals!$H17</f>
-        <v>146310.82338435226</v>
+        <v>71043.468433302914</v>
       </c>
       <c r="C14" s="1">
         <f>Summary_Removals!$H16</f>
-        <v>155264.68709237207</v>
+        <v>75367.548887754921</v>
       </c>
       <c r="D14" s="6">
         <f>Summary_Removals!$H15</f>
-        <v>165553.96851509219</v>
+        <v>80334.731962822014</v>
       </c>
       <c r="E14" s="6">
         <f>Summary_Removals!$H14</f>
-        <v>177982.11384188163</v>
+        <v>86332.13483317825</v>
       </c>
       <c r="F14" s="6">
         <f>Summary_Removals!$H13</f>
-        <v>194048.27906657202</v>
+        <v>94082.138369954962</v>
       </c>
       <c r="G14" s="6">
         <f>Summary_Removals!$H12</f>
-        <v>216572.19855997927</v>
+        <v>104943.51551237612</v>
       </c>
       <c r="H14" s="6">
         <f>Summary_Removals!$H11</f>
-        <v>250887.14356731428</v>
+        <v>121486.32310306156</v>
       </c>
       <c r="I14" s="6">
         <f>Summary_Removals!$H10</f>
-        <v>307130.15902394621</v>
+        <v>148595.57025444848</v>
       </c>
       <c r="J14" s="6">
         <f>Summary_Removals!$H9</f>
-        <v>404681.68458168616</v>
+        <v>195610.66434031486</v>
       </c>
       <c r="K14" s="6">
         <f>Summary_Removals!$H8</f>
-        <v>580916.41733733937</v>
+        <v>280542.4127075728</v>
       </c>
       <c r="L14" s="5">
         <f t="shared" si="0"/>
-        <v>2599347.4749705354</v>
+        <v>1258338.5084047869</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -11389,47 +11414,47 @@
       </c>
       <c r="B15" s="1">
         <f>Summary_Removals!$H18</f>
-        <v>138256.27862276728</v>
+        <v>67152.396502738513</v>
       </c>
       <c r="C15" s="1">
         <f>Summary_Removals!$H17</f>
-        <v>146310.82338435226</v>
+        <v>71043.468433302914</v>
       </c>
       <c r="D15" s="6">
         <f>Summary_Removals!$H16</f>
-        <v>155264.68709237207</v>
+        <v>75367.548887754921</v>
       </c>
       <c r="E15" s="6">
         <f>Summary_Removals!$H15</f>
-        <v>165553.96851509219</v>
+        <v>80334.731962822014</v>
       </c>
       <c r="F15" s="6">
         <f>Summary_Removals!$H14</f>
-        <v>177982.11384188163</v>
+        <v>86332.13483317825</v>
       </c>
       <c r="G15" s="6">
         <f>Summary_Removals!$H13</f>
-        <v>194048.27906657202</v>
+        <v>94082.138369954962</v>
       </c>
       <c r="H15" s="6">
         <f>Summary_Removals!$H12</f>
-        <v>216572.19855997927</v>
+        <v>104943.51551237612</v>
       </c>
       <c r="I15" s="6">
         <f>Summary_Removals!$H11</f>
-        <v>250887.14356731428</v>
+        <v>121486.32310306156</v>
       </c>
       <c r="J15" s="6">
         <f>Summary_Removals!$H10</f>
-        <v>307130.15902394621</v>
+        <v>148595.57025444848</v>
       </c>
       <c r="K15" s="6">
         <f>Summary_Removals!$H9</f>
-        <v>404681.68458168616</v>
+        <v>195610.66434031486</v>
       </c>
       <c r="L15" s="5">
         <f>SUM(B15:K15)</f>
-        <v>2156687.3362559634</v>
+        <v>1044948.4921999525</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -11438,47 +11463,47 @@
       </c>
       <c r="B16" s="1">
         <f>Summary_Removals!$H19</f>
-        <v>130859.41280213727</v>
+        <v>63577.945426597624</v>
       </c>
       <c r="C16" s="1">
         <f>Summary_Removals!$H18</f>
-        <v>138256.27862276728</v>
+        <v>67152.396502738513</v>
       </c>
       <c r="D16" s="6">
         <f>Summary_Removals!$H17</f>
-        <v>146310.82338435226</v>
+        <v>71043.468433302914</v>
       </c>
       <c r="E16" s="6">
         <f>Summary_Removals!$H16</f>
-        <v>155264.68709237207</v>
+        <v>75367.548887754921</v>
       </c>
       <c r="F16" s="6">
         <f>Summary_Removals!$H15</f>
-        <v>165553.96851509219</v>
+        <v>80334.731962822014</v>
       </c>
       <c r="G16" s="6">
         <f>Summary_Removals!$H14</f>
-        <v>177982.11384188163</v>
+        <v>86332.13483317825</v>
       </c>
       <c r="H16" s="6">
         <f>Summary_Removals!$H13</f>
-        <v>194048.27906657202</v>
+        <v>94082.138369954962</v>
       </c>
       <c r="I16" s="6">
         <f>Summary_Removals!$H12</f>
-        <v>216572.19855997927</v>
+        <v>104943.51551237612</v>
       </c>
       <c r="J16" s="6">
         <f>Summary_Removals!$H11</f>
-        <v>250887.14356731428</v>
+        <v>121486.32310306156</v>
       </c>
       <c r="K16" s="6">
         <f>Summary_Removals!$H10</f>
-        <v>307130.15902394621</v>
+        <v>148595.57025444848</v>
       </c>
       <c r="L16" s="5">
         <f t="shared" si="0"/>
-        <v>1882865.0644764144</v>
+        <v>912915.77328623529</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -11487,47 +11512,47 @@
       </c>
       <c r="B17" s="1">
         <f>Summary_Removals!$H20</f>
-        <v>123981.89516052275</v>
+        <v>60253.508215713257</v>
       </c>
       <c r="C17" s="1">
         <f>Summary_Removals!$H19</f>
-        <v>130859.41280213727</v>
+        <v>63577.945426597624</v>
       </c>
       <c r="D17" s="6">
         <f>Summary_Removals!$H18</f>
-        <v>138256.27862276728</v>
+        <v>67152.396502738513</v>
       </c>
       <c r="E17" s="6">
         <f>Summary_Removals!$H17</f>
-        <v>146310.82338435226</v>
+        <v>71043.468433302914</v>
       </c>
       <c r="F17" s="6">
         <f>Summary_Removals!$H16</f>
-        <v>155264.68709237207</v>
+        <v>75367.548887754921</v>
       </c>
       <c r="G17" s="6">
         <f>Summary_Removals!$H15</f>
-        <v>165553.96851509219</v>
+        <v>80334.731962822014</v>
       </c>
       <c r="H17" s="6">
         <f>Summary_Removals!$H14</f>
-        <v>177982.11384188163</v>
+        <v>86332.13483317825</v>
       </c>
       <c r="I17" s="6">
         <f>Summary_Removals!$H13</f>
-        <v>194048.27906657202</v>
+        <v>94082.138369954962</v>
       </c>
       <c r="J17" s="6">
         <f>Summary_Removals!$H12</f>
-        <v>216572.19855997927</v>
+        <v>104943.51551237612</v>
       </c>
       <c r="K17" s="6">
         <f>Summary_Removals!$H11</f>
-        <v>250887.14356731428</v>
+        <v>121486.32310306156</v>
       </c>
       <c r="L17" s="5">
         <f t="shared" si="0"/>
-        <v>1699716.800612991</v>
+        <v>824573.71124750015</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -11536,47 +11561,47 @@
       </c>
       <c r="B18" s="1">
         <f>Summary_Removals!$H21</f>
-        <v>117540.59521858906</v>
+        <v>57139.074565888819</v>
       </c>
       <c r="C18" s="1">
         <f>Summary_Removals!$H20</f>
-        <v>123981.89516052275</v>
+        <v>60253.508215713257</v>
       </c>
       <c r="D18" s="6">
         <f>Summary_Removals!$H19</f>
-        <v>130859.41280213727</v>
+        <v>63577.945426597624</v>
       </c>
       <c r="E18" s="6">
         <f>Summary_Removals!$H18</f>
-        <v>138256.27862276728</v>
+        <v>67152.396502738513</v>
       </c>
       <c r="F18" s="6">
         <f>Summary_Removals!$H17</f>
-        <v>146310.82338435226</v>
+        <v>71043.468433302914</v>
       </c>
       <c r="G18" s="6">
         <f>Summary_Removals!$H16</f>
-        <v>155264.68709237207</v>
+        <v>75367.548887754921</v>
       </c>
       <c r="H18" s="6">
         <f>Summary_Removals!$H15</f>
-        <v>165553.96851509219</v>
+        <v>80334.731962822014</v>
       </c>
       <c r="I18" s="6">
         <f>Summary_Removals!$H14</f>
-        <v>177982.11384188163</v>
+        <v>86332.13483317825</v>
       </c>
       <c r="J18" s="6">
         <f>Summary_Removals!$H13</f>
-        <v>194048.27906657202</v>
+        <v>94082.138369954962</v>
       </c>
       <c r="K18" s="6">
         <f>Summary_Removals!$H12</f>
-        <v>216572.19855997927</v>
+        <v>104943.51551237612</v>
       </c>
       <c r="L18" s="5">
         <f t="shared" si="0"/>
-        <v>1566370.2522642657</v>
+        <v>760226.46271032747</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -11585,47 +11610,47 @@
       </c>
       <c r="B19" s="1">
         <f>Summary_Removals!$H22</f>
-        <v>111482.1591971474</v>
+        <v>54208.979240103537</v>
       </c>
       <c r="C19" s="1">
         <f>Summary_Removals!$H21</f>
-        <v>117540.59521858906</v>
+        <v>57139.074565888819</v>
       </c>
       <c r="D19" s="6">
         <f>Summary_Removals!$H20</f>
-        <v>123981.89516052275</v>
+        <v>60253.508215713257</v>
       </c>
       <c r="E19" s="6">
         <f>Summary_Removals!$H19</f>
-        <v>130859.41280213727</v>
+        <v>63577.945426597624</v>
       </c>
       <c r="F19" s="6">
         <f>Summary_Removals!$H18</f>
-        <v>138256.27862276728</v>
+        <v>67152.396502738513</v>
       </c>
       <c r="G19" s="6">
         <f>Summary_Removals!$H17</f>
-        <v>146310.82338435226</v>
+        <v>71043.468433302914</v>
       </c>
       <c r="H19" s="6">
         <f>Summary_Removals!$H16</f>
-        <v>155264.68709237207</v>
+        <v>75367.548887754921</v>
       </c>
       <c r="I19" s="6">
         <f>Summary_Removals!$H15</f>
-        <v>165553.96851509219</v>
+        <v>80334.731962822014</v>
       </c>
       <c r="J19" s="6">
         <f>Summary_Removals!$H14</f>
-        <v>177982.11384188163</v>
+        <v>86332.13483317825</v>
       </c>
       <c r="K19" s="6">
         <f>Summary_Removals!$H13</f>
-        <v>194048.27906657202</v>
+        <v>94082.138369954962</v>
       </c>
       <c r="L19" s="5">
         <f t="shared" si="0"/>
-        <v>1461280.2129014339</v>
+        <v>709491.92643805488</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -11634,47 +11659,47 @@
       </c>
       <c r="B20" s="1">
         <f>Summary_Removals!$H23</f>
-        <v>105769.5513813343</v>
+        <v>51445.416516802092</v>
       </c>
       <c r="C20" s="1">
         <f>Summary_Removals!$H22</f>
-        <v>111482.1591971474</v>
+        <v>54208.979240103537</v>
       </c>
       <c r="D20" s="6">
         <f>Summary_Removals!$H21</f>
-        <v>117540.59521858906</v>
+        <v>57139.074565888819</v>
       </c>
       <c r="E20" s="6">
         <f>Summary_Removals!$H20</f>
-        <v>123981.89516052275</v>
+        <v>60253.508215713257</v>
       </c>
       <c r="F20" s="6">
         <f>Summary_Removals!$H19</f>
-        <v>130859.41280213727</v>
+        <v>63577.945426597624</v>
       </c>
       <c r="G20" s="6">
         <f>Summary_Removals!$H18</f>
-        <v>138256.27862276728</v>
+        <v>67152.396502738513</v>
       </c>
       <c r="H20" s="6">
         <f>Summary_Removals!$H17</f>
-        <v>146310.82338435226</v>
+        <v>71043.468433302914</v>
       </c>
       <c r="I20" s="6">
         <f>Summary_Removals!$H16</f>
-        <v>155264.68709237207</v>
+        <v>75367.548887754921</v>
       </c>
       <c r="J20" s="6">
         <f>Summary_Removals!$H15</f>
-        <v>165553.96851509219</v>
+        <v>80334.731962822014</v>
       </c>
       <c r="K20" s="6">
         <f>Summary_Removals!$H14</f>
-        <v>177982.11384188163</v>
+        <v>86332.13483317825</v>
       </c>
       <c r="L20" s="5">
         <f t="shared" si="0"/>
-        <v>1373001.4852161962</v>
+        <v>666855.20458490192</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -11683,47 +11708,47 @@
       </c>
       <c r="B21" s="1">
         <f>Summary_Removals!$H24</f>
-        <v>100374.90991334268</v>
+        <v>48834.997638395005</v>
       </c>
       <c r="C21" s="1">
         <f>Summary_Removals!$H23</f>
-        <v>105769.5513813343</v>
+        <v>51445.416516802092</v>
       </c>
       <c r="D21" s="6">
         <f>Summary_Removals!$H22</f>
-        <v>111482.1591971474</v>
+        <v>54208.979240103537</v>
       </c>
       <c r="E21" s="6">
         <f>Summary_Removals!$H21</f>
-        <v>117540.59521858906</v>
+        <v>57139.074565888819</v>
       </c>
       <c r="F21" s="6">
         <f>Summary_Removals!$H20</f>
-        <v>123981.89516052275</v>
+        <v>60253.508215713257</v>
       </c>
       <c r="G21" s="6">
         <f>Summary_Removals!$H19</f>
-        <v>130859.41280213727</v>
+        <v>63577.945426597624</v>
       </c>
       <c r="H21" s="6">
         <f>Summary_Removals!$H18</f>
-        <v>138256.27862276728</v>
+        <v>67152.396502738513</v>
       </c>
       <c r="I21" s="6">
         <f>Summary_Removals!$H17</f>
-        <v>146310.82338435226</v>
+        <v>71043.468433302914</v>
       </c>
       <c r="J21" s="6">
         <f>Summary_Removals!$H16</f>
-        <v>155264.68709237207</v>
+        <v>75367.548887754921</v>
       </c>
       <c r="K21" s="6">
         <f>Summary_Removals!$H15</f>
-        <v>165553.96851509219</v>
+        <v>80334.731962822014</v>
       </c>
       <c r="L21" s="5">
         <f t="shared" si="0"/>
-        <v>1295394.2812876573</v>
+        <v>629358.06739011873</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -11732,47 +11757,47 @@
       </c>
       <c r="B22" s="1">
         <f>Summary_Removals!$H25</f>
-        <v>95275.737215576897</v>
+        <v>46366.915248670673</v>
       </c>
       <c r="C22" s="1">
         <f>Summary_Removals!$H24</f>
-        <v>100374.90991334268</v>
+        <v>48834.997638395005</v>
       </c>
       <c r="D22" s="6">
         <f>Summary_Removals!$H23</f>
-        <v>105769.5513813343</v>
+        <v>51445.416516802092</v>
       </c>
       <c r="E22" s="6">
         <f>Summary_Removals!$H22</f>
-        <v>111482.1591971474</v>
+        <v>54208.979240103537</v>
       </c>
       <c r="F22" s="6">
         <f>Summary_Removals!$H21</f>
-        <v>117540.59521858906</v>
+        <v>57139.074565888819</v>
       </c>
       <c r="G22" s="6">
         <f>Summary_Removals!$H20</f>
-        <v>123981.89516052275</v>
+        <v>60253.508215713257</v>
       </c>
       <c r="H22" s="6">
         <f>Summary_Removals!$H19</f>
-        <v>130859.41280213727</v>
+        <v>63577.945426597624</v>
       </c>
       <c r="I22" s="6">
         <f>Summary_Removals!$H18</f>
-        <v>138256.27862276728</v>
+        <v>67152.396502738513</v>
       </c>
       <c r="J22" s="6">
         <f>Summary_Removals!$H17</f>
-        <v>146310.82338435226</v>
+        <v>71043.468433302914</v>
       </c>
       <c r="K22" s="6">
         <f>Summary_Removals!$H16</f>
-        <v>155264.68709237207</v>
+        <v>75367.548887754921</v>
       </c>
       <c r="L22" s="5">
         <f t="shared" si="0"/>
-        <v>1225116.049988142</v>
+        <v>595390.25067596731</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -11781,47 +11806,47 @@
       </c>
       <c r="B23" s="1">
         <f>Summary_Removals!$H26</f>
-        <v>90452.853042336705</v>
+        <v>44031.957245805876</v>
       </c>
       <c r="C23" s="1">
         <f>Summary_Removals!$H25</f>
-        <v>95275.737215576897</v>
+        <v>46366.915248670673</v>
       </c>
       <c r="D23" s="6">
         <f>Summary_Removals!$H24</f>
-        <v>100374.90991334268</v>
+        <v>48834.997638395005</v>
       </c>
       <c r="E23" s="6">
         <f>Summary_Removals!$H23</f>
-        <v>105769.5513813343</v>
+        <v>51445.416516802092</v>
       </c>
       <c r="F23" s="6">
         <f>Summary_Removals!$H22</f>
-        <v>111482.1591971474</v>
+        <v>54208.979240103537</v>
       </c>
       <c r="G23" s="6">
         <f>Summary_Removals!$H21</f>
-        <v>117540.59521858906</v>
+        <v>57139.074565888819</v>
       </c>
       <c r="H23" s="6">
         <f>Summary_Removals!$H20</f>
-        <v>123981.89516052275</v>
+        <v>60253.508215713257</v>
       </c>
       <c r="I23" s="6">
         <f>Summary_Removals!$H19</f>
-        <v>130859.41280213727</v>
+        <v>63577.945426597624</v>
       </c>
       <c r="J23" s="6">
         <f>Summary_Removals!$H18</f>
-        <v>138256.27862276728</v>
+        <v>67152.396502738513</v>
       </c>
       <c r="K23" s="6">
         <f>Summary_Removals!$H17</f>
-        <v>146310.82338435226</v>
+        <v>71043.468433302914</v>
       </c>
       <c r="L23" s="5">
         <f t="shared" si="0"/>
-        <v>1160304.2159381066</v>
+        <v>564054.65903401829</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -11830,47 +11855,47 @@
       </c>
       <c r="B24" s="1">
         <f>Summary_Removals!$H27</f>
-        <v>85889.280552191049</v>
+        <v>41821.970249623686</v>
       </c>
       <c r="C24" s="1">
         <f>Summary_Removals!$H26</f>
-        <v>90452.853042336705</v>
+        <v>44031.957245805876</v>
       </c>
       <c r="D24" s="6">
         <f>Summary_Removals!$H25</f>
-        <v>95275.737215576897</v>
+        <v>46366.915248670673</v>
       </c>
       <c r="E24" s="6">
         <f>Summary_Removals!$H24</f>
-        <v>100374.90991334268</v>
+        <v>48834.997638395005</v>
       </c>
       <c r="F24" s="6">
         <f>Summary_Removals!$H23</f>
-        <v>105769.5513813343</v>
+        <v>51445.416516802092</v>
       </c>
       <c r="G24" s="6">
         <f>Summary_Removals!$H22</f>
-        <v>111482.1591971474</v>
+        <v>54208.979240103537</v>
       </c>
       <c r="H24" s="6">
         <f>Summary_Removals!$H21</f>
-        <v>117540.59521858906</v>
+        <v>57139.074565888819</v>
       </c>
       <c r="I24" s="6">
         <f>Summary_Removals!$H20</f>
-        <v>123981.89516052275</v>
+        <v>60253.508215713257</v>
       </c>
       <c r="J24" s="6">
         <f>Summary_Removals!$H19</f>
-        <v>130859.41280213727</v>
+        <v>63577.945426597624</v>
       </c>
       <c r="K24" s="6">
         <f>Summary_Removals!$H18</f>
-        <v>138256.27862276728</v>
+        <v>67152.396502738513</v>
       </c>
       <c r="L24" s="5">
         <f t="shared" si="0"/>
-        <v>1099882.6731059453</v>
+        <v>534833.1608503391</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -11879,47 +11904,47 @@
       </c>
       <c r="B25" s="1">
         <f>Summary_Removals!$H28</f>
-        <v>81569.627408180371</v>
+        <v>39729.561607948839</v>
       </c>
       <c r="C25" s="1">
         <f>Summary_Removals!$H27</f>
-        <v>85889.280552191049</v>
+        <v>41821.970249623686</v>
       </c>
       <c r="D25" s="6">
         <f>Summary_Removals!$H26</f>
-        <v>90452.853042336705</v>
+        <v>44031.957245805876</v>
       </c>
       <c r="E25" s="6">
         <f>Summary_Removals!$H25</f>
-        <v>95275.737215576897</v>
+        <v>46366.915248670673</v>
       </c>
       <c r="F25" s="6">
         <f>Summary_Removals!$H24</f>
-        <v>100374.90991334268</v>
+        <v>48834.997638395005</v>
       </c>
       <c r="G25" s="6">
         <f>Summary_Removals!$H23</f>
-        <v>105769.5513813343</v>
+        <v>51445.416516802092</v>
       </c>
       <c r="H25" s="6">
         <f>Summary_Removals!$H22</f>
-        <v>111482.1591971474</v>
+        <v>54208.979240103537</v>
       </c>
       <c r="I25" s="6">
         <f>Summary_Removals!$H21</f>
-        <v>117540.59521858906</v>
+        <v>57139.074565888819</v>
       </c>
       <c r="J25" s="6">
         <f>Summary_Removals!$H20</f>
-        <v>123981.89516052275</v>
+        <v>60253.508215713257</v>
       </c>
       <c r="K25" s="6">
         <f>Summary_Removals!$H19</f>
-        <v>130859.41280213727</v>
+        <v>63577.945426597624</v>
       </c>
       <c r="L25" s="5">
         <f t="shared" si="0"/>
-        <v>1043196.0218913585</v>
+        <v>507410.32595554943</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -11928,47 +11953,47 @@
       </c>
       <c r="B26" s="1">
         <f>Summary_Removals!$H29</f>
-        <v>77479.730541748184</v>
+        <v>37747.928445136684</v>
       </c>
       <c r="C26" s="1">
         <f>Summary_Removals!$H28</f>
-        <v>81569.627408180371</v>
+        <v>39729.561607948839</v>
       </c>
       <c r="D26" s="6">
         <f>Summary_Removals!$H27</f>
-        <v>85889.280552191049</v>
+        <v>41821.970249623686</v>
       </c>
       <c r="E26" s="6">
         <f>Summary_Removals!$H26</f>
-        <v>90452.853042336705</v>
+        <v>44031.957245805876</v>
       </c>
       <c r="F26" s="6">
         <f>Summary_Removals!$H25</f>
-        <v>95275.737215576897</v>
+        <v>46366.915248670673</v>
       </c>
       <c r="G26" s="6">
         <f>Summary_Removals!$H24</f>
-        <v>100374.90991334268</v>
+        <v>48834.997638395005</v>
       </c>
       <c r="H26" s="6">
         <f>Summary_Removals!$H23</f>
-        <v>105769.5513813343</v>
+        <v>51445.416516802092</v>
       </c>
       <c r="I26" s="6">
         <f>Summary_Removals!$H22</f>
-        <v>111482.1591971474</v>
+        <v>54208.979240103537</v>
       </c>
       <c r="J26" s="6">
         <f>Summary_Removals!$H21</f>
-        <v>117540.59521858906</v>
+        <v>57139.074565888819</v>
       </c>
       <c r="K26" s="6">
         <f>Summary_Removals!$H20</f>
-        <v>123981.89516052275</v>
+        <v>60253.508215713257</v>
       </c>
       <c r="L26" s="5">
         <f t="shared" si="0"/>
-        <v>989816.33963096945</v>
+        <v>481580.30897408846</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -11977,47 +12002,47 @@
       </c>
       <c r="B27" s="1">
         <f>Summary_Removals!$H30</f>
-        <v>73606.442265620717</v>
+        <v>35870.754808756719</v>
       </c>
       <c r="C27" s="1">
         <f>Summary_Removals!$H29</f>
-        <v>77479.730541748184</v>
+        <v>37747.928445136684</v>
       </c>
       <c r="D27" s="6">
         <f>Summary_Removals!$H28</f>
-        <v>81569.627408180371</v>
+        <v>39729.561607948839</v>
       </c>
       <c r="E27" s="6">
         <f>Summary_Removals!$H27</f>
-        <v>85889.280552191049</v>
+        <v>41821.970249623686</v>
       </c>
       <c r="F27" s="6">
         <f>Summary_Removals!$H26</f>
-        <v>90452.853042336705</v>
+        <v>44031.957245805876</v>
       </c>
       <c r="G27" s="6">
         <f>Summary_Removals!$H25</f>
-        <v>95275.737215576897</v>
+        <v>46366.915248670673</v>
       </c>
       <c r="H27" s="6">
         <f>Summary_Removals!$H24</f>
-        <v>100374.90991334268</v>
+        <v>48834.997638395005</v>
       </c>
       <c r="I27" s="6">
         <f>Summary_Removals!$H23</f>
-        <v>105769.5513813343</v>
+        <v>51445.416516802092</v>
       </c>
       <c r="J27" s="6">
         <f>Summary_Removals!$H22</f>
-        <v>111482.1591971474</v>
+        <v>54208.979240103537</v>
       </c>
       <c r="K27" s="6">
         <f>Summary_Removals!$H21</f>
-        <v>117540.59521858906</v>
+        <v>57139.074565888819</v>
       </c>
       <c r="L27" s="5">
         <f t="shared" si="0"/>
-        <v>939440.88673606736</v>
+        <v>457197.55556713196</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -12026,47 +12051,47 @@
       </c>
       <c r="B28" s="1">
         <f>Summary_Removals!$H31</f>
-        <v>69937.492987972088</v>
+        <v>34092.145713041056</v>
       </c>
       <c r="C28" s="1">
         <f>Summary_Removals!$H30</f>
-        <v>73606.442265620717</v>
+        <v>35870.754808756719</v>
       </c>
       <c r="D28" s="6">
         <f>Summary_Removals!$H29</f>
-        <v>77479.730541748184</v>
+        <v>37747.928445136684</v>
       </c>
       <c r="E28" s="6">
         <f>Summary_Removals!$H28</f>
-        <v>81569.627408180371</v>
+        <v>39729.561607948839</v>
       </c>
       <c r="F28" s="6">
         <f>Summary_Removals!$H27</f>
-        <v>85889.280552191049</v>
+        <v>41821.970249623686</v>
       </c>
       <c r="G28" s="6">
         <f>Summary_Removals!$H26</f>
-        <v>90452.853042336705</v>
+        <v>44031.957245805876</v>
       </c>
       <c r="H28" s="6">
         <f>Summary_Removals!$H25</f>
-        <v>95275.737215576897</v>
+        <v>46366.915248670673</v>
       </c>
       <c r="I28" s="6">
         <f>Summary_Removals!$H24</f>
-        <v>100374.90991334268</v>
+        <v>48834.997638395005</v>
       </c>
       <c r="J28" s="6">
         <f>Summary_Removals!$H23</f>
-        <v>105769.5513813343</v>
+        <v>51445.416516802092</v>
       </c>
       <c r="K28" s="6">
         <f>Summary_Removals!$H22</f>
-        <v>111482.1591971474</v>
+        <v>54208.979240103537</v>
       </c>
       <c r="L28" s="5">
         <f t="shared" si="0"/>
-        <v>891837.78450545028</v>
+        <v>434150.62671428418</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -12075,47 +12100,47 @@
       </c>
       <c r="B29" s="1">
         <f>Summary_Removals!$H32</f>
-        <v>66461.396180462776</v>
+        <v>32406.58152806999</v>
       </c>
       <c r="C29" s="1">
         <f>Summary_Removals!$H31</f>
-        <v>69937.492987972088</v>
+        <v>34092.145713041056</v>
       </c>
       <c r="D29" s="6">
         <f>Summary_Removals!$H30</f>
-        <v>73606.442265620717</v>
+        <v>35870.754808756719</v>
       </c>
       <c r="E29" s="6">
         <f>Summary_Removals!$H29</f>
-        <v>77479.730541748184</v>
+        <v>37747.928445136684</v>
       </c>
       <c r="F29" s="6">
         <f>Summary_Removals!$H28</f>
-        <v>81569.627408180371</v>
+        <v>39729.561607948839</v>
       </c>
       <c r="G29" s="6">
         <f>Summary_Removals!$H27</f>
-        <v>85889.280552191049</v>
+        <v>41821.970249623686</v>
       </c>
       <c r="H29" s="6">
         <f>Summary_Removals!$H26</f>
-        <v>90452.853042336705</v>
+        <v>44031.957245805876</v>
       </c>
       <c r="I29" s="6">
         <f>Summary_Removals!$H25</f>
-        <v>95275.737215576897</v>
+        <v>46366.915248670673</v>
       </c>
       <c r="J29" s="6">
         <f>Summary_Removals!$H24</f>
-        <v>100374.90991334268</v>
+        <v>48834.997638395005</v>
       </c>
       <c r="K29" s="6">
         <f>Summary_Removals!$H23</f>
-        <v>105769.5513813343</v>
+        <v>51445.416516802092</v>
       </c>
       <c r="L29" s="5">
         <f t="shared" si="0"/>
-        <v>846817.02148876584</v>
+        <v>412348.22900225065</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -12124,47 +12149,47 @@
       </c>
       <c r="B30" s="1">
         <f>Summary_Removals!$H33</f>
-        <v>63167.377314750454</v>
+        <v>30808.883904145074</v>
       </c>
       <c r="C30" s="1">
         <f>Summary_Removals!$H32</f>
-        <v>66461.396180462776</v>
+        <v>32406.58152806999</v>
       </c>
       <c r="D30" s="6">
         <f>Summary_Removals!$H31</f>
-        <v>69937.492987972088</v>
+        <v>34092.145713041056</v>
       </c>
       <c r="E30" s="6">
         <f>Summary_Removals!$H30</f>
-        <v>73606.442265620717</v>
+        <v>35870.754808756719</v>
       </c>
       <c r="F30" s="6">
         <f>Summary_Removals!$H29</f>
-        <v>77479.730541748184</v>
+        <v>37747.928445136684</v>
       </c>
       <c r="G30" s="6">
         <f>Summary_Removals!$H28</f>
-        <v>81569.627408180371</v>
+        <v>39729.561607948839</v>
       </c>
       <c r="H30" s="6">
         <f>Summary_Removals!$H27</f>
-        <v>85889.280552191049</v>
+        <v>41821.970249623686</v>
       </c>
       <c r="I30" s="6">
         <f>Summary_Removals!$H26</f>
-        <v>90452.853042336705</v>
+        <v>44031.957245805876</v>
       </c>
       <c r="J30" s="6">
         <f>Summary_Removals!$H25</f>
-        <v>95275.737215576897</v>
+        <v>46366.915248670673</v>
       </c>
       <c r="K30" s="6">
         <f>Summary_Removals!$H24</f>
-        <v>100374.90991334268</v>
+        <v>48834.997638395005</v>
       </c>
       <c r="L30" s="5">
         <f t="shared" si="0"/>
-        <v>804214.84742218186</v>
+        <v>391711.69638959365</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -12173,47 +12198,47 @@
       </c>
       <c r="B31" s="1">
         <f>Summary_Removals!$H34</f>
-        <v>60045.316975332556</v>
+        <v>29294.188513732159</v>
       </c>
       <c r="C31" s="1">
         <f>Summary_Removals!$H33</f>
-        <v>63167.377314750454</v>
+        <v>30808.883904145074</v>
       </c>
       <c r="D31" s="6">
         <f>Summary_Removals!$H32</f>
-        <v>66461.396180462776</v>
+        <v>32406.58152806999</v>
       </c>
       <c r="E31" s="6">
         <f>Summary_Removals!$H31</f>
-        <v>69937.492987972088</v>
+        <v>34092.145713041056</v>
       </c>
       <c r="F31" s="6">
         <f>Summary_Removals!$H30</f>
-        <v>73606.442265620717</v>
+        <v>35870.754808756719</v>
       </c>
       <c r="G31" s="6">
         <f>Summary_Removals!$H29</f>
-        <v>77479.730541748184</v>
+        <v>37747.928445136684</v>
       </c>
       <c r="H31" s="6">
         <f>Summary_Removals!$H28</f>
-        <v>81569.627408180371</v>
+        <v>39729.561607948839</v>
       </c>
       <c r="I31" s="6">
         <f>Summary_Removals!$H27</f>
-        <v>85889.280552191049</v>
+        <v>41821.970249623686</v>
       </c>
       <c r="J31" s="6">
         <f>Summary_Removals!$H26</f>
-        <v>90452.853042336705</v>
+        <v>44031.957245805876</v>
       </c>
       <c r="K31" s="6">
         <f>Summary_Removals!$H25</f>
-        <v>95275.737215576897</v>
+        <v>46366.915248670673</v>
       </c>
       <c r="L31" s="5">
         <f t="shared" si="0"/>
-        <v>763885.25448417175</v>
+        <v>372170.88726493082</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -12222,47 +12247,47 @@
       </c>
       <c r="B32" s="1">
         <f>Summary_Removals!$H35</f>
-        <v>57085.702853182986</v>
+        <v>27857.922060236546</v>
       </c>
       <c r="C32" s="1">
         <f>Summary_Removals!$H34</f>
-        <v>60045.316975332556</v>
+        <v>29294.188513732159</v>
       </c>
       <c r="D32" s="6">
         <f>Summary_Removals!$H33</f>
-        <v>63167.377314750454</v>
+        <v>30808.883904145074</v>
       </c>
       <c r="E32" s="6">
         <f>Summary_Removals!$H32</f>
-        <v>66461.396180462776</v>
+        <v>32406.58152806999</v>
       </c>
       <c r="F32" s="6">
         <f>Summary_Removals!$H31</f>
-        <v>69937.492987972088</v>
+        <v>34092.145713041056</v>
       </c>
       <c r="G32" s="6">
         <f>Summary_Removals!$H30</f>
-        <v>73606.442265620717</v>
+        <v>35870.754808756719</v>
       </c>
       <c r="H32" s="6">
         <f>Summary_Removals!$H29</f>
-        <v>77479.730541748184</v>
+        <v>37747.928445136684</v>
       </c>
       <c r="I32" s="6">
         <f>Summary_Removals!$H28</f>
-        <v>81569.627408180371</v>
+        <v>39729.561607948839</v>
       </c>
       <c r="J32" s="6">
         <f>Summary_Removals!$H27</f>
-        <v>85889.280552191049</v>
+        <v>41821.970249623686</v>
       </c>
       <c r="K32" s="6">
         <f>Summary_Removals!$H26</f>
-        <v>90452.853042336705</v>
+        <v>44031.957245805876</v>
       </c>
       <c r="L32" s="5">
         <f t="shared" si="0"/>
-        <v>725695.22012177785</v>
+        <v>353661.89407649665</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -12271,47 +12296,47 @@
       </c>
       <c r="B33" s="1">
         <f>Summary_Removals!$H36</f>
-        <v>54279.587710543572</v>
+        <v>26495.782152554246</v>
       </c>
       <c r="C33" s="1">
         <f>Summary_Removals!$H35</f>
-        <v>57085.702853182986</v>
+        <v>27857.922060236546</v>
       </c>
       <c r="D33" s="6">
         <f>Summary_Removals!$H34</f>
-        <v>60045.316975332556</v>
+        <v>29294.188513732159</v>
       </c>
       <c r="E33" s="6">
         <f>Summary_Removals!$H33</f>
-        <v>63167.377314750454</v>
+        <v>30808.883904145074</v>
       </c>
       <c r="F33" s="6">
         <f>Summary_Removals!$H32</f>
-        <v>66461.396180462776</v>
+        <v>32406.58152806999</v>
       </c>
       <c r="G33" s="6">
         <f>Summary_Removals!$H31</f>
-        <v>69937.492987972088</v>
+        <v>34092.145713041056</v>
       </c>
       <c r="H33" s="6">
         <f>Summary_Removals!$H30</f>
-        <v>73606.442265620717</v>
+        <v>35870.754808756719</v>
       </c>
       <c r="I33" s="6">
         <f>Summary_Removals!$H29</f>
-        <v>77479.730541748184</v>
+        <v>37747.928445136684</v>
       </c>
       <c r="J33" s="6">
         <f>Summary_Removals!$H28</f>
-        <v>81569.627408180371</v>
+        <v>39729.561607948839</v>
       </c>
       <c r="K33" s="6">
         <f>Summary_Removals!$H27</f>
-        <v>85889.280552191049</v>
+        <v>41821.970249623686</v>
       </c>
       <c r="L33" s="5">
         <f t="shared" si="0"/>
-        <v>689521.95478998474</v>
+        <v>336125.71898324502</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -12320,47 +12345,47 @@
       </c>
       <c r="B34" s="1">
         <f>Summary_Removals!$H37</f>
-        <v>51618.551677162621</v>
+        <v>25203.719256242061</v>
       </c>
       <c r="C34" s="1">
         <f>Summary_Removals!$H36</f>
-        <v>54279.587710543572</v>
+        <v>26495.782152554246</v>
       </c>
       <c r="D34" s="6">
         <f>Summary_Removals!$H35</f>
-        <v>57085.702853182986</v>
+        <v>27857.922060236546</v>
       </c>
       <c r="E34" s="6">
         <f>Summary_Removals!$H34</f>
-        <v>60045.316975332556</v>
+        <v>29294.188513732159</v>
       </c>
       <c r="F34" s="6">
         <f>Summary_Removals!$H33</f>
-        <v>63167.377314750454</v>
+        <v>30808.883904145074</v>
       </c>
       <c r="G34" s="6">
         <f>Summary_Removals!$H32</f>
-        <v>66461.396180462776</v>
+        <v>32406.58152806999</v>
       </c>
       <c r="H34" s="6">
         <f>Summary_Removals!$H31</f>
-        <v>69937.492987972088</v>
+        <v>34092.145713041056</v>
       </c>
       <c r="I34" s="6">
         <f>Summary_Removals!$H30</f>
-        <v>73606.442265620717</v>
+        <v>35870.754808756719</v>
       </c>
       <c r="J34" s="6">
         <f>Summary_Removals!$H29</f>
-        <v>77479.730541748184</v>
+        <v>37747.928445136684</v>
       </c>
       <c r="K34" s="6">
         <f>Summary_Removals!$H28</f>
-        <v>81569.627408180371</v>
+        <v>39729.561607948839</v>
       </c>
       <c r="L34" s="5">
         <f t="shared" si="0"/>
-        <v>655251.22591495642</v>
+        <v>319507.46798986342</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -12369,47 +12394,47 @@
       </c>
       <c r="B35" s="1">
         <f>Summary_Removals!$H38</f>
-        <v>49094.667918374587</v>
+        <v>23977.920259800765</v>
       </c>
       <c r="C35" s="1">
         <f>Summary_Removals!$H37</f>
-        <v>51618.551677162621</v>
+        <v>25203.719256242061</v>
       </c>
       <c r="D35" s="6">
         <f>Summary_Removals!$H36</f>
-        <v>54279.587710543572</v>
+        <v>26495.782152554246</v>
       </c>
       <c r="E35" s="6">
         <f>Summary_Removals!$H35</f>
-        <v>57085.702853182986</v>
+        <v>27857.922060236546</v>
       </c>
       <c r="F35" s="6">
         <f>Summary_Removals!$H34</f>
-        <v>60045.316975332556</v>
+        <v>29294.188513732159</v>
       </c>
       <c r="G35" s="6">
         <f>Summary_Removals!$H33</f>
-        <v>63167.377314750454</v>
+        <v>30808.883904145074</v>
       </c>
       <c r="H35" s="6">
         <f>Summary_Removals!$H32</f>
-        <v>66461.396180462776</v>
+        <v>32406.58152806999</v>
       </c>
       <c r="I35" s="6">
         <f>Summary_Removals!$H31</f>
-        <v>69937.492987972088</v>
+        <v>34092.145713041056</v>
       </c>
       <c r="J35" s="6">
         <f>Summary_Removals!$H30</f>
-        <v>73606.442265620717</v>
+        <v>35870.754808756719</v>
       </c>
       <c r="K35" s="6">
         <f>Summary_Removals!$H29</f>
-        <v>77479.730541748184</v>
+        <v>37747.928445136684</v>
       </c>
       <c r="L35" s="5">
         <f t="shared" si="0"/>
-        <v>622776.26642515056</v>
+        <v>303755.82664171531</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -12418,47 +12443,47 @@
       </c>
       <c r="B36" s="1">
         <f>Summary_Removals!$H39</f>
-        <v>46700.471083183729</v>
+        <v>22814.793371703556</v>
       </c>
       <c r="C36" s="1">
         <f>Summary_Removals!$H38</f>
-        <v>49094.667918374587</v>
+        <v>23977.920259800765</v>
       </c>
       <c r="D36" s="6">
         <f>Summary_Removals!$H37</f>
-        <v>51618.551677162621</v>
+        <v>25203.719256242061</v>
       </c>
       <c r="E36" s="6">
         <f>Summary_Removals!$H36</f>
-        <v>54279.587710543572</v>
+        <v>26495.782152554246</v>
       </c>
       <c r="F36" s="6">
         <f>Summary_Removals!$H35</f>
-        <v>57085.702853182986</v>
+        <v>27857.922060236546</v>
       </c>
       <c r="G36" s="6">
         <f>Summary_Removals!$H34</f>
-        <v>60045.316975332556</v>
+        <v>29294.188513732159</v>
       </c>
       <c r="H36" s="6">
         <f>Summary_Removals!$H33</f>
-        <v>63167.377314750454</v>
+        <v>30808.883904145074</v>
       </c>
       <c r="I36" s="6">
         <f>Summary_Removals!$H32</f>
-        <v>66461.396180462776</v>
+        <v>32406.58152806999</v>
       </c>
       <c r="J36" s="6">
         <f>Summary_Removals!$H31</f>
-        <v>69937.492987972088</v>
+        <v>34092.145713041056</v>
       </c>
       <c r="K36" s="6">
         <f>Summary_Removals!$H30</f>
-        <v>73606.442265620717</v>
+        <v>35870.754808756719</v>
       </c>
       <c r="L36" s="5">
         <f t="shared" si="0"/>
-        <v>591997.00696658611</v>
+        <v>288822.69156828214</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -12467,47 +12492,47 @@
       </c>
       <c r="B37" s="1">
         <f>Summary_Removals!$H40</f>
-        <v>44428.928141826371</v>
+        <v>21710.954160741589</v>
       </c>
       <c r="C37" s="1">
         <f>Summary_Removals!$H39</f>
-        <v>46700.471083183729</v>
+        <v>22814.793371703556</v>
       </c>
       <c r="D37" s="6">
         <f>Summary_Removals!$H38</f>
-        <v>49094.667918374587</v>
+        <v>23977.920259800765</v>
       </c>
       <c r="E37" s="6">
         <f>Summary_Removals!$H37</f>
-        <v>51618.551677162621</v>
+        <v>25203.719256242061</v>
       </c>
       <c r="F37" s="6">
         <f>Summary_Removals!$H36</f>
-        <v>54279.587710543572</v>
+        <v>26495.782152554246</v>
       </c>
       <c r="G37" s="6">
         <f>Summary_Removals!$H35</f>
-        <v>57085.702853182986</v>
+        <v>27857.922060236546</v>
       </c>
       <c r="H37" s="6">
         <f>Summary_Removals!$H34</f>
-        <v>60045.316975332556</v>
+        <v>29294.188513732159</v>
       </c>
       <c r="I37" s="6">
         <f>Summary_Removals!$H33</f>
-        <v>63167.377314750454</v>
+        <v>30808.883904145074</v>
       </c>
       <c r="J37" s="6">
         <f>Summary_Removals!$H32</f>
-        <v>66461.396180462776</v>
+        <v>32406.58152806999</v>
       </c>
       <c r="K37" s="6">
         <f>Summary_Removals!$H31</f>
-        <v>69937.492987972088</v>
+        <v>34092.145713041056</v>
       </c>
       <c r="L37" s="5">
         <f t="shared" si="0"/>
-        <v>562819.49284279172</v>
+        <v>274662.89092026703</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -12516,47 +12541,47 @@
       </c>
       <c r="B38" s="1">
         <f>Summary_Removals!$H41</f>
-        <v>42273.411336037148</v>
+        <v>20663.212606998179</v>
       </c>
       <c r="C38" s="1">
         <f>Summary_Removals!$H40</f>
-        <v>44428.928141826371</v>
+        <v>21710.954160741589</v>
       </c>
       <c r="D38" s="6">
         <f>Summary_Removals!$H39</f>
-        <v>46700.471083183729</v>
+        <v>22814.793371703556</v>
       </c>
       <c r="E38" s="6">
         <f>Summary_Removals!$H38</f>
-        <v>49094.667918374587</v>
+        <v>23977.920259800765</v>
       </c>
       <c r="F38" s="6">
         <f>Summary_Removals!$H37</f>
-        <v>51618.551677162621</v>
+        <v>25203.719256242061</v>
       </c>
       <c r="G38" s="6">
         <f>Summary_Removals!$H36</f>
-        <v>54279.587710543572</v>
+        <v>26495.782152554246</v>
       </c>
       <c r="H38" s="6">
         <f>Summary_Removals!$H35</f>
-        <v>57085.702853182986</v>
+        <v>27857.922060236546</v>
       </c>
       <c r="I38" s="6">
         <f>Summary_Removals!$H34</f>
-        <v>60045.316975332556</v>
+        <v>29294.188513732159</v>
       </c>
       <c r="J38" s="6">
         <f>Summary_Removals!$H33</f>
-        <v>63167.377314750454</v>
+        <v>30808.883904145074</v>
       </c>
       <c r="K38" s="6">
         <f>Summary_Removals!$H32</f>
-        <v>66461.396180462776</v>
+        <v>32406.58152806999</v>
       </c>
       <c r="L38" s="5">
         <f t="shared" si="0"/>
-        <v>535155.41119085671</v>
+        <v>261233.95781422418</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -12565,47 +12590,47 @@
       </c>
       <c r="B39" s="1">
         <f>Summary_Removals!$H42</f>
-        <v>40227.673030995742</v>
+        <v>19668.561062386794</v>
       </c>
       <c r="C39" s="1">
         <f>Summary_Removals!$H41</f>
-        <v>42273.411336037148</v>
+        <v>20663.212606998179</v>
       </c>
       <c r="D39" s="6">
         <f>Summary_Removals!$H40</f>
-        <v>44428.928141826371</v>
+        <v>21710.954160741589</v>
       </c>
       <c r="E39" s="6">
         <f>Summary_Removals!$H39</f>
-        <v>46700.471083183729</v>
+        <v>22814.793371703556</v>
       </c>
       <c r="F39" s="6">
         <f>Summary_Removals!$H38</f>
-        <v>49094.667918374587</v>
+        <v>23977.920259800765</v>
       </c>
       <c r="G39" s="6">
         <f>Summary_Removals!$H37</f>
-        <v>51618.551677162621</v>
+        <v>25203.719256242061</v>
       </c>
       <c r="H39" s="6">
         <f>Summary_Removals!$H36</f>
-        <v>54279.587710543572</v>
+        <v>26495.782152554246</v>
       </c>
       <c r="I39" s="6">
         <f>Summary_Removals!$H35</f>
-        <v>57085.702853182986</v>
+        <v>27857.922060236546</v>
       </c>
       <c r="J39" s="6">
         <f>Summary_Removals!$H34</f>
-        <v>60045.316975332556</v>
+        <v>29294.188513732159</v>
       </c>
       <c r="K39" s="6">
         <f>Summary_Removals!$H33</f>
-        <v>63167.377314750454</v>
+        <v>30808.883904145074</v>
       </c>
       <c r="L39" s="5">
         <f t="shared" si="0"/>
-        <v>508921.6880413898</v>
+        <v>248495.93734854099</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -12614,47 +12639,47 @@
       </c>
       <c r="B40" s="1">
         <f>Summary_Removals!$H43</f>
-        <v>38285.822298469793</v>
+        <v>18724.163039163599</v>
       </c>
       <c r="C40" s="1">
         <f>Summary_Removals!$H42</f>
-        <v>40227.673030995742</v>
+        <v>19668.561062386794</v>
       </c>
       <c r="D40" s="6">
         <f>Summary_Removals!$H41</f>
-        <v>42273.411336037148</v>
+        <v>20663.212606998179</v>
       </c>
       <c r="E40" s="6">
         <f>Summary_Removals!$H40</f>
-        <v>44428.928141826371</v>
+        <v>21710.954160741589</v>
       </c>
       <c r="F40" s="6">
         <f>Summary_Removals!$H39</f>
-        <v>46700.471083183729</v>
+        <v>22814.793371703556</v>
       </c>
       <c r="G40" s="6">
         <f>Summary_Removals!$H38</f>
-        <v>49094.667918374587</v>
+        <v>23977.920259800765</v>
       </c>
       <c r="H40" s="6">
         <f>Summary_Removals!$H37</f>
-        <v>51618.551677162621</v>
+        <v>25203.719256242061</v>
       </c>
       <c r="I40" s="6">
         <f>Summary_Removals!$H36</f>
-        <v>54279.587710543572</v>
+        <v>26495.782152554246</v>
       </c>
       <c r="J40" s="6">
         <f>Summary_Removals!$H35</f>
-        <v>57085.702853182986</v>
+        <v>27857.922060236546</v>
       </c>
       <c r="K40" s="6">
         <f>Summary_Removals!$H34</f>
-        <v>60045.316975332556</v>
+        <v>29294.188513732159</v>
       </c>
       <c r="L40" s="5">
         <f t="shared" si="0"/>
-        <v>484040.13302510913</v>
+        <v>236411.21648355952</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -12663,47 +12688,47 @@
       </c>
       <c r="B41" s="1">
         <f>Summary_Removals!$H44</f>
-        <v>36442.303087138236</v>
+        <v>17827.342757527626</v>
       </c>
       <c r="C41" s="1">
         <f>Summary_Removals!$H43</f>
-        <v>38285.822298469793</v>
+        <v>18724.163039163599</v>
       </c>
       <c r="D41" s="6">
         <f>Summary_Removals!$H42</f>
-        <v>40227.673030995742</v>
+        <v>19668.561062386794</v>
       </c>
       <c r="E41" s="6">
         <f>Summary_Removals!$H41</f>
-        <v>42273.411336037148</v>
+        <v>20663.212606998179</v>
       </c>
       <c r="F41" s="6">
         <f>Summary_Removals!$H40</f>
-        <v>44428.928141826371</v>
+        <v>21710.954160741589</v>
       </c>
       <c r="G41" s="6">
         <f>Summary_Removals!$H39</f>
-        <v>46700.471083183729</v>
+        <v>22814.793371703556</v>
       </c>
       <c r="H41" s="6">
         <f>Summary_Removals!$H38</f>
-        <v>49094.667918374587</v>
+        <v>23977.920259800765</v>
       </c>
       <c r="I41" s="6">
         <f>Summary_Removals!$H37</f>
-        <v>51618.551677162621</v>
+        <v>25203.719256242061</v>
       </c>
       <c r="J41" s="6">
         <f>Summary_Removals!$H36</f>
-        <v>54279.587710543572</v>
+        <v>26495.782152554246</v>
       </c>
       <c r="K41" s="6">
         <f>Summary_Removals!$H35</f>
-        <v>57085.702853182986</v>
+        <v>27857.922060236546</v>
       </c>
       <c r="L41" s="5">
         <f t="shared" si="0"/>
-        <v>460437.11913691479</v>
+        <v>224944.37072735498</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -12712,47 +12737,47 @@
       </c>
       <c r="B42" s="1">
         <f>Summary_Removals!$H45</f>
-        <v>34691.873854222504</v>
+        <v>16975.57539212154</v>
       </c>
       <c r="C42" s="1">
         <f>Summary_Removals!$H44</f>
-        <v>36442.303087138236</v>
+        <v>17827.342757527626</v>
       </c>
       <c r="D42" s="6">
         <f>Summary_Removals!$H43</f>
-        <v>38285.822298469793</v>
+        <v>18724.163039163599</v>
       </c>
       <c r="E42" s="6">
         <f>Summary_Removals!$H42</f>
-        <v>40227.673030995742</v>
+        <v>19668.561062386794</v>
       </c>
       <c r="F42" s="6">
         <f>Summary_Removals!$H41</f>
-        <v>42273.411336037148</v>
+        <v>20663.212606998179</v>
       </c>
       <c r="G42" s="6">
         <f>Summary_Removals!$H40</f>
-        <v>44428.928141826371</v>
+        <v>21710.954160741589</v>
       </c>
       <c r="H42" s="6">
         <f>Summary_Removals!$H39</f>
-        <v>46700.471083183729</v>
+        <v>22814.793371703556</v>
       </c>
       <c r="I42" s="6">
         <f>Summary_Removals!$H38</f>
-        <v>49094.667918374587</v>
+        <v>23977.920259800765</v>
       </c>
       <c r="J42" s="6">
         <f>Summary_Removals!$H37</f>
-        <v>51618.551677162621</v>
+        <v>25203.719256242061</v>
       </c>
       <c r="K42" s="6">
         <f>Summary_Removals!$H36</f>
-        <v>54279.587710543572</v>
+        <v>26495.782152554246</v>
       </c>
       <c r="L42" s="5">
         <f t="shared" si="0"/>
-        <v>438043.29013795435</v>
+        <v>214062.02405923998</v>
       </c>
     </row>
     <row r="43" spans="1:12">
@@ -12783,7 +12808,7 @@
       </c>
       <c r="L44" s="1">
         <f>SUM(B3:K42)</f>
-        <v>71189705.816566929</v>
+        <v>34471375.452411287</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -12798,7 +12823,7 @@
       </c>
       <c r="L45" s="1">
         <f>L44/40</f>
-        <v>1779742.6454141731</v>
+        <v>861784.38631028216</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -12819,7 +12844,7 @@
       </c>
       <c r="L47" s="5">
         <f>SUM(L3:L12)</f>
-        <v>37753899.330158517</v>
+        <v>18226221.779386558</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -12831,7 +12856,7 @@
       </c>
       <c r="L48" s="5">
         <f>L47/10</f>
-        <v>3775389.9330158518</v>
+        <v>1822622.1779386557</v>
       </c>
     </row>
     <row r="49" spans="9:11">
@@ -13002,6 +13027,7 @@
         <f t="shared" si="0"/>
         <v>52780.463343848314</v>
       </c>
+      <c r="L6" s="12"/>
     </row>
     <row r="7" spans="1:12">
       <c r="A7">
@@ -13877,7 +13903,9 @@
   <dimension ref="A1:P42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="27.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="5" max="16384" width="27.83203125" style="1"/>
+    <col min="5" max="13" width="27.83203125" style="1"/>
+    <col min="14" max="14" width="15.83203125" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="27.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -15643,14 +15671,14 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA3A5171-09C2-EF45-9A29-949687B747C9}">
-  <dimension ref="A1:R43"/>
+  <dimension ref="A1:Q43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="26.1640625" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="2" width="26.1640625" style="1"/>
     <col min="5" max="16384" width="26.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:17">
       <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
@@ -15668,7 +15696,7 @@
       <c r="L1" s="11"/>
       <c r="M1" s="11"/>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:17">
       <c r="A2" s="9" t="s">
         <v>31</v>
       </c>
@@ -15709,7 +15737,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:17">
       <c r="A3">
         <v>416.71665774793968</v>
       </c>
@@ -15737,11 +15765,11 @@
         <v>412.45920139910947</v>
       </c>
       <c r="M3"/>
-      <c r="R3" s="10" t="s">
+      <c r="Q3" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:17">
       <c r="A4">
         <v>357.8210322969839</v>
       </c>
@@ -15779,14 +15807,14 @@
         <v>65.156266421994474</v>
       </c>
       <c r="O4" s="1">
-        <f>(0.5*(C4*0.6 + F4*0.34) + 0.5*(J4*0.6 + M4*0.34))*$R$4</f>
+        <f>(0.5*(C4*0.6 + F4*0.34) + 0.5*(J4*0.6 + M4*0.34))*$Q$4</f>
         <v>293852.47100765549</v>
       </c>
-      <c r="R4" s="2">
+      <c r="Q4" s="2">
         <v>5120</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:17">
       <c r="A5">
         <v>326.86955697169179</v>
       </c>
@@ -15825,11 +15853,11 @@
         <v>34.273157800133568</v>
       </c>
       <c r="O5" s="1">
-        <f t="shared" ref="O5:O43" si="0">(0.5*(C5*0.6 + F5*0.34) + 0.5*(J5*0.6 + M5*0.34))*$R$4</f>
+        <f t="shared" ref="O5:O43" si="0">(0.5*(C5*0.6 + F5*0.34) + 0.5*(J5*0.6 + M5*0.34))*$Q$4</f>
         <v>154483.80788139781</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:17">
       <c r="A6">
         <v>307.42797602697527</v>
       </c>
@@ -15870,8 +15898,9 @@
         <f t="shared" si="0"/>
         <v>97119.403974104367</v>
       </c>
-    </row>
-    <row r="7" spans="1:18">
+      <c r="Q6" s="6"/>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7">
         <v>294.13742272955898</v>
       </c>
@@ -15912,8 +15941,9 @@
         <f t="shared" si="0"/>
         <v>66493.779851270898</v>
       </c>
-    </row>
-    <row r="8" spans="1:18">
+      <c r="Q7" s="13"/>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8">
         <v>284.22364962389918</v>
       </c>
@@ -15955,7 +15985,7 @@
         <v>49706.643740710497</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:17">
       <c r="A9">
         <v>276.23311809961592</v>
       </c>
@@ -15997,7 +16027,7 @@
         <v>40166.661929896138</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:17">
       <c r="A10">
         <v>269.39657775485199</v>
       </c>
@@ -16039,7 +16069,7 @@
         <v>34459.223887246808</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:17">
       <c r="A11">
         <v>263.30231853755748</v>
       </c>
@@ -16081,7 +16111,7 @@
         <v>30800.578502703233</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:17">
       <c r="A12">
         <v>257.7264799297763</v>
       </c>
@@ -16123,7 +16153,7 @@
         <v>28253.838852825902</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
+    <row r="13" spans="1:17">
       <c r="A13">
         <v>252.5443342103936</v>
       </c>
@@ -16165,7 +16195,7 @@
         <v>26324.807383370891</v>
       </c>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" spans="1:17">
       <c r="A14">
         <v>247.6837187973068</v>
       </c>
@@ -16207,7 +16237,7 @@
         <v>24751.614772213681</v>
       </c>
     </row>
-    <row r="15" spans="1:18">
+    <row r="15" spans="1:17">
       <c r="A15">
         <v>243.10052923970389</v>
       </c>
@@ -16249,7 +16279,7 @@
         <v>23394.631636197359</v>
       </c>
     </row>
-    <row r="16" spans="1:18">
+    <row r="16" spans="1:17">
       <c r="A16">
         <v>238.7657955054143</v>
       </c>
@@ -17436,13 +17466,13 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A50DF0E0-E6D0-CC4C-B19B-7767FC3863D6}">
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="26" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="16384" width="26" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:10">
       <c r="A1" s="9" t="s">
         <v>45</v>
       </c>
@@ -17465,7 +17495,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:10">
       <c r="A2">
         <v>416.71665774793968</v>
       </c>
@@ -17480,11 +17510,11 @@
         <v>416.72222644454649</v>
       </c>
       <c r="F2"/>
-      <c r="K2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:10">
       <c r="A3">
         <v>368.65755604950971</v>
       </c>
@@ -17504,14 +17534,14 @@
         <v>38.431023274028099</v>
       </c>
       <c r="H3" s="1">
-        <f>(C3*0.57 + F3*0.3)*$K$3</f>
+        <f>(C3*0.57 + F3*0.3)*$J$3</f>
         <v>597779.32853249332</v>
       </c>
-      <c r="K3" s="3">
+      <c r="J3" s="3">
         <v>15358</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:10">
       <c r="A4">
         <v>343.43555335646801</v>
       </c>
@@ -17531,11 +17561,11 @@
         <v>20.14499321580071</v>
       </c>
       <c r="H4" s="1">
-        <f t="shared" ref="H4:H42" si="0">(C4*0.57 + F4*0.3)*$K$3</f>
+        <f t="shared" ref="H4:H42" si="0">(C4*0.57 + F4*0.3)*$J$3</f>
         <v>313610.94121317234</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:10">
       <c r="A5">
         <v>327.64656357989168</v>
       </c>
@@ -17559,7 +17589,7 @@
         <v>196147.62538190183</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>316.91822029092822</v>
       </c>
@@ -17582,8 +17612,9 @@
         <f t="shared" si="0"/>
         <v>133069.60136381543</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="J6" s="12"/>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7">
         <v>308.98408859533589</v>
       </c>
@@ -17607,7 +17638,7 @@
         <v>98192.793756630184</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:10">
       <c r="A8">
         <v>302.65426406679268</v>
       </c>
@@ -17631,7 +17662,7 @@
         <v>78130.548728042835</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:10">
       <c r="A9">
         <v>297.29699009901532</v>
       </c>
@@ -17655,7 +17686,7 @@
         <v>65940.904703421926</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:10">
       <c r="A10">
         <v>292.57242612780698</v>
       </c>
@@ -17679,7 +17710,7 @@
         <v>57992.097235869296</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:10">
       <c r="A11">
         <v>288.29431731906482</v>
       </c>
@@ -17703,7 +17734,7 @@
         <v>52372.539340622607</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:10">
       <c r="A12">
         <v>284.35762839428128</v>
       </c>
@@ -17727,7 +17758,7 @@
         <v>48070.702410939186</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:10">
       <c r="A13">
         <v>280.70052896462403</v>
       </c>
@@ -17751,7 +17782,7 @@
         <v>44547.97599131403</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:10">
       <c r="A14">
         <v>277.28436785817098</v>
       </c>
@@ -17775,7 +17806,7 @@
         <v>41514.952167199583</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:10">
       <c r="A15">
         <v>274.083098497751</v>
       </c>
@@ -17799,7 +17830,7 @@
         <v>38813.87024049896</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:10">
       <c r="A16">
         <v>271.07767956490068</v>
       </c>
@@ -18454,13 +18485,13 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{736FD4D8-5019-BD44-95E6-DECAB01CDB7E}">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="26.33203125" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="16384" width="26.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="9" t="s">
         <v>45</v>
       </c>
@@ -18474,7 +18505,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>416.71665774793968</v>
       </c>
@@ -18482,11 +18513,11 @@
         <v>416.71616545329988</v>
       </c>
       <c r="C2"/>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>370.64525247623919</v>
       </c>
@@ -18497,14 +18528,14 @@
         <v>46.071402082960411</v>
       </c>
       <c r="E3" s="1">
-        <f>C3*$F$3</f>
-        <v>445879.02935889084</v>
-      </c>
-      <c r="F3" s="3">
+        <f>C3*0.8645*$G$3</f>
+        <v>385462.42088076117</v>
+      </c>
+      <c r="G3" s="3">
         <v>9678</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>346.47246254458781</v>
       </c>
@@ -18515,11 +18546,11 @@
         <v>24.172787027358272</v>
       </c>
       <c r="E4" s="1">
-        <f t="shared" ref="E4:E42" si="0">C4*$F$3</f>
-        <v>233944.23285077335</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <f t="shared" ref="E4:E42" si="0">C4*0.8645*$G$3</f>
+        <v>202244.78929949357</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>331.34964403122279</v>
       </c>
@@ -18531,10 +18562,10 @@
       </c>
       <c r="E5" s="1">
         <f t="shared" si="0"/>
-        <v>146358.61197190915</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>126527.02004971547</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>321.08528742337171</v>
       </c>
@@ -18546,10 +18577,11 @@
       </c>
       <c r="E6" s="1">
         <f t="shared" si="0"/>
-        <v>99338.419933995916</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>85878.064032939481</v>
+      </c>
+      <c r="G6" s="12"/>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>313.50616866073352</v>
       </c>
@@ -18561,10 +18593,10 @@
       </c>
       <c r="E7" s="1">
         <f t="shared" si="0"/>
-        <v>73350.690147965259</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>63411.671632915975</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>307.47087273556502</v>
       </c>
@@ -18576,10 +18608,10 @@
       </c>
       <c r="E8" s="1">
         <f t="shared" si="0"/>
-        <v>58409.57462133708</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>50495.07726014591</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>302.37301704251882</v>
       </c>
@@ -18591,10 +18623,10 @@
       </c>
       <c r="E9" s="1">
         <f t="shared" si="0"/>
-        <v>49337.029780273231</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>42651.862245046214</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>297.88609955336739</v>
       </c>
@@ -18606,10 +18638,10 @@
       </c>
       <c r="E10" s="1">
         <f t="shared" si="0"/>
-        <v>43424.371414480527</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>37540.369087818421</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>293.83091283189532</v>
       </c>
@@ -18621,10 +18653,10 @@
       </c>
       <c r="E11" s="1">
         <f t="shared" si="0"/>
-        <v>39246.082476200289</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>33928.238300675148</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>290.10617449125277</v>
       </c>
@@ -18636,10 +18668,10 @@
       </c>
       <c r="E12" s="1">
         <f t="shared" si="0"/>
-        <v>36048.004350171024</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>31163.499760722858</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>286.65208112808932</v>
       </c>
@@ -18651,10 +18683,10 @@
       </c>
       <c r="E13" s="1">
         <f t="shared" si="0"/>
-        <v>33428.703445477724</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>28899.114128615496</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>283.43110517554783</v>
       </c>
@@ -18666,10 +18698,10 @@
       </c>
       <c r="E14" s="1">
         <f t="shared" si="0"/>
-        <v>31172.594226910951</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>26948.707709164519</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>280.41785186546571</v>
       </c>
@@ -18681,10 +18713,10 @@
       </c>
       <c r="E15" s="1">
         <f t="shared" si="0"/>
-        <v>29162.255478156829</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>25210.769860866581</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>277.59368628729248</v>
       </c>
@@ -18696,7 +18728,7 @@
       </c>
       <c r="E16" s="1">
         <f t="shared" si="0"/>
-        <v>27332.265305845256</v>
+        <v>23628.743356903222</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -18711,7 +18743,7 @@
       </c>
       <c r="E17" s="1">
         <f t="shared" si="0"/>
-        <v>25644.861469344843</v>
+        <v>22169.982740248615</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -18726,7 +18758,7 @@
       </c>
       <c r="E18" s="1">
         <f t="shared" si="0"/>
-        <v>24077.092891597324</v>
+        <v>20814.646804785887</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -18741,7 +18773,7 @@
       </c>
       <c r="E19" s="1">
         <f t="shared" si="0"/>
-        <v>22614.027431293842</v>
+        <v>19549.826714353527</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -18756,7 +18788,7 @@
       </c>
       <c r="E20" s="1">
         <f t="shared" si="0"/>
-        <v>21245.153857786834</v>
+        <v>18366.435510056719</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -18771,7 +18803,7 @@
       </c>
       <c r="E21" s="1">
         <f t="shared" si="0"/>
-        <v>19962.46964245506</v>
+        <v>17257.555005902399</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -18786,7 +18818,7 @@
       </c>
       <c r="E22" s="1">
         <f t="shared" si="0"/>
-        <v>18759.459175170097</v>
+        <v>16217.552456934549</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -18801,7 +18833,7 @@
       </c>
       <c r="E23" s="1">
         <f t="shared" si="0"/>
-        <v>17630.542809778308</v>
+        <v>15241.604259053349</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -18816,7 +18848,7 @@
       </c>
       <c r="E24" s="1">
         <f t="shared" si="0"/>
-        <v>16570.775298477311</v>
+        <v>14325.435245533636</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -18831,7 +18863,7 @@
       </c>
       <c r="E25" s="1">
         <f t="shared" si="0"/>
-        <v>15575.676695813205</v>
+        <v>13465.172503530517</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -18846,7 +18878,7 @@
       </c>
       <c r="E26" s="1">
         <f t="shared" si="0"/>
-        <v>14641.133959223729</v>
+        <v>12657.260307748915</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -18861,7 +18893,7 @@
       </c>
       <c r="E27" s="1">
         <f t="shared" si="0"/>
-        <v>13763.340576437413</v>
+        <v>11898.407928330145</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -18876,7 +18908,7 @@
       </c>
       <c r="E28" s="1">
         <f t="shared" si="0"/>
-        <v>12938.756914317193</v>
+        <v>11185.555352427215</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -18891,7 +18923,7 @@
       </c>
       <c r="E29" s="1">
         <f t="shared" si="0"/>
-        <v>12164.082098323282</v>
+        <v>10515.848974000479</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -18906,7 +18938,7 @@
       </c>
       <c r="E30" s="1">
         <f t="shared" si="0"/>
-        <v>11436.232520002264</v>
+        <v>9886.6230135419592</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -18921,7 +18953,7 @@
       </c>
       <c r="E31" s="1">
         <f t="shared" si="0"/>
-        <v>10752.324338510973</v>
+        <v>9295.3843906427355</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -18936,7 +18968,7 @@
       </c>
       <c r="E32" s="1">
         <f t="shared" si="0"/>
-        <v>10109.658543984497</v>
+        <v>8739.7998112745972</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -18951,7 +18983,7 @@
       </c>
       <c r="E33" s="1">
         <f t="shared" si="0"/>
-        <v>9505.7077891888257</v>
+        <v>8217.6843837537417</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -18966,7 +18998,7 @@
       </c>
       <c r="E34" s="1">
         <f t="shared" si="0"/>
-        <v>8938.1045363726644</v>
+        <v>7726.9913716941683</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -18981,7 +19013,7 @@
       </c>
       <c r="E35" s="1">
         <f t="shared" si="0"/>
-        <v>8404.6302492476661</v>
+        <v>7265.802850474608</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -18996,7 +19028,7 @@
       </c>
       <c r="E36" s="1">
         <f t="shared" si="0"/>
-        <v>7903.2054596060716</v>
+        <v>6832.3211198294493</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -19011,7 +19043,7 @@
       </c>
       <c r="E37" s="1">
         <f t="shared" si="0"/>
-        <v>7431.880592938749</v>
+        <v>6424.860772595549</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -19026,7 +19058,7 @@
       </c>
       <c r="E38" s="1">
         <f t="shared" si="0"/>
-        <v>6988.8274689356977</v>
+        <v>6041.8413468949102</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -19041,7 +19073,7 @@
       </c>
       <c r="E39" s="1">
         <f t="shared" si="0"/>
-        <v>6572.3314112335784</v>
+        <v>5681.7805050114284</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -19056,7 +19088,7 @@
       </c>
       <c r="E40" s="1">
         <f t="shared" si="0"/>
-        <v>6180.7839124915054</v>
+        <v>5343.2876923489066</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -19071,7 +19103,7 @@
       </c>
       <c r="E41" s="1">
         <f t="shared" si="0"/>
-        <v>5812.6758087305207</v>
+        <v>5025.0582366475355</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -19086,7 +19118,7 @@
       </c>
       <c r="E42" s="1">
         <f t="shared" si="0"/>
-        <v>5466.5909223573517</v>
+        <v>4725.8678523779299</v>
       </c>
     </row>
   </sheetData>

--- a/Realistic_ER_Estimate/ER_Summary.xlsx
+++ b/Realistic_ER_Estimate/ER_Summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mihirbendre/Documents/Gazelle/Gazelle_2026/Kenya_Project/Agricentric_SOC_Modeling/Realistic_ER_Estimate/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{079945BD-A94D-0E46-9BFA-DF8D58CB2920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B82A7676-8781-A441-91B2-D3EAE792B5E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" activeTab="2" xr2:uid="{72AD1D35-862B-EB40-AF7A-21135E5EFD45}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="29400" windowHeight="18400" activeTab="1" xr2:uid="{72AD1D35-862B-EB40-AF7A-21135E5EFD45}"/>
   </bookViews>
   <sheets>
     <sheet name="Net_Summary" sheetId="9" r:id="rId1"/>
@@ -336,7 +336,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -350,11 +350,12 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -3362,7 +3363,7 @@
             <c:numRef>
               <c:f>Summary_Reductions!$H$8:$H$47</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>483.48297300000007</c:v>
@@ -3588,7 +3589,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -8462,7 +8463,7 @@
       <c r="A3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G3" s="12">
+      <c r="G3" s="11">
         <v>0.5</v>
       </c>
     </row>
@@ -9690,7 +9691,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8796C41C-1BC9-EA45-B875-C5F0B93D7AE5}">
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
@@ -9792,7 +9793,7 @@
         <v>144.30597800000001</v>
       </c>
       <c r="C8">
-        <f t="shared" ref="C8:F27" si="0">C$3*C$2</f>
+        <f t="shared" ref="C8:F23" si="0">C$3*C$2</f>
         <v>449.55292000000003</v>
       </c>
       <c r="D8">
@@ -9807,7 +9808,7 @@
         <f>F$3*F$2</f>
         <v>98.473650000000006</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="14">
         <f>SUM(B8:F8) * 0.5</f>
         <v>483.48297300000007</v>
       </c>
@@ -9817,7 +9818,7 @@
         <v>2027</v>
       </c>
       <c r="B9">
-        <f t="shared" ref="B9:F28" si="1">B$3*B$2</f>
+        <f t="shared" ref="B9:F24" si="1">B$3*B$2</f>
         <v>144.30597800000001</v>
       </c>
       <c r="C9">
@@ -9836,7 +9837,7 @@
         <f t="shared" si="0"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="14">
         <f t="shared" ref="H9:H47" si="2">SUM(B9:F9) * 0.5</f>
         <v>483.48297300000007</v>
       </c>
@@ -9865,7 +9866,7 @@
         <f t="shared" si="0"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -9894,7 +9895,7 @@
         <f t="shared" si="0"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -9923,7 +9924,7 @@
         <f t="shared" si="0"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -9952,7 +9953,7 @@
         <f t="shared" si="0"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -9981,7 +9982,7 @@
         <f t="shared" si="0"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10010,7 +10011,7 @@
         <f t="shared" si="0"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10039,7 +10040,7 @@
         <f t="shared" si="0"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10068,7 +10069,7 @@
         <f t="shared" si="0"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10097,7 +10098,7 @@
         <f t="shared" si="0"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10126,7 +10127,7 @@
         <f t="shared" si="0"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10155,7 +10156,7 @@
         <f t="shared" si="0"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10184,7 +10185,7 @@
         <f t="shared" si="0"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10213,7 +10214,7 @@
         <f t="shared" si="0"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10242,7 +10243,7 @@
         <f t="shared" si="0"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10271,7 +10272,7 @@
         <f t="shared" si="1"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10281,7 +10282,7 @@
         <v>2043</v>
       </c>
       <c r="B25">
-        <f t="shared" ref="B25:F51" si="3">B$3*B$2</f>
+        <f t="shared" ref="B25:F47" si="3">B$3*B$2</f>
         <v>144.30597800000001</v>
       </c>
       <c r="C25">
@@ -10300,7 +10301,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10329,7 +10330,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10358,7 +10359,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10387,7 +10388,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10416,7 +10417,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10445,7 +10446,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10474,7 +10475,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10503,7 +10504,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10532,7 +10533,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H33">
+      <c r="H33" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10561,7 +10562,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10590,7 +10591,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H35">
+      <c r="H35" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10619,7 +10620,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H36">
+      <c r="H36" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10648,7 +10649,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H37">
+      <c r="H37" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10677,7 +10678,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H38">
+      <c r="H38" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10706,7 +10707,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H39">
+      <c r="H39" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10735,7 +10736,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H40">
+      <c r="H40" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10764,7 +10765,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H41">
+      <c r="H41" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10793,7 +10794,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H42">
+      <c r="H42" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10822,7 +10823,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H43">
+      <c r="H43" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10851,7 +10852,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H44">
+      <c r="H44" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10880,7 +10881,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H45">
+      <c r="H45" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10909,7 +10910,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H46">
+      <c r="H46" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10938,9 +10939,15 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H47">
+      <c r="H47" s="14">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
+      </c>
+    </row>
+    <row r="49" spans="8:8">
+      <c r="H49" s="14">
+        <f>SUM(H8:H47)</f>
+        <v>19339.318919999991</v>
       </c>
     </row>
   </sheetData>
@@ -13027,7 +13034,7 @@
         <f t="shared" si="0"/>
         <v>52780.463343848314</v>
       </c>
-      <c r="L6" s="12"/>
+      <c r="L6" s="11"/>
     </row>
     <row r="7" spans="1:12">
       <c r="A7">
@@ -15679,22 +15686,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="H1" s="11" t="s">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="H1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="9" t="s">
@@ -15941,7 +15948,7 @@
         <f t="shared" si="0"/>
         <v>66493.779851270898</v>
       </c>
-      <c r="Q7" s="13"/>
+      <c r="Q7" s="12"/>
     </row>
     <row r="8" spans="1:17">
       <c r="A8">
@@ -17612,7 +17619,7 @@
         <f t="shared" si="0"/>
         <v>133069.60136381543</v>
       </c>
-      <c r="J6" s="12"/>
+      <c r="J6" s="11"/>
     </row>
     <row r="7" spans="1:10">
       <c r="A7">
@@ -18579,7 +18586,7 @@
         <f t="shared" si="0"/>
         <v>85878.064032939481</v>
       </c>
-      <c r="G6" s="12"/>
+      <c r="G6" s="11"/>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">

--- a/Realistic_ER_Estimate/ER_Summary.xlsx
+++ b/Realistic_ER_Estimate/ER_Summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mihirbendre/Documents/Gazelle/Gazelle_2026/Kenya_Project/Agricentric_SOC_Modeling/Realistic_ER_Estimate/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B82A7676-8781-A441-91B2-D3EAE792B5E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A021FB7B-F980-C34A-96B3-BAB0BAC40ACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="29400" windowHeight="18400" activeTab="1" xr2:uid="{72AD1D35-862B-EB40-AF7A-21135E5EFD45}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="29400" windowHeight="18400" xr2:uid="{72AD1D35-862B-EB40-AF7A-21135E5EFD45}"/>
   </bookViews>
   <sheets>
     <sheet name="Net_Summary" sheetId="9" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="54">
   <si>
     <t>Nth</t>
   </si>
@@ -223,6 +223,12 @@
   <si>
     <t>Conservative Buffer (20% buffer + 20% model uncertainty-deduction + 10% other updates):</t>
   </si>
+  <si>
+    <t>Adoption rate: 10%</t>
+  </si>
+  <si>
+    <t>Total ERs:</t>
+  </si>
 </sst>
 </file>
 
@@ -231,7 +237,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -290,6 +296,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -332,11 +346,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -352,13 +367,15 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -7253,16 +7270,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>454393</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>77551</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>769353</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>47071</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>85649</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>180217</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>400609</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>149737</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7766,16 +7783,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53C74460-226A-484F-A8DD-FFF53BF916A1}">
-  <dimension ref="A2:E44"/>
+  <dimension ref="A2:F44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="14.1640625" customWidth="1"/>
     <col min="3" max="3" width="13.33203125" customWidth="1"/>
     <col min="4" max="4" width="10.83203125" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -7788,8 +7806,11 @@
       <c r="E2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2" s="14" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>2026</v>
       </c>
@@ -7805,8 +7826,12 @@
         <f>SUM(B3:C3)</f>
         <v>821584.90334901295</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3" s="5">
+        <f>0.1*E3</f>
+        <v>82158.490334901304</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>2027</v>
       </c>
@@ -7821,8 +7846,12 @@
         <f t="shared" ref="E4:E42" si="0">SUM(B4:C4)</f>
         <v>439102.27272334381</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F4" s="5">
+        <f>0.2*E4</f>
+        <v>87820.45454466877</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>2028</v>
       </c>
@@ -7837,8 +7866,12 @@
         <f t="shared" si="0"/>
         <v>281025.89568057278</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5" s="5">
+        <f>0.3*E5</f>
+        <v>84307.768704171831</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>2029</v>
       </c>
@@ -7853,8 +7886,12 @@
         <f t="shared" si="0"/>
         <v>196094.14731331487</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6" s="5">
+        <f>0.4*E6</f>
+        <v>78437.658925325944</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>2030</v>
       </c>
@@ -7869,8 +7906,12 @@
         <f t="shared" si="0"/>
         <v>149079.05322744849</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="F7" s="5">
+        <f>0.5*E7</f>
+        <v>74539.526613724243</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>2031</v>
       </c>
@@ -7885,8 +7926,12 @@
         <f t="shared" si="0"/>
         <v>121969.80607606156</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="F8" s="5">
+        <f>0.6*E8</f>
+        <v>73181.883645636932</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>2032</v>
       </c>
@@ -7901,8 +7946,12 @@
         <f t="shared" si="0"/>
         <v>105426.99848537613</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="F9" s="5">
+        <f>0.7*E9</f>
+        <v>73798.898939763283</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>2033</v>
       </c>
@@ -7917,8 +7966,12 @@
         <f t="shared" si="0"/>
         <v>94565.621342954968</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="F10" s="5">
+        <f>0.8*E10</f>
+        <v>75652.497074363971</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>2034</v>
       </c>
@@ -7933,8 +7986,12 @@
         <f t="shared" si="0"/>
         <v>86815.617806178256</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="F11" s="5">
+        <f>0.9*E11</f>
+        <v>78134.056025560436</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>2035</v>
       </c>
@@ -7949,8 +8006,12 @@
         <f t="shared" si="0"/>
         <v>80818.214935822019</v>
       </c>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="F12" s="5">
+        <f>1*E12</f>
+        <v>80818.214935822019</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>2036</v>
       </c>
@@ -7965,8 +8026,12 @@
         <f t="shared" si="0"/>
         <v>75851.031860754927</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="F13" s="5">
+        <f>1*E13</f>
+        <v>75851.031860754927</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>2037</v>
       </c>
@@ -7981,8 +8046,12 @@
         <f>SUM(B14:C14)</f>
         <v>71526.95140630292</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="F14" s="5">
+        <f t="shared" ref="F14:F42" si="1">1*E14</f>
+        <v>71526.95140630292</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>2038</v>
       </c>
@@ -7997,8 +8066,12 @@
         <f t="shared" si="0"/>
         <v>67635.879475738519</v>
       </c>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="F15" s="5">
+        <f t="shared" si="1"/>
+        <v>67635.879475738519</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>2039</v>
       </c>
@@ -8013,8 +8086,12 @@
         <f t="shared" si="0"/>
         <v>64061.428399597622</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16" s="5">
+        <f t="shared" si="1"/>
+        <v>64061.428399597622</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>2040</v>
       </c>
@@ -8029,8 +8106,12 @@
         <f t="shared" si="0"/>
         <v>60736.991188713255</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17" s="5">
+        <f t="shared" si="1"/>
+        <v>60736.991188713255</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>2041</v>
       </c>
@@ -8045,8 +8126,12 @@
         <f t="shared" si="0"/>
         <v>57622.557538888817</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="F18" s="5">
+        <f t="shared" si="1"/>
+        <v>57622.557538888817</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>2042</v>
       </c>
@@ -8061,8 +8146,12 @@
         <f t="shared" si="0"/>
         <v>54692.462213103536</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="F19" s="5">
+        <f t="shared" si="1"/>
+        <v>54692.462213103536</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20">
         <v>2043</v>
       </c>
@@ -8077,8 +8166,12 @@
         <f t="shared" si="0"/>
         <v>51928.89948980209</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="F20" s="5">
+        <f t="shared" si="1"/>
+        <v>51928.89948980209</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>2044</v>
       </c>
@@ -8093,8 +8186,12 @@
         <f t="shared" si="0"/>
         <v>49318.480611395004</v>
       </c>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="F21" s="5">
+        <f t="shared" si="1"/>
+        <v>49318.480611395004</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22">
         <v>2045</v>
       </c>
@@ -8109,8 +8206,12 @@
         <f t="shared" si="0"/>
         <v>46850.398221670672</v>
       </c>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="F22" s="5">
+        <f t="shared" si="1"/>
+        <v>46850.398221670672</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23">
         <v>2046</v>
       </c>
@@ -8125,8 +8226,12 @@
         <f t="shared" si="0"/>
         <v>44515.440218805874</v>
       </c>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="F23" s="5">
+        <f t="shared" si="1"/>
+        <v>44515.440218805874</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24">
         <v>2047</v>
       </c>
@@ -8141,8 +8246,12 @@
         <f t="shared" si="0"/>
         <v>42305.453222623684</v>
       </c>
-    </row>
-    <row r="25" spans="1:5">
+      <c r="F24" s="5">
+        <f t="shared" si="1"/>
+        <v>42305.453222623684</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25">
         <v>2048</v>
       </c>
@@ -8157,8 +8266,12 @@
         <f t="shared" si="0"/>
         <v>40213.044580948837</v>
       </c>
-    </row>
-    <row r="26" spans="1:5">
+      <c r="F25" s="5">
+        <f t="shared" si="1"/>
+        <v>40213.044580948837</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26">
         <v>2049</v>
       </c>
@@ -8173,8 +8286,12 @@
         <f t="shared" si="0"/>
         <v>38231.411418136682</v>
       </c>
-    </row>
-    <row r="27" spans="1:5">
+      <c r="F26" s="5">
+        <f t="shared" si="1"/>
+        <v>38231.411418136682</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27">
         <v>2050</v>
       </c>
@@ -8189,8 +8306,12 @@
         <f t="shared" si="0"/>
         <v>36354.237781756718</v>
       </c>
-    </row>
-    <row r="28" spans="1:5">
+      <c r="F27" s="5">
+        <f t="shared" si="1"/>
+        <v>36354.237781756718</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28">
         <v>2051</v>
       </c>
@@ -8205,8 +8326,12 @@
         <f t="shared" si="0"/>
         <v>34575.628686041055</v>
       </c>
-    </row>
-    <row r="29" spans="1:5">
+      <c r="F28" s="5">
+        <f t="shared" si="1"/>
+        <v>34575.628686041055</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29">
         <v>2052</v>
       </c>
@@ -8221,8 +8346,12 @@
         <f t="shared" si="0"/>
         <v>32890.064501069988</v>
       </c>
-    </row>
-    <row r="30" spans="1:5">
+      <c r="F29" s="5">
+        <f t="shared" si="1"/>
+        <v>32890.064501069988</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30">
         <v>2053</v>
       </c>
@@ -8237,8 +8366,12 @@
         <f t="shared" si="0"/>
         <v>31292.366877145072</v>
       </c>
-    </row>
-    <row r="31" spans="1:5">
+      <c r="F30" s="5">
+        <f t="shared" si="1"/>
+        <v>31292.366877145072</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31">
         <v>2054</v>
       </c>
@@ -8253,8 +8386,12 @@
         <f t="shared" si="0"/>
         <v>29777.671486732157</v>
       </c>
-    </row>
-    <row r="32" spans="1:5">
+      <c r="F31" s="5">
+        <f t="shared" si="1"/>
+        <v>29777.671486732157</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32">
         <v>2055</v>
       </c>
@@ -8269,8 +8406,12 @@
         <f t="shared" si="0"/>
         <v>28341.405033236544</v>
       </c>
-    </row>
-    <row r="33" spans="1:5">
+      <c r="F32" s="5">
+        <f t="shared" si="1"/>
+        <v>28341.405033236544</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33">
         <v>2056</v>
       </c>
@@ -8285,8 +8426,12 @@
         <f t="shared" si="0"/>
         <v>26979.265125554244</v>
       </c>
-    </row>
-    <row r="34" spans="1:5">
+      <c r="F33" s="5">
+        <f t="shared" si="1"/>
+        <v>26979.265125554244</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34">
         <v>2057</v>
       </c>
@@ -8301,8 +8446,12 @@
         <f t="shared" si="0"/>
         <v>25687.202229242059</v>
       </c>
-    </row>
-    <row r="35" spans="1:5">
+      <c r="F34" s="5">
+        <f t="shared" si="1"/>
+        <v>25687.202229242059</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35">
         <v>2058</v>
       </c>
@@ -8317,8 +8466,12 @@
         <f t="shared" si="0"/>
         <v>24461.403232800763</v>
       </c>
-    </row>
-    <row r="36" spans="1:5">
+      <c r="F35" s="5">
+        <f t="shared" si="1"/>
+        <v>24461.403232800763</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36">
         <v>2059</v>
       </c>
@@ -8333,8 +8486,12 @@
         <f t="shared" si="0"/>
         <v>23298.276344703554</v>
       </c>
-    </row>
-    <row r="37" spans="1:5">
+      <c r="F36" s="5">
+        <f t="shared" si="1"/>
+        <v>23298.276344703554</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37">
         <v>2060</v>
       </c>
@@ -8349,8 +8506,12 @@
         <f t="shared" si="0"/>
         <v>22194.437133741587</v>
       </c>
-    </row>
-    <row r="38" spans="1:5">
+      <c r="F37" s="5">
+        <f t="shared" si="1"/>
+        <v>22194.437133741587</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38">
         <v>2061</v>
       </c>
@@ -8365,8 +8526,12 @@
         <f t="shared" si="0"/>
         <v>21146.695579998177</v>
       </c>
-    </row>
-    <row r="39" spans="1:5">
+      <c r="F38" s="5">
+        <f t="shared" si="1"/>
+        <v>21146.695579998177</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39">
         <v>2062</v>
       </c>
@@ -8381,8 +8546,12 @@
         <f t="shared" si="0"/>
         <v>20152.044035386793</v>
       </c>
-    </row>
-    <row r="40" spans="1:5">
+      <c r="F39" s="5">
+        <f t="shared" si="1"/>
+        <v>20152.044035386793</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40">
         <v>2063</v>
       </c>
@@ -8397,8 +8566,12 @@
         <f t="shared" si="0"/>
         <v>19207.646012163597</v>
       </c>
-    </row>
-    <row r="41" spans="1:5">
+      <c r="F40" s="5">
+        <f t="shared" si="1"/>
+        <v>19207.646012163597</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41">
         <v>2064</v>
       </c>
@@ -8413,8 +8586,12 @@
         <f t="shared" si="0"/>
         <v>18310.825730527624</v>
       </c>
-    </row>
-    <row r="42" spans="1:5">
+      <c r="F41" s="5">
+        <f t="shared" si="1"/>
+        <v>18310.825730527624</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42">
         <v>2065</v>
       </c>
@@ -8429,17 +8606,31 @@
         <f t="shared" si="0"/>
         <v>17459.058365121538</v>
       </c>
-    </row>
-    <row r="44" spans="1:5">
+      <c r="F42" s="5">
+        <f t="shared" si="1"/>
+        <v>17459.058365121538</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="D44" t="s">
+        <v>53</v>
+      </c>
       <c r="E44" s="5">
         <f>SUM(E3:E42)</f>
         <v>3554101.1889417893</v>
       </c>
+      <c r="F44" s="5">
+        <f>SUM(F3:F42)</f>
+        <v>1966468.1077456428</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{611845FF-8744-854D-B8AD-D4609FE516B6}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -9808,7 +9999,7 @@
         <f>F$3*F$2</f>
         <v>98.473650000000006</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="13">
         <f>SUM(B8:F8) * 0.5</f>
         <v>483.48297300000007</v>
       </c>
@@ -9837,7 +10028,7 @@
         <f t="shared" si="0"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H9" s="14">
+      <c r="H9" s="13">
         <f t="shared" ref="H9:H47" si="2">SUM(B9:F9) * 0.5</f>
         <v>483.48297300000007</v>
       </c>
@@ -9866,7 +10057,7 @@
         <f t="shared" si="0"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H10" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -9895,7 +10086,7 @@
         <f t="shared" si="0"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H11" s="14">
+      <c r="H11" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -9924,7 +10115,7 @@
         <f t="shared" si="0"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H12" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -9953,7 +10144,7 @@
         <f t="shared" si="0"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H13" s="14">
+      <c r="H13" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -9982,7 +10173,7 @@
         <f t="shared" si="0"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H14" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10011,7 +10202,7 @@
         <f t="shared" si="0"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H15" s="14">
+      <c r="H15" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10040,7 +10231,7 @@
         <f t="shared" si="0"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H16" s="14">
+      <c r="H16" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10069,7 +10260,7 @@
         <f t="shared" si="0"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H17" s="14">
+      <c r="H17" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10098,7 +10289,7 @@
         <f t="shared" si="0"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H18" s="14">
+      <c r="H18" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10127,7 +10318,7 @@
         <f t="shared" si="0"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H19" s="14">
+      <c r="H19" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10156,7 +10347,7 @@
         <f t="shared" si="0"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H20" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10185,7 +10376,7 @@
         <f t="shared" si="0"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H21" s="14">
+      <c r="H21" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10214,7 +10405,7 @@
         <f t="shared" si="0"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H22" s="14">
+      <c r="H22" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10243,7 +10434,7 @@
         <f t="shared" si="0"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H23" s="14">
+      <c r="H23" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10272,7 +10463,7 @@
         <f t="shared" si="1"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H24" s="14">
+      <c r="H24" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10301,7 +10492,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H25" s="14">
+      <c r="H25" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10330,7 +10521,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H26" s="14">
+      <c r="H26" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10359,7 +10550,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H27" s="14">
+      <c r="H27" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10388,7 +10579,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H28" s="14">
+      <c r="H28" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10417,7 +10608,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H29" s="14">
+      <c r="H29" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10446,7 +10637,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H30" s="14">
+      <c r="H30" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10475,7 +10666,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H31" s="14">
+      <c r="H31" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10504,7 +10695,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H32" s="14">
+      <c r="H32" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10533,7 +10724,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H33" s="14">
+      <c r="H33" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10562,7 +10753,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H34" s="14">
+      <c r="H34" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10591,7 +10782,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H35" s="14">
+      <c r="H35" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10620,7 +10811,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H36" s="14">
+      <c r="H36" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10649,7 +10840,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H37" s="14">
+      <c r="H37" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10678,7 +10869,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H38" s="14">
+      <c r="H38" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10707,7 +10898,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H39" s="14">
+      <c r="H39" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10736,7 +10927,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H40" s="14">
+      <c r="H40" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10765,7 +10956,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H41" s="14">
+      <c r="H41" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10794,7 +10985,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H42" s="14">
+      <c r="H42" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10823,7 +11014,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H43" s="14">
+      <c r="H43" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10852,7 +11043,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H44" s="14">
+      <c r="H44" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10881,7 +11072,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H45" s="14">
+      <c r="H45" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10910,7 +11101,7 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H46" s="14">
+      <c r="H46" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
@@ -10939,13 +11130,13 @@
         <f t="shared" si="3"/>
         <v>98.473650000000006</v>
       </c>
-      <c r="H47" s="14">
+      <c r="H47" s="13">
         <f t="shared" si="2"/>
         <v>483.48297300000007</v>
       </c>
     </row>
     <row r="49" spans="8:8">
-      <c r="H49" s="14">
+      <c r="H49" s="13">
         <f>SUM(H8:H47)</f>
         <v>19339.318919999991</v>
       </c>
@@ -15686,22 +15877,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="H1" s="13" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="H1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="9" t="s">

--- a/Realistic_ER_Estimate/ER_Summary.xlsx
+++ b/Realistic_ER_Estimate/ER_Summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mihirbendre/Documents/Gazelle/Gazelle_2026/Kenya_Project/Agricentric_SOC_Modeling/Realistic_ER_Estimate/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A021FB7B-F980-C34A-96B3-BAB0BAC40ACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15AA954A-780F-6144-9F6B-561EF27E11FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="29400" windowHeight="18400" xr2:uid="{72AD1D35-862B-EB40-AF7A-21135E5EFD45}"/>
+    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" xr2:uid="{72AD1D35-862B-EB40-AF7A-21135E5EFD45}"/>
   </bookViews>
   <sheets>
     <sheet name="Net_Summary" sheetId="9" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="65">
   <si>
     <t>Nth</t>
   </si>
@@ -229,6 +229,39 @@
   <si>
     <t>Total ERs:</t>
   </si>
+  <si>
+    <t>Yr 1</t>
+  </si>
+  <si>
+    <t>Yr 2</t>
+  </si>
+  <si>
+    <t>Yr 3</t>
+  </si>
+  <si>
+    <t>Yr 4</t>
+  </si>
+  <si>
+    <t>Yr 5</t>
+  </si>
+  <si>
+    <t>Yr 6</t>
+  </si>
+  <si>
+    <t>Yr 7</t>
+  </si>
+  <si>
+    <t>Yr 8</t>
+  </si>
+  <si>
+    <t>Yr 9</t>
+  </si>
+  <si>
+    <t>Yr 10</t>
+  </si>
+  <si>
+    <t>Year in which farmers adopt practice</t>
+  </si>
 </sst>
 </file>
 
@@ -351,7 +384,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -370,6 +403,9 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -7270,16 +7306,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>769353</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>47071</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>669907</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>202698</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>400609</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>149737</xdr:rowOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>304903</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>101776</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7783,17 +7819,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53C74460-226A-484F-A8DD-FFF53BF916A1}">
-  <dimension ref="A2:F44"/>
+  <dimension ref="A1:R44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="14.1640625" customWidth="1"/>
     <col min="3" max="3" width="13.33203125" customWidth="1"/>
     <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="13.6640625" customWidth="1"/>
+    <col min="5" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="17.83203125" customWidth="1"/>
+    <col min="8" max="8" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6">
+    <row r="1" spans="1:18">
+      <c r="I1" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -7806,11 +7858,41 @@
       <c r="E2" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="G2" s="14" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="I2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K2" t="s">
+        <v>56</v>
+      </c>
+      <c r="L2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M2" t="s">
+        <v>58</v>
+      </c>
+      <c r="N2" t="s">
+        <v>59</v>
+      </c>
+      <c r="O2" t="s">
+        <v>60</v>
+      </c>
+      <c r="P2" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>62</v>
+      </c>
+      <c r="R2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3">
         <v>2026</v>
       </c>
@@ -7826,12 +7908,17 @@
         <f>SUM(B3:C3)</f>
         <v>821584.90334901295</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="5"/>
+      <c r="G3" s="5">
+        <f>SUM(I3:R3)</f>
+        <v>82158.490334901304</v>
+      </c>
+      <c r="I3" s="5">
         <f>0.1*E3</f>
         <v>82158.490334901304</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:18">
       <c r="A4">
         <v>2027</v>
       </c>
@@ -7846,12 +7933,21 @@
         <f t="shared" ref="E4:E42" si="0">SUM(B4:C4)</f>
         <v>439102.27272334381</v>
       </c>
-      <c r="F4" s="5">
-        <f>0.2*E4</f>
-        <v>87820.45454466877</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="F4" s="5"/>
+      <c r="G4" s="5">
+        <f>SUM(I4:R4)</f>
+        <v>126068.71760723568</v>
+      </c>
+      <c r="I4" s="5">
+        <f>0.1*E4</f>
+        <v>43910.227272334385</v>
+      </c>
+      <c r="J4" s="5">
+        <f>0.1*E3</f>
+        <v>82158.490334901304</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5">
         <v>2028</v>
       </c>
@@ -7866,12 +7962,25 @@
         <f t="shared" si="0"/>
         <v>281025.89568057278</v>
       </c>
-      <c r="F5" s="5">
-        <f>0.3*E5</f>
-        <v>84307.768704171831</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="F5" s="5"/>
+      <c r="G5" s="5">
+        <f t="shared" ref="G4:G42" si="1">SUM(I5:R5)</f>
+        <v>154171.30717529298</v>
+      </c>
+      <c r="I5" s="5">
+        <f>0.1*E5</f>
+        <v>28102.589568057279</v>
+      </c>
+      <c r="J5" s="5">
+        <f>0.1*E4</f>
+        <v>43910.227272334385</v>
+      </c>
+      <c r="K5" s="5">
+        <f>0.1*E3</f>
+        <v>82158.490334901304</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6">
         <v>2029</v>
       </c>
@@ -7886,12 +7995,29 @@
         <f t="shared" si="0"/>
         <v>196094.14731331487</v>
       </c>
-      <c r="F6" s="5">
-        <f>0.4*E6</f>
-        <v>78437.658925325944</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="F6" s="5"/>
+      <c r="G6" s="5">
+        <f t="shared" si="1"/>
+        <v>173780.72190662444</v>
+      </c>
+      <c r="I6" s="5">
+        <f>0.1*E6</f>
+        <v>19609.414731331486</v>
+      </c>
+      <c r="J6" s="5">
+        <f>0.1*E5</f>
+        <v>28102.589568057279</v>
+      </c>
+      <c r="K6" s="5">
+        <f>0.1*E4</f>
+        <v>43910.227272334385</v>
+      </c>
+      <c r="L6" s="5">
+        <f>0.1*E3</f>
+        <v>82158.490334901304</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7">
         <v>2030</v>
       </c>
@@ -7906,12 +8032,33 @@
         <f t="shared" si="0"/>
         <v>149079.05322744849</v>
       </c>
-      <c r="F7" s="5">
-        <f>0.5*E7</f>
-        <v>74539.526613724243</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="F7" s="5"/>
+      <c r="G7" s="5">
+        <f t="shared" si="1"/>
+        <v>188688.6272293693</v>
+      </c>
+      <c r="I7" s="5">
+        <f>0.1*E7</f>
+        <v>14907.905322744849</v>
+      </c>
+      <c r="J7" s="5">
+        <f>0.1*E6</f>
+        <v>19609.414731331486</v>
+      </c>
+      <c r="K7" s="5">
+        <f>0.1*E5</f>
+        <v>28102.589568057279</v>
+      </c>
+      <c r="L7" s="5">
+        <f>0.1*E4</f>
+        <v>43910.227272334385</v>
+      </c>
+      <c r="M7" s="5">
+        <f>0.1*E3</f>
+        <v>82158.490334901304</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8">
         <v>2031</v>
       </c>
@@ -7926,12 +8073,37 @@
         <f t="shared" si="0"/>
         <v>121969.80607606156</v>
       </c>
-      <c r="F8" s="5">
-        <f>0.6*E8</f>
-        <v>73181.883645636932</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="F8" s="5"/>
+      <c r="G8" s="5">
+        <f t="shared" si="1"/>
+        <v>200885.60783697548</v>
+      </c>
+      <c r="I8" s="5">
+        <f>0.1*E8</f>
+        <v>12196.980607606158</v>
+      </c>
+      <c r="J8" s="5">
+        <f>0.1*E7</f>
+        <v>14907.905322744849</v>
+      </c>
+      <c r="K8" s="5">
+        <f>0.1*E6</f>
+        <v>19609.414731331486</v>
+      </c>
+      <c r="L8" s="5">
+        <f>0.1*E5</f>
+        <v>28102.589568057279</v>
+      </c>
+      <c r="M8" s="5">
+        <f>0.1*E4</f>
+        <v>43910.227272334385</v>
+      </c>
+      <c r="N8" s="5">
+        <f>0.1*E3</f>
+        <v>82158.490334901304</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9">
         <v>2032</v>
       </c>
@@ -7946,12 +8118,41 @@
         <f t="shared" si="0"/>
         <v>105426.99848537613</v>
       </c>
-      <c r="F9" s="5">
-        <f>0.7*E9</f>
-        <v>73798.898939763283</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="F9" s="5"/>
+      <c r="G9" s="5">
+        <f t="shared" si="1"/>
+        <v>211428.30768551311</v>
+      </c>
+      <c r="I9" s="5">
+        <f>0.1*E9</f>
+        <v>10542.699848537613</v>
+      </c>
+      <c r="J9" s="5">
+        <f>0.1*E8</f>
+        <v>12196.980607606158</v>
+      </c>
+      <c r="K9" s="5">
+        <f>0.1*E7</f>
+        <v>14907.905322744849</v>
+      </c>
+      <c r="L9" s="5">
+        <f>0.1*E6</f>
+        <v>19609.414731331486</v>
+      </c>
+      <c r="M9" s="5">
+        <f>0.1*E5</f>
+        <v>28102.589568057279</v>
+      </c>
+      <c r="N9" s="5">
+        <f>0.1*E4</f>
+        <v>43910.227272334385</v>
+      </c>
+      <c r="O9" s="5">
+        <f>0.1*E3</f>
+        <v>82158.490334901304</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
       <c r="A10">
         <v>2033</v>
       </c>
@@ -7966,12 +8167,45 @@
         <f t="shared" si="0"/>
         <v>94565.621342954968</v>
       </c>
-      <c r="F10" s="5">
-        <f>0.8*E10</f>
-        <v>75652.497074363971</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="F10" s="5"/>
+      <c r="G10" s="5">
+        <f t="shared" si="1"/>
+        <v>220884.86981980858</v>
+      </c>
+      <c r="I10" s="5">
+        <f>0.1*E10</f>
+        <v>9456.5621342954964</v>
+      </c>
+      <c r="J10" s="5">
+        <f>0.1*E9</f>
+        <v>10542.699848537613</v>
+      </c>
+      <c r="K10" s="5">
+        <f>0.1*E8</f>
+        <v>12196.980607606158</v>
+      </c>
+      <c r="L10" s="5">
+        <f>0.1*E7</f>
+        <v>14907.905322744849</v>
+      </c>
+      <c r="M10" s="5">
+        <f>0.1*E6</f>
+        <v>19609.414731331486</v>
+      </c>
+      <c r="N10" s="5">
+        <f>0.1*E5</f>
+        <v>28102.589568057279</v>
+      </c>
+      <c r="O10" s="5">
+        <f>0.1*E4</f>
+        <v>43910.227272334385</v>
+      </c>
+      <c r="P10" s="5">
+        <f>0.1*E3</f>
+        <v>82158.490334901304</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11">
         <v>2034</v>
       </c>
@@ -7986,12 +8220,49 @@
         <f t="shared" si="0"/>
         <v>86815.617806178256</v>
       </c>
-      <c r="F11" s="5">
-        <f>0.9*E11</f>
-        <v>78134.056025560436</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="F11" s="5"/>
+      <c r="G11" s="5">
+        <f t="shared" si="1"/>
+        <v>229566.43160042638</v>
+      </c>
+      <c r="I11" s="5">
+        <f>0.1*E11</f>
+        <v>8681.5617806178252</v>
+      </c>
+      <c r="J11" s="5">
+        <f>0.1*E10</f>
+        <v>9456.5621342954964</v>
+      </c>
+      <c r="K11" s="5">
+        <f>0.1*E9</f>
+        <v>10542.699848537613</v>
+      </c>
+      <c r="L11" s="5">
+        <f>0.1*E8</f>
+        <v>12196.980607606158</v>
+      </c>
+      <c r="M11" s="5">
+        <f>0.1*E7</f>
+        <v>14907.905322744849</v>
+      </c>
+      <c r="N11" s="5">
+        <f>0.1*E6</f>
+        <v>19609.414731331486</v>
+      </c>
+      <c r="O11" s="5">
+        <f>0.1*E5</f>
+        <v>28102.589568057279</v>
+      </c>
+      <c r="P11" s="5">
+        <f>0.1*E4</f>
+        <v>43910.227272334385</v>
+      </c>
+      <c r="Q11" s="5">
+        <f>0.1*E3</f>
+        <v>82158.490334901304</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12">
         <v>2035</v>
       </c>
@@ -8006,12 +8277,53 @@
         <f t="shared" si="0"/>
         <v>80818.214935822019</v>
       </c>
-      <c r="F12" s="5">
-        <f>1*E12</f>
-        <v>80818.214935822019</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="F12" s="5"/>
+      <c r="G12" s="5">
+        <f t="shared" si="1"/>
+        <v>237648.2530940086</v>
+      </c>
+      <c r="I12" s="5">
+        <f>0.1*E12</f>
+        <v>8081.8214935822025</v>
+      </c>
+      <c r="J12" s="5">
+        <f>0.1*E11</f>
+        <v>8681.5617806178252</v>
+      </c>
+      <c r="K12" s="5">
+        <f>0.1*E10</f>
+        <v>9456.5621342954964</v>
+      </c>
+      <c r="L12" s="5">
+        <f>0.1*E9</f>
+        <v>10542.699848537613</v>
+      </c>
+      <c r="M12" s="5">
+        <f>0.1*E8</f>
+        <v>12196.980607606158</v>
+      </c>
+      <c r="N12" s="5">
+        <f>0.1*E7</f>
+        <v>14907.905322744849</v>
+      </c>
+      <c r="O12" s="5">
+        <f>0.1*E6</f>
+        <v>19609.414731331486</v>
+      </c>
+      <c r="P12" s="5">
+        <f>0.1*E5</f>
+        <v>28102.589568057279</v>
+      </c>
+      <c r="Q12" s="5">
+        <f>0.1*E4</f>
+        <v>43910.227272334385</v>
+      </c>
+      <c r="R12" s="5">
+        <f>0.1*E3</f>
+        <v>82158.490334901304</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="A13">
         <v>2036</v>
       </c>
@@ -8026,12 +8338,53 @@
         <f t="shared" si="0"/>
         <v>75851.031860754927</v>
       </c>
-      <c r="F13" s="5">
-        <f>1*E13</f>
-        <v>75851.031860754927</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="F13" s="5"/>
+      <c r="G13" s="5">
+        <f t="shared" si="1"/>
+        <v>163074.8659451828</v>
+      </c>
+      <c r="I13" s="5">
+        <f>0.1*E13</f>
+        <v>7585.1031860754929</v>
+      </c>
+      <c r="J13" s="5">
+        <f>0.1*E12</f>
+        <v>8081.8214935822025</v>
+      </c>
+      <c r="K13" s="5">
+        <f>0.1*E11</f>
+        <v>8681.5617806178252</v>
+      </c>
+      <c r="L13" s="5">
+        <f>0.1*E10</f>
+        <v>9456.5621342954964</v>
+      </c>
+      <c r="M13" s="5">
+        <f>0.1*E9</f>
+        <v>10542.699848537613</v>
+      </c>
+      <c r="N13" s="5">
+        <f>0.1*E8</f>
+        <v>12196.980607606158</v>
+      </c>
+      <c r="O13" s="5">
+        <f>0.1*E7</f>
+        <v>14907.905322744849</v>
+      </c>
+      <c r="P13" s="5">
+        <f>0.1*E6</f>
+        <v>19609.414731331486</v>
+      </c>
+      <c r="Q13" s="5">
+        <f>0.1*E5</f>
+        <v>28102.589568057279</v>
+      </c>
+      <c r="R13" s="5">
+        <f>0.1*E4</f>
+        <v>43910.227272334385</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
       <c r="A14">
         <v>2037</v>
       </c>
@@ -8046,12 +8399,53 @@
         <f>SUM(B14:C14)</f>
         <v>71526.95140630292</v>
       </c>
-      <c r="F14" s="5">
-        <f t="shared" ref="F14:F42" si="1">1*E14</f>
-        <v>71526.95140630292</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="F14" s="5"/>
+      <c r="G14" s="5">
+        <f t="shared" si="1"/>
+        <v>126317.3338134787</v>
+      </c>
+      <c r="I14" s="5">
+        <f>0.1*E14</f>
+        <v>7152.6951406302924</v>
+      </c>
+      <c r="J14" s="5">
+        <f>0.1*E13</f>
+        <v>7585.1031860754929</v>
+      </c>
+      <c r="K14" s="5">
+        <f>0.1*E12</f>
+        <v>8081.8214935822025</v>
+      </c>
+      <c r="L14" s="5">
+        <f>0.1*E11</f>
+        <v>8681.5617806178252</v>
+      </c>
+      <c r="M14" s="5">
+        <f>0.1*E10</f>
+        <v>9456.5621342954964</v>
+      </c>
+      <c r="N14" s="5">
+        <f>0.1*E9</f>
+        <v>10542.699848537613</v>
+      </c>
+      <c r="O14" s="5">
+        <f>0.1*E8</f>
+        <v>12196.980607606158</v>
+      </c>
+      <c r="P14" s="5">
+        <f>0.1*E7</f>
+        <v>14907.905322744849</v>
+      </c>
+      <c r="Q14" s="5">
+        <f>0.1*E6</f>
+        <v>19609.414731331486</v>
+      </c>
+      <c r="R14" s="5">
+        <f>0.1*E5</f>
+        <v>28102.589568057279</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15">
         <v>2038</v>
       </c>
@@ -8066,12 +8460,53 @@
         <f t="shared" si="0"/>
         <v>67635.879475738519</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="5"/>
+      <c r="G15" s="5">
         <f t="shared" si="1"/>
-        <v>67635.879475738519</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>104978.33219299528</v>
+      </c>
+      <c r="I15" s="5">
+        <f>0.1*E15</f>
+        <v>6763.587947573852</v>
+      </c>
+      <c r="J15" s="5">
+        <f>0.1*E14</f>
+        <v>7152.6951406302924</v>
+      </c>
+      <c r="K15" s="5">
+        <f>0.1*E13</f>
+        <v>7585.1031860754929</v>
+      </c>
+      <c r="L15" s="5">
+        <f>0.1*E12</f>
+        <v>8081.8214935822025</v>
+      </c>
+      <c r="M15" s="5">
+        <f>0.1*E11</f>
+        <v>8681.5617806178252</v>
+      </c>
+      <c r="N15" s="5">
+        <f>0.1*E10</f>
+        <v>9456.5621342954964</v>
+      </c>
+      <c r="O15" s="5">
+        <f>0.1*E9</f>
+        <v>10542.699848537613</v>
+      </c>
+      <c r="P15" s="5">
+        <f>0.1*E8</f>
+        <v>12196.980607606158</v>
+      </c>
+      <c r="Q15" s="5">
+        <f>0.1*E7</f>
+        <v>14907.905322744849</v>
+      </c>
+      <c r="R15" s="5">
+        <f>0.1*E6</f>
+        <v>19609.414731331486</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
       <c r="A16">
         <v>2039</v>
       </c>
@@ -8086,12 +8521,53 @@
         <f t="shared" si="0"/>
         <v>64061.428399597622</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="5"/>
+      <c r="G16" s="5">
         <f t="shared" si="1"/>
-        <v>64061.428399597622</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>91775.060301623555</v>
+      </c>
+      <c r="I16" s="5">
+        <f>0.1*E16</f>
+        <v>6406.1428399597626</v>
+      </c>
+      <c r="J16" s="5">
+        <f>0.1*E15</f>
+        <v>6763.587947573852</v>
+      </c>
+      <c r="K16" s="5">
+        <f>0.1*E14</f>
+        <v>7152.6951406302924</v>
+      </c>
+      <c r="L16" s="5">
+        <f>0.1*E13</f>
+        <v>7585.1031860754929</v>
+      </c>
+      <c r="M16" s="5">
+        <f>0.1*E12</f>
+        <v>8081.8214935822025</v>
+      </c>
+      <c r="N16" s="5">
+        <f>0.1*E11</f>
+        <v>8681.5617806178252</v>
+      </c>
+      <c r="O16" s="5">
+        <f>0.1*E10</f>
+        <v>9456.5621342954964</v>
+      </c>
+      <c r="P16" s="5">
+        <f>0.1*E9</f>
+        <v>10542.699848537613</v>
+      </c>
+      <c r="Q16" s="5">
+        <f>0.1*E8</f>
+        <v>12196.980607606158</v>
+      </c>
+      <c r="R16" s="5">
+        <f>0.1*E7</f>
+        <v>14907.905322744849</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
       <c r="A17">
         <v>2040</v>
       </c>
@@ -8106,12 +8582,53 @@
         <f t="shared" si="0"/>
         <v>60736.991188713255</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="5"/>
+      <c r="G17" s="5">
         <f t="shared" si="1"/>
-        <v>60736.991188713255</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <v>82940.854097750038</v>
+      </c>
+      <c r="I17" s="5">
+        <f>0.1*E17</f>
+        <v>6073.6991188713255</v>
+      </c>
+      <c r="J17" s="5">
+        <f>0.1*E16</f>
+        <v>6406.1428399597626</v>
+      </c>
+      <c r="K17" s="5">
+        <f>0.1*E15</f>
+        <v>6763.587947573852</v>
+      </c>
+      <c r="L17" s="5">
+        <f>0.1*E14</f>
+        <v>7152.6951406302924</v>
+      </c>
+      <c r="M17" s="5">
+        <f>0.1*E13</f>
+        <v>7585.1031860754929</v>
+      </c>
+      <c r="N17" s="5">
+        <f>0.1*E12</f>
+        <v>8081.8214935822025</v>
+      </c>
+      <c r="O17" s="5">
+        <f>0.1*E11</f>
+        <v>8681.5617806178252</v>
+      </c>
+      <c r="P17" s="5">
+        <f>0.1*E10</f>
+        <v>9456.5621342954964</v>
+      </c>
+      <c r="Q17" s="5">
+        <f>0.1*E9</f>
+        <v>10542.699848537613</v>
+      </c>
+      <c r="R17" s="5">
+        <f>0.1*E8</f>
+        <v>12196.980607606158</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18">
         <v>2041</v>
       </c>
@@ -8126,12 +8643,53 @@
         <f t="shared" si="0"/>
         <v>57622.557538888817</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="5"/>
+      <c r="G18" s="5">
         <f t="shared" si="1"/>
-        <v>57622.557538888817</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+        <v>76506.129244032752</v>
+      </c>
+      <c r="I18" s="5">
+        <f>0.1*E18</f>
+        <v>5762.2557538888823</v>
+      </c>
+      <c r="J18" s="5">
+        <f>0.1*E17</f>
+        <v>6073.6991188713255</v>
+      </c>
+      <c r="K18" s="5">
+        <f>0.1*E16</f>
+        <v>6406.1428399597626</v>
+      </c>
+      <c r="L18" s="5">
+        <f>0.1*E15</f>
+        <v>6763.587947573852</v>
+      </c>
+      <c r="M18" s="5">
+        <f>0.1*E14</f>
+        <v>7152.6951406302924</v>
+      </c>
+      <c r="N18" s="5">
+        <f>0.1*E13</f>
+        <v>7585.1031860754929</v>
+      </c>
+      <c r="O18" s="5">
+        <f>0.1*E12</f>
+        <v>8081.8214935822025</v>
+      </c>
+      <c r="P18" s="5">
+        <f>0.1*E11</f>
+        <v>8681.5617806178252</v>
+      </c>
+      <c r="Q18" s="5">
+        <f>0.1*E10</f>
+        <v>9456.5621342954964</v>
+      </c>
+      <c r="R18" s="5">
+        <f>0.1*E9</f>
+        <v>10542.699848537613</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
       <c r="A19">
         <v>2042</v>
       </c>
@@ -8146,12 +8704,53 @@
         <f t="shared" si="0"/>
         <v>54692.462213103536</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="5"/>
+      <c r="G19" s="5">
         <f t="shared" si="1"/>
-        <v>54692.462213103536</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+        <v>71432.675616805485</v>
+      </c>
+      <c r="I19" s="5">
+        <f>0.1*E19</f>
+        <v>5469.2462213103536</v>
+      </c>
+      <c r="J19" s="5">
+        <f>0.1*E18</f>
+        <v>5762.2557538888823</v>
+      </c>
+      <c r="K19" s="5">
+        <f>0.1*E17</f>
+        <v>6073.6991188713255</v>
+      </c>
+      <c r="L19" s="5">
+        <f>0.1*E16</f>
+        <v>6406.1428399597626</v>
+      </c>
+      <c r="M19" s="5">
+        <f>0.1*E15</f>
+        <v>6763.587947573852</v>
+      </c>
+      <c r="N19" s="5">
+        <f>0.1*E14</f>
+        <v>7152.6951406302924</v>
+      </c>
+      <c r="O19" s="5">
+        <f>0.1*E13</f>
+        <v>7585.1031860754929</v>
+      </c>
+      <c r="P19" s="5">
+        <f>0.1*E12</f>
+        <v>8081.8214935822025</v>
+      </c>
+      <c r="Q19" s="5">
+        <f>0.1*E11</f>
+        <v>8681.5617806178252</v>
+      </c>
+      <c r="R19" s="5">
+        <f>0.1*E10</f>
+        <v>9456.5621342954964</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
       <c r="A20">
         <v>2043</v>
       </c>
@@ -8166,12 +8765,53 @@
         <f t="shared" si="0"/>
         <v>51928.89948980209</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20" s="5"/>
+      <c r="G20" s="5">
         <f t="shared" si="1"/>
-        <v>51928.89948980209</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+        <v>67169.0034314902</v>
+      </c>
+      <c r="I20" s="5">
+        <f>0.1*E20</f>
+        <v>5192.8899489802097</v>
+      </c>
+      <c r="J20" s="5">
+        <f>0.1*E19</f>
+        <v>5469.2462213103536</v>
+      </c>
+      <c r="K20" s="5">
+        <f>0.1*E18</f>
+        <v>5762.2557538888823</v>
+      </c>
+      <c r="L20" s="5">
+        <f>0.1*E17</f>
+        <v>6073.6991188713255</v>
+      </c>
+      <c r="M20" s="5">
+        <f>0.1*E16</f>
+        <v>6406.1428399597626</v>
+      </c>
+      <c r="N20" s="5">
+        <f>0.1*E15</f>
+        <v>6763.587947573852</v>
+      </c>
+      <c r="O20" s="5">
+        <f>0.1*E14</f>
+        <v>7152.6951406302924</v>
+      </c>
+      <c r="P20" s="5">
+        <f>0.1*E13</f>
+        <v>7585.1031860754929</v>
+      </c>
+      <c r="Q20" s="5">
+        <f>0.1*E12</f>
+        <v>8081.8214935822025</v>
+      </c>
+      <c r="R20" s="5">
+        <f>0.1*E11</f>
+        <v>8681.5617806178252</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
       <c r="A21">
         <v>2044</v>
       </c>
@@ -8186,12 +8826,53 @@
         <f t="shared" si="0"/>
         <v>49318.480611395004</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F21" s="5"/>
+      <c r="G21" s="5">
         <f t="shared" si="1"/>
-        <v>49318.480611395004</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+        <v>63419.28971201188</v>
+      </c>
+      <c r="I21" s="5">
+        <f>0.1*E21</f>
+        <v>4931.8480611395007</v>
+      </c>
+      <c r="J21" s="5">
+        <f>0.1*E20</f>
+        <v>5192.8899489802097</v>
+      </c>
+      <c r="K21" s="5">
+        <f>0.1*E19</f>
+        <v>5469.2462213103536</v>
+      </c>
+      <c r="L21" s="5">
+        <f>0.1*E18</f>
+        <v>5762.2557538888823</v>
+      </c>
+      <c r="M21" s="5">
+        <f>0.1*E17</f>
+        <v>6073.6991188713255</v>
+      </c>
+      <c r="N21" s="5">
+        <f>0.1*E16</f>
+        <v>6406.1428399597626</v>
+      </c>
+      <c r="O21" s="5">
+        <f>0.1*E15</f>
+        <v>6763.587947573852</v>
+      </c>
+      <c r="P21" s="5">
+        <f>0.1*E14</f>
+        <v>7152.6951406302924</v>
+      </c>
+      <c r="Q21" s="5">
+        <f>0.1*E13</f>
+        <v>7585.1031860754929</v>
+      </c>
+      <c r="R21" s="5">
+        <f>0.1*E12</f>
+        <v>8081.8214935822025</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
       <c r="A22">
         <v>2045</v>
       </c>
@@ -8206,12 +8887,53 @@
         <f t="shared" si="0"/>
         <v>46850.398221670672</v>
       </c>
-      <c r="F22" s="5">
+      <c r="F22" s="5"/>
+      <c r="G22" s="5">
         <f t="shared" si="1"/>
-        <v>46850.398221670672</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+        <v>60022.508040596746</v>
+      </c>
+      <c r="I22" s="5">
+        <f>0.1*E22</f>
+        <v>4685.0398221670675</v>
+      </c>
+      <c r="J22" s="5">
+        <f>0.1*E21</f>
+        <v>4931.8480611395007</v>
+      </c>
+      <c r="K22" s="5">
+        <f>0.1*E20</f>
+        <v>5192.8899489802097</v>
+      </c>
+      <c r="L22" s="5">
+        <f>0.1*E19</f>
+        <v>5469.2462213103536</v>
+      </c>
+      <c r="M22" s="5">
+        <f>0.1*E18</f>
+        <v>5762.2557538888823</v>
+      </c>
+      <c r="N22" s="5">
+        <f>0.1*E17</f>
+        <v>6073.6991188713255</v>
+      </c>
+      <c r="O22" s="5">
+        <f>0.1*E16</f>
+        <v>6406.1428399597626</v>
+      </c>
+      <c r="P22" s="5">
+        <f>0.1*E15</f>
+        <v>6763.587947573852</v>
+      </c>
+      <c r="Q22" s="5">
+        <f>0.1*E14</f>
+        <v>7152.6951406302924</v>
+      </c>
+      <c r="R22" s="5">
+        <f>0.1*E13</f>
+        <v>7585.1031860754929</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
       <c r="A23">
         <v>2046</v>
       </c>
@@ -8226,12 +8948,53 @@
         <f t="shared" si="0"/>
         <v>44515.440218805874</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23" s="5"/>
+      <c r="G23" s="5">
         <f t="shared" si="1"/>
-        <v>44515.440218805874</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+        <v>56888.948876401832</v>
+      </c>
+      <c r="I23" s="5">
+        <f>0.1*E23</f>
+        <v>4451.5440218805879</v>
+      </c>
+      <c r="J23" s="5">
+        <f>0.1*E22</f>
+        <v>4685.0398221670675</v>
+      </c>
+      <c r="K23" s="5">
+        <f>0.1*E21</f>
+        <v>4931.8480611395007</v>
+      </c>
+      <c r="L23" s="5">
+        <f>0.1*E20</f>
+        <v>5192.8899489802097</v>
+      </c>
+      <c r="M23" s="5">
+        <f>0.1*E19</f>
+        <v>5469.2462213103536</v>
+      </c>
+      <c r="N23" s="5">
+        <f>0.1*E18</f>
+        <v>5762.2557538888823</v>
+      </c>
+      <c r="O23" s="5">
+        <f>0.1*E17</f>
+        <v>6073.6991188713255</v>
+      </c>
+      <c r="P23" s="5">
+        <f>0.1*E16</f>
+        <v>6406.1428399597626</v>
+      </c>
+      <c r="Q23" s="5">
+        <f>0.1*E15</f>
+        <v>6763.587947573852</v>
+      </c>
+      <c r="R23" s="5">
+        <f>0.1*E14</f>
+        <v>7152.6951406302924</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
       <c r="A24">
         <v>2047</v>
       </c>
@@ -8246,12 +9009,53 @@
         <f t="shared" si="0"/>
         <v>42305.453222623684</v>
       </c>
-      <c r="F24" s="5">
+      <c r="F24" s="5"/>
+      <c r="G24" s="5">
         <f t="shared" si="1"/>
-        <v>42305.453222623684</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+        <v>53966.799058033917</v>
+      </c>
+      <c r="I24" s="5">
+        <f>0.1*E24</f>
+        <v>4230.5453222623682</v>
+      </c>
+      <c r="J24" s="5">
+        <f>0.1*E23</f>
+        <v>4451.5440218805879</v>
+      </c>
+      <c r="K24" s="5">
+        <f>0.1*E22</f>
+        <v>4685.0398221670675</v>
+      </c>
+      <c r="L24" s="5">
+        <f>0.1*E21</f>
+        <v>4931.8480611395007</v>
+      </c>
+      <c r="M24" s="5">
+        <f>0.1*E20</f>
+        <v>5192.8899489802097</v>
+      </c>
+      <c r="N24" s="5">
+        <f>0.1*E19</f>
+        <v>5469.2462213103536</v>
+      </c>
+      <c r="O24" s="5">
+        <f>0.1*E18</f>
+        <v>5762.2557538888823</v>
+      </c>
+      <c r="P24" s="5">
+        <f>0.1*E17</f>
+        <v>6073.6991188713255</v>
+      </c>
+      <c r="Q24" s="5">
+        <f>0.1*E16</f>
+        <v>6406.1428399597626</v>
+      </c>
+      <c r="R24" s="5">
+        <f>0.1*E15</f>
+        <v>6763.587947573852</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
       <c r="A25">
         <v>2048</v>
       </c>
@@ -8266,12 +9070,53 @@
         <f t="shared" si="0"/>
         <v>40213.044580948837</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F25" s="5"/>
+      <c r="G25" s="5">
         <f t="shared" si="1"/>
-        <v>40213.044580948837</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+        <v>51224.51556855494</v>
+      </c>
+      <c r="I25" s="5">
+        <f>0.1*E25</f>
+        <v>4021.304458094884</v>
+      </c>
+      <c r="J25" s="5">
+        <f>0.1*E24</f>
+        <v>4230.5453222623682</v>
+      </c>
+      <c r="K25" s="5">
+        <f>0.1*E23</f>
+        <v>4451.5440218805879</v>
+      </c>
+      <c r="L25" s="5">
+        <f>0.1*E22</f>
+        <v>4685.0398221670675</v>
+      </c>
+      <c r="M25" s="5">
+        <f>0.1*E21</f>
+        <v>4931.8480611395007</v>
+      </c>
+      <c r="N25" s="5">
+        <f>0.1*E20</f>
+        <v>5192.8899489802097</v>
+      </c>
+      <c r="O25" s="5">
+        <f>0.1*E19</f>
+        <v>5469.2462213103536</v>
+      </c>
+      <c r="P25" s="5">
+        <f>0.1*E18</f>
+        <v>5762.2557538888823</v>
+      </c>
+      <c r="Q25" s="5">
+        <f>0.1*E17</f>
+        <v>6073.6991188713255</v>
+      </c>
+      <c r="R25" s="5">
+        <f>0.1*E16</f>
+        <v>6406.1428399597626</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
       <c r="A26">
         <v>2049</v>
       </c>
@@ -8286,12 +9131,53 @@
         <f t="shared" si="0"/>
         <v>38231.411418136682</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F26" s="5"/>
+      <c r="G26" s="5">
         <f t="shared" si="1"/>
-        <v>38231.411418136682</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+        <v>48641.513870408846</v>
+      </c>
+      <c r="I26" s="5">
+        <f>0.1*E26</f>
+        <v>3823.1411418136686</v>
+      </c>
+      <c r="J26" s="5">
+        <f>0.1*E25</f>
+        <v>4021.304458094884</v>
+      </c>
+      <c r="K26" s="5">
+        <f>0.1*E24</f>
+        <v>4230.5453222623682</v>
+      </c>
+      <c r="L26" s="5">
+        <f>0.1*E23</f>
+        <v>4451.5440218805879</v>
+      </c>
+      <c r="M26" s="5">
+        <f>0.1*E22</f>
+        <v>4685.0398221670675</v>
+      </c>
+      <c r="N26" s="5">
+        <f>0.1*E21</f>
+        <v>4931.8480611395007</v>
+      </c>
+      <c r="O26" s="5">
+        <f>0.1*E20</f>
+        <v>5192.8899489802097</v>
+      </c>
+      <c r="P26" s="5">
+        <f>0.1*E19</f>
+        <v>5469.2462213103536</v>
+      </c>
+      <c r="Q26" s="5">
+        <f>0.1*E18</f>
+        <v>5762.2557538888823</v>
+      </c>
+      <c r="R26" s="5">
+        <f>0.1*E17</f>
+        <v>6073.6991188713255</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
       <c r="A27">
         <v>2050</v>
       </c>
@@ -8306,12 +9192,53 @@
         <f t="shared" si="0"/>
         <v>36354.237781756718</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F27" s="5"/>
+      <c r="G27" s="5">
         <f t="shared" si="1"/>
-        <v>36354.237781756718</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+        <v>46203.238529713199</v>
+      </c>
+      <c r="I27" s="5">
+        <f>0.1*E27</f>
+        <v>3635.4237781756719</v>
+      </c>
+      <c r="J27" s="5">
+        <f>0.1*E26</f>
+        <v>3823.1411418136686</v>
+      </c>
+      <c r="K27" s="5">
+        <f>0.1*E25</f>
+        <v>4021.304458094884</v>
+      </c>
+      <c r="L27" s="5">
+        <f>0.1*E24</f>
+        <v>4230.5453222623682</v>
+      </c>
+      <c r="M27" s="5">
+        <f>0.1*E23</f>
+        <v>4451.5440218805879</v>
+      </c>
+      <c r="N27" s="5">
+        <f>0.1*E22</f>
+        <v>4685.0398221670675</v>
+      </c>
+      <c r="O27" s="5">
+        <f>0.1*E21</f>
+        <v>4931.8480611395007</v>
+      </c>
+      <c r="P27" s="5">
+        <f>0.1*E20</f>
+        <v>5192.8899489802097</v>
+      </c>
+      <c r="Q27" s="5">
+        <f>0.1*E19</f>
+        <v>5469.2462213103536</v>
+      </c>
+      <c r="R27" s="5">
+        <f>0.1*E18</f>
+        <v>5762.2557538888823</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
       <c r="A28">
         <v>2051</v>
       </c>
@@ -8326,12 +9253,53 @@
         <f t="shared" si="0"/>
         <v>34575.628686041055</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F28" s="5"/>
+      <c r="G28" s="5">
         <f t="shared" si="1"/>
-        <v>34575.628686041055</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
+        <v>43898.545644428421</v>
+      </c>
+      <c r="I28" s="5">
+        <f>0.1*E28</f>
+        <v>3457.5628686041055</v>
+      </c>
+      <c r="J28" s="5">
+        <f>0.1*E27</f>
+        <v>3635.4237781756719</v>
+      </c>
+      <c r="K28" s="5">
+        <f>0.1*E26</f>
+        <v>3823.1411418136686</v>
+      </c>
+      <c r="L28" s="5">
+        <f>0.1*E25</f>
+        <v>4021.304458094884</v>
+      </c>
+      <c r="M28" s="5">
+        <f>0.1*E24</f>
+        <v>4230.5453222623682</v>
+      </c>
+      <c r="N28" s="5">
+        <f>0.1*E23</f>
+        <v>4451.5440218805879</v>
+      </c>
+      <c r="O28" s="5">
+        <f>0.1*E22</f>
+        <v>4685.0398221670675</v>
+      </c>
+      <c r="P28" s="5">
+        <f>0.1*E21</f>
+        <v>4931.8480611395007</v>
+      </c>
+      <c r="Q28" s="5">
+        <f>0.1*E20</f>
+        <v>5192.8899489802097</v>
+      </c>
+      <c r="R28" s="5">
+        <f>0.1*E19</f>
+        <v>5469.2462213103536</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18">
       <c r="A29">
         <v>2052</v>
       </c>
@@ -8346,12 +9314,53 @@
         <f t="shared" si="0"/>
         <v>32890.064501069988</v>
       </c>
-      <c r="F29" s="5">
+      <c r="F29" s="5"/>
+      <c r="G29" s="5">
         <f t="shared" si="1"/>
-        <v>32890.064501069988</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+        <v>41718.305873225065</v>
+      </c>
+      <c r="I29" s="5">
+        <f>0.1*E29</f>
+        <v>3289.0064501069992</v>
+      </c>
+      <c r="J29" s="5">
+        <f>0.1*E28</f>
+        <v>3457.5628686041055</v>
+      </c>
+      <c r="K29" s="5">
+        <f>0.1*E27</f>
+        <v>3635.4237781756719</v>
+      </c>
+      <c r="L29" s="5">
+        <f>0.1*E26</f>
+        <v>3823.1411418136686</v>
+      </c>
+      <c r="M29" s="5">
+        <f>0.1*E25</f>
+        <v>4021.304458094884</v>
+      </c>
+      <c r="N29" s="5">
+        <f>0.1*E24</f>
+        <v>4230.5453222623682</v>
+      </c>
+      <c r="O29" s="5">
+        <f>0.1*E23</f>
+        <v>4451.5440218805879</v>
+      </c>
+      <c r="P29" s="5">
+        <f>0.1*E22</f>
+        <v>4685.0398221670675</v>
+      </c>
+      <c r="Q29" s="5">
+        <f>0.1*E21</f>
+        <v>4931.8480611395007</v>
+      </c>
+      <c r="R29" s="5">
+        <f>0.1*E20</f>
+        <v>5192.8899489802097</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18">
       <c r="A30">
         <v>2053</v>
       </c>
@@ -8366,12 +9375,53 @@
         <f t="shared" si="0"/>
         <v>31292.366877145072</v>
       </c>
-      <c r="F30" s="5">
+      <c r="F30" s="5"/>
+      <c r="G30" s="5">
         <f t="shared" si="1"/>
-        <v>31292.366877145072</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+        <v>39654.652611959362</v>
+      </c>
+      <c r="I30" s="5">
+        <f>0.1*E30</f>
+        <v>3129.2366877145073</v>
+      </c>
+      <c r="J30" s="5">
+        <f>0.1*E29</f>
+        <v>3289.0064501069992</v>
+      </c>
+      <c r="K30" s="5">
+        <f>0.1*E28</f>
+        <v>3457.5628686041055</v>
+      </c>
+      <c r="L30" s="5">
+        <f>0.1*E27</f>
+        <v>3635.4237781756719</v>
+      </c>
+      <c r="M30" s="5">
+        <f>0.1*E26</f>
+        <v>3823.1411418136686</v>
+      </c>
+      <c r="N30" s="5">
+        <f>0.1*E25</f>
+        <v>4021.304458094884</v>
+      </c>
+      <c r="O30" s="5">
+        <f>0.1*E24</f>
+        <v>4230.5453222623682</v>
+      </c>
+      <c r="P30" s="5">
+        <f>0.1*E23</f>
+        <v>4451.5440218805879</v>
+      </c>
+      <c r="Q30" s="5">
+        <f>0.1*E22</f>
+        <v>4685.0398221670675</v>
+      </c>
+      <c r="R30" s="5">
+        <f>0.1*E21</f>
+        <v>4931.8480611395007</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18">
       <c r="A31">
         <v>2054</v>
       </c>
@@ -8386,12 +9436,53 @@
         <f t="shared" si="0"/>
         <v>29777.671486732157</v>
       </c>
-      <c r="F31" s="5">
+      <c r="F31" s="5"/>
+      <c r="G31" s="5">
         <f t="shared" si="1"/>
-        <v>29777.671486732157</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+        <v>37700.571699493077</v>
+      </c>
+      <c r="I31" s="5">
+        <f>0.1*E31</f>
+        <v>2977.7671486732161</v>
+      </c>
+      <c r="J31" s="5">
+        <f>0.1*E30</f>
+        <v>3129.2366877145073</v>
+      </c>
+      <c r="K31" s="5">
+        <f>0.1*E29</f>
+        <v>3289.0064501069992</v>
+      </c>
+      <c r="L31" s="5">
+        <f>0.1*E28</f>
+        <v>3457.5628686041055</v>
+      </c>
+      <c r="M31" s="5">
+        <f>0.1*E27</f>
+        <v>3635.4237781756719</v>
+      </c>
+      <c r="N31" s="5">
+        <f>0.1*E26</f>
+        <v>3823.1411418136686</v>
+      </c>
+      <c r="O31" s="5">
+        <f>0.1*E25</f>
+        <v>4021.304458094884</v>
+      </c>
+      <c r="P31" s="5">
+        <f>0.1*E24</f>
+        <v>4230.5453222623682</v>
+      </c>
+      <c r="Q31" s="5">
+        <f>0.1*E23</f>
+        <v>4451.5440218805879</v>
+      </c>
+      <c r="R31" s="5">
+        <f>0.1*E22</f>
+        <v>4685.0398221670675</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18">
       <c r="A32">
         <v>2055</v>
       </c>
@@ -8406,12 +9497,53 @@
         <f t="shared" si="0"/>
         <v>28341.405033236544</v>
       </c>
-      <c r="F32" s="5">
+      <c r="F32" s="5"/>
+      <c r="G32" s="5">
         <f t="shared" si="1"/>
-        <v>28341.405033236544</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+        <v>35849.672380649667</v>
+      </c>
+      <c r="I32" s="5">
+        <f>0.1*E32</f>
+        <v>2834.1405033236547</v>
+      </c>
+      <c r="J32" s="5">
+        <f>0.1*E31</f>
+        <v>2977.7671486732161</v>
+      </c>
+      <c r="K32" s="5">
+        <f>0.1*E30</f>
+        <v>3129.2366877145073</v>
+      </c>
+      <c r="L32" s="5">
+        <f>0.1*E29</f>
+        <v>3289.0064501069992</v>
+      </c>
+      <c r="M32" s="5">
+        <f>0.1*E28</f>
+        <v>3457.5628686041055</v>
+      </c>
+      <c r="N32" s="5">
+        <f>0.1*E27</f>
+        <v>3635.4237781756719</v>
+      </c>
+      <c r="O32" s="5">
+        <f>0.1*E26</f>
+        <v>3823.1411418136686</v>
+      </c>
+      <c r="P32" s="5">
+        <f>0.1*E25</f>
+        <v>4021.304458094884</v>
+      </c>
+      <c r="Q32" s="5">
+        <f>0.1*E24</f>
+        <v>4230.5453222623682</v>
+      </c>
+      <c r="R32" s="5">
+        <f>0.1*E23</f>
+        <v>4451.5440218805879</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18">
       <c r="A33">
         <v>2056</v>
       </c>
@@ -8426,12 +9558,53 @@
         <f t="shared" si="0"/>
         <v>26979.265125554244</v>
       </c>
-      <c r="F33" s="5">
+      <c r="F33" s="5"/>
+      <c r="G33" s="5">
         <f t="shared" si="1"/>
-        <v>26979.265125554244</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
+        <v>34096.054871324501</v>
+      </c>
+      <c r="I33" s="5">
+        <f>0.1*E33</f>
+        <v>2697.9265125554248</v>
+      </c>
+      <c r="J33" s="5">
+        <f>0.1*E32</f>
+        <v>2834.1405033236547</v>
+      </c>
+      <c r="K33" s="5">
+        <f>0.1*E31</f>
+        <v>2977.7671486732161</v>
+      </c>
+      <c r="L33" s="5">
+        <f>0.1*E30</f>
+        <v>3129.2366877145073</v>
+      </c>
+      <c r="M33" s="5">
+        <f>0.1*E29</f>
+        <v>3289.0064501069992</v>
+      </c>
+      <c r="N33" s="5">
+        <f>0.1*E28</f>
+        <v>3457.5628686041055</v>
+      </c>
+      <c r="O33" s="5">
+        <f>0.1*E27</f>
+        <v>3635.4237781756719</v>
+      </c>
+      <c r="P33" s="5">
+        <f>0.1*E26</f>
+        <v>3823.1411418136686</v>
+      </c>
+      <c r="Q33" s="5">
+        <f>0.1*E25</f>
+        <v>4021.304458094884</v>
+      </c>
+      <c r="R33" s="5">
+        <f>0.1*E24</f>
+        <v>4230.5453222623682</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18">
       <c r="A34">
         <v>2057</v>
       </c>
@@ -8446,12 +9619,53 @@
         <f t="shared" si="0"/>
         <v>25687.202229242059</v>
       </c>
-      <c r="F34" s="5">
+      <c r="F34" s="5"/>
+      <c r="G34" s="5">
         <f t="shared" si="1"/>
-        <v>25687.202229242059</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
+        <v>32434.229771986342</v>
+      </c>
+      <c r="I34" s="5">
+        <f>0.1*E34</f>
+        <v>2568.7202229242062</v>
+      </c>
+      <c r="J34" s="5">
+        <f>0.1*E33</f>
+        <v>2697.9265125554248</v>
+      </c>
+      <c r="K34" s="5">
+        <f>0.1*E32</f>
+        <v>2834.1405033236547</v>
+      </c>
+      <c r="L34" s="5">
+        <f>0.1*E31</f>
+        <v>2977.7671486732161</v>
+      </c>
+      <c r="M34" s="5">
+        <f>0.1*E30</f>
+        <v>3129.2366877145073</v>
+      </c>
+      <c r="N34" s="5">
+        <f>0.1*E29</f>
+        <v>3289.0064501069992</v>
+      </c>
+      <c r="O34" s="5">
+        <f>0.1*E28</f>
+        <v>3457.5628686041055</v>
+      </c>
+      <c r="P34" s="5">
+        <f>0.1*E27</f>
+        <v>3635.4237781756719</v>
+      </c>
+      <c r="Q34" s="5">
+        <f>0.1*E26</f>
+        <v>3823.1411418136686</v>
+      </c>
+      <c r="R34" s="5">
+        <f>0.1*E25</f>
+        <v>4021.304458094884</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18">
       <c r="A35">
         <v>2058</v>
       </c>
@@ -8466,12 +9680,53 @@
         <f t="shared" si="0"/>
         <v>24461.403232800763</v>
       </c>
-      <c r="F35" s="5">
+      <c r="F35" s="5"/>
+      <c r="G35" s="5">
         <f t="shared" si="1"/>
-        <v>24461.403232800763</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
+        <v>30859.06563717153</v>
+      </c>
+      <c r="I35" s="5">
+        <f>0.1*E35</f>
+        <v>2446.1403232800762</v>
+      </c>
+      <c r="J35" s="5">
+        <f>0.1*E34</f>
+        <v>2568.7202229242062</v>
+      </c>
+      <c r="K35" s="5">
+        <f>0.1*E33</f>
+        <v>2697.9265125554248</v>
+      </c>
+      <c r="L35" s="5">
+        <f>0.1*E32</f>
+        <v>2834.1405033236547</v>
+      </c>
+      <c r="M35" s="5">
+        <f>0.1*E31</f>
+        <v>2977.7671486732161</v>
+      </c>
+      <c r="N35" s="5">
+        <f>0.1*E30</f>
+        <v>3129.2366877145073</v>
+      </c>
+      <c r="O35" s="5">
+        <f>0.1*E29</f>
+        <v>3289.0064501069992</v>
+      </c>
+      <c r="P35" s="5">
+        <f>0.1*E28</f>
+        <v>3457.5628686041055</v>
+      </c>
+      <c r="Q35" s="5">
+        <f>0.1*E27</f>
+        <v>3635.4237781756719</v>
+      </c>
+      <c r="R35" s="5">
+        <f>0.1*E26</f>
+        <v>3823.1411418136686</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18">
       <c r="A36">
         <v>2059</v>
       </c>
@@ -8486,12 +9741,53 @@
         <f t="shared" si="0"/>
         <v>23298.276344703554</v>
       </c>
-      <c r="F36" s="5">
+      <c r="F36" s="5"/>
+      <c r="G36" s="5">
         <f t="shared" si="1"/>
-        <v>23298.276344703554</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
+        <v>29365.752129828215</v>
+      </c>
+      <c r="I36" s="5">
+        <f>0.1*E36</f>
+        <v>2329.8276344703554</v>
+      </c>
+      <c r="J36" s="5">
+        <f>0.1*E35</f>
+        <v>2446.1403232800762</v>
+      </c>
+      <c r="K36" s="5">
+        <f>0.1*E34</f>
+        <v>2568.7202229242062</v>
+      </c>
+      <c r="L36" s="5">
+        <f>0.1*E33</f>
+        <v>2697.9265125554248</v>
+      </c>
+      <c r="M36" s="5">
+        <f>0.1*E32</f>
+        <v>2834.1405033236547</v>
+      </c>
+      <c r="N36" s="5">
+        <f>0.1*E31</f>
+        <v>2977.7671486732161</v>
+      </c>
+      <c r="O36" s="5">
+        <f>0.1*E30</f>
+        <v>3129.2366877145073</v>
+      </c>
+      <c r="P36" s="5">
+        <f>0.1*E29</f>
+        <v>3289.0064501069992</v>
+      </c>
+      <c r="Q36" s="5">
+        <f>0.1*E28</f>
+        <v>3457.5628686041055</v>
+      </c>
+      <c r="R36" s="5">
+        <f>0.1*E27</f>
+        <v>3635.4237781756719</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18">
       <c r="A37">
         <v>2060</v>
       </c>
@@ -8506,12 +9802,53 @@
         <f t="shared" si="0"/>
         <v>22194.437133741587</v>
       </c>
-      <c r="F37" s="5">
+      <c r="F37" s="5"/>
+      <c r="G37" s="5">
         <f t="shared" si="1"/>
-        <v>22194.437133741587</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
+        <v>27949.772065026704</v>
+      </c>
+      <c r="I37" s="5">
+        <f>0.1*E37</f>
+        <v>2219.443713374159</v>
+      </c>
+      <c r="J37" s="5">
+        <f>0.1*E36</f>
+        <v>2329.8276344703554</v>
+      </c>
+      <c r="K37" s="5">
+        <f>0.1*E35</f>
+        <v>2446.1403232800762</v>
+      </c>
+      <c r="L37" s="5">
+        <f>0.1*E34</f>
+        <v>2568.7202229242062</v>
+      </c>
+      <c r="M37" s="5">
+        <f>0.1*E33</f>
+        <v>2697.9265125554248</v>
+      </c>
+      <c r="N37" s="5">
+        <f>0.1*E32</f>
+        <v>2834.1405033236547</v>
+      </c>
+      <c r="O37" s="5">
+        <f>0.1*E31</f>
+        <v>2977.7671486732161</v>
+      </c>
+      <c r="P37" s="5">
+        <f>0.1*E30</f>
+        <v>3129.2366877145073</v>
+      </c>
+      <c r="Q37" s="5">
+        <f>0.1*E29</f>
+        <v>3289.0064501069992</v>
+      </c>
+      <c r="R37" s="5">
+        <f>0.1*E28</f>
+        <v>3457.5628686041055</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18">
       <c r="A38">
         <v>2061</v>
       </c>
@@ -8526,12 +9863,53 @@
         <f t="shared" si="0"/>
         <v>21146.695579998177</v>
       </c>
-      <c r="F38" s="5">
+      <c r="F38" s="5"/>
+      <c r="G38" s="5">
         <f t="shared" si="1"/>
-        <v>21146.695579998177</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+        <v>26606.878754422418</v>
+      </c>
+      <c r="I38" s="5">
+        <f>0.1*E38</f>
+        <v>2114.6695579998177</v>
+      </c>
+      <c r="J38" s="5">
+        <f>0.1*E37</f>
+        <v>2219.443713374159</v>
+      </c>
+      <c r="K38" s="5">
+        <f>0.1*E36</f>
+        <v>2329.8276344703554</v>
+      </c>
+      <c r="L38" s="5">
+        <f>0.1*E35</f>
+        <v>2446.1403232800762</v>
+      </c>
+      <c r="M38" s="5">
+        <f>0.1*E34</f>
+        <v>2568.7202229242062</v>
+      </c>
+      <c r="N38" s="5">
+        <f>0.1*E33</f>
+        <v>2697.9265125554248</v>
+      </c>
+      <c r="O38" s="5">
+        <f>0.1*E32</f>
+        <v>2834.1405033236547</v>
+      </c>
+      <c r="P38" s="5">
+        <f>0.1*E31</f>
+        <v>2977.7671486732161</v>
+      </c>
+      <c r="Q38" s="5">
+        <f>0.1*E30</f>
+        <v>3129.2366877145073</v>
+      </c>
+      <c r="R38" s="5">
+        <f>0.1*E29</f>
+        <v>3289.0064501069992</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18">
       <c r="A39">
         <v>2062</v>
       </c>
@@ -8546,12 +9924,53 @@
         <f t="shared" si="0"/>
         <v>20152.044035386793</v>
       </c>
-      <c r="F39" s="5">
+      <c r="F39" s="5"/>
+      <c r="G39" s="5">
         <f t="shared" si="1"/>
-        <v>20152.044035386793</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
+        <v>25333.076707854099</v>
+      </c>
+      <c r="I39" s="5">
+        <f>0.1*E39</f>
+        <v>2015.2044035386793</v>
+      </c>
+      <c r="J39" s="5">
+        <f>0.1*E38</f>
+        <v>2114.6695579998177</v>
+      </c>
+      <c r="K39" s="5">
+        <f>0.1*E37</f>
+        <v>2219.443713374159</v>
+      </c>
+      <c r="L39" s="5">
+        <f>0.1*E36</f>
+        <v>2329.8276344703554</v>
+      </c>
+      <c r="M39" s="5">
+        <f>0.1*E35</f>
+        <v>2446.1403232800762</v>
+      </c>
+      <c r="N39" s="5">
+        <f>0.1*E34</f>
+        <v>2568.7202229242062</v>
+      </c>
+      <c r="O39" s="5">
+        <f>0.1*E33</f>
+        <v>2697.9265125554248</v>
+      </c>
+      <c r="P39" s="5">
+        <f>0.1*E32</f>
+        <v>2834.1405033236547</v>
+      </c>
+      <c r="Q39" s="5">
+        <f>0.1*E31</f>
+        <v>2977.7671486732161</v>
+      </c>
+      <c r="R39" s="5">
+        <f>0.1*E30</f>
+        <v>3129.2366877145073</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18">
       <c r="A40">
         <v>2063</v>
       </c>
@@ -8566,12 +9985,53 @@
         <f t="shared" si="0"/>
         <v>19207.646012163597</v>
       </c>
-      <c r="F40" s="5">
+      <c r="F40" s="5"/>
+      <c r="G40" s="5">
         <f t="shared" si="1"/>
-        <v>19207.646012163597</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
+        <v>24124.604621355953</v>
+      </c>
+      <c r="I40" s="5">
+        <f>0.1*E40</f>
+        <v>1920.7646012163598</v>
+      </c>
+      <c r="J40" s="5">
+        <f>0.1*E39</f>
+        <v>2015.2044035386793</v>
+      </c>
+      <c r="K40" s="5">
+        <f>0.1*E38</f>
+        <v>2114.6695579998177</v>
+      </c>
+      <c r="L40" s="5">
+        <f>0.1*E37</f>
+        <v>2219.443713374159</v>
+      </c>
+      <c r="M40" s="5">
+        <f>0.1*E36</f>
+        <v>2329.8276344703554</v>
+      </c>
+      <c r="N40" s="5">
+        <f>0.1*E35</f>
+        <v>2446.1403232800762</v>
+      </c>
+      <c r="O40" s="5">
+        <f>0.1*E34</f>
+        <v>2568.7202229242062</v>
+      </c>
+      <c r="P40" s="5">
+        <f>0.1*E33</f>
+        <v>2697.9265125554248</v>
+      </c>
+      <c r="Q40" s="5">
+        <f>0.1*E32</f>
+        <v>2834.1405033236547</v>
+      </c>
+      <c r="R40" s="5">
+        <f>0.1*E31</f>
+        <v>2977.7671486732161</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18">
       <c r="A41">
         <v>2064</v>
       </c>
@@ -8586,12 +10046,53 @@
         <f t="shared" si="0"/>
         <v>18310.825730527624</v>
       </c>
-      <c r="F41" s="5">
+      <c r="F41" s="5"/>
+      <c r="G41" s="5">
         <f t="shared" si="1"/>
-        <v>18310.825730527624</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
+        <v>22977.920045735493</v>
+      </c>
+      <c r="I41" s="5">
+        <f>0.1*E41</f>
+        <v>1831.0825730527624</v>
+      </c>
+      <c r="J41" s="5">
+        <f>0.1*E40</f>
+        <v>1920.7646012163598</v>
+      </c>
+      <c r="K41" s="5">
+        <f>0.1*E39</f>
+        <v>2015.2044035386793</v>
+      </c>
+      <c r="L41" s="5">
+        <f>0.1*E38</f>
+        <v>2114.6695579998177</v>
+      </c>
+      <c r="M41" s="5">
+        <f>0.1*E37</f>
+        <v>2219.443713374159</v>
+      </c>
+      <c r="N41" s="5">
+        <f>0.1*E36</f>
+        <v>2329.8276344703554</v>
+      </c>
+      <c r="O41" s="5">
+        <f>0.1*E35</f>
+        <v>2446.1403232800762</v>
+      </c>
+      <c r="P41" s="5">
+        <f>0.1*E34</f>
+        <v>2568.7202229242062</v>
+      </c>
+      <c r="Q41" s="5">
+        <f>0.1*E33</f>
+        <v>2697.9265125554248</v>
+      </c>
+      <c r="R41" s="5">
+        <f>0.1*E32</f>
+        <v>2834.1405033236547</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18">
       <c r="A42">
         <v>2065</v>
       </c>
@@ -8606,12 +10107,53 @@
         <f t="shared" si="0"/>
         <v>17459.058365121538</v>
       </c>
-      <c r="F42" s="5">
+      <c r="F42" s="5"/>
+      <c r="G42" s="5">
         <f t="shared" si="1"/>
-        <v>17459.058365121538</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
+        <v>21889.685378923998</v>
+      </c>
+      <c r="I42" s="5">
+        <f>0.1*E42</f>
+        <v>1745.9058365121539</v>
+      </c>
+      <c r="J42" s="5">
+        <f>0.1*E41</f>
+        <v>1831.0825730527624</v>
+      </c>
+      <c r="K42" s="5">
+        <f>0.1*E40</f>
+        <v>1920.7646012163598</v>
+      </c>
+      <c r="L42" s="5">
+        <f>0.1*E39</f>
+        <v>2015.2044035386793</v>
+      </c>
+      <c r="M42" s="5">
+        <f>0.1*E38</f>
+        <v>2114.6695579998177</v>
+      </c>
+      <c r="N42" s="5">
+        <f>0.1*E37</f>
+        <v>2219.443713374159</v>
+      </c>
+      <c r="O42" s="5">
+        <f>0.1*E36</f>
+        <v>2329.8276344703554</v>
+      </c>
+      <c r="P42" s="5">
+        <f>0.1*E35</f>
+        <v>2446.1403232800762</v>
+      </c>
+      <c r="Q42" s="5">
+        <f>0.1*E34</f>
+        <v>2568.7202229242062</v>
+      </c>
+      <c r="R42" s="5">
+        <f>0.1*E33</f>
+        <v>2697.9265125554248</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18">
       <c r="D44" t="s">
         <v>53</v>
       </c>
@@ -8619,15 +10161,20 @@
         <f>SUM(E3:E42)</f>
         <v>3554101.1889417893</v>
       </c>
-      <c r="F44" s="5">
-        <f>SUM(F3:F42)</f>
-        <v>1966468.1077456428</v>
-      </c>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5">
+        <f>SUM(G3:G42)</f>
+        <v>3464301.1907826201</v>
+      </c>
+      <c r="I44" s="5"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="I1:R1"/>
+  </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{611845FF-8744-854D-B8AD-D4609FE516B6}"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{611845FF-8744-854D-B8AD-D4609FE516B6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>

--- a/Realistic_ER_Estimate/ER_Summary.xlsx
+++ b/Realistic_ER_Estimate/ER_Summary.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mihirbendre/Documents/Gazelle/Gazelle_2026/Kenya_Project/Agricentric_SOC_Modeling/Realistic_ER_Estimate/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15AA954A-780F-6144-9F6B-561EF27E11FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A0EA635-2DE3-324F-B881-BA751044D350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" xr2:uid="{72AD1D35-862B-EB40-AF7A-21135E5EFD45}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{72AD1D35-862B-EB40-AF7A-21135E5EFD45}"/>
   </bookViews>
   <sheets>
     <sheet name="Net_Summary" sheetId="9" r:id="rId1"/>
-    <sheet name="Summary_Removals" sheetId="6" r:id="rId2"/>
-    <sheet name="Summary_Reductions" sheetId="8" r:id="rId3"/>
-    <sheet name="Additional_Coop_Projections" sheetId="7" r:id="rId4"/>
-    <sheet name="Eor" sheetId="1" r:id="rId5"/>
-    <sheet name="Lanyuak" sheetId="2" r:id="rId6"/>
-    <sheet name="Mumberes" sheetId="3" r:id="rId7"/>
-    <sheet name="Kabianga" sheetId="4" r:id="rId8"/>
-    <sheet name="Kipsigis" sheetId="5" r:id="rId9"/>
+    <sheet name="Subtracting_Biochar_Removals" sheetId="12" r:id="rId2"/>
+    <sheet name="Summary_Removals" sheetId="6" r:id="rId3"/>
+    <sheet name="Summary_Reductions" sheetId="8" r:id="rId4"/>
+    <sheet name="Additional_Coop_Projections" sheetId="7" r:id="rId5"/>
+    <sheet name="Eor" sheetId="1" r:id="rId6"/>
+    <sheet name="Lanyuak" sheetId="2" r:id="rId7"/>
+    <sheet name="Mumberes" sheetId="3" r:id="rId8"/>
+    <sheet name="Kabianga" sheetId="4" r:id="rId9"/>
+    <sheet name="Kipsigis" sheetId="5" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,30 +44,28 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={51D8FB6B-0583-8244-BA62-9F39A23EDA91}</author>
+  </authors>
+  <commentList>
+    <comment ref="C11" authorId="0" shapeId="0" xr:uid="{51D8FB6B-0583-8244-BA62-9F39A23EDA91}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    At this stage the ERRs are mostly coming from soil carbon sequestration, from organic fertilizer addition.
+Reply:
+    These ERRs are coming from maintaining SOC at current levels, not increasing from current levels.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="91">
   <si>
     <t>Nth</t>
   </si>
@@ -141,9 +140,6 @@
   </si>
   <si>
     <t>Net Reductions</t>
-  </si>
-  <si>
-    <t>Total ERRs</t>
   </si>
   <si>
     <t xml:space="preserve"> Net Total Project ERs (QA3) </t>
@@ -262,6 +258,87 @@
   <si>
     <t>Year in which farmers adopt practice</t>
   </si>
+  <si>
+    <t>ERRs before adoption rate</t>
+  </si>
+  <si>
+    <t>Biochar C content</t>
+  </si>
+  <si>
+    <t>Organic matter in HYGROW organic fertilizer</t>
+  </si>
+  <si>
+    <t>Approximate estimations</t>
+  </si>
+  <si>
+    <t>Reference</t>
+  </si>
+  <si>
+    <t>HYGROW Technical Sheet</t>
+  </si>
+  <si>
+    <t>Calculation</t>
+  </si>
+  <si>
+    <t>Estimate from literature</t>
+  </si>
+  <si>
+    <t>Estimate data from HYGROW</t>
+  </si>
+  <si>
+    <t>Biochar w/in organic fertilizer</t>
+  </si>
+  <si>
+    <t>Compost w/in organic fertilizer</t>
+  </si>
+  <si>
+    <t>30% of fertilizer organic content</t>
+  </si>
+  <si>
+    <t>70% of fertilizer organic content</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/2311-5629/9/3/67</t>
+  </si>
+  <si>
+    <t>Parameters</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>After subtracting compost production-related emissions from reductions (from offsetting synthetic fertilizer) and removals (from SOC sequestration)</t>
+  </si>
+  <si>
+    <t>Research reference</t>
+  </si>
+  <si>
+    <t>EPA technical sheet</t>
+  </si>
+  <si>
+    <t>Emission removals from compost (MTCO2e per ton of organic matter in compost)</t>
+  </si>
+  <si>
+    <t>0.13 MTCO2e/ton organic matter in MSW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.epa.gov/system/files/documents/2023-12/warm_organic_materials_v16_dec.pdf </t>
+  </si>
+  <si>
+    <t>Biochar (estimated) carbon credit deduction (tCO2e)</t>
+  </si>
+  <si>
+    <t>Net Summary Removals (tCO2e)</t>
+  </si>
+  <si>
+    <t>Net ERRs after subtracting biochar</t>
+  </si>
+  <si>
+    <t>(compost's contribution to removals)</t>
+  </si>
+  <si>
+    <t>ERRs after applying adoption rate</t>
+  </si>
 </sst>
 </file>
 
@@ -270,7 +347,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -337,6 +414,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -384,7 +467,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -402,11 +485,27 @@
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -482,11 +581,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Net_Summary!$E$2</c:f>
+              <c:f>Net_Summary!$G$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Total ERRs</c:v>
+                  <c:v>ERRs after applying adoption rate</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -634,129 +733,129 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Net_Summary!$E$3:$E$42</c:f>
+              <c:f>Net_Summary!$G$3:$G$42</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="40"/>
                 <c:pt idx="0">
-                  <c:v>821584.90334901295</c:v>
+                  <c:v>70088.299455373912</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>439102.27272334381</c:v>
+                  <c:v>107550.83051837824</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>281025.89568057278</c:v>
+                  <c:v>131529.4466196342</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>196094.14731331487</c:v>
+                  <c:v>148263.38458516309</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>149079.05322744849</c:v>
+                  <c:v>160986.93502516754</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>121969.80607606156</c:v>
+                  <c:v>171398.06668315869</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>105426.99848537613</c:v>
+                  <c:v>180398.09685366438</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>94565.621342954968</c:v>
+                  <c:v>188471.65155392152</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>86815.617806178256</c:v>
+                  <c:v>195884.1309524916</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>80818.214935822019</c:v>
+                  <c:v>202785.03188622033</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>75851.031860754927</c:v>
+                  <c:v>139173.93264827193</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>71526.95140630292</c:v>
+                  <c:v>107819.75773992833</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>67635.879475738519</c:v>
+                  <c:v>89617.589357655976</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>64061.428399597622</c:v>
+                  <c:v>78355.198434315884</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>60736.991188713255</c:v>
+                  <c:v>70819.620542411765</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>57622.557538888817</c:v>
+                  <c:v>65330.800242190933</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>54692.462213103536</c:v>
+                  <c:v>61003.14429816608</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>51928.89948980209</c:v>
+                  <c:v>57366.231924092142</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>49318.480611395004</c:v>
+                  <c:v>54167.726121377127</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46850.398221670672</c:v>
+                  <c:v>51270.271355660014</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>44515.440218805874</c:v>
+                  <c:v>48597.34538860176</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>42305.453222623684</c:v>
+                  <c:v>46104.751593533932</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>40213.044580948837</c:v>
+                  <c:v>43765.583777008374</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>38231.411418136682</c:v>
+                  <c:v>41562.28332848975</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>36354.237781756718</c:v>
+                  <c:v>39482.434462876357</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>34575.628686041055</c:v>
+                  <c:v>37516.531431728443</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>32890.064501069988</c:v>
+                  <c:v>35656.786906891975</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>31292.366877145072</c:v>
+                  <c:v>33896.490675032335</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>29777.671486732157</c:v>
+                  <c:v>32229.659656698594</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>28341.405033236544</c:v>
+                  <c:v>30650.842537725166</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>26979.265125554244</c:v>
+                  <c:v>29155.006802270796</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>25687.202229242059</c:v>
+                  <c:v>27737.469992535349</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>24461.403232800763</c:v>
+                  <c:v>26393.854985538321</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>23298.276344703554</c:v>
+                  <c:v>25120.058563774473</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>22194.437133741587</c:v>
+                  <c:v>23912.227568498784</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>21146.695579998177</c:v>
+                  <c:v>22766.739574553321</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>20152.044035386793</c:v>
+                  <c:v>21680.186428830544</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>19207.646012163597</c:v>
+                  <c:v>20649.359739047624</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>18310.825730527624</c:v>
+                  <c:v>19671.237796043377</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>17459.058365121538</c:v>
+                  <c:v>18742.973625253169</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7306,16 +7405,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>669907</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>202698</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>663325</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>182957</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>304903</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>101776</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>94331</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>82035</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7347,16 +7446,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>115732</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>94560</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>445932</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>107260</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>555192</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>10886</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>59892</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>23586</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7383,16 +7482,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>27214</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>110822</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>319314</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>98122</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>471713</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>8315</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>763813</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>198815</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7500,6 +7599,12 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Bendre, Mihir Y" id="{8218466F-29F2-9E46-91A3-668DA1A57351}" userId="S::myb358@my.utexas.edu::5603340f-c1e2-4a78-972e-9f726e020435" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7817,105 +7922,120 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="C11" dT="2026-06-25T23:42:14.87" personId="{8218466F-29F2-9E46-91A3-668DA1A57351}" id="{51D8FB6B-0583-8244-BA62-9F39A23EDA91}">
+    <text>At this stage the ERRs are mostly coming from soil carbon sequestration, from organic fertilizer addition.</text>
+  </threadedComment>
+  <threadedComment ref="C11" dT="2026-06-25T23:44:19.48" personId="{8218466F-29F2-9E46-91A3-668DA1A57351}" id="{24AEF77C-7D5D-154B-8BEF-C9A219B02913}" parentId="{51D8FB6B-0583-8244-BA62-9F39A23EDA91}">
+    <text>These ERRs are coming from maintaining SOC at current levels, not increasing from current levels.</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53C74460-226A-484F-A8DD-FFF53BF916A1}">
   <dimension ref="A1:R44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="2" max="2" width="14.1640625" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="10.83203125" customWidth="1"/>
     <col min="5" max="6" width="14.83203125" customWidth="1"/>
     <col min="7" max="7" width="17.83203125" customWidth="1"/>
     <col min="8" max="8" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13" hidden="1" customWidth="1"/>
+    <col min="10" max="18" width="10.83203125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="I1" s="16" t="s">
+      <c r="E1" t="s">
         <v>64</v>
       </c>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16"/>
+      <c r="G1" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E2" t="s">
-        <v>25</v>
-      </c>
       <c r="G2" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J2" t="s">
         <v>54</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>55</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>56</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>57</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>58</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>59</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>60</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>61</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>62</v>
-      </c>
-      <c r="R2" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3">
         <v>2026</v>
       </c>
-      <c r="B3" s="1" cm="1">
-        <f t="array" ref="B3:B42">Summary_Removals!H6:H45</f>
-        <v>821101.42037601292</v>
-      </c>
-      <c r="C3">
+      <c r="B3" s="1">
+        <f>Subtracting_Biochar_Removals!F13</f>
+        <v>700399.51158073905</v>
+      </c>
+      <c r="C3" s="1">
         <f>Summary_Reductions!H8</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E3" s="5">
         <f>SUM(B3:C3)</f>
-        <v>821584.90334901295</v>
+        <v>700882.99455373909</v>
       </c>
       <c r="F3" s="5"/>
-      <c r="G3" s="5">
+      <c r="G3" s="17">
         <f>SUM(I3:R3)</f>
-        <v>82158.490334901304</v>
+        <v>70088.299455373912</v>
       </c>
       <c r="I3" s="5">
-        <f>0.1*E3</f>
-        <v>82158.490334901304</v>
+        <f t="shared" ref="I3:I42" si="0">0.1*E3</f>
+        <v>70088.299455373912</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -7923,28 +8043,29 @@
         <v>2027</v>
       </c>
       <c r="B4" s="1">
-        <v>438618.78975034383</v>
-      </c>
-      <c r="C4">
+        <f>Subtracting_Biochar_Removals!F14</f>
+        <v>374141.82765704329</v>
+      </c>
+      <c r="C4" s="1">
         <f>Summary_Reductions!H9</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E4" s="5">
-        <f t="shared" ref="E4:E42" si="0">SUM(B4:C4)</f>
-        <v>439102.27272334381</v>
+        <f t="shared" ref="E4:E42" si="1">SUM(B4:C4)</f>
+        <v>374625.31063004327</v>
       </c>
       <c r="F4" s="5"/>
-      <c r="G4" s="5">
+      <c r="G4" s="17">
         <f>SUM(I4:R4)</f>
-        <v>126068.71760723568</v>
+        <v>107550.83051837824</v>
       </c>
       <c r="I4" s="5">
-        <f>0.1*E4</f>
-        <v>43910.227272334385</v>
+        <f t="shared" si="0"/>
+        <v>37462.531063004331</v>
       </c>
       <c r="J4" s="5">
-        <f>0.1*E3</f>
-        <v>82158.490334901304</v>
+        <f t="shared" ref="J4:J42" si="2">0.1*E3</f>
+        <v>70088.299455373912</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -7952,32 +8073,33 @@
         <v>2028</v>
       </c>
       <c r="B5" s="1">
-        <v>280542.4127075728</v>
-      </c>
-      <c r="C5">
+        <f>Subtracting_Biochar_Removals!F15</f>
+        <v>239302.6780395596</v>
+      </c>
+      <c r="C5" s="1">
         <f>Summary_Reductions!H10</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E5" s="5">
-        <f t="shared" si="0"/>
-        <v>281025.89568057278</v>
+        <f t="shared" si="1"/>
+        <v>239786.16101255961</v>
       </c>
       <c r="F5" s="5"/>
-      <c r="G5" s="5">
-        <f t="shared" ref="G4:G42" si="1">SUM(I5:R5)</f>
-        <v>154171.30717529298</v>
+      <c r="G5" s="17">
+        <f t="shared" ref="G5:G42" si="3">SUM(I5:R5)</f>
+        <v>131529.4466196342</v>
       </c>
       <c r="I5" s="5">
-        <f>0.1*E5</f>
-        <v>28102.589568057279</v>
+        <f t="shared" si="0"/>
+        <v>23978.616101255961</v>
       </c>
       <c r="J5" s="5">
-        <f>0.1*E4</f>
-        <v>43910.227272334385</v>
+        <f t="shared" si="2"/>
+        <v>37462.531063004331</v>
       </c>
       <c r="K5" s="5">
-        <f>0.1*E3</f>
-        <v>82158.490334901304</v>
+        <f t="shared" ref="K5:K42" si="4">0.1*E3</f>
+        <v>70088.299455373912</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -7985,36 +8107,37 @@
         <v>2029</v>
       </c>
       <c r="B6" s="1">
-        <v>195610.66434031486</v>
-      </c>
-      <c r="C6">
+        <f>Subtracting_Biochar_Removals!F16</f>
+        <v>166855.89668228858</v>
+      </c>
+      <c r="C6" s="1">
         <f>Summary_Reductions!H11</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E6" s="5">
-        <f t="shared" si="0"/>
-        <v>196094.14731331487</v>
+        <f t="shared" si="1"/>
+        <v>167339.37965528859</v>
       </c>
       <c r="F6" s="5"/>
-      <c r="G6" s="5">
-        <f t="shared" si="1"/>
-        <v>173780.72190662444</v>
+      <c r="G6" s="17">
+        <f t="shared" si="3"/>
+        <v>148263.38458516309</v>
       </c>
       <c r="I6" s="5">
-        <f>0.1*E6</f>
-        <v>19609.414731331486</v>
+        <f t="shared" si="0"/>
+        <v>16733.937965528861</v>
       </c>
       <c r="J6" s="5">
-        <f>0.1*E5</f>
-        <v>28102.589568057279</v>
+        <f t="shared" si="2"/>
+        <v>23978.616101255961</v>
       </c>
       <c r="K6" s="5">
-        <f>0.1*E4</f>
-        <v>43910.227272334385</v>
+        <f t="shared" si="4"/>
+        <v>37462.531063004331</v>
       </c>
       <c r="L6" s="5">
-        <f>0.1*E3</f>
-        <v>82158.490334901304</v>
+        <f t="shared" ref="L6:L42" si="5">0.1*E3</f>
+        <v>70088.299455373912</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -8022,40 +8145,41 @@
         <v>2030</v>
       </c>
       <c r="B7" s="1">
-        <v>148595.57025444848</v>
-      </c>
-      <c r="C7">
+        <f>Subtracting_Biochar_Removals!F17</f>
+        <v>126752.02142704456</v>
+      </c>
+      <c r="C7" s="1">
         <f>Summary_Reductions!H12</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E7" s="5">
-        <f t="shared" si="0"/>
-        <v>149079.05322744849</v>
+        <f t="shared" si="1"/>
+        <v>127235.50440004456</v>
       </c>
       <c r="F7" s="5"/>
-      <c r="G7" s="5">
-        <f t="shared" si="1"/>
-        <v>188688.6272293693</v>
+      <c r="G7" s="17">
+        <f t="shared" si="3"/>
+        <v>160986.93502516754</v>
       </c>
       <c r="I7" s="5">
-        <f>0.1*E7</f>
-        <v>14907.905322744849</v>
+        <f t="shared" si="0"/>
+        <v>12723.550440004457</v>
       </c>
       <c r="J7" s="5">
-        <f>0.1*E6</f>
-        <v>19609.414731331486</v>
+        <f t="shared" si="2"/>
+        <v>16733.937965528861</v>
       </c>
       <c r="K7" s="5">
-        <f>0.1*E5</f>
-        <v>28102.589568057279</v>
+        <f t="shared" si="4"/>
+        <v>23978.616101255961</v>
       </c>
       <c r="L7" s="5">
-        <f>0.1*E4</f>
-        <v>43910.227272334385</v>
+        <f t="shared" si="5"/>
+        <v>37462.531063004331</v>
       </c>
       <c r="M7" s="5">
-        <f>0.1*E3</f>
-        <v>82158.490334901304</v>
+        <f t="shared" ref="M7:M42" si="6">0.1*E3</f>
+        <v>70088.299455373912</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -8063,44 +8187,45 @@
         <v>2031</v>
       </c>
       <c r="B8" s="1">
-        <v>121486.32310306156</v>
-      </c>
-      <c r="C8">
+        <f>Subtracting_Biochar_Removals!F18</f>
+        <v>103627.8336069115</v>
+      </c>
+      <c r="C8" s="1">
         <f>Summary_Reductions!H13</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E8" s="5">
-        <f t="shared" si="0"/>
-        <v>121969.80607606156</v>
+        <f t="shared" si="1"/>
+        <v>104111.31657991151</v>
       </c>
       <c r="F8" s="5"/>
-      <c r="G8" s="5">
-        <f t="shared" si="1"/>
-        <v>200885.60783697548</v>
+      <c r="G8" s="17">
+        <f t="shared" si="3"/>
+        <v>171398.06668315869</v>
       </c>
       <c r="I8" s="5">
-        <f>0.1*E8</f>
-        <v>12196.980607606158</v>
+        <f t="shared" si="0"/>
+        <v>10411.131657991151</v>
       </c>
       <c r="J8" s="5">
-        <f>0.1*E7</f>
-        <v>14907.905322744849</v>
+        <f t="shared" si="2"/>
+        <v>12723.550440004457</v>
       </c>
       <c r="K8" s="5">
-        <f>0.1*E6</f>
-        <v>19609.414731331486</v>
+        <f t="shared" si="4"/>
+        <v>16733.937965528861</v>
       </c>
       <c r="L8" s="5">
-        <f>0.1*E5</f>
-        <v>28102.589568057279</v>
+        <f t="shared" si="5"/>
+        <v>23978.616101255961</v>
       </c>
       <c r="M8" s="5">
-        <f>0.1*E4</f>
-        <v>43910.227272334385</v>
+        <f t="shared" si="6"/>
+        <v>37462.531063004331</v>
       </c>
       <c r="N8" s="5">
-        <f>0.1*E3</f>
-        <v>82158.490334901304</v>
+        <f t="shared" ref="N8:N42" si="7">0.1*E3</f>
+        <v>70088.299455373912</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -8108,48 +8233,49 @@
         <v>2032</v>
       </c>
       <c r="B9" s="1">
-        <v>104943.51551237612</v>
-      </c>
-      <c r="C9">
+        <f>Subtracting_Biochar_Removals!F19</f>
+        <v>89516.818732056825</v>
+      </c>
+      <c r="C9" s="1">
         <f>Summary_Reductions!H14</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E9" s="5">
-        <f t="shared" si="0"/>
-        <v>105426.99848537613</v>
+        <f t="shared" si="1"/>
+        <v>90000.301705056831</v>
       </c>
       <c r="F9" s="5"/>
-      <c r="G9" s="5">
-        <f t="shared" si="1"/>
-        <v>211428.30768551311</v>
+      <c r="G9" s="17">
+        <f t="shared" si="3"/>
+        <v>180398.09685366438</v>
       </c>
       <c r="I9" s="5">
-        <f>0.1*E9</f>
-        <v>10542.699848537613</v>
+        <f t="shared" si="0"/>
+        <v>9000.0301705056827</v>
       </c>
       <c r="J9" s="5">
-        <f>0.1*E8</f>
-        <v>12196.980607606158</v>
+        <f t="shared" si="2"/>
+        <v>10411.131657991151</v>
       </c>
       <c r="K9" s="5">
-        <f>0.1*E7</f>
-        <v>14907.905322744849</v>
+        <f t="shared" si="4"/>
+        <v>12723.550440004457</v>
       </c>
       <c r="L9" s="5">
-        <f>0.1*E6</f>
-        <v>19609.414731331486</v>
+        <f t="shared" si="5"/>
+        <v>16733.937965528861</v>
       </c>
       <c r="M9" s="5">
-        <f>0.1*E5</f>
-        <v>28102.589568057279</v>
+        <f t="shared" si="6"/>
+        <v>23978.616101255961</v>
       </c>
       <c r="N9" s="5">
-        <f>0.1*E4</f>
-        <v>43910.227272334385</v>
+        <f t="shared" si="7"/>
+        <v>37462.531063004331</v>
       </c>
       <c r="O9" s="5">
-        <f>0.1*E3</f>
-        <v>82158.490334901304</v>
+        <f t="shared" ref="O9:O42" si="8">0.1*E3</f>
+        <v>70088.299455373912</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -8157,52 +8283,53 @@
         <v>2033</v>
       </c>
       <c r="B10" s="1">
-        <v>94082.138369954962</v>
-      </c>
-      <c r="C10">
+        <f>Subtracting_Biochar_Removals!F20</f>
+        <v>80252.064029571586</v>
+      </c>
+      <c r="C10" s="1">
         <f>Summary_Reductions!H15</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E10" s="5">
-        <f t="shared" si="0"/>
-        <v>94565.621342954968</v>
+        <f t="shared" si="1"/>
+        <v>80735.547002571591</v>
       </c>
       <c r="F10" s="5"/>
-      <c r="G10" s="5">
-        <f t="shared" si="1"/>
-        <v>220884.86981980858</v>
+      <c r="G10" s="17">
+        <f t="shared" si="3"/>
+        <v>188471.65155392152</v>
       </c>
       <c r="I10" s="5">
-        <f>0.1*E10</f>
-        <v>9456.5621342954964</v>
+        <f t="shared" si="0"/>
+        <v>8073.5547002571593</v>
       </c>
       <c r="J10" s="5">
-        <f>0.1*E9</f>
-        <v>10542.699848537613</v>
+        <f t="shared" si="2"/>
+        <v>9000.0301705056827</v>
       </c>
       <c r="K10" s="5">
-        <f>0.1*E8</f>
-        <v>12196.980607606158</v>
+        <f t="shared" si="4"/>
+        <v>10411.131657991151</v>
       </c>
       <c r="L10" s="5">
-        <f>0.1*E7</f>
-        <v>14907.905322744849</v>
+        <f t="shared" si="5"/>
+        <v>12723.550440004457</v>
       </c>
       <c r="M10" s="5">
-        <f>0.1*E6</f>
-        <v>19609.414731331486</v>
+        <f t="shared" si="6"/>
+        <v>16733.937965528861</v>
       </c>
       <c r="N10" s="5">
-        <f>0.1*E5</f>
-        <v>28102.589568057279</v>
+        <f t="shared" si="7"/>
+        <v>23978.616101255961</v>
       </c>
       <c r="O10" s="5">
-        <f>0.1*E4</f>
-        <v>43910.227272334385</v>
+        <f t="shared" si="8"/>
+        <v>37462.531063004331</v>
       </c>
       <c r="P10" s="5">
-        <f>0.1*E3</f>
-        <v>82158.490334901304</v>
+        <f t="shared" ref="P10:P42" si="9">0.1*E3</f>
+        <v>70088.299455373912</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -8210,56 +8337,57 @@
         <v>2034</v>
       </c>
       <c r="B11" s="1">
-        <v>86332.13483317825</v>
-      </c>
-      <c r="C11">
+        <f>Subtracting_Biochar_Removals!F21</f>
+        <v>73641.311012701044</v>
+      </c>
+      <c r="C11" s="1">
         <f>Summary_Reductions!H16</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E11" s="5">
-        <f t="shared" si="0"/>
-        <v>86815.617806178256</v>
+        <f t="shared" si="1"/>
+        <v>74124.79398570105</v>
       </c>
       <c r="F11" s="5"/>
-      <c r="G11" s="5">
-        <f t="shared" si="1"/>
-        <v>229566.43160042638</v>
+      <c r="G11" s="17">
+        <f t="shared" si="3"/>
+        <v>195884.1309524916</v>
       </c>
       <c r="I11" s="5">
-        <f>0.1*E11</f>
-        <v>8681.5617806178252</v>
+        <f t="shared" si="0"/>
+        <v>7412.4793985701053</v>
       </c>
       <c r="J11" s="5">
-        <f>0.1*E10</f>
-        <v>9456.5621342954964</v>
+        <f t="shared" si="2"/>
+        <v>8073.5547002571593</v>
       </c>
       <c r="K11" s="5">
-        <f>0.1*E9</f>
-        <v>10542.699848537613</v>
+        <f t="shared" si="4"/>
+        <v>9000.0301705056827</v>
       </c>
       <c r="L11" s="5">
-        <f>0.1*E8</f>
-        <v>12196.980607606158</v>
+        <f t="shared" si="5"/>
+        <v>10411.131657991151</v>
       </c>
       <c r="M11" s="5">
-        <f>0.1*E7</f>
-        <v>14907.905322744849</v>
+        <f t="shared" si="6"/>
+        <v>12723.550440004457</v>
       </c>
       <c r="N11" s="5">
-        <f>0.1*E6</f>
-        <v>19609.414731331486</v>
+        <f t="shared" si="7"/>
+        <v>16733.937965528861</v>
       </c>
       <c r="O11" s="5">
-        <f>0.1*E5</f>
-        <v>28102.589568057279</v>
+        <f t="shared" si="8"/>
+        <v>23978.616101255961</v>
       </c>
       <c r="P11" s="5">
-        <f>0.1*E4</f>
-        <v>43910.227272334385</v>
+        <f t="shared" si="9"/>
+        <v>37462.531063004331</v>
       </c>
       <c r="Q11" s="5">
-        <f>0.1*E3</f>
-        <v>82158.490334901304</v>
+        <f t="shared" ref="Q11:Q42" si="10">0.1*E3</f>
+        <v>70088.299455373912</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -8267,60 +8395,61 @@
         <v>2035</v>
       </c>
       <c r="B12" s="1">
-        <v>80334.731962822014</v>
-      </c>
-      <c r="C12">
+        <f>Subtracting_Biochar_Removals!F22</f>
+        <v>68525.526364287172</v>
+      </c>
+      <c r="C12" s="1">
         <f>Summary_Reductions!H17</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E12" s="5">
-        <f t="shared" si="0"/>
-        <v>80818.214935822019</v>
+        <f t="shared" si="1"/>
+        <v>69009.009337287178</v>
       </c>
       <c r="F12" s="5"/>
-      <c r="G12" s="5">
-        <f t="shared" si="1"/>
-        <v>237648.2530940086</v>
+      <c r="G12" s="17">
+        <f t="shared" si="3"/>
+        <v>202785.03188622033</v>
       </c>
       <c r="I12" s="5">
-        <f>0.1*E12</f>
-        <v>8081.8214935822025</v>
+        <f t="shared" si="0"/>
+        <v>6900.900933728718</v>
       </c>
       <c r="J12" s="5">
-        <f>0.1*E11</f>
-        <v>8681.5617806178252</v>
+        <f t="shared" si="2"/>
+        <v>7412.4793985701053</v>
       </c>
       <c r="K12" s="5">
-        <f>0.1*E10</f>
-        <v>9456.5621342954964</v>
+        <f t="shared" si="4"/>
+        <v>8073.5547002571593</v>
       </c>
       <c r="L12" s="5">
-        <f>0.1*E9</f>
-        <v>10542.699848537613</v>
+        <f t="shared" si="5"/>
+        <v>9000.0301705056827</v>
       </c>
       <c r="M12" s="5">
-        <f>0.1*E8</f>
-        <v>12196.980607606158</v>
+        <f t="shared" si="6"/>
+        <v>10411.131657991151</v>
       </c>
       <c r="N12" s="5">
-        <f>0.1*E7</f>
-        <v>14907.905322744849</v>
+        <f t="shared" si="7"/>
+        <v>12723.550440004457</v>
       </c>
       <c r="O12" s="5">
-        <f>0.1*E6</f>
-        <v>19609.414731331486</v>
+        <f t="shared" si="8"/>
+        <v>16733.937965528861</v>
       </c>
       <c r="P12" s="5">
-        <f>0.1*E5</f>
-        <v>28102.589568057279</v>
+        <f t="shared" si="9"/>
+        <v>23978.616101255961</v>
       </c>
       <c r="Q12" s="5">
-        <f>0.1*E4</f>
-        <v>43910.227272334385</v>
+        <f t="shared" si="10"/>
+        <v>37462.531063004331</v>
       </c>
       <c r="R12" s="5">
-        <f>0.1*E3</f>
-        <v>82158.490334901304</v>
+        <f t="shared" ref="R12:R42" si="11">0.1*E3</f>
+        <v>70088.299455373912</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -8328,60 +8457,61 @@
         <v>2036</v>
       </c>
       <c r="B13" s="1">
-        <v>75367.548887754921</v>
-      </c>
-      <c r="C13">
+        <f>Subtracting_Biochar_Removals!F23</f>
+        <v>64288.519201254952</v>
+      </c>
+      <c r="C13" s="1">
         <f>Summary_Reductions!H18</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E13" s="5">
-        <f t="shared" si="0"/>
-        <v>75851.031860754927</v>
+        <f t="shared" si="1"/>
+        <v>64772.002174254951</v>
       </c>
       <c r="F13" s="5"/>
-      <c r="G13" s="5">
-        <f t="shared" si="1"/>
-        <v>163074.8659451828</v>
+      <c r="G13" s="17">
+        <f t="shared" si="3"/>
+        <v>139173.93264827193</v>
       </c>
       <c r="I13" s="5">
-        <f>0.1*E13</f>
-        <v>7585.1031860754929</v>
+        <f t="shared" si="0"/>
+        <v>6477.2002174254958</v>
       </c>
       <c r="J13" s="5">
-        <f>0.1*E12</f>
-        <v>8081.8214935822025</v>
+        <f t="shared" si="2"/>
+        <v>6900.900933728718</v>
       </c>
       <c r="K13" s="5">
-        <f>0.1*E11</f>
-        <v>8681.5617806178252</v>
+        <f t="shared" si="4"/>
+        <v>7412.4793985701053</v>
       </c>
       <c r="L13" s="5">
-        <f>0.1*E10</f>
-        <v>9456.5621342954964</v>
+        <f t="shared" si="5"/>
+        <v>8073.5547002571593</v>
       </c>
       <c r="M13" s="5">
-        <f>0.1*E9</f>
-        <v>10542.699848537613</v>
+        <f t="shared" si="6"/>
+        <v>9000.0301705056827</v>
       </c>
       <c r="N13" s="5">
-        <f>0.1*E8</f>
-        <v>12196.980607606158</v>
+        <f t="shared" si="7"/>
+        <v>10411.131657991151</v>
       </c>
       <c r="O13" s="5">
-        <f>0.1*E7</f>
-        <v>14907.905322744849</v>
+        <f t="shared" si="8"/>
+        <v>12723.550440004457</v>
       </c>
       <c r="P13" s="5">
-        <f>0.1*E6</f>
-        <v>19609.414731331486</v>
+        <f t="shared" si="9"/>
+        <v>16733.937965528861</v>
       </c>
       <c r="Q13" s="5">
-        <f>0.1*E5</f>
-        <v>28102.589568057279</v>
+        <f t="shared" si="10"/>
+        <v>23978.616101255961</v>
       </c>
       <c r="R13" s="5">
-        <f>0.1*E4</f>
-        <v>43910.227272334385</v>
+        <f t="shared" si="11"/>
+        <v>37462.531063004331</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -8389,60 +8519,61 @@
         <v>2037</v>
       </c>
       <c r="B14" s="1">
-        <v>71043.468433302914</v>
-      </c>
-      <c r="C14">
+        <f>Subtracting_Biochar_Removals!F24</f>
+        <v>60600.078573607389</v>
+      </c>
+      <c r="C14" s="1">
         <f>Summary_Reductions!H19</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E14" s="5">
         <f>SUM(B14:C14)</f>
-        <v>71526.95140630292</v>
+        <v>61083.561546607387</v>
       </c>
       <c r="F14" s="5"/>
-      <c r="G14" s="5">
-        <f t="shared" si="1"/>
-        <v>126317.3338134787</v>
+      <c r="G14" s="17">
+        <f t="shared" si="3"/>
+        <v>107819.75773992833</v>
       </c>
       <c r="I14" s="5">
-        <f>0.1*E14</f>
-        <v>7152.6951406302924</v>
+        <f t="shared" si="0"/>
+        <v>6108.3561546607389</v>
       </c>
       <c r="J14" s="5">
-        <f>0.1*E13</f>
-        <v>7585.1031860754929</v>
+        <f t="shared" si="2"/>
+        <v>6477.2002174254958</v>
       </c>
       <c r="K14" s="5">
-        <f>0.1*E12</f>
-        <v>8081.8214935822025</v>
+        <f t="shared" si="4"/>
+        <v>6900.900933728718</v>
       </c>
       <c r="L14" s="5">
-        <f>0.1*E11</f>
-        <v>8681.5617806178252</v>
+        <f t="shared" si="5"/>
+        <v>7412.4793985701053</v>
       </c>
       <c r="M14" s="5">
-        <f>0.1*E10</f>
-        <v>9456.5621342954964</v>
+        <f t="shared" si="6"/>
+        <v>8073.5547002571593</v>
       </c>
       <c r="N14" s="5">
-        <f>0.1*E9</f>
-        <v>10542.699848537613</v>
+        <f t="shared" si="7"/>
+        <v>9000.0301705056827</v>
       </c>
       <c r="O14" s="5">
-        <f>0.1*E8</f>
-        <v>12196.980607606158</v>
+        <f t="shared" si="8"/>
+        <v>10411.131657991151</v>
       </c>
       <c r="P14" s="5">
-        <f>0.1*E7</f>
-        <v>14907.905322744849</v>
+        <f t="shared" si="9"/>
+        <v>12723.550440004457</v>
       </c>
       <c r="Q14" s="5">
-        <f>0.1*E6</f>
-        <v>19609.414731331486</v>
+        <f t="shared" si="10"/>
+        <v>16733.937965528861</v>
       </c>
       <c r="R14" s="5">
-        <f>0.1*E5</f>
-        <v>28102.589568057279</v>
+        <f t="shared" si="11"/>
+        <v>23978.616101255961</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -8450,60 +8581,61 @@
         <v>2038</v>
       </c>
       <c r="B15" s="1">
-        <v>67152.396502738513</v>
-      </c>
-      <c r="C15">
+        <f>Subtracting_Biochar_Removals!F25</f>
+        <v>57280.994216835956</v>
+      </c>
+      <c r="C15" s="1">
         <f>Summary_Reductions!H20</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E15" s="5">
-        <f t="shared" si="0"/>
-        <v>67635.879475738519</v>
+        <f t="shared" si="1"/>
+        <v>57764.477189835954</v>
       </c>
       <c r="F15" s="5"/>
-      <c r="G15" s="5">
-        <f t="shared" si="1"/>
-        <v>104978.33219299528</v>
+      <c r="G15" s="17">
+        <f t="shared" si="3"/>
+        <v>89617.589357655976</v>
       </c>
       <c r="I15" s="5">
-        <f>0.1*E15</f>
-        <v>6763.587947573852</v>
+        <f t="shared" si="0"/>
+        <v>5776.4477189835961</v>
       </c>
       <c r="J15" s="5">
-        <f>0.1*E14</f>
-        <v>7152.6951406302924</v>
+        <f t="shared" si="2"/>
+        <v>6108.3561546607389</v>
       </c>
       <c r="K15" s="5">
-        <f>0.1*E13</f>
-        <v>7585.1031860754929</v>
+        <f t="shared" si="4"/>
+        <v>6477.2002174254958</v>
       </c>
       <c r="L15" s="5">
-        <f>0.1*E12</f>
-        <v>8081.8214935822025</v>
+        <f t="shared" si="5"/>
+        <v>6900.900933728718</v>
       </c>
       <c r="M15" s="5">
-        <f>0.1*E11</f>
-        <v>8681.5617806178252</v>
+        <f t="shared" si="6"/>
+        <v>7412.4793985701053</v>
       </c>
       <c r="N15" s="5">
-        <f>0.1*E10</f>
-        <v>9456.5621342954964</v>
+        <f t="shared" si="7"/>
+        <v>8073.5547002571593</v>
       </c>
       <c r="O15" s="5">
-        <f>0.1*E9</f>
-        <v>10542.699848537613</v>
+        <f t="shared" si="8"/>
+        <v>9000.0301705056827</v>
       </c>
       <c r="P15" s="5">
-        <f>0.1*E8</f>
-        <v>12196.980607606158</v>
+        <f t="shared" si="9"/>
+        <v>10411.131657991151</v>
       </c>
       <c r="Q15" s="5">
-        <f>0.1*E7</f>
-        <v>14907.905322744849</v>
+        <f t="shared" si="10"/>
+        <v>12723.550440004457</v>
       </c>
       <c r="R15" s="5">
-        <f>0.1*E6</f>
-        <v>19609.414731331486</v>
+        <f t="shared" si="11"/>
+        <v>16733.937965528861</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -8511,60 +8643,61 @@
         <v>2039</v>
       </c>
       <c r="B16" s="1">
-        <v>63577.945426597624</v>
-      </c>
-      <c r="C16">
+        <f>Subtracting_Biochar_Removals!F26</f>
+        <v>54231.987448887776</v>
+      </c>
+      <c r="C16" s="1">
         <f>Summary_Reductions!H21</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E16" s="5">
-        <f t="shared" si="0"/>
-        <v>64061.428399597622</v>
+        <f t="shared" si="1"/>
+        <v>54715.470421887774</v>
       </c>
       <c r="F16" s="5"/>
-      <c r="G16" s="5">
-        <f t="shared" si="1"/>
-        <v>91775.060301623555</v>
+      <c r="G16" s="17">
+        <f t="shared" si="3"/>
+        <v>78355.198434315884</v>
       </c>
       <c r="I16" s="5">
-        <f>0.1*E16</f>
-        <v>6406.1428399597626</v>
+        <f t="shared" si="0"/>
+        <v>5471.5470421887776</v>
       </c>
       <c r="J16" s="5">
-        <f>0.1*E15</f>
-        <v>6763.587947573852</v>
+        <f t="shared" si="2"/>
+        <v>5776.4477189835961</v>
       </c>
       <c r="K16" s="5">
-        <f>0.1*E14</f>
-        <v>7152.6951406302924</v>
+        <f t="shared" si="4"/>
+        <v>6108.3561546607389</v>
       </c>
       <c r="L16" s="5">
-        <f>0.1*E13</f>
-        <v>7585.1031860754929</v>
+        <f t="shared" si="5"/>
+        <v>6477.2002174254958</v>
       </c>
       <c r="M16" s="5">
-        <f>0.1*E12</f>
-        <v>8081.8214935822025</v>
+        <f t="shared" si="6"/>
+        <v>6900.900933728718</v>
       </c>
       <c r="N16" s="5">
-        <f>0.1*E11</f>
-        <v>8681.5617806178252</v>
+        <f t="shared" si="7"/>
+        <v>7412.4793985701053</v>
       </c>
       <c r="O16" s="5">
-        <f>0.1*E10</f>
-        <v>9456.5621342954964</v>
+        <f t="shared" si="8"/>
+        <v>8073.5547002571593</v>
       </c>
       <c r="P16" s="5">
-        <f>0.1*E9</f>
-        <v>10542.699848537613</v>
+        <f t="shared" si="9"/>
+        <v>9000.0301705056827</v>
       </c>
       <c r="Q16" s="5">
-        <f>0.1*E8</f>
-        <v>12196.980607606158</v>
+        <f t="shared" si="10"/>
+        <v>10411.131657991151</v>
       </c>
       <c r="R16" s="5">
-        <f>0.1*E7</f>
-        <v>14907.905322744849</v>
+        <f t="shared" si="11"/>
+        <v>12723.550440004457</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -8572,60 +8705,61 @@
         <v>2040</v>
       </c>
       <c r="B17" s="1">
-        <v>60253.508215713257</v>
-      </c>
-      <c r="C17">
+        <f>Subtracting_Biochar_Removals!F27</f>
+        <v>51396.242508003408</v>
+      </c>
+      <c r="C17" s="1">
         <f>Summary_Reductions!H22</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E17" s="5">
-        <f t="shared" si="0"/>
-        <v>60736.991188713255</v>
+        <f t="shared" si="1"/>
+        <v>51879.725481003406</v>
       </c>
       <c r="F17" s="5"/>
-      <c r="G17" s="5">
-        <f t="shared" si="1"/>
-        <v>82940.854097750038</v>
+      <c r="G17" s="17">
+        <f t="shared" si="3"/>
+        <v>70819.620542411765</v>
       </c>
       <c r="I17" s="5">
-        <f>0.1*E17</f>
-        <v>6073.6991188713255</v>
+        <f t="shared" si="0"/>
+        <v>5187.9725481003406</v>
       </c>
       <c r="J17" s="5">
-        <f>0.1*E16</f>
-        <v>6406.1428399597626</v>
+        <f t="shared" si="2"/>
+        <v>5471.5470421887776</v>
       </c>
       <c r="K17" s="5">
-        <f>0.1*E15</f>
-        <v>6763.587947573852</v>
+        <f t="shared" si="4"/>
+        <v>5776.4477189835961</v>
       </c>
       <c r="L17" s="5">
-        <f>0.1*E14</f>
-        <v>7152.6951406302924</v>
+        <f t="shared" si="5"/>
+        <v>6108.3561546607389</v>
       </c>
       <c r="M17" s="5">
-        <f>0.1*E13</f>
-        <v>7585.1031860754929</v>
+        <f t="shared" si="6"/>
+        <v>6477.2002174254958</v>
       </c>
       <c r="N17" s="5">
-        <f>0.1*E12</f>
-        <v>8081.8214935822025</v>
+        <f t="shared" si="7"/>
+        <v>6900.900933728718</v>
       </c>
       <c r="O17" s="5">
-        <f>0.1*E11</f>
-        <v>8681.5617806178252</v>
+        <f t="shared" si="8"/>
+        <v>7412.4793985701053</v>
       </c>
       <c r="P17" s="5">
-        <f>0.1*E10</f>
-        <v>9456.5621342954964</v>
+        <f t="shared" si="9"/>
+        <v>8073.5547002571593</v>
       </c>
       <c r="Q17" s="5">
-        <f>0.1*E9</f>
-        <v>10542.699848537613</v>
+        <f t="shared" si="10"/>
+        <v>9000.0301705056827</v>
       </c>
       <c r="R17" s="5">
-        <f>0.1*E8</f>
-        <v>12196.980607606158</v>
+        <f t="shared" si="11"/>
+        <v>10411.131657991151</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -8633,60 +8767,61 @@
         <v>2041</v>
       </c>
       <c r="B18" s="1">
-        <v>57139.074565888819</v>
-      </c>
-      <c r="C18">
+        <f>Subtracting_Biochar_Removals!F28</f>
+        <v>48739.630604703161</v>
+      </c>
+      <c r="C18" s="1">
         <f>Summary_Reductions!H23</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E18" s="5">
-        <f t="shared" si="0"/>
-        <v>57622.557538888817</v>
+        <f t="shared" si="1"/>
+        <v>49223.11357770316</v>
       </c>
       <c r="F18" s="5"/>
-      <c r="G18" s="5">
-        <f t="shared" si="1"/>
-        <v>76506.129244032752</v>
+      <c r="G18" s="17">
+        <f t="shared" si="3"/>
+        <v>65330.800242190933</v>
       </c>
       <c r="I18" s="5">
-        <f>0.1*E18</f>
-        <v>5762.2557538888823</v>
+        <f t="shared" si="0"/>
+        <v>4922.3113577703161</v>
       </c>
       <c r="J18" s="5">
-        <f>0.1*E17</f>
-        <v>6073.6991188713255</v>
+        <f t="shared" si="2"/>
+        <v>5187.9725481003406</v>
       </c>
       <c r="K18" s="5">
-        <f>0.1*E16</f>
-        <v>6406.1428399597626</v>
+        <f t="shared" si="4"/>
+        <v>5471.5470421887776</v>
       </c>
       <c r="L18" s="5">
-        <f>0.1*E15</f>
-        <v>6763.587947573852</v>
+        <f t="shared" si="5"/>
+        <v>5776.4477189835961</v>
       </c>
       <c r="M18" s="5">
-        <f>0.1*E14</f>
-        <v>7152.6951406302924</v>
+        <f t="shared" si="6"/>
+        <v>6108.3561546607389</v>
       </c>
       <c r="N18" s="5">
-        <f>0.1*E13</f>
-        <v>7585.1031860754929</v>
+        <f t="shared" si="7"/>
+        <v>6477.2002174254958</v>
       </c>
       <c r="O18" s="5">
-        <f>0.1*E12</f>
-        <v>8081.8214935822025</v>
+        <f t="shared" si="8"/>
+        <v>6900.900933728718</v>
       </c>
       <c r="P18" s="5">
-        <f>0.1*E11</f>
-        <v>8681.5617806178252</v>
+        <f t="shared" si="9"/>
+        <v>7412.4793985701053</v>
       </c>
       <c r="Q18" s="5">
-        <f>0.1*E10</f>
-        <v>9456.5621342954964</v>
+        <f t="shared" si="10"/>
+        <v>8073.5547002571593</v>
       </c>
       <c r="R18" s="5">
-        <f>0.1*E9</f>
-        <v>10542.699848537613</v>
+        <f t="shared" si="11"/>
+        <v>9000.0301705056827</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -8694,60 +8829,61 @@
         <v>2042</v>
       </c>
       <c r="B19" s="1">
-        <v>54208.979240103537</v>
-      </c>
-      <c r="C19">
+        <f>Subtracting_Biochar_Removals!F29</f>
+        <v>46240.259291808317</v>
+      </c>
+      <c r="C19" s="1">
         <f>Summary_Reductions!H24</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E19" s="5">
-        <f t="shared" si="0"/>
-        <v>54692.462213103536</v>
+        <f t="shared" si="1"/>
+        <v>46723.742264808316</v>
       </c>
       <c r="F19" s="5"/>
-      <c r="G19" s="5">
-        <f t="shared" si="1"/>
-        <v>71432.675616805485</v>
+      <c r="G19" s="17">
+        <f t="shared" si="3"/>
+        <v>61003.14429816608</v>
       </c>
       <c r="I19" s="5">
-        <f>0.1*E19</f>
-        <v>5469.2462213103536</v>
+        <f t="shared" si="0"/>
+        <v>4672.3742264808316</v>
       </c>
       <c r="J19" s="5">
-        <f>0.1*E18</f>
-        <v>5762.2557538888823</v>
+        <f t="shared" si="2"/>
+        <v>4922.3113577703161</v>
       </c>
       <c r="K19" s="5">
-        <f>0.1*E17</f>
-        <v>6073.6991188713255</v>
+        <f t="shared" si="4"/>
+        <v>5187.9725481003406</v>
       </c>
       <c r="L19" s="5">
-        <f>0.1*E16</f>
-        <v>6406.1428399597626</v>
+        <f t="shared" si="5"/>
+        <v>5471.5470421887776</v>
       </c>
       <c r="M19" s="5">
-        <f>0.1*E15</f>
-        <v>6763.587947573852</v>
+        <f t="shared" si="6"/>
+        <v>5776.4477189835961</v>
       </c>
       <c r="N19" s="5">
-        <f>0.1*E14</f>
-        <v>7152.6951406302924</v>
+        <f t="shared" si="7"/>
+        <v>6108.3561546607389</v>
       </c>
       <c r="O19" s="5">
-        <f>0.1*E13</f>
-        <v>7585.1031860754929</v>
+        <f t="shared" si="8"/>
+        <v>6477.2002174254958</v>
       </c>
       <c r="P19" s="5">
-        <f>0.1*E12</f>
-        <v>8081.8214935822025</v>
+        <f t="shared" si="9"/>
+        <v>6900.900933728718</v>
       </c>
       <c r="Q19" s="5">
-        <f>0.1*E11</f>
-        <v>8681.5617806178252</v>
+        <f t="shared" si="10"/>
+        <v>7412.4793985701053</v>
       </c>
       <c r="R19" s="5">
-        <f>0.1*E10</f>
-        <v>9456.5621342954964</v>
+        <f t="shared" si="11"/>
+        <v>8073.5547002571593</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -8755,60 +8891,61 @@
         <v>2043</v>
       </c>
       <c r="B20" s="1">
-        <v>51445.416516802092</v>
-      </c>
-      <c r="C20">
+        <f>Subtracting_Biochar_Removals!F30</f>
+        <v>43882.940288832186</v>
+      </c>
+      <c r="C20" s="1">
         <f>Summary_Reductions!H25</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E20" s="5">
-        <f t="shared" si="0"/>
-        <v>51928.89948980209</v>
+        <f t="shared" si="1"/>
+        <v>44366.423261832184</v>
       </c>
       <c r="F20" s="5"/>
-      <c r="G20" s="5">
-        <f t="shared" si="1"/>
-        <v>67169.0034314902</v>
+      <c r="G20" s="17">
+        <f t="shared" si="3"/>
+        <v>57366.231924092142</v>
       </c>
       <c r="I20" s="5">
-        <f>0.1*E20</f>
-        <v>5192.8899489802097</v>
+        <f t="shared" si="0"/>
+        <v>4436.6423261832188</v>
       </c>
       <c r="J20" s="5">
-        <f>0.1*E19</f>
-        <v>5469.2462213103536</v>
+        <f t="shared" si="2"/>
+        <v>4672.3742264808316</v>
       </c>
       <c r="K20" s="5">
-        <f>0.1*E18</f>
-        <v>5762.2557538888823</v>
+        <f t="shared" si="4"/>
+        <v>4922.3113577703161</v>
       </c>
       <c r="L20" s="5">
-        <f>0.1*E17</f>
-        <v>6073.6991188713255</v>
+        <f t="shared" si="5"/>
+        <v>5187.9725481003406</v>
       </c>
       <c r="M20" s="5">
-        <f>0.1*E16</f>
-        <v>6406.1428399597626</v>
+        <f t="shared" si="6"/>
+        <v>5471.5470421887776</v>
       </c>
       <c r="N20" s="5">
-        <f>0.1*E15</f>
-        <v>6763.587947573852</v>
+        <f t="shared" si="7"/>
+        <v>5776.4477189835961</v>
       </c>
       <c r="O20" s="5">
-        <f>0.1*E14</f>
-        <v>7152.6951406302924</v>
+        <f t="shared" si="8"/>
+        <v>6108.3561546607389</v>
       </c>
       <c r="P20" s="5">
-        <f>0.1*E13</f>
-        <v>7585.1031860754929</v>
+        <f t="shared" si="9"/>
+        <v>6477.2002174254958</v>
       </c>
       <c r="Q20" s="5">
-        <f>0.1*E12</f>
-        <v>8081.8214935822025</v>
+        <f t="shared" si="10"/>
+        <v>6900.900933728718</v>
       </c>
       <c r="R20" s="5">
-        <f>0.1*E11</f>
-        <v>8681.5617806178252</v>
+        <f t="shared" si="11"/>
+        <v>7412.4793985701053</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -8816,60 +8953,61 @@
         <v>2044</v>
       </c>
       <c r="B21" s="1">
-        <v>48834.997638395005</v>
-      </c>
-      <c r="C21">
+        <f>Subtracting_Biochar_Removals!F31</f>
+        <v>41656.252985550942</v>
+      </c>
+      <c r="C21" s="1">
         <f>Summary_Reductions!H26</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E21" s="5">
-        <f t="shared" si="0"/>
-        <v>49318.480611395004</v>
+        <f t="shared" si="1"/>
+        <v>42139.73595855094</v>
       </c>
       <c r="F21" s="5"/>
-      <c r="G21" s="5">
-        <f t="shared" si="1"/>
-        <v>63419.28971201188</v>
+      <c r="G21" s="17">
+        <f t="shared" si="3"/>
+        <v>54167.726121377127</v>
       </c>
       <c r="I21" s="5">
-        <f>0.1*E21</f>
-        <v>4931.8480611395007</v>
+        <f t="shared" si="0"/>
+        <v>4213.9735958550946</v>
       </c>
       <c r="J21" s="5">
-        <f>0.1*E20</f>
-        <v>5192.8899489802097</v>
+        <f t="shared" si="2"/>
+        <v>4436.6423261832188</v>
       </c>
       <c r="K21" s="5">
-        <f>0.1*E19</f>
-        <v>5469.2462213103536</v>
+        <f t="shared" si="4"/>
+        <v>4672.3742264808316</v>
       </c>
       <c r="L21" s="5">
-        <f>0.1*E18</f>
-        <v>5762.2557538888823</v>
+        <f t="shared" si="5"/>
+        <v>4922.3113577703161</v>
       </c>
       <c r="M21" s="5">
-        <f>0.1*E17</f>
-        <v>6073.6991188713255</v>
+        <f t="shared" si="6"/>
+        <v>5187.9725481003406</v>
       </c>
       <c r="N21" s="5">
-        <f>0.1*E16</f>
-        <v>6406.1428399597626</v>
+        <f t="shared" si="7"/>
+        <v>5471.5470421887776</v>
       </c>
       <c r="O21" s="5">
-        <f>0.1*E15</f>
-        <v>6763.587947573852</v>
+        <f t="shared" si="8"/>
+        <v>5776.4477189835961</v>
       </c>
       <c r="P21" s="5">
-        <f>0.1*E14</f>
-        <v>7152.6951406302924</v>
+        <f t="shared" si="9"/>
+        <v>6108.3561546607389</v>
       </c>
       <c r="Q21" s="5">
-        <f>0.1*E13</f>
-        <v>7585.1031860754929</v>
+        <f t="shared" si="10"/>
+        <v>6477.2002174254958</v>
       </c>
       <c r="R21" s="5">
-        <f>0.1*E12</f>
-        <v>8081.8214935822025</v>
+        <f t="shared" si="11"/>
+        <v>6900.900933728718</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -8877,60 +9015,61 @@
         <v>2045</v>
       </c>
       <c r="B22" s="1">
-        <v>46366.915248670673</v>
-      </c>
-      <c r="C22">
+        <f>Subtracting_Biochar_Removals!F32</f>
+        <v>39550.978707116083</v>
+      </c>
+      <c r="C22" s="1">
         <f>Summary_Reductions!H27</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E22" s="5">
-        <f t="shared" si="0"/>
-        <v>46850.398221670672</v>
+        <f t="shared" si="1"/>
+        <v>40034.461680116081</v>
       </c>
       <c r="F22" s="5"/>
-      <c r="G22" s="5">
-        <f t="shared" si="1"/>
-        <v>60022.508040596746</v>
+      <c r="G22" s="17">
+        <f t="shared" si="3"/>
+        <v>51270.271355660014</v>
       </c>
       <c r="I22" s="5">
-        <f>0.1*E22</f>
-        <v>4685.0398221670675</v>
+        <f t="shared" si="0"/>
+        <v>4003.4461680116083</v>
       </c>
       <c r="J22" s="5">
-        <f>0.1*E21</f>
-        <v>4931.8480611395007</v>
+        <f t="shared" si="2"/>
+        <v>4213.9735958550946</v>
       </c>
       <c r="K22" s="5">
-        <f>0.1*E20</f>
-        <v>5192.8899489802097</v>
+        <f t="shared" si="4"/>
+        <v>4436.6423261832188</v>
       </c>
       <c r="L22" s="5">
-        <f>0.1*E19</f>
-        <v>5469.2462213103536</v>
+        <f t="shared" si="5"/>
+        <v>4672.3742264808316</v>
       </c>
       <c r="M22" s="5">
-        <f>0.1*E18</f>
-        <v>5762.2557538888823</v>
+        <f t="shared" si="6"/>
+        <v>4922.3113577703161</v>
       </c>
       <c r="N22" s="5">
-        <f>0.1*E17</f>
-        <v>6073.6991188713255</v>
+        <f t="shared" si="7"/>
+        <v>5187.9725481003406</v>
       </c>
       <c r="O22" s="5">
-        <f>0.1*E16</f>
-        <v>6406.1428399597626</v>
+        <f t="shared" si="8"/>
+        <v>5471.5470421887776</v>
       </c>
       <c r="P22" s="5">
-        <f>0.1*E15</f>
-        <v>6763.587947573852</v>
+        <f t="shared" si="9"/>
+        <v>5776.4477189835961</v>
       </c>
       <c r="Q22" s="5">
-        <f>0.1*E14</f>
-        <v>7152.6951406302924</v>
+        <f t="shared" si="10"/>
+        <v>6108.3561546607389</v>
       </c>
       <c r="R22" s="5">
-        <f>0.1*E13</f>
-        <v>7585.1031860754929</v>
+        <f t="shared" si="11"/>
+        <v>6477.2002174254958</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -8938,60 +9077,61 @@
         <v>2046</v>
       </c>
       <c r="B23" s="1">
-        <v>44031.957245805876</v>
-      </c>
-      <c r="C23">
+        <f>Subtracting_Biochar_Removals!F33</f>
+        <v>37559.259530672411</v>
+      </c>
+      <c r="C23" s="1">
         <f>Summary_Reductions!H28</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E23" s="5">
-        <f t="shared" si="0"/>
-        <v>44515.440218805874</v>
+        <f t="shared" si="1"/>
+        <v>38042.742503672409</v>
       </c>
       <c r="F23" s="5"/>
-      <c r="G23" s="5">
-        <f t="shared" si="1"/>
-        <v>56888.948876401832</v>
+      <c r="G23" s="17">
+        <f t="shared" si="3"/>
+        <v>48597.34538860176</v>
       </c>
       <c r="I23" s="5">
-        <f>0.1*E23</f>
-        <v>4451.5440218805879</v>
+        <f t="shared" si="0"/>
+        <v>3804.2742503672412</v>
       </c>
       <c r="J23" s="5">
-        <f>0.1*E22</f>
-        <v>4685.0398221670675</v>
+        <f t="shared" si="2"/>
+        <v>4003.4461680116083</v>
       </c>
       <c r="K23" s="5">
-        <f>0.1*E21</f>
-        <v>4931.8480611395007</v>
+        <f t="shared" si="4"/>
+        <v>4213.9735958550946</v>
       </c>
       <c r="L23" s="5">
-        <f>0.1*E20</f>
-        <v>5192.8899489802097</v>
+        <f t="shared" si="5"/>
+        <v>4436.6423261832188</v>
       </c>
       <c r="M23" s="5">
-        <f>0.1*E19</f>
-        <v>5469.2462213103536</v>
+        <f t="shared" si="6"/>
+        <v>4672.3742264808316</v>
       </c>
       <c r="N23" s="5">
-        <f>0.1*E18</f>
-        <v>5762.2557538888823</v>
+        <f t="shared" si="7"/>
+        <v>4922.3113577703161</v>
       </c>
       <c r="O23" s="5">
-        <f>0.1*E17</f>
-        <v>6073.6991188713255</v>
+        <f t="shared" si="8"/>
+        <v>5187.9725481003406</v>
       </c>
       <c r="P23" s="5">
-        <f>0.1*E16</f>
-        <v>6406.1428399597626</v>
+        <f t="shared" si="9"/>
+        <v>5471.5470421887776</v>
       </c>
       <c r="Q23" s="5">
-        <f>0.1*E15</f>
-        <v>6763.587947573852</v>
+        <f t="shared" si="10"/>
+        <v>5776.4477189835961</v>
       </c>
       <c r="R23" s="5">
-        <f>0.1*E14</f>
-        <v>7152.6951406302924</v>
+        <f t="shared" si="11"/>
+        <v>6108.3561546607389</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -8999,60 +9139,61 @@
         <v>2047</v>
       </c>
       <c r="B24" s="1">
-        <v>41821.970249623686</v>
-      </c>
-      <c r="C24">
+        <f>Subtracting_Biochar_Removals!F34</f>
+        <v>35674.140622929001</v>
+      </c>
+      <c r="C24" s="1">
         <f>Summary_Reductions!H29</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E24" s="5">
-        <f t="shared" si="0"/>
-        <v>42305.453222623684</v>
+        <f t="shared" si="1"/>
+        <v>36157.623595928999</v>
       </c>
       <c r="F24" s="5"/>
-      <c r="G24" s="5">
-        <f t="shared" si="1"/>
-        <v>53966.799058033917</v>
+      <c r="G24" s="17">
+        <f t="shared" si="3"/>
+        <v>46104.751593533932</v>
       </c>
       <c r="I24" s="5">
-        <f>0.1*E24</f>
-        <v>4230.5453222623682</v>
+        <f t="shared" si="0"/>
+        <v>3615.7623595928999</v>
       </c>
       <c r="J24" s="5">
-        <f>0.1*E23</f>
-        <v>4451.5440218805879</v>
+        <f t="shared" si="2"/>
+        <v>3804.2742503672412</v>
       </c>
       <c r="K24" s="5">
-        <f>0.1*E22</f>
-        <v>4685.0398221670675</v>
+        <f t="shared" si="4"/>
+        <v>4003.4461680116083</v>
       </c>
       <c r="L24" s="5">
-        <f>0.1*E21</f>
-        <v>4931.8480611395007</v>
+        <f t="shared" si="5"/>
+        <v>4213.9735958550946</v>
       </c>
       <c r="M24" s="5">
-        <f>0.1*E20</f>
-        <v>5192.8899489802097</v>
+        <f t="shared" si="6"/>
+        <v>4436.6423261832188</v>
       </c>
       <c r="N24" s="5">
-        <f>0.1*E19</f>
-        <v>5469.2462213103536</v>
+        <f t="shared" si="7"/>
+        <v>4672.3742264808316</v>
       </c>
       <c r="O24" s="5">
-        <f>0.1*E18</f>
-        <v>5762.2557538888823</v>
+        <f t="shared" si="8"/>
+        <v>4922.3113577703161</v>
       </c>
       <c r="P24" s="5">
-        <f>0.1*E17</f>
-        <v>6073.6991188713255</v>
+        <f t="shared" si="9"/>
+        <v>5187.9725481003406</v>
       </c>
       <c r="Q24" s="5">
-        <f>0.1*E16</f>
-        <v>6406.1428399597626</v>
+        <f t="shared" si="10"/>
+        <v>5471.5470421887776</v>
       </c>
       <c r="R24" s="5">
-        <f>0.1*E15</f>
-        <v>6763.587947573852</v>
+        <f t="shared" si="11"/>
+        <v>5776.4477189835961</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -9060,60 +9201,61 @@
         <v>2048</v>
       </c>
       <c r="B25" s="1">
-        <v>39729.561607948839</v>
-      </c>
-      <c r="C25">
+        <f>Subtracting_Biochar_Removals!F35</f>
+        <v>33889.316051580361</v>
+      </c>
+      <c r="C25" s="1">
         <f>Summary_Reductions!H30</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E25" s="5">
-        <f t="shared" si="0"/>
-        <v>40213.044580948837</v>
+        <f t="shared" si="1"/>
+        <v>34372.799024580359</v>
       </c>
       <c r="F25" s="5"/>
-      <c r="G25" s="5">
-        <f t="shared" si="1"/>
-        <v>51224.51556855494</v>
+      <c r="G25" s="17">
+        <f t="shared" si="3"/>
+        <v>43765.583777008374</v>
       </c>
       <c r="I25" s="5">
-        <f>0.1*E25</f>
-        <v>4021.304458094884</v>
+        <f t="shared" si="0"/>
+        <v>3437.2799024580363</v>
       </c>
       <c r="J25" s="5">
-        <f>0.1*E24</f>
-        <v>4230.5453222623682</v>
+        <f t="shared" si="2"/>
+        <v>3615.7623595928999</v>
       </c>
       <c r="K25" s="5">
-        <f>0.1*E23</f>
-        <v>4451.5440218805879</v>
+        <f t="shared" si="4"/>
+        <v>3804.2742503672412</v>
       </c>
       <c r="L25" s="5">
-        <f>0.1*E22</f>
-        <v>4685.0398221670675</v>
+        <f t="shared" si="5"/>
+        <v>4003.4461680116083</v>
       </c>
       <c r="M25" s="5">
-        <f>0.1*E21</f>
-        <v>4931.8480611395007</v>
+        <f t="shared" si="6"/>
+        <v>4213.9735958550946</v>
       </c>
       <c r="N25" s="5">
-        <f>0.1*E20</f>
-        <v>5192.8899489802097</v>
+        <f t="shared" si="7"/>
+        <v>4436.6423261832188</v>
       </c>
       <c r="O25" s="5">
-        <f>0.1*E19</f>
-        <v>5469.2462213103536</v>
+        <f t="shared" si="8"/>
+        <v>4672.3742264808316</v>
       </c>
       <c r="P25" s="5">
-        <f>0.1*E18</f>
-        <v>5762.2557538888823</v>
+        <f t="shared" si="9"/>
+        <v>4922.3113577703161</v>
       </c>
       <c r="Q25" s="5">
-        <f>0.1*E17</f>
-        <v>6073.6991188713255</v>
+        <f t="shared" si="10"/>
+        <v>5187.9725481003406</v>
       </c>
       <c r="R25" s="5">
-        <f>0.1*E16</f>
-        <v>6406.1428399597626</v>
+        <f t="shared" si="11"/>
+        <v>5471.5470421887776</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -9121,60 +9263,61 @@
         <v>2049</v>
       </c>
       <c r="B26" s="1">
-        <v>37747.928445136684</v>
-      </c>
-      <c r="C26">
+        <f>Subtracting_Biochar_Removals!F36</f>
+        <v>32198.982963701594</v>
+      </c>
+      <c r="C26" s="1">
         <f>Summary_Reductions!H31</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E26" s="5">
-        <f t="shared" si="0"/>
-        <v>38231.411418136682</v>
+        <f t="shared" si="1"/>
+        <v>32682.465936701592</v>
       </c>
       <c r="F26" s="5"/>
-      <c r="G26" s="5">
-        <f t="shared" si="1"/>
-        <v>48641.513870408846</v>
+      <c r="G26" s="17">
+        <f t="shared" si="3"/>
+        <v>41562.28332848975</v>
       </c>
       <c r="I26" s="5">
-        <f>0.1*E26</f>
-        <v>3823.1411418136686</v>
+        <f t="shared" si="0"/>
+        <v>3268.2465936701592</v>
       </c>
       <c r="J26" s="5">
-        <f>0.1*E25</f>
-        <v>4021.304458094884</v>
+        <f t="shared" si="2"/>
+        <v>3437.2799024580363</v>
       </c>
       <c r="K26" s="5">
-        <f>0.1*E24</f>
-        <v>4230.5453222623682</v>
+        <f t="shared" si="4"/>
+        <v>3615.7623595928999</v>
       </c>
       <c r="L26" s="5">
-        <f>0.1*E23</f>
-        <v>4451.5440218805879</v>
+        <f t="shared" si="5"/>
+        <v>3804.2742503672412</v>
       </c>
       <c r="M26" s="5">
-        <f>0.1*E22</f>
-        <v>4685.0398221670675</v>
+        <f t="shared" si="6"/>
+        <v>4003.4461680116083</v>
       </c>
       <c r="N26" s="5">
-        <f>0.1*E21</f>
-        <v>4931.8480611395007</v>
+        <f t="shared" si="7"/>
+        <v>4213.9735958550946</v>
       </c>
       <c r="O26" s="5">
-        <f>0.1*E20</f>
-        <v>5192.8899489802097</v>
+        <f t="shared" si="8"/>
+        <v>4436.6423261832188</v>
       </c>
       <c r="P26" s="5">
-        <f>0.1*E19</f>
-        <v>5469.2462213103536</v>
+        <f t="shared" si="9"/>
+        <v>4672.3742264808316</v>
       </c>
       <c r="Q26" s="5">
-        <f>0.1*E18</f>
-        <v>5762.2557538888823</v>
+        <f t="shared" si="10"/>
+        <v>4922.3113577703161</v>
       </c>
       <c r="R26" s="5">
-        <f>0.1*E17</f>
-        <v>6073.6991188713255</v>
+        <f t="shared" si="11"/>
+        <v>5187.9725481003406</v>
       </c>
     </row>
     <row r="27" spans="1:18">
@@ -9182,60 +9325,61 @@
         <v>2050</v>
       </c>
       <c r="B27" s="1">
-        <v>35870.754808756719</v>
-      </c>
-      <c r="C27">
+        <f>Subtracting_Biochar_Removals!F37</f>
+        <v>30597.753851869482</v>
+      </c>
+      <c r="C27" s="1">
         <f>Summary_Reductions!H32</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E27" s="5">
-        <f t="shared" si="0"/>
-        <v>36354.237781756718</v>
+        <f t="shared" si="1"/>
+        <v>31081.23682486948</v>
       </c>
       <c r="F27" s="5"/>
-      <c r="G27" s="5">
-        <f t="shared" si="1"/>
-        <v>46203.238529713199</v>
+      <c r="G27" s="17">
+        <f t="shared" si="3"/>
+        <v>39482.434462876357</v>
       </c>
       <c r="I27" s="5">
-        <f>0.1*E27</f>
-        <v>3635.4237781756719</v>
+        <f t="shared" si="0"/>
+        <v>3108.1236824869484</v>
       </c>
       <c r="J27" s="5">
-        <f>0.1*E26</f>
-        <v>3823.1411418136686</v>
+        <f t="shared" si="2"/>
+        <v>3268.2465936701592</v>
       </c>
       <c r="K27" s="5">
-        <f>0.1*E25</f>
-        <v>4021.304458094884</v>
+        <f t="shared" si="4"/>
+        <v>3437.2799024580363</v>
       </c>
       <c r="L27" s="5">
-        <f>0.1*E24</f>
-        <v>4230.5453222623682</v>
+        <f t="shared" si="5"/>
+        <v>3615.7623595928999</v>
       </c>
       <c r="M27" s="5">
-        <f>0.1*E23</f>
-        <v>4451.5440218805879</v>
+        <f t="shared" si="6"/>
+        <v>3804.2742503672412</v>
       </c>
       <c r="N27" s="5">
-        <f>0.1*E22</f>
-        <v>4685.0398221670675</v>
+        <f t="shared" si="7"/>
+        <v>4003.4461680116083</v>
       </c>
       <c r="O27" s="5">
-        <f>0.1*E21</f>
-        <v>4931.8480611395007</v>
+        <f t="shared" si="8"/>
+        <v>4213.9735958550946</v>
       </c>
       <c r="P27" s="5">
-        <f>0.1*E20</f>
-        <v>5192.8899489802097</v>
+        <f t="shared" si="9"/>
+        <v>4436.6423261832188</v>
       </c>
       <c r="Q27" s="5">
-        <f>0.1*E19</f>
-        <v>5469.2462213103536</v>
+        <f t="shared" si="10"/>
+        <v>4672.3742264808316</v>
       </c>
       <c r="R27" s="5">
-        <f>0.1*E18</f>
-        <v>5762.2557538888823</v>
+        <f t="shared" si="11"/>
+        <v>4922.3113577703161</v>
       </c>
     </row>
     <row r="28" spans="1:18">
@@ -9243,60 +9387,61 @@
         <v>2051</v>
       </c>
       <c r="B28" s="1">
-        <v>34092.145713041056</v>
-      </c>
-      <c r="C28">
+        <f>Subtracting_Biochar_Removals!F38</f>
+        <v>29080.600293224023</v>
+      </c>
+      <c r="C28" s="1">
         <f>Summary_Reductions!H33</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E28" s="5">
-        <f t="shared" si="0"/>
-        <v>34575.628686041055</v>
+        <f t="shared" si="1"/>
+        <v>29564.083266224021</v>
       </c>
       <c r="F28" s="5"/>
-      <c r="G28" s="5">
-        <f t="shared" si="1"/>
-        <v>43898.545644428421</v>
+      <c r="G28" s="17">
+        <f t="shared" si="3"/>
+        <v>37516.531431728443</v>
       </c>
       <c r="I28" s="5">
-        <f>0.1*E28</f>
-        <v>3457.5628686041055</v>
+        <f t="shared" si="0"/>
+        <v>2956.4083266224025</v>
       </c>
       <c r="J28" s="5">
-        <f>0.1*E27</f>
-        <v>3635.4237781756719</v>
+        <f t="shared" si="2"/>
+        <v>3108.1236824869484</v>
       </c>
       <c r="K28" s="5">
-        <f>0.1*E26</f>
-        <v>3823.1411418136686</v>
+        <f t="shared" si="4"/>
+        <v>3268.2465936701592</v>
       </c>
       <c r="L28" s="5">
-        <f>0.1*E25</f>
-        <v>4021.304458094884</v>
+        <f t="shared" si="5"/>
+        <v>3437.2799024580363</v>
       </c>
       <c r="M28" s="5">
-        <f>0.1*E24</f>
-        <v>4230.5453222623682</v>
+        <f t="shared" si="6"/>
+        <v>3615.7623595928999</v>
       </c>
       <c r="N28" s="5">
-        <f>0.1*E23</f>
-        <v>4451.5440218805879</v>
+        <f t="shared" si="7"/>
+        <v>3804.2742503672412</v>
       </c>
       <c r="O28" s="5">
-        <f>0.1*E22</f>
-        <v>4685.0398221670675</v>
+        <f t="shared" si="8"/>
+        <v>4003.4461680116083</v>
       </c>
       <c r="P28" s="5">
-        <f>0.1*E21</f>
-        <v>4931.8480611395007</v>
+        <f t="shared" si="9"/>
+        <v>4213.9735958550946</v>
       </c>
       <c r="Q28" s="5">
-        <f>0.1*E20</f>
-        <v>5192.8899489802097</v>
+        <f t="shared" si="10"/>
+        <v>4436.6423261832188</v>
       </c>
       <c r="R28" s="5">
-        <f>0.1*E19</f>
-        <v>5469.2462213103536</v>
+        <f t="shared" si="11"/>
+        <v>4672.3742264808316</v>
       </c>
     </row>
     <row r="29" spans="1:18">
@@ -9304,60 +9449,61 @@
         <v>2052</v>
       </c>
       <c r="B29" s="1">
-        <v>32406.58152806999</v>
-      </c>
-      <c r="C29">
+        <f>Subtracting_Biochar_Removals!F39</f>
+        <v>27642.814043443701</v>
+      </c>
+      <c r="C29" s="1">
         <f>Summary_Reductions!H34</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E29" s="5">
-        <f t="shared" si="0"/>
-        <v>32890.064501069988</v>
+        <f t="shared" si="1"/>
+        <v>28126.297016443699</v>
       </c>
       <c r="F29" s="5"/>
-      <c r="G29" s="5">
-        <f t="shared" si="1"/>
-        <v>41718.305873225065</v>
+      <c r="G29" s="17">
+        <f t="shared" si="3"/>
+        <v>35656.786906891975</v>
       </c>
       <c r="I29" s="5">
-        <f>0.1*E29</f>
-        <v>3289.0064501069992</v>
+        <f t="shared" si="0"/>
+        <v>2812.62970164437</v>
       </c>
       <c r="J29" s="5">
-        <f>0.1*E28</f>
-        <v>3457.5628686041055</v>
+        <f t="shared" si="2"/>
+        <v>2956.4083266224025</v>
       </c>
       <c r="K29" s="5">
-        <f>0.1*E27</f>
-        <v>3635.4237781756719</v>
+        <f t="shared" si="4"/>
+        <v>3108.1236824869484</v>
       </c>
       <c r="L29" s="5">
-        <f>0.1*E26</f>
-        <v>3823.1411418136686</v>
+        <f t="shared" si="5"/>
+        <v>3268.2465936701592</v>
       </c>
       <c r="M29" s="5">
-        <f>0.1*E25</f>
-        <v>4021.304458094884</v>
+        <f t="shared" si="6"/>
+        <v>3437.2799024580363</v>
       </c>
       <c r="N29" s="5">
-        <f>0.1*E24</f>
-        <v>4230.5453222623682</v>
+        <f t="shared" si="7"/>
+        <v>3615.7623595928999</v>
       </c>
       <c r="O29" s="5">
-        <f>0.1*E23</f>
-        <v>4451.5440218805879</v>
+        <f t="shared" si="8"/>
+        <v>3804.2742503672412</v>
       </c>
       <c r="P29" s="5">
-        <f>0.1*E22</f>
-        <v>4685.0398221670675</v>
+        <f t="shared" si="9"/>
+        <v>4003.4461680116083</v>
       </c>
       <c r="Q29" s="5">
-        <f>0.1*E21</f>
-        <v>4931.8480611395007</v>
+        <f t="shared" si="10"/>
+        <v>4213.9735958550946</v>
       </c>
       <c r="R29" s="5">
-        <f>0.1*E20</f>
-        <v>5192.8899489802097</v>
+        <f t="shared" si="11"/>
+        <v>4436.6423261832188</v>
       </c>
     </row>
     <row r="30" spans="1:18">
@@ -9365,60 +9511,61 @@
         <v>2053</v>
       </c>
       <c r="B30" s="1">
-        <v>30808.883904145074</v>
-      </c>
-      <c r="C30">
+        <f>Subtracting_Biochar_Removals!F40</f>
+        <v>26279.977970235748</v>
+      </c>
+      <c r="C30" s="1">
         <f>Summary_Reductions!H35</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E30" s="5">
-        <f t="shared" si="0"/>
-        <v>31292.366877145072</v>
+        <f t="shared" si="1"/>
+        <v>26763.460943235747</v>
       </c>
       <c r="F30" s="5"/>
-      <c r="G30" s="5">
-        <f t="shared" si="1"/>
-        <v>39654.652611959362</v>
+      <c r="G30" s="17">
+        <f t="shared" si="3"/>
+        <v>33896.490675032335</v>
       </c>
       <c r="I30" s="5">
-        <f>0.1*E30</f>
-        <v>3129.2366877145073</v>
+        <f t="shared" si="0"/>
+        <v>2676.346094323575</v>
       </c>
       <c r="J30" s="5">
-        <f>0.1*E29</f>
-        <v>3289.0064501069992</v>
+        <f t="shared" si="2"/>
+        <v>2812.62970164437</v>
       </c>
       <c r="K30" s="5">
-        <f>0.1*E28</f>
-        <v>3457.5628686041055</v>
+        <f t="shared" si="4"/>
+        <v>2956.4083266224025</v>
       </c>
       <c r="L30" s="5">
-        <f>0.1*E27</f>
-        <v>3635.4237781756719</v>
+        <f t="shared" si="5"/>
+        <v>3108.1236824869484</v>
       </c>
       <c r="M30" s="5">
-        <f>0.1*E26</f>
-        <v>3823.1411418136686</v>
+        <f t="shared" si="6"/>
+        <v>3268.2465936701592</v>
       </c>
       <c r="N30" s="5">
-        <f>0.1*E25</f>
-        <v>4021.304458094884</v>
+        <f t="shared" si="7"/>
+        <v>3437.2799024580363</v>
       </c>
       <c r="O30" s="5">
-        <f>0.1*E24</f>
-        <v>4230.5453222623682</v>
+        <f t="shared" si="8"/>
+        <v>3615.7623595928999</v>
       </c>
       <c r="P30" s="5">
-        <f>0.1*E23</f>
-        <v>4451.5440218805879</v>
+        <f t="shared" si="9"/>
+        <v>3804.2742503672412</v>
       </c>
       <c r="Q30" s="5">
-        <f>0.1*E22</f>
-        <v>4685.0398221670675</v>
+        <f t="shared" si="10"/>
+        <v>4003.4461680116083</v>
       </c>
       <c r="R30" s="5">
-        <f>0.1*E21</f>
-        <v>4931.8480611395007</v>
+        <f t="shared" si="11"/>
+        <v>4213.9735958550946</v>
       </c>
     </row>
     <row r="31" spans="1:18">
@@ -9426,60 +9573,61 @@
         <v>2054</v>
       </c>
       <c r="B31" s="1">
-        <v>29294.188513732159</v>
-      </c>
-      <c r="C31">
+        <f>Subtracting_Biochar_Removals!F41</f>
+        <v>24987.942802213533</v>
+      </c>
+      <c r="C31" s="1">
         <f>Summary_Reductions!H36</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E31" s="5">
-        <f t="shared" si="0"/>
-        <v>29777.671486732157</v>
+        <f t="shared" si="1"/>
+        <v>25471.425775213531</v>
       </c>
       <c r="F31" s="5"/>
-      <c r="G31" s="5">
-        <f t="shared" si="1"/>
-        <v>37700.571699493077</v>
+      <c r="G31" s="17">
+        <f t="shared" si="3"/>
+        <v>32229.659656698594</v>
       </c>
       <c r="I31" s="5">
-        <f>0.1*E31</f>
-        <v>2977.7671486732161</v>
+        <f t="shared" si="0"/>
+        <v>2547.1425775213534</v>
       </c>
       <c r="J31" s="5">
-        <f>0.1*E30</f>
-        <v>3129.2366877145073</v>
+        <f t="shared" si="2"/>
+        <v>2676.346094323575</v>
       </c>
       <c r="K31" s="5">
-        <f>0.1*E29</f>
-        <v>3289.0064501069992</v>
+        <f t="shared" si="4"/>
+        <v>2812.62970164437</v>
       </c>
       <c r="L31" s="5">
-        <f>0.1*E28</f>
-        <v>3457.5628686041055</v>
+        <f t="shared" si="5"/>
+        <v>2956.4083266224025</v>
       </c>
       <c r="M31" s="5">
-        <f>0.1*E27</f>
-        <v>3635.4237781756719</v>
+        <f t="shared" si="6"/>
+        <v>3108.1236824869484</v>
       </c>
       <c r="N31" s="5">
-        <f>0.1*E26</f>
-        <v>3823.1411418136686</v>
+        <f t="shared" si="7"/>
+        <v>3268.2465936701592</v>
       </c>
       <c r="O31" s="5">
-        <f>0.1*E25</f>
-        <v>4021.304458094884</v>
+        <f t="shared" si="8"/>
+        <v>3437.2799024580363</v>
       </c>
       <c r="P31" s="5">
-        <f>0.1*E24</f>
-        <v>4230.5453222623682</v>
+        <f t="shared" si="9"/>
+        <v>3615.7623595928999</v>
       </c>
       <c r="Q31" s="5">
-        <f>0.1*E23</f>
-        <v>4451.5440218805879</v>
+        <f t="shared" si="10"/>
+        <v>3804.2742503672412</v>
       </c>
       <c r="R31" s="5">
-        <f>0.1*E22</f>
-        <v>4685.0398221670675</v>
+        <f t="shared" si="11"/>
+        <v>4003.4461680116083</v>
       </c>
     </row>
     <row r="32" spans="1:18">
@@ -9487,60 +9635,61 @@
         <v>2055</v>
       </c>
       <c r="B32" s="1">
-        <v>27857.922060236546</v>
-      </c>
-      <c r="C32">
+        <f>Subtracting_Biochar_Removals!F42</f>
+        <v>23762.807517381774</v>
+      </c>
+      <c r="C32" s="1">
         <f>Summary_Reductions!H37</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E32" s="5">
-        <f t="shared" si="0"/>
-        <v>28341.405033236544</v>
+        <f t="shared" si="1"/>
+        <v>24246.290490381773</v>
       </c>
       <c r="F32" s="5"/>
-      <c r="G32" s="5">
-        <f t="shared" si="1"/>
-        <v>35849.672380649667</v>
+      <c r="G32" s="17">
+        <f t="shared" si="3"/>
+        <v>30650.842537725166</v>
       </c>
       <c r="I32" s="5">
-        <f>0.1*E32</f>
-        <v>2834.1405033236547</v>
+        <f t="shared" si="0"/>
+        <v>2424.6290490381775</v>
       </c>
       <c r="J32" s="5">
-        <f>0.1*E31</f>
-        <v>2977.7671486732161</v>
+        <f t="shared" si="2"/>
+        <v>2547.1425775213534</v>
       </c>
       <c r="K32" s="5">
-        <f>0.1*E30</f>
-        <v>3129.2366877145073</v>
+        <f t="shared" si="4"/>
+        <v>2676.346094323575</v>
       </c>
       <c r="L32" s="5">
-        <f>0.1*E29</f>
-        <v>3289.0064501069992</v>
+        <f t="shared" si="5"/>
+        <v>2812.62970164437</v>
       </c>
       <c r="M32" s="5">
-        <f>0.1*E28</f>
-        <v>3457.5628686041055</v>
+        <f t="shared" si="6"/>
+        <v>2956.4083266224025</v>
       </c>
       <c r="N32" s="5">
-        <f>0.1*E27</f>
-        <v>3635.4237781756719</v>
+        <f t="shared" si="7"/>
+        <v>3108.1236824869484</v>
       </c>
       <c r="O32" s="5">
-        <f>0.1*E26</f>
-        <v>3823.1411418136686</v>
+        <f t="shared" si="8"/>
+        <v>3268.2465936701592</v>
       </c>
       <c r="P32" s="5">
-        <f>0.1*E25</f>
-        <v>4021.304458094884</v>
+        <f t="shared" si="9"/>
+        <v>3437.2799024580363</v>
       </c>
       <c r="Q32" s="5">
-        <f>0.1*E24</f>
-        <v>4230.5453222623682</v>
+        <f t="shared" si="10"/>
+        <v>3615.7623595928999</v>
       </c>
       <c r="R32" s="5">
-        <f>0.1*E23</f>
-        <v>4451.5440218805879</v>
+        <f t="shared" si="11"/>
+        <v>3804.2742503672412</v>
       </c>
     </row>
     <row r="33" spans="1:18">
@@ -9548,60 +9697,61 @@
         <v>2056</v>
       </c>
       <c r="B33" s="1">
-        <v>26495.782152554246</v>
-      </c>
-      <c r="C33">
+        <f>Subtracting_Biochar_Removals!F43</f>
+        <v>22600.902176128773</v>
+      </c>
+      <c r="C33" s="1">
         <f>Summary_Reductions!H38</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E33" s="5">
-        <f t="shared" si="0"/>
-        <v>26979.265125554244</v>
+        <f t="shared" si="1"/>
+        <v>23084.385149128771</v>
       </c>
       <c r="F33" s="5"/>
-      <c r="G33" s="5">
-        <f t="shared" si="1"/>
-        <v>34096.054871324501</v>
+      <c r="G33" s="17">
+        <f t="shared" si="3"/>
+        <v>29155.006802270796</v>
       </c>
       <c r="I33" s="5">
-        <f>0.1*E33</f>
-        <v>2697.9265125554248</v>
+        <f t="shared" si="0"/>
+        <v>2308.4385149128771</v>
       </c>
       <c r="J33" s="5">
-        <f>0.1*E32</f>
-        <v>2834.1405033236547</v>
+        <f t="shared" si="2"/>
+        <v>2424.6290490381775</v>
       </c>
       <c r="K33" s="5">
-        <f>0.1*E31</f>
-        <v>2977.7671486732161</v>
+        <f t="shared" si="4"/>
+        <v>2547.1425775213534</v>
       </c>
       <c r="L33" s="5">
-        <f>0.1*E30</f>
-        <v>3129.2366877145073</v>
+        <f t="shared" si="5"/>
+        <v>2676.346094323575</v>
       </c>
       <c r="M33" s="5">
-        <f>0.1*E29</f>
-        <v>3289.0064501069992</v>
+        <f t="shared" si="6"/>
+        <v>2812.62970164437</v>
       </c>
       <c r="N33" s="5">
-        <f>0.1*E28</f>
-        <v>3457.5628686041055</v>
+        <f t="shared" si="7"/>
+        <v>2956.4083266224025</v>
       </c>
       <c r="O33" s="5">
-        <f>0.1*E27</f>
-        <v>3635.4237781756719</v>
+        <f t="shared" si="8"/>
+        <v>3108.1236824869484</v>
       </c>
       <c r="P33" s="5">
-        <f>0.1*E26</f>
-        <v>3823.1411418136686</v>
+        <f t="shared" si="9"/>
+        <v>3268.2465936701592</v>
       </c>
       <c r="Q33" s="5">
-        <f>0.1*E25</f>
-        <v>4021.304458094884</v>
+        <f t="shared" si="10"/>
+        <v>3437.2799024580363</v>
       </c>
       <c r="R33" s="5">
-        <f>0.1*E24</f>
-        <v>4230.5453222623682</v>
+        <f t="shared" si="11"/>
+        <v>3615.7623595928999</v>
       </c>
     </row>
     <row r="34" spans="1:18">
@@ -9609,60 +9759,61 @@
         <v>2057</v>
       </c>
       <c r="B34" s="1">
-        <v>25203.719256242061</v>
-      </c>
-      <c r="C34">
+        <f>Subtracting_Biochar_Removals!F44</f>
+        <v>21498.772525574477</v>
+      </c>
+      <c r="C34" s="1">
         <f>Summary_Reductions!H39</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E34" s="5">
-        <f t="shared" si="0"/>
-        <v>25687.202229242059</v>
+        <f t="shared" si="1"/>
+        <v>21982.255498574475</v>
       </c>
       <c r="F34" s="5"/>
-      <c r="G34" s="5">
-        <f t="shared" si="1"/>
-        <v>32434.229771986342</v>
+      <c r="G34" s="17">
+        <f t="shared" si="3"/>
+        <v>27737.469992535349</v>
       </c>
       <c r="I34" s="5">
-        <f>0.1*E34</f>
-        <v>2568.7202229242062</v>
+        <f t="shared" si="0"/>
+        <v>2198.2255498574477</v>
       </c>
       <c r="J34" s="5">
-        <f>0.1*E33</f>
-        <v>2697.9265125554248</v>
+        <f t="shared" si="2"/>
+        <v>2308.4385149128771</v>
       </c>
       <c r="K34" s="5">
-        <f>0.1*E32</f>
-        <v>2834.1405033236547</v>
+        <f t="shared" si="4"/>
+        <v>2424.6290490381775</v>
       </c>
       <c r="L34" s="5">
-        <f>0.1*E31</f>
-        <v>2977.7671486732161</v>
+        <f t="shared" si="5"/>
+        <v>2547.1425775213534</v>
       </c>
       <c r="M34" s="5">
-        <f>0.1*E30</f>
-        <v>3129.2366877145073</v>
+        <f t="shared" si="6"/>
+        <v>2676.346094323575</v>
       </c>
       <c r="N34" s="5">
-        <f>0.1*E29</f>
-        <v>3289.0064501069992</v>
+        <f t="shared" si="7"/>
+        <v>2812.62970164437</v>
       </c>
       <c r="O34" s="5">
-        <f>0.1*E28</f>
-        <v>3457.5628686041055</v>
+        <f t="shared" si="8"/>
+        <v>2956.4083266224025</v>
       </c>
       <c r="P34" s="5">
-        <f>0.1*E27</f>
-        <v>3635.4237781756719</v>
+        <f t="shared" si="9"/>
+        <v>3108.1236824869484</v>
       </c>
       <c r="Q34" s="5">
-        <f>0.1*E26</f>
-        <v>3823.1411418136686</v>
+        <f t="shared" si="10"/>
+        <v>3268.2465936701592</v>
       </c>
       <c r="R34" s="5">
-        <f>0.1*E25</f>
-        <v>4021.304458094884</v>
+        <f t="shared" si="11"/>
+        <v>3437.2799024580363</v>
       </c>
     </row>
     <row r="35" spans="1:18">
@@ -9670,60 +9821,61 @@
         <v>2058</v>
       </c>
       <c r="B35" s="1">
-        <v>23977.920259800765</v>
-      </c>
-      <c r="C35">
+        <f>Subtracting_Biochar_Removals!F45</f>
+        <v>20453.165981610051</v>
+      </c>
+      <c r="C35" s="1">
         <f>Summary_Reductions!H40</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E35" s="5">
-        <f t="shared" si="0"/>
-        <v>24461.403232800763</v>
+        <f t="shared" si="1"/>
+        <v>20936.648954610049</v>
       </c>
       <c r="F35" s="5"/>
-      <c r="G35" s="5">
-        <f t="shared" si="1"/>
-        <v>30859.06563717153</v>
+      <c r="G35" s="17">
+        <f t="shared" si="3"/>
+        <v>26393.854985538321</v>
       </c>
       <c r="I35" s="5">
-        <f>0.1*E35</f>
-        <v>2446.1403232800762</v>
+        <f t="shared" si="0"/>
+        <v>2093.664895461005</v>
       </c>
       <c r="J35" s="5">
-        <f>0.1*E34</f>
-        <v>2568.7202229242062</v>
+        <f t="shared" si="2"/>
+        <v>2198.2255498574477</v>
       </c>
       <c r="K35" s="5">
-        <f>0.1*E33</f>
-        <v>2697.9265125554248</v>
+        <f t="shared" si="4"/>
+        <v>2308.4385149128771</v>
       </c>
       <c r="L35" s="5">
-        <f>0.1*E32</f>
-        <v>2834.1405033236547</v>
+        <f t="shared" si="5"/>
+        <v>2424.6290490381775</v>
       </c>
       <c r="M35" s="5">
-        <f>0.1*E31</f>
-        <v>2977.7671486732161</v>
+        <f t="shared" si="6"/>
+        <v>2547.1425775213534</v>
       </c>
       <c r="N35" s="5">
-        <f>0.1*E30</f>
-        <v>3129.2366877145073</v>
+        <f t="shared" si="7"/>
+        <v>2676.346094323575</v>
       </c>
       <c r="O35" s="5">
-        <f>0.1*E29</f>
-        <v>3289.0064501069992</v>
+        <f t="shared" si="8"/>
+        <v>2812.62970164437</v>
       </c>
       <c r="P35" s="5">
-        <f>0.1*E28</f>
-        <v>3457.5628686041055</v>
+        <f t="shared" si="9"/>
+        <v>2956.4083266224025</v>
       </c>
       <c r="Q35" s="5">
-        <f>0.1*E27</f>
-        <v>3635.4237781756719</v>
+        <f t="shared" si="10"/>
+        <v>3108.1236824869484</v>
       </c>
       <c r="R35" s="5">
-        <f>0.1*E26</f>
-        <v>3823.1411418136686</v>
+        <f t="shared" si="11"/>
+        <v>3268.2465936701592</v>
       </c>
     </row>
     <row r="36" spans="1:18">
@@ -9731,60 +9883,61 @@
         <v>2059</v>
       </c>
       <c r="B36" s="1">
-        <v>22814.793371703556</v>
-      </c>
-      <c r="C36">
+        <f>Subtracting_Biochar_Removals!F46</f>
+        <v>19461.018746063135</v>
+      </c>
+      <c r="C36" s="1">
         <f>Summary_Reductions!H41</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E36" s="5">
-        <f t="shared" si="0"/>
-        <v>23298.276344703554</v>
+        <f t="shared" si="1"/>
+        <v>19944.501719063133</v>
       </c>
       <c r="F36" s="5"/>
-      <c r="G36" s="5">
-        <f t="shared" si="1"/>
-        <v>29365.752129828215</v>
+      <c r="G36" s="17">
+        <f t="shared" si="3"/>
+        <v>25120.058563774473</v>
       </c>
       <c r="I36" s="5">
-        <f>0.1*E36</f>
-        <v>2329.8276344703554</v>
+        <f t="shared" si="0"/>
+        <v>1994.4501719063135</v>
       </c>
       <c r="J36" s="5">
-        <f>0.1*E35</f>
-        <v>2446.1403232800762</v>
+        <f t="shared" si="2"/>
+        <v>2093.664895461005</v>
       </c>
       <c r="K36" s="5">
-        <f>0.1*E34</f>
-        <v>2568.7202229242062</v>
+        <f t="shared" si="4"/>
+        <v>2198.2255498574477</v>
       </c>
       <c r="L36" s="5">
-        <f>0.1*E33</f>
-        <v>2697.9265125554248</v>
+        <f t="shared" si="5"/>
+        <v>2308.4385149128771</v>
       </c>
       <c r="M36" s="5">
-        <f>0.1*E32</f>
-        <v>2834.1405033236547</v>
+        <f t="shared" si="6"/>
+        <v>2424.6290490381775</v>
       </c>
       <c r="N36" s="5">
-        <f>0.1*E31</f>
-        <v>2977.7671486732161</v>
+        <f t="shared" si="7"/>
+        <v>2547.1425775213534</v>
       </c>
       <c r="O36" s="5">
-        <f>0.1*E30</f>
-        <v>3129.2366877145073</v>
+        <f t="shared" si="8"/>
+        <v>2676.346094323575</v>
       </c>
       <c r="P36" s="5">
-        <f>0.1*E29</f>
-        <v>3289.0064501069992</v>
+        <f t="shared" si="9"/>
+        <v>2812.62970164437</v>
       </c>
       <c r="Q36" s="5">
-        <f>0.1*E28</f>
-        <v>3457.5628686041055</v>
+        <f t="shared" si="10"/>
+        <v>2956.4083266224025</v>
       </c>
       <c r="R36" s="5">
-        <f>0.1*E27</f>
-        <v>3635.4237781756719</v>
+        <f t="shared" si="11"/>
+        <v>3108.1236824869484</v>
       </c>
     </row>
     <row r="37" spans="1:18">
@@ -9792,60 +9945,61 @@
         <v>2060</v>
       </c>
       <c r="B37" s="1">
-        <v>21710.954160741589</v>
-      </c>
-      <c r="C37">
+        <f>Subtracting_Biochar_Removals!F47</f>
+        <v>18519.443899112575</v>
+      </c>
+      <c r="C37" s="1">
         <f>Summary_Reductions!H42</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E37" s="5">
-        <f t="shared" si="0"/>
-        <v>22194.437133741587</v>
+        <f t="shared" si="1"/>
+        <v>19002.926872112574</v>
       </c>
       <c r="F37" s="5"/>
-      <c r="G37" s="5">
-        <f t="shared" si="1"/>
-        <v>27949.772065026704</v>
+      <c r="G37" s="17">
+        <f t="shared" si="3"/>
+        <v>23912.227568498784</v>
       </c>
       <c r="I37" s="5">
-        <f>0.1*E37</f>
-        <v>2219.443713374159</v>
+        <f t="shared" si="0"/>
+        <v>1900.2926872112575</v>
       </c>
       <c r="J37" s="5">
-        <f>0.1*E36</f>
-        <v>2329.8276344703554</v>
+        <f t="shared" si="2"/>
+        <v>1994.4501719063135</v>
       </c>
       <c r="K37" s="5">
-        <f>0.1*E35</f>
-        <v>2446.1403232800762</v>
+        <f t="shared" si="4"/>
+        <v>2093.664895461005</v>
       </c>
       <c r="L37" s="5">
-        <f>0.1*E34</f>
-        <v>2568.7202229242062</v>
+        <f t="shared" si="5"/>
+        <v>2198.2255498574477</v>
       </c>
       <c r="M37" s="5">
-        <f>0.1*E33</f>
-        <v>2697.9265125554248</v>
+        <f t="shared" si="6"/>
+        <v>2308.4385149128771</v>
       </c>
       <c r="N37" s="5">
-        <f>0.1*E32</f>
-        <v>2834.1405033236547</v>
+        <f t="shared" si="7"/>
+        <v>2424.6290490381775</v>
       </c>
       <c r="O37" s="5">
-        <f>0.1*E31</f>
-        <v>2977.7671486732161</v>
+        <f t="shared" si="8"/>
+        <v>2547.1425775213534</v>
       </c>
       <c r="P37" s="5">
-        <f>0.1*E30</f>
-        <v>3129.2366877145073</v>
+        <f t="shared" si="9"/>
+        <v>2676.346094323575</v>
       </c>
       <c r="Q37" s="5">
-        <f>0.1*E29</f>
-        <v>3289.0064501069992</v>
+        <f t="shared" si="10"/>
+        <v>2812.62970164437</v>
       </c>
       <c r="R37" s="5">
-        <f>0.1*E28</f>
-        <v>3457.5628686041055</v>
+        <f t="shared" si="11"/>
+        <v>2956.4083266224025</v>
       </c>
     </row>
     <row r="38" spans="1:18">
@@ -9853,60 +10007,61 @@
         <v>2061</v>
       </c>
       <c r="B38" s="1">
-        <v>20663.212606998179</v>
-      </c>
-      <c r="C38">
+        <f>Subtracting_Biochar_Removals!F48</f>
+        <v>17625.720353769448</v>
+      </c>
+      <c r="C38" s="1">
         <f>Summary_Reductions!H43</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E38" s="5">
-        <f t="shared" si="0"/>
-        <v>21146.695579998177</v>
+        <f t="shared" si="1"/>
+        <v>18109.203326769446</v>
       </c>
       <c r="F38" s="5"/>
-      <c r="G38" s="5">
-        <f t="shared" si="1"/>
-        <v>26606.878754422418</v>
+      <c r="G38" s="17">
+        <f t="shared" si="3"/>
+        <v>22766.739574553321</v>
       </c>
       <c r="I38" s="5">
-        <f>0.1*E38</f>
-        <v>2114.6695579998177</v>
+        <f t="shared" si="0"/>
+        <v>1810.9203326769448</v>
       </c>
       <c r="J38" s="5">
-        <f>0.1*E37</f>
-        <v>2219.443713374159</v>
+        <f t="shared" si="2"/>
+        <v>1900.2926872112575</v>
       </c>
       <c r="K38" s="5">
-        <f>0.1*E36</f>
-        <v>2329.8276344703554</v>
+        <f t="shared" si="4"/>
+        <v>1994.4501719063135</v>
       </c>
       <c r="L38" s="5">
-        <f>0.1*E35</f>
-        <v>2446.1403232800762</v>
+        <f t="shared" si="5"/>
+        <v>2093.664895461005</v>
       </c>
       <c r="M38" s="5">
-        <f>0.1*E34</f>
-        <v>2568.7202229242062</v>
+        <f t="shared" si="6"/>
+        <v>2198.2255498574477</v>
       </c>
       <c r="N38" s="5">
-        <f>0.1*E33</f>
-        <v>2697.9265125554248</v>
+        <f t="shared" si="7"/>
+        <v>2308.4385149128771</v>
       </c>
       <c r="O38" s="5">
-        <f>0.1*E32</f>
-        <v>2834.1405033236547</v>
+        <f t="shared" si="8"/>
+        <v>2424.6290490381775</v>
       </c>
       <c r="P38" s="5">
-        <f>0.1*E31</f>
-        <v>2977.7671486732161</v>
+        <f t="shared" si="9"/>
+        <v>2547.1425775213534</v>
       </c>
       <c r="Q38" s="5">
-        <f>0.1*E30</f>
-        <v>3129.2366877145073</v>
+        <f t="shared" si="10"/>
+        <v>2676.346094323575</v>
       </c>
       <c r="R38" s="5">
-        <f>0.1*E29</f>
-        <v>3289.0064501069992</v>
+        <f t="shared" si="11"/>
+        <v>2812.62970164437</v>
       </c>
     </row>
     <row r="39" spans="1:18">
@@ -9914,60 +10069,61 @@
         <v>2062</v>
       </c>
       <c r="B39" s="1">
-        <v>19668.561062386794</v>
-      </c>
-      <c r="C39">
+        <f>Subtracting_Biochar_Removals!F49</f>
+        <v>16777.282586215937</v>
+      </c>
+      <c r="C39" s="1">
         <f>Summary_Reductions!H44</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E39" s="5">
-        <f t="shared" si="0"/>
-        <v>20152.044035386793</v>
+        <f t="shared" si="1"/>
+        <v>17260.765559215935</v>
       </c>
       <c r="F39" s="5"/>
-      <c r="G39" s="5">
-        <f t="shared" si="1"/>
-        <v>25333.076707854099</v>
+      <c r="G39" s="17">
+        <f t="shared" si="3"/>
+        <v>21680.186428830544</v>
       </c>
       <c r="I39" s="5">
-        <f>0.1*E39</f>
-        <v>2015.2044035386793</v>
+        <f t="shared" si="0"/>
+        <v>1726.0765559215936</v>
       </c>
       <c r="J39" s="5">
-        <f>0.1*E38</f>
-        <v>2114.6695579998177</v>
+        <f t="shared" si="2"/>
+        <v>1810.9203326769448</v>
       </c>
       <c r="K39" s="5">
-        <f>0.1*E37</f>
-        <v>2219.443713374159</v>
+        <f t="shared" si="4"/>
+        <v>1900.2926872112575</v>
       </c>
       <c r="L39" s="5">
-        <f>0.1*E36</f>
-        <v>2329.8276344703554</v>
+        <f t="shared" si="5"/>
+        <v>1994.4501719063135</v>
       </c>
       <c r="M39" s="5">
-        <f>0.1*E35</f>
-        <v>2446.1403232800762</v>
+        <f t="shared" si="6"/>
+        <v>2093.664895461005</v>
       </c>
       <c r="N39" s="5">
-        <f>0.1*E34</f>
-        <v>2568.7202229242062</v>
+        <f t="shared" si="7"/>
+        <v>2198.2255498574477</v>
       </c>
       <c r="O39" s="5">
-        <f>0.1*E33</f>
-        <v>2697.9265125554248</v>
+        <f t="shared" si="8"/>
+        <v>2308.4385149128771</v>
       </c>
       <c r="P39" s="5">
-        <f>0.1*E32</f>
-        <v>2834.1405033236547</v>
+        <f t="shared" si="9"/>
+        <v>2424.6290490381775</v>
       </c>
       <c r="Q39" s="5">
-        <f>0.1*E31</f>
-        <v>2977.7671486732161</v>
+        <f t="shared" si="10"/>
+        <v>2547.1425775213534</v>
       </c>
       <c r="R39" s="5">
-        <f>0.1*E30</f>
-        <v>3129.2366877145073</v>
+        <f t="shared" si="11"/>
+        <v>2676.346094323575</v>
       </c>
     </row>
     <row r="40" spans="1:18">
@@ -9975,60 +10131,61 @@
         <v>2063</v>
       </c>
       <c r="B40" s="1">
-        <v>18724.163039163599</v>
-      </c>
-      <c r="C40">
+        <f>Subtracting_Biochar_Removals!F50</f>
+        <v>15971.71107240655</v>
+      </c>
+      <c r="C40" s="1">
         <f>Summary_Reductions!H45</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E40" s="5">
-        <f t="shared" si="0"/>
-        <v>19207.646012163597</v>
+        <f t="shared" si="1"/>
+        <v>16455.194045406548</v>
       </c>
       <c r="F40" s="5"/>
-      <c r="G40" s="5">
-        <f t="shared" si="1"/>
-        <v>24124.604621355953</v>
+      <c r="G40" s="17">
+        <f t="shared" si="3"/>
+        <v>20649.359739047624</v>
       </c>
       <c r="I40" s="5">
-        <f>0.1*E40</f>
-        <v>1920.7646012163598</v>
+        <f t="shared" si="0"/>
+        <v>1645.5194045406549</v>
       </c>
       <c r="J40" s="5">
-        <f>0.1*E39</f>
-        <v>2015.2044035386793</v>
+        <f t="shared" si="2"/>
+        <v>1726.0765559215936</v>
       </c>
       <c r="K40" s="5">
-        <f>0.1*E38</f>
-        <v>2114.6695579998177</v>
+        <f t="shared" si="4"/>
+        <v>1810.9203326769448</v>
       </c>
       <c r="L40" s="5">
-        <f>0.1*E37</f>
-        <v>2219.443713374159</v>
+        <f t="shared" si="5"/>
+        <v>1900.2926872112575</v>
       </c>
       <c r="M40" s="5">
-        <f>0.1*E36</f>
-        <v>2329.8276344703554</v>
+        <f t="shared" si="6"/>
+        <v>1994.4501719063135</v>
       </c>
       <c r="N40" s="5">
-        <f>0.1*E35</f>
-        <v>2446.1403232800762</v>
+        <f t="shared" si="7"/>
+        <v>2093.664895461005</v>
       </c>
       <c r="O40" s="5">
-        <f>0.1*E34</f>
-        <v>2568.7202229242062</v>
+        <f t="shared" si="8"/>
+        <v>2198.2255498574477</v>
       </c>
       <c r="P40" s="5">
-        <f>0.1*E33</f>
-        <v>2697.9265125554248</v>
+        <f t="shared" si="9"/>
+        <v>2308.4385149128771</v>
       </c>
       <c r="Q40" s="5">
-        <f>0.1*E32</f>
-        <v>2834.1405033236547</v>
+        <f t="shared" si="10"/>
+        <v>2424.6290490381775</v>
       </c>
       <c r="R40" s="5">
-        <f>0.1*E31</f>
-        <v>2977.7671486732161</v>
+        <f t="shared" si="11"/>
+        <v>2547.1425775213534</v>
       </c>
     </row>
     <row r="41" spans="1:18">
@@ -10036,60 +10193,61 @@
         <v>2064</v>
       </c>
       <c r="B41" s="1">
-        <v>17827.342757527626</v>
-      </c>
-      <c r="C41">
+        <f>Subtracting_Biochar_Removals!F51</f>
+        <v>15206.723372171065</v>
+      </c>
+      <c r="C41" s="1">
         <f>Summary_Reductions!H46</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E41" s="5">
-        <f t="shared" si="0"/>
-        <v>18310.825730527624</v>
+        <f t="shared" si="1"/>
+        <v>15690.206345171066</v>
       </c>
       <c r="F41" s="5"/>
-      <c r="G41" s="5">
-        <f t="shared" si="1"/>
-        <v>22977.920045735493</v>
+      <c r="G41" s="17">
+        <f t="shared" si="3"/>
+        <v>19671.237796043377</v>
       </c>
       <c r="I41" s="5">
-        <f>0.1*E41</f>
-        <v>1831.0825730527624</v>
+        <f t="shared" si="0"/>
+        <v>1569.0206345171066</v>
       </c>
       <c r="J41" s="5">
-        <f>0.1*E40</f>
-        <v>1920.7646012163598</v>
+        <f t="shared" si="2"/>
+        <v>1645.5194045406549</v>
       </c>
       <c r="K41" s="5">
-        <f>0.1*E39</f>
-        <v>2015.2044035386793</v>
+        <f t="shared" si="4"/>
+        <v>1726.0765559215936</v>
       </c>
       <c r="L41" s="5">
-        <f>0.1*E38</f>
-        <v>2114.6695579998177</v>
+        <f t="shared" si="5"/>
+        <v>1810.9203326769448</v>
       </c>
       <c r="M41" s="5">
-        <f>0.1*E37</f>
-        <v>2219.443713374159</v>
+        <f t="shared" si="6"/>
+        <v>1900.2926872112575</v>
       </c>
       <c r="N41" s="5">
-        <f>0.1*E36</f>
-        <v>2329.8276344703554</v>
+        <f t="shared" si="7"/>
+        <v>1994.4501719063135</v>
       </c>
       <c r="O41" s="5">
-        <f>0.1*E35</f>
-        <v>2446.1403232800762</v>
+        <f t="shared" si="8"/>
+        <v>2093.664895461005</v>
       </c>
       <c r="P41" s="5">
-        <f>0.1*E34</f>
-        <v>2568.7202229242062</v>
+        <f t="shared" si="9"/>
+        <v>2198.2255498574477</v>
       </c>
       <c r="Q41" s="5">
-        <f>0.1*E33</f>
-        <v>2697.9265125554248</v>
+        <f t="shared" si="10"/>
+        <v>2308.4385149128771</v>
       </c>
       <c r="R41" s="5">
-        <f>0.1*E32</f>
-        <v>2834.1405033236547</v>
+        <f t="shared" si="11"/>
+        <v>2424.6290490381775</v>
       </c>
     </row>
     <row r="42" spans="1:18">
@@ -10097,74 +10255,78 @@
         <v>2065</v>
       </c>
       <c r="B42" s="1">
-        <v>16975.57539212154</v>
-      </c>
-      <c r="C42">
+        <f>Subtracting_Biochar_Removals!F52</f>
+        <v>14480.165809479673</v>
+      </c>
+      <c r="C42" s="1">
         <f>Summary_Reductions!H47</f>
         <v>483.48297300000007</v>
       </c>
       <c r="E42" s="5">
-        <f t="shared" si="0"/>
-        <v>17459.058365121538</v>
+        <f t="shared" si="1"/>
+        <v>14963.648782479673</v>
       </c>
       <c r="F42" s="5"/>
-      <c r="G42" s="5">
-        <f t="shared" si="1"/>
-        <v>21889.685378923998</v>
+      <c r="G42" s="17">
+        <f t="shared" si="3"/>
+        <v>18742.973625253169</v>
       </c>
       <c r="I42" s="5">
-        <f>0.1*E42</f>
-        <v>1745.9058365121539</v>
+        <f t="shared" si="0"/>
+        <v>1496.3648782479675</v>
       </c>
       <c r="J42" s="5">
-        <f>0.1*E41</f>
-        <v>1831.0825730527624</v>
+        <f t="shared" si="2"/>
+        <v>1569.0206345171066</v>
       </c>
       <c r="K42" s="5">
-        <f>0.1*E40</f>
-        <v>1920.7646012163598</v>
+        <f t="shared" si="4"/>
+        <v>1645.5194045406549</v>
       </c>
       <c r="L42" s="5">
-        <f>0.1*E39</f>
-        <v>2015.2044035386793</v>
+        <f t="shared" si="5"/>
+        <v>1726.0765559215936</v>
       </c>
       <c r="M42" s="5">
-        <f>0.1*E38</f>
-        <v>2114.6695579998177</v>
+        <f t="shared" si="6"/>
+        <v>1810.9203326769448</v>
       </c>
       <c r="N42" s="5">
-        <f>0.1*E37</f>
-        <v>2219.443713374159</v>
+        <f t="shared" si="7"/>
+        <v>1900.2926872112575</v>
       </c>
       <c r="O42" s="5">
-        <f>0.1*E36</f>
-        <v>2329.8276344703554</v>
+        <f t="shared" si="8"/>
+        <v>1994.4501719063135</v>
       </c>
       <c r="P42" s="5">
-        <f>0.1*E35</f>
-        <v>2446.1403232800762</v>
+        <f t="shared" si="9"/>
+        <v>2093.664895461005</v>
       </c>
       <c r="Q42" s="5">
-        <f>0.1*E34</f>
-        <v>2568.7202229242062</v>
+        <f t="shared" si="10"/>
+        <v>2198.2255498574477</v>
       </c>
       <c r="R42" s="5">
-        <f>0.1*E33</f>
-        <v>2697.9265125554248</v>
-      </c>
+        <f t="shared" si="11"/>
+        <v>2308.4385149128771</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18">
+      <c r="G43" s="8"/>
     </row>
     <row r="44" spans="1:18">
       <c r="D44" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E44" s="5">
         <f>SUM(E3:E42)</f>
-        <v>3554101.1889417893</v>
+        <v>3034491.1940485877</v>
       </c>
       <c r="F44" s="5"/>
-      <c r="G44" s="5">
+      <c r="G44" s="17">
         <f>SUM(G3:G42)</f>
-        <v>3464301.1907826201</v>
+        <v>2957571.9716321761</v>
       </c>
       <c r="I44" s="5"/>
     </row>
@@ -10181,7 +10343,1385 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{736FD4D8-5019-BD44-95E6-DECAB01CDB7E}">
+  <dimension ref="A1:G42"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="26.33203125" defaultRowHeight="16"/>
+  <cols>
+    <col min="2" max="16384" width="26.33203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>416.71665774793968</v>
+      </c>
+      <c r="B2">
+        <v>416.71616545329988</v>
+      </c>
+      <c r="C2"/>
+      <c r="G2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>370.64525247623919</v>
+      </c>
+      <c r="B3">
+        <v>416.71616226455973</v>
+      </c>
+      <c r="C3">
+        <v>46.071402082960411</v>
+      </c>
+      <c r="E3" s="1">
+        <f>C3*0.8645*$G$3</f>
+        <v>385462.42088076117</v>
+      </c>
+      <c r="G3" s="3">
+        <v>9678</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>346.47246254458781</v>
+      </c>
+      <c r="B4">
+        <v>416.71615936026672</v>
+      </c>
+      <c r="C4">
+        <v>24.172787027358272</v>
+      </c>
+      <c r="E4" s="1">
+        <f t="shared" ref="E4:E42" si="0">C4*0.8645*$G$3</f>
+        <v>202244.78929949357</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>331.34964403122279</v>
+      </c>
+      <c r="B5">
+        <v>416.71615671504679</v>
+      </c>
+      <c r="C5">
+        <v>15.122815868145191</v>
+      </c>
+      <c r="E5" s="1">
+        <f t="shared" si="0"/>
+        <v>126527.02004971547</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>321.08528742337171</v>
+      </c>
+      <c r="B6">
+        <v>416.71615430578998</v>
+      </c>
+      <c r="C6">
+        <v>10.264354198594329</v>
+      </c>
+      <c r="E6" s="1">
+        <f t="shared" si="0"/>
+        <v>85878.064032939481</v>
+      </c>
+      <c r="G6" s="11"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>313.50616866073352</v>
+      </c>
+      <c r="B7">
+        <v>416.71615211144763</v>
+      </c>
+      <c r="C7">
+        <v>7.5791165682956461</v>
+      </c>
+      <c r="E7" s="1">
+        <f t="shared" si="0"/>
+        <v>63411.671632915975</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>307.47087273556502</v>
+      </c>
+      <c r="B8">
+        <v>416.71615011284831</v>
+      </c>
+      <c r="C8">
+        <v>6.0352939265692376</v>
+      </c>
+      <c r="E8" s="1">
+        <f t="shared" si="0"/>
+        <v>50495.07726014591</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>302.37301704251882</v>
+      </c>
+      <c r="B9">
+        <v>416.71614829253127</v>
+      </c>
+      <c r="C9">
+        <v>5.0978538727292033</v>
+      </c>
+      <c r="E9" s="1">
+        <f t="shared" si="0"/>
+        <v>42651.862245046214</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>297.88609955336739</v>
+      </c>
+      <c r="B10">
+        <v>416.71614663459297</v>
+      </c>
+      <c r="C10">
+        <v>4.486915831213115</v>
+      </c>
+      <c r="E10" s="1">
+        <f t="shared" si="0"/>
+        <v>37540.369087818421</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>293.83091283189532</v>
+      </c>
+      <c r="B11">
+        <v>416.71614512454892</v>
+      </c>
+      <c r="C11">
+        <v>4.0551852114280109</v>
+      </c>
+      <c r="E11" s="1">
+        <f t="shared" si="0"/>
+        <v>33928.238300675148</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>290.10617449125277</v>
+      </c>
+      <c r="B12">
+        <v>416.71614374920608</v>
+      </c>
+      <c r="C12">
+        <v>3.7247369652997548</v>
+      </c>
+      <c r="E12" s="1">
+        <f t="shared" si="0"/>
+        <v>31163.499760722858</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>286.65208112808932</v>
+      </c>
+      <c r="B13">
+        <v>416.71614249654863</v>
+      </c>
+      <c r="C13">
+        <v>3.454092110506068</v>
+      </c>
+      <c r="E13" s="1">
+        <f t="shared" si="0"/>
+        <v>28899.114128615496</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>283.43110517554783</v>
+      </c>
+      <c r="B14">
+        <v>416.7161413556326</v>
+      </c>
+      <c r="C14">
+        <v>3.220974811625434</v>
+      </c>
+      <c r="E14" s="1">
+        <f t="shared" si="0"/>
+        <v>26948.707709164519</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>280.41785186546571</v>
+      </c>
+      <c r="B15">
+        <v>416.71614031649051</v>
+      </c>
+      <c r="C15">
+        <v>3.0132522709399492</v>
+      </c>
+      <c r="E15" s="1">
+        <f t="shared" si="0"/>
+        <v>25210.769860866581</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>277.59368628729248</v>
+      </c>
+      <c r="B16">
+        <v>416.71613937004349</v>
+      </c>
+      <c r="C16">
+        <v>2.8241646317261062</v>
+      </c>
+      <c r="E16" s="1">
+        <f t="shared" si="0"/>
+        <v>23628.743356903222</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>274.94387539537468</v>
+      </c>
+      <c r="B17">
+        <v>416.71613850802282</v>
+      </c>
+      <c r="C17">
+        <v>2.6498100298971732</v>
+      </c>
+      <c r="E17" s="1">
+        <f t="shared" si="0"/>
+        <v>22169.982740248615</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>272.45605761380409</v>
+      </c>
+      <c r="B18">
+        <v>416.71613772289737</v>
+      </c>
+      <c r="C18">
+        <v>2.4878169964452699</v>
+      </c>
+      <c r="E18" s="1">
+        <f t="shared" si="0"/>
+        <v>20814.646804785887</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>270.11941426270602</v>
+      </c>
+      <c r="B19">
+        <v>416.7161370078083</v>
+      </c>
+      <c r="C19">
+        <v>2.3366426360088699</v>
+      </c>
+      <c r="E19" s="1">
+        <f t="shared" si="0"/>
+        <v>19549.826714353527</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>267.92421275815201</v>
+      </c>
+      <c r="B20">
+        <v>416.7161363565076</v>
+      </c>
+      <c r="C20">
+        <v>2.1952008532534442</v>
+      </c>
+      <c r="E20" s="1">
+        <f t="shared" si="0"/>
+        <v>18366.435510056719</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>265.86154739511568</v>
+      </c>
+      <c r="B21">
+        <v>416.71613576330549</v>
+      </c>
+      <c r="C21">
+        <v>2.062664769834166</v>
+      </c>
+      <c r="E21" s="1">
+        <f t="shared" si="0"/>
+        <v>17257.555005902399</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>263.92318570839689</v>
+      </c>
+      <c r="B22">
+        <v>416.71613522301891</v>
+      </c>
+      <c r="C22">
+        <v>1.938361146432124</v>
+      </c>
+      <c r="E22" s="1">
+        <f t="shared" si="0"/>
+        <v>16217.552456934549</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>262.10147176210239</v>
+      </c>
+      <c r="B23">
+        <v>416.71613473092748</v>
+      </c>
+      <c r="C23">
+        <v>1.821713454203173</v>
+      </c>
+      <c r="E23" s="1">
+        <f t="shared" si="0"/>
+        <v>15241.604259053349</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>260.38926059904128</v>
+      </c>
+      <c r="B24">
+        <v>416.71613428273281</v>
+      </c>
+      <c r="C24">
+        <v>1.7122107148664301</v>
+      </c>
+      <c r="E24" s="1">
+        <f t="shared" si="0"/>
+        <v>14325.435245533636</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>258.77987016232822</v>
+      </c>
+      <c r="B25">
+        <v>416.71613387451868</v>
+      </c>
+      <c r="C25">
+        <v>1.6093900284989879</v>
+      </c>
+      <c r="E25" s="1">
+        <f t="shared" si="0"/>
+        <v>13465.172503530517</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>257.26704338432597</v>
+      </c>
+      <c r="B26">
+        <v>416.71613350271849</v>
+      </c>
+      <c r="C26">
+        <v>1.51282640620208</v>
+      </c>
+      <c r="E26" s="1">
+        <f t="shared" si="0"/>
+        <v>12657.260307748915</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>255.8449165137184</v>
+      </c>
+      <c r="B27">
+        <v>416.71613316408428</v>
+      </c>
+      <c r="C27">
+        <v>1.422126531973281</v>
+      </c>
+      <c r="E27" s="1">
+        <f t="shared" si="0"/>
+        <v>11898.407928330145</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>254.50799153962541</v>
+      </c>
+      <c r="B28">
+        <v>416.71613285565752</v>
+      </c>
+      <c r="C28">
+        <v>1.33692466566617</v>
+      </c>
+      <c r="E28" s="1">
+        <f t="shared" si="0"/>
+        <v>11185.555352427215</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
+        <v>253.2511115213355</v>
+      </c>
+      <c r="B29">
+        <v>416.71613257474343</v>
+      </c>
+      <c r="C29">
+        <v>1.25687973737583</v>
+      </c>
+      <c r="E29" s="1">
+        <f t="shared" si="0"/>
+        <v>10515.848974000479</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
+        <v>252.06943813880059</v>
+      </c>
+      <c r="B30">
+        <v>416.71613231888767</v>
+      </c>
+      <c r="C30">
+        <v>1.1816731266792999</v>
+      </c>
+      <c r="E30" s="1">
+        <f t="shared" si="0"/>
+        <v>9886.6230135419592</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <v>250.95843105120011</v>
+      </c>
+      <c r="B31">
+        <v>416.71613208585552</v>
+      </c>
+      <c r="C31">
+        <v>1.111006854568193</v>
+      </c>
+      <c r="E31" s="1">
+        <f t="shared" si="0"/>
+        <v>9295.3843906427355</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32">
+        <v>249.91382879886589</v>
+      </c>
+      <c r="B32">
+        <v>416.71613187361049</v>
+      </c>
+      <c r="C32">
+        <v>1.0446020400893259</v>
+      </c>
+      <c r="E32" s="1">
+        <f t="shared" si="0"/>
+        <v>8739.7998112745972</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33">
+        <v>248.93163106585661</v>
+      </c>
+      <c r="B33">
+        <v>416.71613168029847</v>
+      </c>
+      <c r="C33">
+        <v>0.9821975396971302</v>
+      </c>
+      <c r="E33" s="1">
+        <f t="shared" si="0"/>
+        <v>8217.6843837537417</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34">
+        <v>248.00808216728711</v>
+      </c>
+      <c r="B34">
+        <v>416.71613150423082</v>
+      </c>
+      <c r="C34">
+        <v>0.92354872250182518</v>
+      </c>
+      <c r="E34" s="1">
+        <f t="shared" si="0"/>
+        <v>7726.9913716941683</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35">
+        <v>247.13965565341729</v>
+      </c>
+      <c r="B35">
+        <v>416.71613134386871</v>
+      </c>
+      <c r="C35">
+        <v>0.86842635350771502</v>
+      </c>
+      <c r="E35" s="1">
+        <f t="shared" si="0"/>
+        <v>7265.802850474608</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36">
+        <v>246.32303994013489</v>
+      </c>
+      <c r="B36">
+        <v>416.71613119781148</v>
+      </c>
+      <c r="C36">
+        <v>0.81661556722526052</v>
+      </c>
+      <c r="E36" s="1">
+        <f t="shared" si="0"/>
+        <v>6832.3211198294493</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37">
+        <v>245.55512488739811</v>
+      </c>
+      <c r="B37">
+        <v>416.71613106478321</v>
+      </c>
+      <c r="C37">
+        <v>0.76791491970848824</v>
+      </c>
+      <c r="E37" s="1">
+        <f t="shared" si="0"/>
+        <v>6424.860772595549</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38">
+        <v>244.83298925591021</v>
+      </c>
+      <c r="B38">
+        <v>416.71613094362141</v>
+      </c>
+      <c r="C38">
+        <v>0.72213551032606915</v>
+      </c>
+      <c r="E38" s="1">
+        <f t="shared" si="0"/>
+        <v>6041.8413468949102</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39">
+        <v>244.15388897907269</v>
+      </c>
+      <c r="B39">
+        <v>416.71613083326798</v>
+      </c>
+      <c r="C39">
+        <v>0.67910016648414739</v>
+      </c>
+      <c r="E39" s="1">
+        <f t="shared" si="0"/>
+        <v>5681.7805050114284</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40">
+        <v>243.51524619283319</v>
+      </c>
+      <c r="B40">
+        <v>416.71613073275819</v>
+      </c>
+      <c r="C40">
+        <v>0.63864268572964511</v>
+      </c>
+      <c r="E40" s="1">
+        <f t="shared" si="0"/>
+        <v>5343.2876923489066</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41">
+        <v>242.91463897081519</v>
+      </c>
+      <c r="B41">
+        <v>416.71613064121448</v>
+      </c>
+      <c r="C41">
+        <v>0.60060713047432535</v>
+      </c>
+      <c r="E41" s="1">
+        <f t="shared" si="0"/>
+        <v>5025.0582366475355</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42">
+        <v>242.3497917162907</v>
+      </c>
+      <c r="B42">
+        <v>416.71613055783672</v>
+      </c>
+      <c r="C42">
+        <v>0.5648471711466575</v>
+      </c>
+      <c r="E42" s="1">
+        <f t="shared" si="0"/>
+        <v>4725.8678523779299</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF3E4888-FB14-564C-901E-F49C230665D8}">
+  <dimension ref="B1:G54"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" customHeight="1"/>
+  <cols>
+    <col min="3" max="3" width="24.1640625" customWidth="1"/>
+    <col min="4" max="4" width="22.83203125" customWidth="1"/>
+    <col min="5" max="5" width="27.1640625" customWidth="1"/>
+    <col min="6" max="6" width="39.33203125" customWidth="1"/>
+    <col min="7" max="7" width="43.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:7" ht="17" customHeight="1">
+      <c r="C1" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="3:7" ht="17" customHeight="1">
+      <c r="C2" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="19">
+        <v>0.5</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="F2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="3:7" ht="33" customHeight="1">
+      <c r="C3" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" s="19">
+        <v>0.7</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="3:7" ht="20" customHeight="1">
+      <c r="C4" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="19">
+        <f>30%*D3</f>
+        <v>0.21</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="3:7" ht="35" customHeight="1">
+      <c r="C5" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" s="19">
+        <f>70%*D3</f>
+        <v>0.48999999999999994</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="3:7" ht="80" customHeight="1">
+      <c r="C6" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="3:7" ht="48" customHeight="1">
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+    </row>
+    <row r="8" spans="3:7" ht="17" customHeight="1">
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+    </row>
+    <row r="9" spans="3:7" ht="17" customHeight="1">
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+    </row>
+    <row r="10" spans="3:7" ht="17" customHeight="1">
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+    </row>
+    <row r="11" spans="3:7" s="18" customFormat="1" ht="36" customHeight="1">
+      <c r="C11" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="F11" s="21" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="3:7" ht="17" customHeight="1">
+      <c r="E12" s="22"/>
+      <c r="F12" s="8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="13" spans="3:7" ht="17" customHeight="1">
+      <c r="C13" s="1">
+        <f>Summary_Removals!H6</f>
+        <v>821101.42037601292</v>
+      </c>
+      <c r="E13" s="5">
+        <f>$D$4*$D$3 * C13</f>
+        <v>120701.90879527389</v>
+      </c>
+      <c r="F13" s="17">
+        <f>C13-E13</f>
+        <v>700399.51158073905</v>
+      </c>
+    </row>
+    <row r="14" spans="3:7" ht="17" customHeight="1">
+      <c r="C14" s="1">
+        <f>Summary_Removals!H7</f>
+        <v>438618.78975034383</v>
+      </c>
+      <c r="E14" s="5">
+        <f t="shared" ref="E14:E52" si="0">$D$4*$D$3 * C14</f>
+        <v>64476.962093300543</v>
+      </c>
+      <c r="F14" s="17">
+        <f t="shared" ref="F14:F52" si="1">C14-E14</f>
+        <v>374141.82765704329</v>
+      </c>
+    </row>
+    <row r="15" spans="3:7" ht="17" customHeight="1">
+      <c r="C15" s="1">
+        <f>Summary_Removals!H8</f>
+        <v>280542.4127075728</v>
+      </c>
+      <c r="E15" s="5">
+        <f t="shared" si="0"/>
+        <v>41239.734668013203</v>
+      </c>
+      <c r="F15" s="17">
+        <f t="shared" si="1"/>
+        <v>239302.6780395596</v>
+      </c>
+    </row>
+    <row r="16" spans="3:7" ht="17" customHeight="1">
+      <c r="C16" s="1">
+        <f>Summary_Removals!H9</f>
+        <v>195610.66434031486</v>
+      </c>
+      <c r="E16" s="5">
+        <f t="shared" si="0"/>
+        <v>28754.767658026281</v>
+      </c>
+      <c r="F16" s="17">
+        <f t="shared" si="1"/>
+        <v>166855.89668228858</v>
+      </c>
+    </row>
+    <row r="17" spans="3:6" ht="17" customHeight="1">
+      <c r="C17" s="1">
+        <f>Summary_Removals!H10</f>
+        <v>148595.57025444848</v>
+      </c>
+      <c r="E17" s="5">
+        <f t="shared" si="0"/>
+        <v>21843.548827403927</v>
+      </c>
+      <c r="F17" s="17">
+        <f t="shared" si="1"/>
+        <v>126752.02142704456</v>
+      </c>
+    </row>
+    <row r="18" spans="3:6" ht="17" customHeight="1">
+      <c r="C18" s="1">
+        <f>Summary_Removals!H11</f>
+        <v>121486.32310306156</v>
+      </c>
+      <c r="E18" s="5">
+        <f t="shared" si="0"/>
+        <v>17858.489496150047</v>
+      </c>
+      <c r="F18" s="17">
+        <f t="shared" si="1"/>
+        <v>103627.8336069115</v>
+      </c>
+    </row>
+    <row r="19" spans="3:6" ht="17" customHeight="1">
+      <c r="C19" s="1">
+        <f>Summary_Removals!H12</f>
+        <v>104943.51551237612</v>
+      </c>
+      <c r="E19" s="5">
+        <f t="shared" si="0"/>
+        <v>15426.696780319289</v>
+      </c>
+      <c r="F19" s="17">
+        <f t="shared" si="1"/>
+        <v>89516.818732056825</v>
+      </c>
+    </row>
+    <row r="20" spans="3:6" ht="17" customHeight="1">
+      <c r="C20" s="1">
+        <f>Summary_Removals!H13</f>
+        <v>94082.138369954962</v>
+      </c>
+      <c r="E20" s="5">
+        <f t="shared" si="0"/>
+        <v>13830.074340383379</v>
+      </c>
+      <c r="F20" s="17">
+        <f t="shared" si="1"/>
+        <v>80252.064029571586</v>
+      </c>
+    </row>
+    <row r="21" spans="3:6" ht="17" customHeight="1">
+      <c r="C21" s="1">
+        <f>Summary_Removals!H14</f>
+        <v>86332.13483317825</v>
+      </c>
+      <c r="E21" s="5">
+        <f t="shared" si="0"/>
+        <v>12690.823820477202</v>
+      </c>
+      <c r="F21" s="17">
+        <f t="shared" si="1"/>
+        <v>73641.311012701044</v>
+      </c>
+    </row>
+    <row r="22" spans="3:6" ht="17" customHeight="1">
+      <c r="C22" s="1">
+        <f>Summary_Removals!H15</f>
+        <v>80334.731962822014</v>
+      </c>
+      <c r="E22" s="5">
+        <f t="shared" si="0"/>
+        <v>11809.205598534836</v>
+      </c>
+      <c r="F22" s="17">
+        <f t="shared" si="1"/>
+        <v>68525.526364287172</v>
+      </c>
+    </row>
+    <row r="23" spans="3:6" ht="17" customHeight="1">
+      <c r="C23" s="1">
+        <f>Summary_Removals!H16</f>
+        <v>75367.548887754921</v>
+      </c>
+      <c r="E23" s="5">
+        <f t="shared" si="0"/>
+        <v>11079.029686499973</v>
+      </c>
+      <c r="F23" s="17">
+        <f t="shared" si="1"/>
+        <v>64288.519201254952</v>
+      </c>
+    </row>
+    <row r="24" spans="3:6" ht="17" customHeight="1">
+      <c r="C24" s="1">
+        <f>Summary_Removals!H17</f>
+        <v>71043.468433302914</v>
+      </c>
+      <c r="E24" s="5">
+        <f t="shared" si="0"/>
+        <v>10443.389859695528</v>
+      </c>
+      <c r="F24" s="17">
+        <f t="shared" si="1"/>
+        <v>60600.078573607389</v>
+      </c>
+    </row>
+    <row r="25" spans="3:6" ht="17" customHeight="1">
+      <c r="C25" s="1">
+        <f>Summary_Removals!H18</f>
+        <v>67152.396502738513</v>
+      </c>
+      <c r="E25" s="5">
+        <f t="shared" si="0"/>
+        <v>9871.4022859025608</v>
+      </c>
+      <c r="F25" s="17">
+        <f t="shared" si="1"/>
+        <v>57280.994216835956</v>
+      </c>
+    </row>
+    <row r="26" spans="3:6" ht="17" customHeight="1">
+      <c r="C26" s="1">
+        <f>Summary_Removals!H19</f>
+        <v>63577.945426597624</v>
+      </c>
+      <c r="E26" s="5">
+        <f t="shared" si="0"/>
+        <v>9345.9579777098497</v>
+      </c>
+      <c r="F26" s="17">
+        <f t="shared" si="1"/>
+        <v>54231.987448887776</v>
+      </c>
+    </row>
+    <row r="27" spans="3:6" ht="17" customHeight="1">
+      <c r="C27" s="1">
+        <f>Summary_Removals!H20</f>
+        <v>60253.508215713257</v>
+      </c>
+      <c r="E27" s="5">
+        <f t="shared" si="0"/>
+        <v>8857.2657077098484</v>
+      </c>
+      <c r="F27" s="17">
+        <f t="shared" si="1"/>
+        <v>51396.242508003408</v>
+      </c>
+    </row>
+    <row r="28" spans="3:6" ht="17" customHeight="1">
+      <c r="C28" s="1">
+        <f>Summary_Removals!H21</f>
+        <v>57139.074565888819</v>
+      </c>
+      <c r="E28" s="5">
+        <f t="shared" si="0"/>
+        <v>8399.443961185656</v>
+      </c>
+      <c r="F28" s="17">
+        <f t="shared" si="1"/>
+        <v>48739.630604703161</v>
+      </c>
+    </row>
+    <row r="29" spans="3:6" ht="17" customHeight="1">
+      <c r="C29" s="1">
+        <f>Summary_Removals!H22</f>
+        <v>54208.979240103537</v>
+      </c>
+      <c r="E29" s="5">
+        <f t="shared" si="0"/>
+        <v>7968.7199482952192</v>
+      </c>
+      <c r="F29" s="17">
+        <f t="shared" si="1"/>
+        <v>46240.259291808317</v>
+      </c>
+    </row>
+    <row r="30" spans="3:6" ht="17" customHeight="1">
+      <c r="C30" s="1">
+        <f>Summary_Removals!H23</f>
+        <v>51445.416516802092</v>
+      </c>
+      <c r="E30" s="5">
+        <f t="shared" si="0"/>
+        <v>7562.4762279699071</v>
+      </c>
+      <c r="F30" s="17">
+        <f t="shared" si="1"/>
+        <v>43882.940288832186</v>
+      </c>
+    </row>
+    <row r="31" spans="3:6" ht="17" customHeight="1">
+      <c r="C31" s="1">
+        <f>Summary_Removals!H24</f>
+        <v>48834.997638395005</v>
+      </c>
+      <c r="E31" s="5">
+        <f t="shared" si="0"/>
+        <v>7178.7446528440651</v>
+      </c>
+      <c r="F31" s="17">
+        <f t="shared" si="1"/>
+        <v>41656.252985550942</v>
+      </c>
+    </row>
+    <row r="32" spans="3:6" ht="17" customHeight="1">
+      <c r="C32" s="1">
+        <f>Summary_Removals!H25</f>
+        <v>46366.915248670673</v>
+      </c>
+      <c r="E32" s="5">
+        <f t="shared" si="0"/>
+        <v>6815.936541554589</v>
+      </c>
+      <c r="F32" s="17">
+        <f t="shared" si="1"/>
+        <v>39550.978707116083</v>
+      </c>
+    </row>
+    <row r="33" spans="3:6" ht="17" customHeight="1">
+      <c r="C33" s="1">
+        <f>Summary_Removals!H26</f>
+        <v>44031.957245805876</v>
+      </c>
+      <c r="E33" s="5">
+        <f t="shared" si="0"/>
+        <v>6472.6977151334631</v>
+      </c>
+      <c r="F33" s="17">
+        <f t="shared" si="1"/>
+        <v>37559.259530672411</v>
+      </c>
+    </row>
+    <row r="34" spans="3:6" ht="17" customHeight="1">
+      <c r="C34" s="1">
+        <f>Summary_Removals!H27</f>
+        <v>41821.970249623686</v>
+      </c>
+      <c r="E34" s="5">
+        <f t="shared" si="0"/>
+        <v>6147.8296266946818</v>
+      </c>
+      <c r="F34" s="17">
+        <f t="shared" si="1"/>
+        <v>35674.140622929001</v>
+      </c>
+    </row>
+    <row r="35" spans="3:6" ht="17" customHeight="1">
+      <c r="C35" s="1">
+        <f>Summary_Removals!H28</f>
+        <v>39729.561607948839</v>
+      </c>
+      <c r="E35" s="5">
+        <f t="shared" si="0"/>
+        <v>5840.2455563684789</v>
+      </c>
+      <c r="F35" s="17">
+        <f t="shared" si="1"/>
+        <v>33889.316051580361</v>
+      </c>
+    </row>
+    <row r="36" spans="3:6" ht="17" customHeight="1">
+      <c r="C36" s="1">
+        <f>Summary_Removals!H29</f>
+        <v>37747.928445136684</v>
+      </c>
+      <c r="E36" s="5">
+        <f t="shared" si="0"/>
+        <v>5548.945481435092</v>
+      </c>
+      <c r="F36" s="17">
+        <f t="shared" si="1"/>
+        <v>32198.982963701594</v>
+      </c>
+    </row>
+    <row r="37" spans="3:6" ht="17" customHeight="1">
+      <c r="C37" s="1">
+        <f>Summary_Removals!H30</f>
+        <v>35870.754808756719</v>
+      </c>
+      <c r="E37" s="5">
+        <f t="shared" si="0"/>
+        <v>5273.0009568872374</v>
+      </c>
+      <c r="F37" s="17">
+        <f t="shared" si="1"/>
+        <v>30597.753851869482</v>
+      </c>
+    </row>
+    <row r="38" spans="3:6" ht="17" customHeight="1">
+      <c r="C38" s="1">
+        <f>Summary_Removals!H31</f>
+        <v>34092.145713041056</v>
+      </c>
+      <c r="E38" s="5">
+        <f t="shared" si="0"/>
+        <v>5011.5454198170346</v>
+      </c>
+      <c r="F38" s="17">
+        <f t="shared" si="1"/>
+        <v>29080.600293224023</v>
+      </c>
+    </row>
+    <row r="39" spans="3:6" ht="17" customHeight="1">
+      <c r="C39" s="1">
+        <f>Summary_Removals!H32</f>
+        <v>32406.58152806999</v>
+      </c>
+      <c r="E39" s="5">
+        <f t="shared" si="0"/>
+        <v>4763.767484626288</v>
+      </c>
+      <c r="F39" s="17">
+        <f t="shared" si="1"/>
+        <v>27642.814043443701</v>
+      </c>
+    </row>
+    <row r="40" spans="3:6" ht="17" customHeight="1">
+      <c r="C40" s="1">
+        <f>Summary_Removals!H33</f>
+        <v>30808.883904145074</v>
+      </c>
+      <c r="E40" s="5">
+        <f t="shared" si="0"/>
+        <v>4528.9059339093255</v>
+      </c>
+      <c r="F40" s="17">
+        <f t="shared" si="1"/>
+        <v>26279.977970235748</v>
+      </c>
+    </row>
+    <row r="41" spans="3:6" ht="17" customHeight="1">
+      <c r="C41" s="1">
+        <f>Summary_Removals!H34</f>
+        <v>29294.188513732159</v>
+      </c>
+      <c r="E41" s="5">
+        <f t="shared" si="0"/>
+        <v>4306.2457115186271</v>
+      </c>
+      <c r="F41" s="17">
+        <f t="shared" si="1"/>
+        <v>24987.942802213533</v>
+      </c>
+    </row>
+    <row r="42" spans="3:6" ht="17" customHeight="1">
+      <c r="C42" s="1">
+        <f>Summary_Removals!H35</f>
+        <v>27857.922060236546</v>
+      </c>
+      <c r="E42" s="5">
+        <f t="shared" si="0"/>
+        <v>4095.114542854772</v>
+      </c>
+      <c r="F42" s="17">
+        <f t="shared" si="1"/>
+        <v>23762.807517381774</v>
+      </c>
+    </row>
+    <row r="43" spans="3:6" ht="17" customHeight="1">
+      <c r="C43" s="1">
+        <f>Summary_Removals!H36</f>
+        <v>26495.782152554246</v>
+      </c>
+      <c r="E43" s="5">
+        <f t="shared" si="0"/>
+        <v>3894.8799764254741</v>
+      </c>
+      <c r="F43" s="17">
+        <f t="shared" si="1"/>
+        <v>22600.902176128773</v>
+      </c>
+    </row>
+    <row r="44" spans="3:6" ht="17" customHeight="1">
+      <c r="C44" s="1">
+        <f>Summary_Removals!H37</f>
+        <v>25203.719256242061</v>
+      </c>
+      <c r="E44" s="5">
+        <f t="shared" si="0"/>
+        <v>3704.9467306675829</v>
+      </c>
+      <c r="F44" s="17">
+        <f t="shared" si="1"/>
+        <v>21498.772525574477</v>
+      </c>
+    </row>
+    <row r="45" spans="3:6" ht="17" customHeight="1">
+      <c r="C45" s="1">
+        <f>Summary_Removals!H38</f>
+        <v>23977.920259800765</v>
+      </c>
+      <c r="E45" s="5">
+        <f t="shared" si="0"/>
+        <v>3524.7542781907123</v>
+      </c>
+      <c r="F45" s="17">
+        <f t="shared" si="1"/>
+        <v>20453.165981610051</v>
+      </c>
+    </row>
+    <row r="46" spans="3:6" ht="17" customHeight="1">
+      <c r="C46" s="1">
+        <f>Summary_Removals!H39</f>
+        <v>22814.793371703556</v>
+      </c>
+      <c r="E46" s="5">
+        <f t="shared" si="0"/>
+        <v>3353.7746256404225</v>
+      </c>
+      <c r="F46" s="17">
+        <f t="shared" si="1"/>
+        <v>19461.018746063135</v>
+      </c>
+    </row>
+    <row r="47" spans="3:6" ht="17" customHeight="1">
+      <c r="C47" s="1">
+        <f>Summary_Removals!H40</f>
+        <v>21710.954160741589</v>
+      </c>
+      <c r="E47" s="5">
+        <f t="shared" si="0"/>
+        <v>3191.5102616290133</v>
+      </c>
+      <c r="F47" s="17">
+        <f t="shared" si="1"/>
+        <v>18519.443899112575</v>
+      </c>
+    </row>
+    <row r="48" spans="3:6" ht="17" customHeight="1">
+      <c r="C48" s="1">
+        <f>Summary_Removals!H41</f>
+        <v>20663.212606998179</v>
+      </c>
+      <c r="E48" s="5">
+        <f t="shared" si="0"/>
+        <v>3037.4922532287319</v>
+      </c>
+      <c r="F48" s="17">
+        <f t="shared" si="1"/>
+        <v>17625.720353769448</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6" ht="17" customHeight="1">
+      <c r="C49" s="1">
+        <f>Summary_Removals!H42</f>
+        <v>19668.561062386794</v>
+      </c>
+      <c r="E49" s="5">
+        <f t="shared" si="0"/>
+        <v>2891.2784761708585</v>
+      </c>
+      <c r="F49" s="17">
+        <f t="shared" si="1"/>
+        <v>16777.282586215937</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6" ht="17" customHeight="1">
+      <c r="C50" s="1">
+        <f>Summary_Removals!H43</f>
+        <v>18724.163039163599</v>
+      </c>
+      <c r="E50" s="5">
+        <f t="shared" si="0"/>
+        <v>2752.4519667570489</v>
+      </c>
+      <c r="F50" s="17">
+        <f t="shared" si="1"/>
+        <v>15971.71107240655</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" ht="17" customHeight="1">
+      <c r="C51" s="1">
+        <f>Summary_Removals!H44</f>
+        <v>17827.342757527626</v>
+      </c>
+      <c r="E51" s="5">
+        <f t="shared" si="0"/>
+        <v>2620.619385356561</v>
+      </c>
+      <c r="F51" s="17">
+        <f t="shared" si="1"/>
+        <v>15206.723372171065</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6" ht="17" customHeight="1">
+      <c r="C52" s="1">
+        <f>Summary_Removals!H45</f>
+        <v>16975.57539212154</v>
+      </c>
+      <c r="E52" s="5">
+        <f t="shared" si="0"/>
+        <v>2495.4095826418661</v>
+      </c>
+      <c r="F52" s="17">
+        <f t="shared" si="1"/>
+        <v>14480.165809479673</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6" ht="17" customHeight="1">
+      <c r="C53" s="1"/>
+      <c r="F53" s="8"/>
+    </row>
+    <row r="54" spans="2:6" ht="17" customHeight="1">
+      <c r="B54" t="s">
+        <v>12</v>
+      </c>
+      <c r="C54" s="1">
+        <f>Summary_Removals!H47</f>
+        <v>3534761.8700217889</v>
+      </c>
+      <c r="F54" s="17">
+        <f>SUM(F13:F52)</f>
+        <v>3015151.8751285886</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{258BD82D-8F9B-5F46-AD70-FA0AE846534B}"/>
+    <hyperlink ref="G6" r:id="rId2" xr:uid="{0413F7C2-1ABA-4F46-A5A1-A00149A95BCA}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3DABBA3-596E-B946-9E4A-D51BBBAF87D8}">
   <dimension ref="A3:H50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -10199,7 +11739,7 @@
   <sheetData>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G3" s="11">
         <v>0.5</v>
@@ -11384,7 +12924,7 @@
         <v>4725.8678523779299</v>
       </c>
       <c r="H45" s="1">
-        <f t="shared" si="0"/>
+        <f>SUM(B45:F45)*$G$3</f>
         <v>16975.57539212154</v>
       </c>
     </row>
@@ -11427,7 +12967,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8796C41C-1BC9-EA45-B875-C5F0B93D7AE5}">
   <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -11519,7 +13059,7 @@
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -12694,7 +14234,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9AB2BFC-0ECB-3141-9EA5-B06B472A45A9}">
   <dimension ref="A1:L51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="15.33203125" defaultRowHeight="16"/>
@@ -14549,7 +16089,7 @@
       <c r="I44" s="6"/>
       <c r="J44" s="6"/>
       <c r="K44" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L44" s="1">
         <f>SUM(B3:K42)</f>
@@ -14564,7 +16104,7 @@
       <c r="I45" s="6"/>
       <c r="J45" s="6"/>
       <c r="K45" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L45" s="1">
         <f>L44/40</f>
@@ -14585,7 +16125,7 @@
       <c r="I47" s="6"/>
       <c r="J47" s="6"/>
       <c r="K47" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L47" s="5">
         <f>SUM(L3:L12)</f>
@@ -14597,7 +16137,7 @@
       <c r="I48" s="6"/>
       <c r="J48" s="6"/>
       <c r="K48" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L48" s="5">
         <f>L47/10</f>
@@ -14623,7 +16163,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F4CAE5B-3D09-7B43-B8F9-21D8EE6819FF}">
   <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -14636,25 +16176,25 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="H1" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -15643,7 +17183,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4CF8AA5-7D0F-844D-A4B9-F3670363D091}">
   <dimension ref="A1:P42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="27.83203125" defaultRowHeight="16"/>
@@ -15655,43 +17195,43 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="J1" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="J1" s="9" t="s">
+      <c r="K1" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="L1" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="N1" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -17414,7 +18954,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA3A5171-09C2-EF45-9A29-949687B747C9}">
   <dimension ref="A1:Q43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="26.1640625" defaultRowHeight="16"/>
@@ -17424,62 +18964,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="H1" s="15" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="H1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="C2" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="D2" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="E2" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="F2" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F2" s="9" t="s">
-        <v>36</v>
-      </c>
       <c r="H2" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="J2" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="K2" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="L2" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="M2" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="M2" s="9" t="s">
-        <v>36</v>
-      </c>
       <c r="O2" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -19209,7 +20749,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A50DF0E0-E6D0-CC4C-B19B-7767FC3863D6}">
   <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="26" defaultRowHeight="16"/>
@@ -19219,25 +20759,25 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="F1" s="9" t="s">
-        <v>50</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -20221,649 +21761,6 @@
       <c r="H42" s="1">
         <f t="shared" si="0"/>
         <v>7194.0714315191572</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{736FD4D8-5019-BD44-95E6-DECAB01CDB7E}">
-  <dimension ref="A1:G42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="26.33203125" defaultRowHeight="16"/>
-  <cols>
-    <col min="2" max="16384" width="26.33203125" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>416.71665774793968</v>
-      </c>
-      <c r="B2">
-        <v>416.71616545329988</v>
-      </c>
-      <c r="C2"/>
-      <c r="G2" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>370.64525247623919</v>
-      </c>
-      <c r="B3">
-        <v>416.71616226455973</v>
-      </c>
-      <c r="C3">
-        <v>46.071402082960411</v>
-      </c>
-      <c r="E3" s="1">
-        <f>C3*0.8645*$G$3</f>
-        <v>385462.42088076117</v>
-      </c>
-      <c r="G3" s="3">
-        <v>9678</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>346.47246254458781</v>
-      </c>
-      <c r="B4">
-        <v>416.71615936026672</v>
-      </c>
-      <c r="C4">
-        <v>24.172787027358272</v>
-      </c>
-      <c r="E4" s="1">
-        <f t="shared" ref="E4:E42" si="0">C4*0.8645*$G$3</f>
-        <v>202244.78929949357</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>331.34964403122279</v>
-      </c>
-      <c r="B5">
-        <v>416.71615671504679</v>
-      </c>
-      <c r="C5">
-        <v>15.122815868145191</v>
-      </c>
-      <c r="E5" s="1">
-        <f t="shared" si="0"/>
-        <v>126527.02004971547</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>321.08528742337171</v>
-      </c>
-      <c r="B6">
-        <v>416.71615430578998</v>
-      </c>
-      <c r="C6">
-        <v>10.264354198594329</v>
-      </c>
-      <c r="E6" s="1">
-        <f t="shared" si="0"/>
-        <v>85878.064032939481</v>
-      </c>
-      <c r="G6" s="11"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>313.50616866073352</v>
-      </c>
-      <c r="B7">
-        <v>416.71615211144763</v>
-      </c>
-      <c r="C7">
-        <v>7.5791165682956461</v>
-      </c>
-      <c r="E7" s="1">
-        <f t="shared" si="0"/>
-        <v>63411.671632915975</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>307.47087273556502</v>
-      </c>
-      <c r="B8">
-        <v>416.71615011284831</v>
-      </c>
-      <c r="C8">
-        <v>6.0352939265692376</v>
-      </c>
-      <c r="E8" s="1">
-        <f t="shared" si="0"/>
-        <v>50495.07726014591</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>302.37301704251882</v>
-      </c>
-      <c r="B9">
-        <v>416.71614829253127</v>
-      </c>
-      <c r="C9">
-        <v>5.0978538727292033</v>
-      </c>
-      <c r="E9" s="1">
-        <f t="shared" si="0"/>
-        <v>42651.862245046214</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>297.88609955336739</v>
-      </c>
-      <c r="B10">
-        <v>416.71614663459297</v>
-      </c>
-      <c r="C10">
-        <v>4.486915831213115</v>
-      </c>
-      <c r="E10" s="1">
-        <f t="shared" si="0"/>
-        <v>37540.369087818421</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>293.83091283189532</v>
-      </c>
-      <c r="B11">
-        <v>416.71614512454892</v>
-      </c>
-      <c r="C11">
-        <v>4.0551852114280109</v>
-      </c>
-      <c r="E11" s="1">
-        <f t="shared" si="0"/>
-        <v>33928.238300675148</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>290.10617449125277</v>
-      </c>
-      <c r="B12">
-        <v>416.71614374920608</v>
-      </c>
-      <c r="C12">
-        <v>3.7247369652997548</v>
-      </c>
-      <c r="E12" s="1">
-        <f t="shared" si="0"/>
-        <v>31163.499760722858</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>286.65208112808932</v>
-      </c>
-      <c r="B13">
-        <v>416.71614249654863</v>
-      </c>
-      <c r="C13">
-        <v>3.454092110506068</v>
-      </c>
-      <c r="E13" s="1">
-        <f t="shared" si="0"/>
-        <v>28899.114128615496</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>283.43110517554783</v>
-      </c>
-      <c r="B14">
-        <v>416.7161413556326</v>
-      </c>
-      <c r="C14">
-        <v>3.220974811625434</v>
-      </c>
-      <c r="E14" s="1">
-        <f t="shared" si="0"/>
-        <v>26948.707709164519</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>280.41785186546571</v>
-      </c>
-      <c r="B15">
-        <v>416.71614031649051</v>
-      </c>
-      <c r="C15">
-        <v>3.0132522709399492</v>
-      </c>
-      <c r="E15" s="1">
-        <f t="shared" si="0"/>
-        <v>25210.769860866581</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>277.59368628729248</v>
-      </c>
-      <c r="B16">
-        <v>416.71613937004349</v>
-      </c>
-      <c r="C16">
-        <v>2.8241646317261062</v>
-      </c>
-      <c r="E16" s="1">
-        <f t="shared" si="0"/>
-        <v>23628.743356903222</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>274.94387539537468</v>
-      </c>
-      <c r="B17">
-        <v>416.71613850802282</v>
-      </c>
-      <c r="C17">
-        <v>2.6498100298971732</v>
-      </c>
-      <c r="E17" s="1">
-        <f t="shared" si="0"/>
-        <v>22169.982740248615</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>272.45605761380409</v>
-      </c>
-      <c r="B18">
-        <v>416.71613772289737</v>
-      </c>
-      <c r="C18">
-        <v>2.4878169964452699</v>
-      </c>
-      <c r="E18" s="1">
-        <f t="shared" si="0"/>
-        <v>20814.646804785887</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>270.11941426270602</v>
-      </c>
-      <c r="B19">
-        <v>416.7161370078083</v>
-      </c>
-      <c r="C19">
-        <v>2.3366426360088699</v>
-      </c>
-      <c r="E19" s="1">
-        <f t="shared" si="0"/>
-        <v>19549.826714353527</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>267.92421275815201</v>
-      </c>
-      <c r="B20">
-        <v>416.7161363565076</v>
-      </c>
-      <c r="C20">
-        <v>2.1952008532534442</v>
-      </c>
-      <c r="E20" s="1">
-        <f t="shared" si="0"/>
-        <v>18366.435510056719</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>265.86154739511568</v>
-      </c>
-      <c r="B21">
-        <v>416.71613576330549</v>
-      </c>
-      <c r="C21">
-        <v>2.062664769834166</v>
-      </c>
-      <c r="E21" s="1">
-        <f t="shared" si="0"/>
-        <v>17257.555005902399</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>263.92318570839689</v>
-      </c>
-      <c r="B22">
-        <v>416.71613522301891</v>
-      </c>
-      <c r="C22">
-        <v>1.938361146432124</v>
-      </c>
-      <c r="E22" s="1">
-        <f t="shared" si="0"/>
-        <v>16217.552456934549</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
-        <v>262.10147176210239</v>
-      </c>
-      <c r="B23">
-        <v>416.71613473092748</v>
-      </c>
-      <c r="C23">
-        <v>1.821713454203173</v>
-      </c>
-      <c r="E23" s="1">
-        <f t="shared" si="0"/>
-        <v>15241.604259053349</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
-        <v>260.38926059904128</v>
-      </c>
-      <c r="B24">
-        <v>416.71613428273281</v>
-      </c>
-      <c r="C24">
-        <v>1.7122107148664301</v>
-      </c>
-      <c r="E24" s="1">
-        <f t="shared" si="0"/>
-        <v>14325.435245533636</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
-        <v>258.77987016232822</v>
-      </c>
-      <c r="B25">
-        <v>416.71613387451868</v>
-      </c>
-      <c r="C25">
-        <v>1.6093900284989879</v>
-      </c>
-      <c r="E25" s="1">
-        <f t="shared" si="0"/>
-        <v>13465.172503530517</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
-        <v>257.26704338432597</v>
-      </c>
-      <c r="B26">
-        <v>416.71613350271849</v>
-      </c>
-      <c r="C26">
-        <v>1.51282640620208</v>
-      </c>
-      <c r="E26" s="1">
-        <f t="shared" si="0"/>
-        <v>12657.260307748915</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27">
-        <v>255.8449165137184</v>
-      </c>
-      <c r="B27">
-        <v>416.71613316408428</v>
-      </c>
-      <c r="C27">
-        <v>1.422126531973281</v>
-      </c>
-      <c r="E27" s="1">
-        <f t="shared" si="0"/>
-        <v>11898.407928330145</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28">
-        <v>254.50799153962541</v>
-      </c>
-      <c r="B28">
-        <v>416.71613285565752</v>
-      </c>
-      <c r="C28">
-        <v>1.33692466566617</v>
-      </c>
-      <c r="E28" s="1">
-        <f t="shared" si="0"/>
-        <v>11185.555352427215</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29">
-        <v>253.2511115213355</v>
-      </c>
-      <c r="B29">
-        <v>416.71613257474343</v>
-      </c>
-      <c r="C29">
-        <v>1.25687973737583</v>
-      </c>
-      <c r="E29" s="1">
-        <f t="shared" si="0"/>
-        <v>10515.848974000479</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30">
-        <v>252.06943813880059</v>
-      </c>
-      <c r="B30">
-        <v>416.71613231888767</v>
-      </c>
-      <c r="C30">
-        <v>1.1816731266792999</v>
-      </c>
-      <c r="E30" s="1">
-        <f t="shared" si="0"/>
-        <v>9886.6230135419592</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31">
-        <v>250.95843105120011</v>
-      </c>
-      <c r="B31">
-        <v>416.71613208585552</v>
-      </c>
-      <c r="C31">
-        <v>1.111006854568193</v>
-      </c>
-      <c r="E31" s="1">
-        <f t="shared" si="0"/>
-        <v>9295.3843906427355</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32">
-        <v>249.91382879886589</v>
-      </c>
-      <c r="B32">
-        <v>416.71613187361049</v>
-      </c>
-      <c r="C32">
-        <v>1.0446020400893259</v>
-      </c>
-      <c r="E32" s="1">
-        <f t="shared" si="0"/>
-        <v>8739.7998112745972</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33">
-        <v>248.93163106585661</v>
-      </c>
-      <c r="B33">
-        <v>416.71613168029847</v>
-      </c>
-      <c r="C33">
-        <v>0.9821975396971302</v>
-      </c>
-      <c r="E33" s="1">
-        <f t="shared" si="0"/>
-        <v>8217.6843837537417</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34">
-        <v>248.00808216728711</v>
-      </c>
-      <c r="B34">
-        <v>416.71613150423082</v>
-      </c>
-      <c r="C34">
-        <v>0.92354872250182518</v>
-      </c>
-      <c r="E34" s="1">
-        <f t="shared" si="0"/>
-        <v>7726.9913716941683</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35">
-        <v>247.13965565341729</v>
-      </c>
-      <c r="B35">
-        <v>416.71613134386871</v>
-      </c>
-      <c r="C35">
-        <v>0.86842635350771502</v>
-      </c>
-      <c r="E35" s="1">
-        <f t="shared" si="0"/>
-        <v>7265.802850474608</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36">
-        <v>246.32303994013489</v>
-      </c>
-      <c r="B36">
-        <v>416.71613119781148</v>
-      </c>
-      <c r="C36">
-        <v>0.81661556722526052</v>
-      </c>
-      <c r="E36" s="1">
-        <f t="shared" si="0"/>
-        <v>6832.3211198294493</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37">
-        <v>245.55512488739811</v>
-      </c>
-      <c r="B37">
-        <v>416.71613106478321</v>
-      </c>
-      <c r="C37">
-        <v>0.76791491970848824</v>
-      </c>
-      <c r="E37" s="1">
-        <f t="shared" si="0"/>
-        <v>6424.860772595549</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38">
-        <v>244.83298925591021</v>
-      </c>
-      <c r="B38">
-        <v>416.71613094362141</v>
-      </c>
-      <c r="C38">
-        <v>0.72213551032606915</v>
-      </c>
-      <c r="E38" s="1">
-        <f t="shared" si="0"/>
-        <v>6041.8413468949102</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39">
-        <v>244.15388897907269</v>
-      </c>
-      <c r="B39">
-        <v>416.71613083326798</v>
-      </c>
-      <c r="C39">
-        <v>0.67910016648414739</v>
-      </c>
-      <c r="E39" s="1">
-        <f t="shared" si="0"/>
-        <v>5681.7805050114284</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40">
-        <v>243.51524619283319</v>
-      </c>
-      <c r="B40">
-        <v>416.71613073275819</v>
-      </c>
-      <c r="C40">
-        <v>0.63864268572964511</v>
-      </c>
-      <c r="E40" s="1">
-        <f t="shared" si="0"/>
-        <v>5343.2876923489066</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41">
-        <v>242.91463897081519</v>
-      </c>
-      <c r="B41">
-        <v>416.71613064121448</v>
-      </c>
-      <c r="C41">
-        <v>0.60060713047432535</v>
-      </c>
-      <c r="E41" s="1">
-        <f t="shared" si="0"/>
-        <v>5025.0582366475355</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42">
-        <v>242.3497917162907</v>
-      </c>
-      <c r="B42">
-        <v>416.71613055783672</v>
-      </c>
-      <c r="C42">
-        <v>0.5648471711466575</v>
-      </c>
-      <c r="E42" s="1">
-        <f t="shared" si="0"/>
-        <v>4725.8678523779299</v>
       </c>
     </row>
   </sheetData>

--- a/Realistic_ER_Estimate/ER_Summary.xlsx
+++ b/Realistic_ER_Estimate/ER_Summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mihirbendre/Documents/Gazelle/Gazelle_2026/Kenya_Project/Agricentric_SOC_Modeling/Realistic_ER_Estimate/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A0EA635-2DE3-324F-B881-BA751044D350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61969A8D-DE1D-3A47-80C7-253CB108BDC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{72AD1D35-862B-EB40-AF7A-21135E5EFD45}"/>
   </bookViews>
@@ -50,7 +50,7 @@
     <author>tc={51D8FB6B-0583-8244-BA62-9F39A23EDA91}</author>
   </authors>
   <commentList>
-    <comment ref="C11" authorId="0" shapeId="0" xr:uid="{51D8FB6B-0583-8244-BA62-9F39A23EDA91}">
+    <comment ref="C9" authorId="0" shapeId="0" xr:uid="{51D8FB6B-0583-8244-BA62-9F39A23EDA91}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
   <si>
     <t>Nth</t>
   </si>
@@ -331,13 +331,16 @@
     <t>Net Summary Removals (tCO2e)</t>
   </si>
   <si>
-    <t>Net ERRs after subtracting biochar</t>
-  </si>
-  <si>
     <t>(compost's contribution to removals)</t>
   </si>
   <si>
     <t>ERRs after applying adoption rate</t>
+  </si>
+  <si>
+    <t>https://github.com/mihirobendre/Agricentric_SOC_Modeling/blob/main/References/Biochar_Compost_ER_Adjustment/HYGROW%20%20%E2%80%93%20TECHNICAL%20SHEET.pdf</t>
+  </si>
+  <si>
+    <t>Net ERRs after subtracting biochar (tCO2e)</t>
   </si>
 </sst>
 </file>
@@ -347,7 +350,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -414,12 +417,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -429,7 +426,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -461,13 +458,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -485,12 +491,6 @@
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -505,6 +505,16 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7924,10 +7934,10 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="C11" dT="2026-06-25T23:42:14.87" personId="{8218466F-29F2-9E46-91A3-668DA1A57351}" id="{51D8FB6B-0583-8244-BA62-9F39A23EDA91}">
+  <threadedComment ref="C9" dT="2026-06-25T23:42:14.87" personId="{8218466F-29F2-9E46-91A3-668DA1A57351}" id="{51D8FB6B-0583-8244-BA62-9F39A23EDA91}">
     <text>At this stage the ERRs are mostly coming from soil carbon sequestration, from organic fertilizer addition.</text>
   </threadedComment>
-  <threadedComment ref="C11" dT="2026-06-25T23:44:19.48" personId="{8218466F-29F2-9E46-91A3-668DA1A57351}" id="{24AEF77C-7D5D-154B-8BEF-C9A219B02913}" parentId="{51D8FB6B-0583-8244-BA62-9F39A23EDA91}">
+  <threadedComment ref="C9" dT="2026-06-25T23:44:19.48" personId="{8218466F-29F2-9E46-91A3-668DA1A57351}" id="{24AEF77C-7D5D-154B-8BEF-C9A219B02913}" parentId="{51D8FB6B-0583-8244-BA62-9F39A23EDA91}">
     <text>These ERRs are coming from maintaining SOC at current levels, not increasing from current levels.</text>
   </threadedComment>
 </ThreadedComments>
@@ -7953,20 +7963,20 @@
         <v>64</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="I1" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="I1" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="21"/>
+      <c r="P1" s="21"/>
+      <c r="Q1" s="21"/>
+      <c r="R1" s="21"/>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" t="s">
@@ -8017,7 +8027,7 @@
         <v>2026</v>
       </c>
       <c r="B3" s="1">
-        <f>Subtracting_Biochar_Removals!F13</f>
+        <f>Subtracting_Biochar_Removals!F11</f>
         <v>700399.51158073905</v>
       </c>
       <c r="C3" s="1">
@@ -8029,7 +8039,7 @@
         <v>700882.99455373909</v>
       </c>
       <c r="F3" s="5"/>
-      <c r="G3" s="17">
+      <c r="G3" s="15">
         <f>SUM(I3:R3)</f>
         <v>70088.299455373912</v>
       </c>
@@ -8043,7 +8053,7 @@
         <v>2027</v>
       </c>
       <c r="B4" s="1">
-        <f>Subtracting_Biochar_Removals!F14</f>
+        <f>Subtracting_Biochar_Removals!F12</f>
         <v>374141.82765704329</v>
       </c>
       <c r="C4" s="1">
@@ -8055,7 +8065,7 @@
         <v>374625.31063004327</v>
       </c>
       <c r="F4" s="5"/>
-      <c r="G4" s="17">
+      <c r="G4" s="15">
         <f>SUM(I4:R4)</f>
         <v>107550.83051837824</v>
       </c>
@@ -8073,7 +8083,7 @@
         <v>2028</v>
       </c>
       <c r="B5" s="1">
-        <f>Subtracting_Biochar_Removals!F15</f>
+        <f>Subtracting_Biochar_Removals!F13</f>
         <v>239302.6780395596</v>
       </c>
       <c r="C5" s="1">
@@ -8085,7 +8095,7 @@
         <v>239786.16101255961</v>
       </c>
       <c r="F5" s="5"/>
-      <c r="G5" s="17">
+      <c r="G5" s="15">
         <f t="shared" ref="G5:G42" si="3">SUM(I5:R5)</f>
         <v>131529.4466196342</v>
       </c>
@@ -8107,7 +8117,7 @@
         <v>2029</v>
       </c>
       <c r="B6" s="1">
-        <f>Subtracting_Biochar_Removals!F16</f>
+        <f>Subtracting_Biochar_Removals!F14</f>
         <v>166855.89668228858</v>
       </c>
       <c r="C6" s="1">
@@ -8119,7 +8129,7 @@
         <v>167339.37965528859</v>
       </c>
       <c r="F6" s="5"/>
-      <c r="G6" s="17">
+      <c r="G6" s="15">
         <f t="shared" si="3"/>
         <v>148263.38458516309</v>
       </c>
@@ -8145,7 +8155,7 @@
         <v>2030</v>
       </c>
       <c r="B7" s="1">
-        <f>Subtracting_Biochar_Removals!F17</f>
+        <f>Subtracting_Biochar_Removals!F15</f>
         <v>126752.02142704456</v>
       </c>
       <c r="C7" s="1">
@@ -8157,7 +8167,7 @@
         <v>127235.50440004456</v>
       </c>
       <c r="F7" s="5"/>
-      <c r="G7" s="17">
+      <c r="G7" s="15">
         <f t="shared" si="3"/>
         <v>160986.93502516754</v>
       </c>
@@ -8187,7 +8197,7 @@
         <v>2031</v>
       </c>
       <c r="B8" s="1">
-        <f>Subtracting_Biochar_Removals!F18</f>
+        <f>Subtracting_Biochar_Removals!F16</f>
         <v>103627.8336069115</v>
       </c>
       <c r="C8" s="1">
@@ -8199,7 +8209,7 @@
         <v>104111.31657991151</v>
       </c>
       <c r="F8" s="5"/>
-      <c r="G8" s="17">
+      <c r="G8" s="15">
         <f t="shared" si="3"/>
         <v>171398.06668315869</v>
       </c>
@@ -8233,7 +8243,7 @@
         <v>2032</v>
       </c>
       <c r="B9" s="1">
-        <f>Subtracting_Biochar_Removals!F19</f>
+        <f>Subtracting_Biochar_Removals!F17</f>
         <v>89516.818732056825</v>
       </c>
       <c r="C9" s="1">
@@ -8245,7 +8255,7 @@
         <v>90000.301705056831</v>
       </c>
       <c r="F9" s="5"/>
-      <c r="G9" s="17">
+      <c r="G9" s="15">
         <f t="shared" si="3"/>
         <v>180398.09685366438</v>
       </c>
@@ -8283,7 +8293,7 @@
         <v>2033</v>
       </c>
       <c r="B10" s="1">
-        <f>Subtracting_Biochar_Removals!F20</f>
+        <f>Subtracting_Biochar_Removals!F18</f>
         <v>80252.064029571586</v>
       </c>
       <c r="C10" s="1">
@@ -8295,7 +8305,7 @@
         <v>80735.547002571591</v>
       </c>
       <c r="F10" s="5"/>
-      <c r="G10" s="17">
+      <c r="G10" s="15">
         <f t="shared" si="3"/>
         <v>188471.65155392152</v>
       </c>
@@ -8337,7 +8347,7 @@
         <v>2034</v>
       </c>
       <c r="B11" s="1">
-        <f>Subtracting_Biochar_Removals!F21</f>
+        <f>Subtracting_Biochar_Removals!F19</f>
         <v>73641.311012701044</v>
       </c>
       <c r="C11" s="1">
@@ -8349,7 +8359,7 @@
         <v>74124.79398570105</v>
       </c>
       <c r="F11" s="5"/>
-      <c r="G11" s="17">
+      <c r="G11" s="15">
         <f t="shared" si="3"/>
         <v>195884.1309524916</v>
       </c>
@@ -8395,7 +8405,7 @@
         <v>2035</v>
       </c>
       <c r="B12" s="1">
-        <f>Subtracting_Biochar_Removals!F22</f>
+        <f>Subtracting_Biochar_Removals!F20</f>
         <v>68525.526364287172</v>
       </c>
       <c r="C12" s="1">
@@ -8407,7 +8417,7 @@
         <v>69009.009337287178</v>
       </c>
       <c r="F12" s="5"/>
-      <c r="G12" s="17">
+      <c r="G12" s="15">
         <f t="shared" si="3"/>
         <v>202785.03188622033</v>
       </c>
@@ -8457,7 +8467,7 @@
         <v>2036</v>
       </c>
       <c r="B13" s="1">
-        <f>Subtracting_Biochar_Removals!F23</f>
+        <f>Subtracting_Biochar_Removals!F21</f>
         <v>64288.519201254952</v>
       </c>
       <c r="C13" s="1">
@@ -8469,7 +8479,7 @@
         <v>64772.002174254951</v>
       </c>
       <c r="F13" s="5"/>
-      <c r="G13" s="17">
+      <c r="G13" s="15">
         <f t="shared" si="3"/>
         <v>139173.93264827193</v>
       </c>
@@ -8519,7 +8529,7 @@
         <v>2037</v>
       </c>
       <c r="B14" s="1">
-        <f>Subtracting_Biochar_Removals!F24</f>
+        <f>Subtracting_Biochar_Removals!F22</f>
         <v>60600.078573607389</v>
       </c>
       <c r="C14" s="1">
@@ -8531,7 +8541,7 @@
         <v>61083.561546607387</v>
       </c>
       <c r="F14" s="5"/>
-      <c r="G14" s="17">
+      <c r="G14" s="15">
         <f t="shared" si="3"/>
         <v>107819.75773992833</v>
       </c>
@@ -8581,7 +8591,7 @@
         <v>2038</v>
       </c>
       <c r="B15" s="1">
-        <f>Subtracting_Biochar_Removals!F25</f>
+        <f>Subtracting_Biochar_Removals!F23</f>
         <v>57280.994216835956</v>
       </c>
       <c r="C15" s="1">
@@ -8593,7 +8603,7 @@
         <v>57764.477189835954</v>
       </c>
       <c r="F15" s="5"/>
-      <c r="G15" s="17">
+      <c r="G15" s="15">
         <f t="shared" si="3"/>
         <v>89617.589357655976</v>
       </c>
@@ -8643,7 +8653,7 @@
         <v>2039</v>
       </c>
       <c r="B16" s="1">
-        <f>Subtracting_Biochar_Removals!F26</f>
+        <f>Subtracting_Biochar_Removals!F24</f>
         <v>54231.987448887776</v>
       </c>
       <c r="C16" s="1">
@@ -8655,7 +8665,7 @@
         <v>54715.470421887774</v>
       </c>
       <c r="F16" s="5"/>
-      <c r="G16" s="17">
+      <c r="G16" s="15">
         <f t="shared" si="3"/>
         <v>78355.198434315884</v>
       </c>
@@ -8705,7 +8715,7 @@
         <v>2040</v>
       </c>
       <c r="B17" s="1">
-        <f>Subtracting_Biochar_Removals!F27</f>
+        <f>Subtracting_Biochar_Removals!F25</f>
         <v>51396.242508003408</v>
       </c>
       <c r="C17" s="1">
@@ -8717,7 +8727,7 @@
         <v>51879.725481003406</v>
       </c>
       <c r="F17" s="5"/>
-      <c r="G17" s="17">
+      <c r="G17" s="15">
         <f t="shared" si="3"/>
         <v>70819.620542411765</v>
       </c>
@@ -8767,7 +8777,7 @@
         <v>2041</v>
       </c>
       <c r="B18" s="1">
-        <f>Subtracting_Biochar_Removals!F28</f>
+        <f>Subtracting_Biochar_Removals!F26</f>
         <v>48739.630604703161</v>
       </c>
       <c r="C18" s="1">
@@ -8779,7 +8789,7 @@
         <v>49223.11357770316</v>
       </c>
       <c r="F18" s="5"/>
-      <c r="G18" s="17">
+      <c r="G18" s="15">
         <f t="shared" si="3"/>
         <v>65330.800242190933</v>
       </c>
@@ -8829,7 +8839,7 @@
         <v>2042</v>
       </c>
       <c r="B19" s="1">
-        <f>Subtracting_Biochar_Removals!F29</f>
+        <f>Subtracting_Biochar_Removals!F27</f>
         <v>46240.259291808317</v>
       </c>
       <c r="C19" s="1">
@@ -8841,7 +8851,7 @@
         <v>46723.742264808316</v>
       </c>
       <c r="F19" s="5"/>
-      <c r="G19" s="17">
+      <c r="G19" s="15">
         <f t="shared" si="3"/>
         <v>61003.14429816608</v>
       </c>
@@ -8891,7 +8901,7 @@
         <v>2043</v>
       </c>
       <c r="B20" s="1">
-        <f>Subtracting_Biochar_Removals!F30</f>
+        <f>Subtracting_Biochar_Removals!F28</f>
         <v>43882.940288832186</v>
       </c>
       <c r="C20" s="1">
@@ -8903,7 +8913,7 @@
         <v>44366.423261832184</v>
       </c>
       <c r="F20" s="5"/>
-      <c r="G20" s="17">
+      <c r="G20" s="15">
         <f t="shared" si="3"/>
         <v>57366.231924092142</v>
       </c>
@@ -8953,7 +8963,7 @@
         <v>2044</v>
       </c>
       <c r="B21" s="1">
-        <f>Subtracting_Biochar_Removals!F31</f>
+        <f>Subtracting_Biochar_Removals!F29</f>
         <v>41656.252985550942</v>
       </c>
       <c r="C21" s="1">
@@ -8965,7 +8975,7 @@
         <v>42139.73595855094</v>
       </c>
       <c r="F21" s="5"/>
-      <c r="G21" s="17">
+      <c r="G21" s="15">
         <f t="shared" si="3"/>
         <v>54167.726121377127</v>
       </c>
@@ -9015,7 +9025,7 @@
         <v>2045</v>
       </c>
       <c r="B22" s="1">
-        <f>Subtracting_Biochar_Removals!F32</f>
+        <f>Subtracting_Biochar_Removals!F30</f>
         <v>39550.978707116083</v>
       </c>
       <c r="C22" s="1">
@@ -9027,7 +9037,7 @@
         <v>40034.461680116081</v>
       </c>
       <c r="F22" s="5"/>
-      <c r="G22" s="17">
+      <c r="G22" s="15">
         <f t="shared" si="3"/>
         <v>51270.271355660014</v>
       </c>
@@ -9077,7 +9087,7 @@
         <v>2046</v>
       </c>
       <c r="B23" s="1">
-        <f>Subtracting_Biochar_Removals!F33</f>
+        <f>Subtracting_Biochar_Removals!F31</f>
         <v>37559.259530672411</v>
       </c>
       <c r="C23" s="1">
@@ -9089,7 +9099,7 @@
         <v>38042.742503672409</v>
       </c>
       <c r="F23" s="5"/>
-      <c r="G23" s="17">
+      <c r="G23" s="15">
         <f t="shared" si="3"/>
         <v>48597.34538860176</v>
       </c>
@@ -9139,7 +9149,7 @@
         <v>2047</v>
       </c>
       <c r="B24" s="1">
-        <f>Subtracting_Biochar_Removals!F34</f>
+        <f>Subtracting_Biochar_Removals!F32</f>
         <v>35674.140622929001</v>
       </c>
       <c r="C24" s="1">
@@ -9151,7 +9161,7 @@
         <v>36157.623595928999</v>
       </c>
       <c r="F24" s="5"/>
-      <c r="G24" s="17">
+      <c r="G24" s="15">
         <f t="shared" si="3"/>
         <v>46104.751593533932</v>
       </c>
@@ -9201,7 +9211,7 @@
         <v>2048</v>
       </c>
       <c r="B25" s="1">
-        <f>Subtracting_Biochar_Removals!F35</f>
+        <f>Subtracting_Biochar_Removals!F33</f>
         <v>33889.316051580361</v>
       </c>
       <c r="C25" s="1">
@@ -9213,7 +9223,7 @@
         <v>34372.799024580359</v>
       </c>
       <c r="F25" s="5"/>
-      <c r="G25" s="17">
+      <c r="G25" s="15">
         <f t="shared" si="3"/>
         <v>43765.583777008374</v>
       </c>
@@ -9263,7 +9273,7 @@
         <v>2049</v>
       </c>
       <c r="B26" s="1">
-        <f>Subtracting_Biochar_Removals!F36</f>
+        <f>Subtracting_Biochar_Removals!F34</f>
         <v>32198.982963701594</v>
       </c>
       <c r="C26" s="1">
@@ -9275,7 +9285,7 @@
         <v>32682.465936701592</v>
       </c>
       <c r="F26" s="5"/>
-      <c r="G26" s="17">
+      <c r="G26" s="15">
         <f t="shared" si="3"/>
         <v>41562.28332848975</v>
       </c>
@@ -9325,7 +9335,7 @@
         <v>2050</v>
       </c>
       <c r="B27" s="1">
-        <f>Subtracting_Biochar_Removals!F37</f>
+        <f>Subtracting_Biochar_Removals!F35</f>
         <v>30597.753851869482</v>
       </c>
       <c r="C27" s="1">
@@ -9337,7 +9347,7 @@
         <v>31081.23682486948</v>
       </c>
       <c r="F27" s="5"/>
-      <c r="G27" s="17">
+      <c r="G27" s="15">
         <f t="shared" si="3"/>
         <v>39482.434462876357</v>
       </c>
@@ -9387,7 +9397,7 @@
         <v>2051</v>
       </c>
       <c r="B28" s="1">
-        <f>Subtracting_Biochar_Removals!F38</f>
+        <f>Subtracting_Biochar_Removals!F36</f>
         <v>29080.600293224023</v>
       </c>
       <c r="C28" s="1">
@@ -9399,7 +9409,7 @@
         <v>29564.083266224021</v>
       </c>
       <c r="F28" s="5"/>
-      <c r="G28" s="17">
+      <c r="G28" s="15">
         <f t="shared" si="3"/>
         <v>37516.531431728443</v>
       </c>
@@ -9449,7 +9459,7 @@
         <v>2052</v>
       </c>
       <c r="B29" s="1">
-        <f>Subtracting_Biochar_Removals!F39</f>
+        <f>Subtracting_Biochar_Removals!F37</f>
         <v>27642.814043443701</v>
       </c>
       <c r="C29" s="1">
@@ -9461,7 +9471,7 @@
         <v>28126.297016443699</v>
       </c>
       <c r="F29" s="5"/>
-      <c r="G29" s="17">
+      <c r="G29" s="15">
         <f t="shared" si="3"/>
         <v>35656.786906891975</v>
       </c>
@@ -9511,7 +9521,7 @@
         <v>2053</v>
       </c>
       <c r="B30" s="1">
-        <f>Subtracting_Biochar_Removals!F40</f>
+        <f>Subtracting_Biochar_Removals!F38</f>
         <v>26279.977970235748</v>
       </c>
       <c r="C30" s="1">
@@ -9523,7 +9533,7 @@
         <v>26763.460943235747</v>
       </c>
       <c r="F30" s="5"/>
-      <c r="G30" s="17">
+      <c r="G30" s="15">
         <f t="shared" si="3"/>
         <v>33896.490675032335</v>
       </c>
@@ -9573,7 +9583,7 @@
         <v>2054</v>
       </c>
       <c r="B31" s="1">
-        <f>Subtracting_Biochar_Removals!F41</f>
+        <f>Subtracting_Biochar_Removals!F39</f>
         <v>24987.942802213533</v>
       </c>
       <c r="C31" s="1">
@@ -9585,7 +9595,7 @@
         <v>25471.425775213531</v>
       </c>
       <c r="F31" s="5"/>
-      <c r="G31" s="17">
+      <c r="G31" s="15">
         <f t="shared" si="3"/>
         <v>32229.659656698594</v>
       </c>
@@ -9635,7 +9645,7 @@
         <v>2055</v>
       </c>
       <c r="B32" s="1">
-        <f>Subtracting_Biochar_Removals!F42</f>
+        <f>Subtracting_Biochar_Removals!F40</f>
         <v>23762.807517381774</v>
       </c>
       <c r="C32" s="1">
@@ -9647,7 +9657,7 @@
         <v>24246.290490381773</v>
       </c>
       <c r="F32" s="5"/>
-      <c r="G32" s="17">
+      <c r="G32" s="15">
         <f t="shared" si="3"/>
         <v>30650.842537725166</v>
       </c>
@@ -9697,7 +9707,7 @@
         <v>2056</v>
       </c>
       <c r="B33" s="1">
-        <f>Subtracting_Biochar_Removals!F43</f>
+        <f>Subtracting_Biochar_Removals!F41</f>
         <v>22600.902176128773</v>
       </c>
       <c r="C33" s="1">
@@ -9709,7 +9719,7 @@
         <v>23084.385149128771</v>
       </c>
       <c r="F33" s="5"/>
-      <c r="G33" s="17">
+      <c r="G33" s="15">
         <f t="shared" si="3"/>
         <v>29155.006802270796</v>
       </c>
@@ -9759,7 +9769,7 @@
         <v>2057</v>
       </c>
       <c r="B34" s="1">
-        <f>Subtracting_Biochar_Removals!F44</f>
+        <f>Subtracting_Biochar_Removals!F42</f>
         <v>21498.772525574477</v>
       </c>
       <c r="C34" s="1">
@@ -9771,7 +9781,7 @@
         <v>21982.255498574475</v>
       </c>
       <c r="F34" s="5"/>
-      <c r="G34" s="17">
+      <c r="G34" s="15">
         <f t="shared" si="3"/>
         <v>27737.469992535349</v>
       </c>
@@ -9821,7 +9831,7 @@
         <v>2058</v>
       </c>
       <c r="B35" s="1">
-        <f>Subtracting_Biochar_Removals!F45</f>
+        <f>Subtracting_Biochar_Removals!F43</f>
         <v>20453.165981610051</v>
       </c>
       <c r="C35" s="1">
@@ -9833,7 +9843,7 @@
         <v>20936.648954610049</v>
       </c>
       <c r="F35" s="5"/>
-      <c r="G35" s="17">
+      <c r="G35" s="15">
         <f t="shared" si="3"/>
         <v>26393.854985538321</v>
       </c>
@@ -9883,7 +9893,7 @@
         <v>2059</v>
       </c>
       <c r="B36" s="1">
-        <f>Subtracting_Biochar_Removals!F46</f>
+        <f>Subtracting_Biochar_Removals!F44</f>
         <v>19461.018746063135</v>
       </c>
       <c r="C36" s="1">
@@ -9895,7 +9905,7 @@
         <v>19944.501719063133</v>
       </c>
       <c r="F36" s="5"/>
-      <c r="G36" s="17">
+      <c r="G36" s="15">
         <f t="shared" si="3"/>
         <v>25120.058563774473</v>
       </c>
@@ -9945,7 +9955,7 @@
         <v>2060</v>
       </c>
       <c r="B37" s="1">
-        <f>Subtracting_Biochar_Removals!F47</f>
+        <f>Subtracting_Biochar_Removals!F45</f>
         <v>18519.443899112575</v>
       </c>
       <c r="C37" s="1">
@@ -9957,7 +9967,7 @@
         <v>19002.926872112574</v>
       </c>
       <c r="F37" s="5"/>
-      <c r="G37" s="17">
+      <c r="G37" s="15">
         <f t="shared" si="3"/>
         <v>23912.227568498784</v>
       </c>
@@ -10007,7 +10017,7 @@
         <v>2061</v>
       </c>
       <c r="B38" s="1">
-        <f>Subtracting_Biochar_Removals!F48</f>
+        <f>Subtracting_Biochar_Removals!F46</f>
         <v>17625.720353769448</v>
       </c>
       <c r="C38" s="1">
@@ -10019,7 +10029,7 @@
         <v>18109.203326769446</v>
       </c>
       <c r="F38" s="5"/>
-      <c r="G38" s="17">
+      <c r="G38" s="15">
         <f t="shared" si="3"/>
         <v>22766.739574553321</v>
       </c>
@@ -10069,7 +10079,7 @@
         <v>2062</v>
       </c>
       <c r="B39" s="1">
-        <f>Subtracting_Biochar_Removals!F49</f>
+        <f>Subtracting_Biochar_Removals!F47</f>
         <v>16777.282586215937</v>
       </c>
       <c r="C39" s="1">
@@ -10081,7 +10091,7 @@
         <v>17260.765559215935</v>
       </c>
       <c r="F39" s="5"/>
-      <c r="G39" s="17">
+      <c r="G39" s="15">
         <f t="shared" si="3"/>
         <v>21680.186428830544</v>
       </c>
@@ -10131,7 +10141,7 @@
         <v>2063</v>
       </c>
       <c r="B40" s="1">
-        <f>Subtracting_Biochar_Removals!F50</f>
+        <f>Subtracting_Biochar_Removals!F48</f>
         <v>15971.71107240655</v>
       </c>
       <c r="C40" s="1">
@@ -10143,7 +10153,7 @@
         <v>16455.194045406548</v>
       </c>
       <c r="F40" s="5"/>
-      <c r="G40" s="17">
+      <c r="G40" s="15">
         <f t="shared" si="3"/>
         <v>20649.359739047624</v>
       </c>
@@ -10193,7 +10203,7 @@
         <v>2064</v>
       </c>
       <c r="B41" s="1">
-        <f>Subtracting_Biochar_Removals!F51</f>
+        <f>Subtracting_Biochar_Removals!F49</f>
         <v>15206.723372171065</v>
       </c>
       <c r="C41" s="1">
@@ -10205,7 +10215,7 @@
         <v>15690.206345171066</v>
       </c>
       <c r="F41" s="5"/>
-      <c r="G41" s="17">
+      <c r="G41" s="15">
         <f t="shared" si="3"/>
         <v>19671.237796043377</v>
       </c>
@@ -10255,7 +10265,7 @@
         <v>2065</v>
       </c>
       <c r="B42" s="1">
-        <f>Subtracting_Biochar_Removals!F52</f>
+        <f>Subtracting_Biochar_Removals!F50</f>
         <v>14480.165809479673</v>
       </c>
       <c r="C42" s="1">
@@ -10267,7 +10277,7 @@
         <v>14963.648782479673</v>
       </c>
       <c r="F42" s="5"/>
-      <c r="G42" s="17">
+      <c r="G42" s="15">
         <f t="shared" si="3"/>
         <v>18742.973625253169</v>
       </c>
@@ -10324,7 +10334,7 @@
         <v>3034491.1940485877</v>
       </c>
       <c r="F44" s="5"/>
-      <c r="G44" s="17">
+      <c r="G44" s="15">
         <f>SUM(G3:G42)</f>
         <v>2957571.9716321761</v>
       </c>
@@ -10988,7 +10998,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF3E4888-FB14-564C-901E-F49C230665D8}">
-  <dimension ref="B1:G54"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="3" max="3" width="24.1640625" customWidth="1"/>
@@ -10998,7 +11008,7 @@
     <col min="7" max="7" width="43.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:7" ht="17" customHeight="1">
+    <row r="1" spans="1:10" ht="17" customHeight="1">
       <c r="C1" s="8" t="s">
         <v>78</v>
       </c>
@@ -11015,699 +11025,704 @@
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="3:7" ht="17" customHeight="1">
-      <c r="C2" s="18" t="s">
+    <row r="2" spans="1:10" ht="17" customHeight="1">
+      <c r="C2" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="17">
         <v>0.5</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="16" t="s">
         <v>71</v>
       </c>
       <c r="F2" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="18" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="3:7" ht="33" customHeight="1">
-      <c r="C3" s="18" t="s">
+    <row r="3" spans="1:10" ht="33" customHeight="1">
+      <c r="C3" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="17">
         <v>0.7</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="16" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="4" spans="3:7" ht="20" customHeight="1">
-      <c r="C4" s="18" t="s">
+      <c r="G3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="20" customHeight="1">
+      <c r="C4" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="17">
         <f>30%*D3</f>
         <v>0.21</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="16" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="5" spans="3:7" ht="35" customHeight="1">
-      <c r="C5" s="18" t="s">
+      <c r="G4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="35" customHeight="1">
+      <c r="C5" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="17">
         <f>70%*D3</f>
         <v>0.48999999999999994</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="16" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="6" spans="3:7" ht="80" customHeight="1">
-      <c r="C6" s="18" t="s">
+      <c r="G5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="80" customHeight="1">
+      <c r="C6" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="G6" s="20" t="s">
+      <c r="G6" s="18" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="7" spans="3:7" ht="48" customHeight="1">
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-    </row>
-    <row r="8" spans="3:7" ht="17" customHeight="1">
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-    </row>
-    <row r="9" spans="3:7" ht="17" customHeight="1">
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-    </row>
-    <row r="10" spans="3:7" ht="17" customHeight="1">
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-    </row>
-    <row r="11" spans="3:7" s="18" customFormat="1" ht="36" customHeight="1">
-      <c r="C11" s="21" t="s">
+    <row r="7" spans="1:10" ht="48" customHeight="1" thickBot="1">
+      <c r="A7" s="23"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="23"/>
+    </row>
+    <row r="8" spans="1:10" ht="17" customHeight="1">
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+    </row>
+    <row r="9" spans="1:10" s="16" customFormat="1" ht="36" customHeight="1">
+      <c r="A9"/>
+      <c r="B9"/>
+      <c r="C9" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="E9" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="F11" s="21" t="s">
+      <c r="F9" s="19" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="17" customHeight="1">
+      <c r="E10" s="20"/>
+      <c r="F10" s="8" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="3:7" ht="17" customHeight="1">
-      <c r="E12" s="22"/>
-      <c r="F12" s="8" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="13" spans="3:7" ht="17" customHeight="1">
-      <c r="C13" s="1">
+    <row r="11" spans="1:10" ht="17" customHeight="1">
+      <c r="C11" s="1">
         <f>Summary_Removals!H6</f>
         <v>821101.42037601292</v>
       </c>
-      <c r="E13" s="5">
-        <f>$D$4*$D$3 * C13</f>
+      <c r="E11" s="5">
+        <f>$D$4*$D$3 * C11</f>
         <v>120701.90879527389</v>
       </c>
-      <c r="F13" s="17">
-        <f>C13-E13</f>
+      <c r="F11" s="15">
+        <f>C11-E11</f>
         <v>700399.51158073905</v>
       </c>
     </row>
-    <row r="14" spans="3:7" ht="17" customHeight="1">
-      <c r="C14" s="1">
+    <row r="12" spans="1:10" ht="17" customHeight="1">
+      <c r="C12" s="1">
         <f>Summary_Removals!H7</f>
         <v>438618.78975034383</v>
       </c>
-      <c r="E14" s="5">
-        <f t="shared" ref="E14:E52" si="0">$D$4*$D$3 * C14</f>
+      <c r="E12" s="5">
+        <f t="shared" ref="E12:E50" si="0">$D$4*$D$3 * C12</f>
         <v>64476.962093300543</v>
       </c>
-      <c r="F14" s="17">
-        <f t="shared" ref="F14:F52" si="1">C14-E14</f>
+      <c r="F12" s="15">
+        <f t="shared" ref="F12:F50" si="1">C12-E12</f>
         <v>374141.82765704329</v>
       </c>
     </row>
-    <row r="15" spans="3:7" ht="17" customHeight="1">
-      <c r="C15" s="1">
+    <row r="13" spans="1:10" ht="17" customHeight="1">
+      <c r="C13" s="1">
         <f>Summary_Removals!H8</f>
         <v>280542.4127075728</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E13" s="5">
         <f t="shared" si="0"/>
         <v>41239.734668013203</v>
       </c>
-      <c r="F15" s="17">
+      <c r="F13" s="15">
         <f t="shared" si="1"/>
         <v>239302.6780395596</v>
       </c>
     </row>
-    <row r="16" spans="3:7" ht="17" customHeight="1">
-      <c r="C16" s="1">
+    <row r="14" spans="1:10" ht="17" customHeight="1">
+      <c r="C14" s="1">
         <f>Summary_Removals!H9</f>
         <v>195610.66434031486</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E14" s="5">
         <f t="shared" si="0"/>
         <v>28754.767658026281</v>
       </c>
-      <c r="F16" s="17">
+      <c r="F14" s="15">
         <f t="shared" si="1"/>
         <v>166855.89668228858</v>
       </c>
     </row>
+    <row r="15" spans="1:10" ht="17" customHeight="1">
+      <c r="C15" s="1">
+        <f>Summary_Removals!H10</f>
+        <v>148595.57025444848</v>
+      </c>
+      <c r="E15" s="5">
+        <f t="shared" si="0"/>
+        <v>21843.548827403927</v>
+      </c>
+      <c r="F15" s="15">
+        <f t="shared" si="1"/>
+        <v>126752.02142704456</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="17" customHeight="1">
+      <c r="C16" s="1">
+        <f>Summary_Removals!H11</f>
+        <v>121486.32310306156</v>
+      </c>
+      <c r="E16" s="5">
+        <f t="shared" si="0"/>
+        <v>17858.489496150047</v>
+      </c>
+      <c r="F16" s="15">
+        <f t="shared" si="1"/>
+        <v>103627.8336069115</v>
+      </c>
+    </row>
     <row r="17" spans="3:6" ht="17" customHeight="1">
       <c r="C17" s="1">
-        <f>Summary_Removals!H10</f>
-        <v>148595.57025444848</v>
+        <f>Summary_Removals!H12</f>
+        <v>104943.51551237612</v>
       </c>
       <c r="E17" s="5">
         <f t="shared" si="0"/>
-        <v>21843.548827403927</v>
-      </c>
-      <c r="F17" s="17">
+        <v>15426.696780319289</v>
+      </c>
+      <c r="F17" s="15">
         <f t="shared" si="1"/>
-        <v>126752.02142704456</v>
+        <v>89516.818732056825</v>
       </c>
     </row>
     <row r="18" spans="3:6" ht="17" customHeight="1">
       <c r="C18" s="1">
-        <f>Summary_Removals!H11</f>
-        <v>121486.32310306156</v>
+        <f>Summary_Removals!H13</f>
+        <v>94082.138369954962</v>
       </c>
       <c r="E18" s="5">
         <f t="shared" si="0"/>
-        <v>17858.489496150047</v>
-      </c>
-      <c r="F18" s="17">
+        <v>13830.074340383379</v>
+      </c>
+      <c r="F18" s="15">
         <f t="shared" si="1"/>
-        <v>103627.8336069115</v>
+        <v>80252.064029571586</v>
       </c>
     </row>
     <row r="19" spans="3:6" ht="17" customHeight="1">
       <c r="C19" s="1">
-        <f>Summary_Removals!H12</f>
-        <v>104943.51551237612</v>
+        <f>Summary_Removals!H14</f>
+        <v>86332.13483317825</v>
       </c>
       <c r="E19" s="5">
         <f t="shared" si="0"/>
-        <v>15426.696780319289</v>
-      </c>
-      <c r="F19" s="17">
+        <v>12690.823820477202</v>
+      </c>
+      <c r="F19" s="15">
         <f t="shared" si="1"/>
-        <v>89516.818732056825</v>
+        <v>73641.311012701044</v>
       </c>
     </row>
     <row r="20" spans="3:6" ht="17" customHeight="1">
       <c r="C20" s="1">
-        <f>Summary_Removals!H13</f>
-        <v>94082.138369954962</v>
+        <f>Summary_Removals!H15</f>
+        <v>80334.731962822014</v>
       </c>
       <c r="E20" s="5">
         <f t="shared" si="0"/>
-        <v>13830.074340383379</v>
-      </c>
-      <c r="F20" s="17">
+        <v>11809.205598534836</v>
+      </c>
+      <c r="F20" s="15">
         <f t="shared" si="1"/>
-        <v>80252.064029571586</v>
+        <v>68525.526364287172</v>
       </c>
     </row>
     <row r="21" spans="3:6" ht="17" customHeight="1">
       <c r="C21" s="1">
-        <f>Summary_Removals!H14</f>
-        <v>86332.13483317825</v>
+        <f>Summary_Removals!H16</f>
+        <v>75367.548887754921</v>
       </c>
       <c r="E21" s="5">
         <f t="shared" si="0"/>
-        <v>12690.823820477202</v>
-      </c>
-      <c r="F21" s="17">
+        <v>11079.029686499973</v>
+      </c>
+      <c r="F21" s="15">
         <f t="shared" si="1"/>
-        <v>73641.311012701044</v>
+        <v>64288.519201254952</v>
       </c>
     </row>
     <row r="22" spans="3:6" ht="17" customHeight="1">
       <c r="C22" s="1">
-        <f>Summary_Removals!H15</f>
-        <v>80334.731962822014</v>
+        <f>Summary_Removals!H17</f>
+        <v>71043.468433302914</v>
       </c>
       <c r="E22" s="5">
         <f t="shared" si="0"/>
-        <v>11809.205598534836</v>
-      </c>
-      <c r="F22" s="17">
+        <v>10443.389859695528</v>
+      </c>
+      <c r="F22" s="15">
         <f t="shared" si="1"/>
-        <v>68525.526364287172</v>
+        <v>60600.078573607389</v>
       </c>
     </row>
     <row r="23" spans="3:6" ht="17" customHeight="1">
       <c r="C23" s="1">
-        <f>Summary_Removals!H16</f>
-        <v>75367.548887754921</v>
+        <f>Summary_Removals!H18</f>
+        <v>67152.396502738513</v>
       </c>
       <c r="E23" s="5">
         <f t="shared" si="0"/>
-        <v>11079.029686499973</v>
-      </c>
-      <c r="F23" s="17">
+        <v>9871.4022859025608</v>
+      </c>
+      <c r="F23" s="15">
         <f t="shared" si="1"/>
-        <v>64288.519201254952</v>
+        <v>57280.994216835956</v>
       </c>
     </row>
     <row r="24" spans="3:6" ht="17" customHeight="1">
       <c r="C24" s="1">
-        <f>Summary_Removals!H17</f>
-        <v>71043.468433302914</v>
+        <f>Summary_Removals!H19</f>
+        <v>63577.945426597624</v>
       </c>
       <c r="E24" s="5">
         <f t="shared" si="0"/>
-        <v>10443.389859695528</v>
-      </c>
-      <c r="F24" s="17">
+        <v>9345.9579777098497</v>
+      </c>
+      <c r="F24" s="15">
         <f t="shared" si="1"/>
-        <v>60600.078573607389</v>
+        <v>54231.987448887776</v>
       </c>
     </row>
     <row r="25" spans="3:6" ht="17" customHeight="1">
       <c r="C25" s="1">
-        <f>Summary_Removals!H18</f>
-        <v>67152.396502738513</v>
+        <f>Summary_Removals!H20</f>
+        <v>60253.508215713257</v>
       </c>
       <c r="E25" s="5">
         <f t="shared" si="0"/>
-        <v>9871.4022859025608</v>
-      </c>
-      <c r="F25" s="17">
+        <v>8857.2657077098484</v>
+      </c>
+      <c r="F25" s="15">
         <f t="shared" si="1"/>
-        <v>57280.994216835956</v>
+        <v>51396.242508003408</v>
       </c>
     </row>
     <row r="26" spans="3:6" ht="17" customHeight="1">
       <c r="C26" s="1">
-        <f>Summary_Removals!H19</f>
-        <v>63577.945426597624</v>
+        <f>Summary_Removals!H21</f>
+        <v>57139.074565888819</v>
       </c>
       <c r="E26" s="5">
         <f t="shared" si="0"/>
-        <v>9345.9579777098497</v>
-      </c>
-      <c r="F26" s="17">
+        <v>8399.443961185656</v>
+      </c>
+      <c r="F26" s="15">
         <f t="shared" si="1"/>
-        <v>54231.987448887776</v>
+        <v>48739.630604703161</v>
       </c>
     </row>
     <row r="27" spans="3:6" ht="17" customHeight="1">
       <c r="C27" s="1">
-        <f>Summary_Removals!H20</f>
-        <v>60253.508215713257</v>
+        <f>Summary_Removals!H22</f>
+        <v>54208.979240103537</v>
       </c>
       <c r="E27" s="5">
         <f t="shared" si="0"/>
-        <v>8857.2657077098484</v>
-      </c>
-      <c r="F27" s="17">
+        <v>7968.7199482952192</v>
+      </c>
+      <c r="F27" s="15">
         <f t="shared" si="1"/>
-        <v>51396.242508003408</v>
+        <v>46240.259291808317</v>
       </c>
     </row>
     <row r="28" spans="3:6" ht="17" customHeight="1">
       <c r="C28" s="1">
-        <f>Summary_Removals!H21</f>
-        <v>57139.074565888819</v>
+        <f>Summary_Removals!H23</f>
+        <v>51445.416516802092</v>
       </c>
       <c r="E28" s="5">
         <f t="shared" si="0"/>
-        <v>8399.443961185656</v>
-      </c>
-      <c r="F28" s="17">
+        <v>7562.4762279699071</v>
+      </c>
+      <c r="F28" s="15">
         <f t="shared" si="1"/>
-        <v>48739.630604703161</v>
+        <v>43882.940288832186</v>
       </c>
     </row>
     <row r="29" spans="3:6" ht="17" customHeight="1">
       <c r="C29" s="1">
-        <f>Summary_Removals!H22</f>
-        <v>54208.979240103537</v>
+        <f>Summary_Removals!H24</f>
+        <v>48834.997638395005</v>
       </c>
       <c r="E29" s="5">
         <f t="shared" si="0"/>
-        <v>7968.7199482952192</v>
-      </c>
-      <c r="F29" s="17">
+        <v>7178.7446528440651</v>
+      </c>
+      <c r="F29" s="15">
         <f t="shared" si="1"/>
-        <v>46240.259291808317</v>
+        <v>41656.252985550942</v>
       </c>
     </row>
     <row r="30" spans="3:6" ht="17" customHeight="1">
       <c r="C30" s="1">
-        <f>Summary_Removals!H23</f>
-        <v>51445.416516802092</v>
+        <f>Summary_Removals!H25</f>
+        <v>46366.915248670673</v>
       </c>
       <c r="E30" s="5">
         <f t="shared" si="0"/>
-        <v>7562.4762279699071</v>
-      </c>
-      <c r="F30" s="17">
+        <v>6815.936541554589</v>
+      </c>
+      <c r="F30" s="15">
         <f t="shared" si="1"/>
-        <v>43882.940288832186</v>
+        <v>39550.978707116083</v>
       </c>
     </row>
     <row r="31" spans="3:6" ht="17" customHeight="1">
       <c r="C31" s="1">
-        <f>Summary_Removals!H24</f>
-        <v>48834.997638395005</v>
+        <f>Summary_Removals!H26</f>
+        <v>44031.957245805876</v>
       </c>
       <c r="E31" s="5">
         <f t="shared" si="0"/>
-        <v>7178.7446528440651</v>
-      </c>
-      <c r="F31" s="17">
+        <v>6472.6977151334631</v>
+      </c>
+      <c r="F31" s="15">
         <f t="shared" si="1"/>
-        <v>41656.252985550942</v>
+        <v>37559.259530672411</v>
       </c>
     </row>
     <row r="32" spans="3:6" ht="17" customHeight="1">
       <c r="C32" s="1">
-        <f>Summary_Removals!H25</f>
-        <v>46366.915248670673</v>
+        <f>Summary_Removals!H27</f>
+        <v>41821.970249623686</v>
       </c>
       <c r="E32" s="5">
         <f t="shared" si="0"/>
-        <v>6815.936541554589</v>
-      </c>
-      <c r="F32" s="17">
+        <v>6147.8296266946818</v>
+      </c>
+      <c r="F32" s="15">
         <f t="shared" si="1"/>
-        <v>39550.978707116083</v>
+        <v>35674.140622929001</v>
       </c>
     </row>
     <row r="33" spans="3:6" ht="17" customHeight="1">
       <c r="C33" s="1">
-        <f>Summary_Removals!H26</f>
-        <v>44031.957245805876</v>
+        <f>Summary_Removals!H28</f>
+        <v>39729.561607948839</v>
       </c>
       <c r="E33" s="5">
         <f t="shared" si="0"/>
-        <v>6472.6977151334631</v>
-      </c>
-      <c r="F33" s="17">
+        <v>5840.2455563684789</v>
+      </c>
+      <c r="F33" s="15">
         <f t="shared" si="1"/>
-        <v>37559.259530672411</v>
+        <v>33889.316051580361</v>
       </c>
     </row>
     <row r="34" spans="3:6" ht="17" customHeight="1">
       <c r="C34" s="1">
-        <f>Summary_Removals!H27</f>
-        <v>41821.970249623686</v>
+        <f>Summary_Removals!H29</f>
+        <v>37747.928445136684</v>
       </c>
       <c r="E34" s="5">
         <f t="shared" si="0"/>
-        <v>6147.8296266946818</v>
-      </c>
-      <c r="F34" s="17">
+        <v>5548.945481435092</v>
+      </c>
+      <c r="F34" s="15">
         <f t="shared" si="1"/>
-        <v>35674.140622929001</v>
+        <v>32198.982963701594</v>
       </c>
     </row>
     <row r="35" spans="3:6" ht="17" customHeight="1">
       <c r="C35" s="1">
-        <f>Summary_Removals!H28</f>
-        <v>39729.561607948839</v>
+        <f>Summary_Removals!H30</f>
+        <v>35870.754808756719</v>
       </c>
       <c r="E35" s="5">
         <f t="shared" si="0"/>
-        <v>5840.2455563684789</v>
-      </c>
-      <c r="F35" s="17">
+        <v>5273.0009568872374</v>
+      </c>
+      <c r="F35" s="15">
         <f t="shared" si="1"/>
-        <v>33889.316051580361</v>
+        <v>30597.753851869482</v>
       </c>
     </row>
     <row r="36" spans="3:6" ht="17" customHeight="1">
       <c r="C36" s="1">
-        <f>Summary_Removals!H29</f>
-        <v>37747.928445136684</v>
+        <f>Summary_Removals!H31</f>
+        <v>34092.145713041056</v>
       </c>
       <c r="E36" s="5">
         <f t="shared" si="0"/>
-        <v>5548.945481435092</v>
-      </c>
-      <c r="F36" s="17">
+        <v>5011.5454198170346</v>
+      </c>
+      <c r="F36" s="15">
         <f t="shared" si="1"/>
-        <v>32198.982963701594</v>
+        <v>29080.600293224023</v>
       </c>
     </row>
     <row r="37" spans="3:6" ht="17" customHeight="1">
       <c r="C37" s="1">
-        <f>Summary_Removals!H30</f>
-        <v>35870.754808756719</v>
+        <f>Summary_Removals!H32</f>
+        <v>32406.58152806999</v>
       </c>
       <c r="E37" s="5">
         <f t="shared" si="0"/>
-        <v>5273.0009568872374</v>
-      </c>
-      <c r="F37" s="17">
+        <v>4763.767484626288</v>
+      </c>
+      <c r="F37" s="15">
         <f t="shared" si="1"/>
-        <v>30597.753851869482</v>
+        <v>27642.814043443701</v>
       </c>
     </row>
     <row r="38" spans="3:6" ht="17" customHeight="1">
       <c r="C38" s="1">
-        <f>Summary_Removals!H31</f>
-        <v>34092.145713041056</v>
+        <f>Summary_Removals!H33</f>
+        <v>30808.883904145074</v>
       </c>
       <c r="E38" s="5">
         <f t="shared" si="0"/>
-        <v>5011.5454198170346</v>
-      </c>
-      <c r="F38" s="17">
+        <v>4528.9059339093255</v>
+      </c>
+      <c r="F38" s="15">
         <f t="shared" si="1"/>
-        <v>29080.600293224023</v>
+        <v>26279.977970235748</v>
       </c>
     </row>
     <row r="39" spans="3:6" ht="17" customHeight="1">
       <c r="C39" s="1">
-        <f>Summary_Removals!H32</f>
-        <v>32406.58152806999</v>
+        <f>Summary_Removals!H34</f>
+        <v>29294.188513732159</v>
       </c>
       <c r="E39" s="5">
         <f t="shared" si="0"/>
-        <v>4763.767484626288</v>
-      </c>
-      <c r="F39" s="17">
+        <v>4306.2457115186271</v>
+      </c>
+      <c r="F39" s="15">
         <f t="shared" si="1"/>
-        <v>27642.814043443701</v>
+        <v>24987.942802213533</v>
       </c>
     </row>
     <row r="40" spans="3:6" ht="17" customHeight="1">
       <c r="C40" s="1">
-        <f>Summary_Removals!H33</f>
-        <v>30808.883904145074</v>
+        <f>Summary_Removals!H35</f>
+        <v>27857.922060236546</v>
       </c>
       <c r="E40" s="5">
         <f t="shared" si="0"/>
-        <v>4528.9059339093255</v>
-      </c>
-      <c r="F40" s="17">
+        <v>4095.114542854772</v>
+      </c>
+      <c r="F40" s="15">
         <f t="shared" si="1"/>
-        <v>26279.977970235748</v>
+        <v>23762.807517381774</v>
       </c>
     </row>
     <row r="41" spans="3:6" ht="17" customHeight="1">
       <c r="C41" s="1">
-        <f>Summary_Removals!H34</f>
-        <v>29294.188513732159</v>
+        <f>Summary_Removals!H36</f>
+        <v>26495.782152554246</v>
       </c>
       <c r="E41" s="5">
         <f t="shared" si="0"/>
-        <v>4306.2457115186271</v>
-      </c>
-      <c r="F41" s="17">
+        <v>3894.8799764254741</v>
+      </c>
+      <c r="F41" s="15">
         <f t="shared" si="1"/>
-        <v>24987.942802213533</v>
+        <v>22600.902176128773</v>
       </c>
     </row>
     <row r="42" spans="3:6" ht="17" customHeight="1">
       <c r="C42" s="1">
-        <f>Summary_Removals!H35</f>
-        <v>27857.922060236546</v>
+        <f>Summary_Removals!H37</f>
+        <v>25203.719256242061</v>
       </c>
       <c r="E42" s="5">
         <f t="shared" si="0"/>
-        <v>4095.114542854772</v>
-      </c>
-      <c r="F42" s="17">
+        <v>3704.9467306675829</v>
+      </c>
+      <c r="F42" s="15">
         <f t="shared" si="1"/>
-        <v>23762.807517381774</v>
+        <v>21498.772525574477</v>
       </c>
     </row>
     <row r="43" spans="3:6" ht="17" customHeight="1">
       <c r="C43" s="1">
-        <f>Summary_Removals!H36</f>
-        <v>26495.782152554246</v>
+        <f>Summary_Removals!H38</f>
+        <v>23977.920259800765</v>
       </c>
       <c r="E43" s="5">
         <f t="shared" si="0"/>
-        <v>3894.8799764254741</v>
-      </c>
-      <c r="F43" s="17">
+        <v>3524.7542781907123</v>
+      </c>
+      <c r="F43" s="15">
         <f t="shared" si="1"/>
-        <v>22600.902176128773</v>
+        <v>20453.165981610051</v>
       </c>
     </row>
     <row r="44" spans="3:6" ht="17" customHeight="1">
       <c r="C44" s="1">
-        <f>Summary_Removals!H37</f>
-        <v>25203.719256242061</v>
+        <f>Summary_Removals!H39</f>
+        <v>22814.793371703556</v>
       </c>
       <c r="E44" s="5">
         <f t="shared" si="0"/>
-        <v>3704.9467306675829</v>
-      </c>
-      <c r="F44" s="17">
+        <v>3353.7746256404225</v>
+      </c>
+      <c r="F44" s="15">
         <f t="shared" si="1"/>
-        <v>21498.772525574477</v>
+        <v>19461.018746063135</v>
       </c>
     </row>
     <row r="45" spans="3:6" ht="17" customHeight="1">
       <c r="C45" s="1">
-        <f>Summary_Removals!H38</f>
-        <v>23977.920259800765</v>
+        <f>Summary_Removals!H40</f>
+        <v>21710.954160741589</v>
       </c>
       <c r="E45" s="5">
         <f t="shared" si="0"/>
-        <v>3524.7542781907123</v>
-      </c>
-      <c r="F45" s="17">
+        <v>3191.5102616290133</v>
+      </c>
+      <c r="F45" s="15">
         <f t="shared" si="1"/>
-        <v>20453.165981610051</v>
+        <v>18519.443899112575</v>
       </c>
     </row>
     <row r="46" spans="3:6" ht="17" customHeight="1">
       <c r="C46" s="1">
-        <f>Summary_Removals!H39</f>
-        <v>22814.793371703556</v>
+        <f>Summary_Removals!H41</f>
+        <v>20663.212606998179</v>
       </c>
       <c r="E46" s="5">
         <f t="shared" si="0"/>
-        <v>3353.7746256404225</v>
-      </c>
-      <c r="F46" s="17">
+        <v>3037.4922532287319</v>
+      </c>
+      <c r="F46" s="15">
         <f t="shared" si="1"/>
-        <v>19461.018746063135</v>
+        <v>17625.720353769448</v>
       </c>
     </row>
     <row r="47" spans="3:6" ht="17" customHeight="1">
       <c r="C47" s="1">
-        <f>Summary_Removals!H40</f>
-        <v>21710.954160741589</v>
+        <f>Summary_Removals!H42</f>
+        <v>19668.561062386794</v>
       </c>
       <c r="E47" s="5">
         <f t="shared" si="0"/>
-        <v>3191.5102616290133</v>
-      </c>
-      <c r="F47" s="17">
+        <v>2891.2784761708585</v>
+      </c>
+      <c r="F47" s="15">
         <f t="shared" si="1"/>
-        <v>18519.443899112575</v>
+        <v>16777.282586215937</v>
       </c>
     </row>
     <row r="48" spans="3:6" ht="17" customHeight="1">
       <c r="C48" s="1">
-        <f>Summary_Removals!H41</f>
-        <v>20663.212606998179</v>
+        <f>Summary_Removals!H43</f>
+        <v>18724.163039163599</v>
       </c>
       <c r="E48" s="5">
         <f t="shared" si="0"/>
-        <v>3037.4922532287319</v>
-      </c>
-      <c r="F48" s="17">
+        <v>2752.4519667570489</v>
+      </c>
+      <c r="F48" s="15">
         <f t="shared" si="1"/>
-        <v>17625.720353769448</v>
+        <v>15971.71107240655</v>
       </c>
     </row>
     <row r="49" spans="2:6" ht="17" customHeight="1">
       <c r="C49" s="1">
-        <f>Summary_Removals!H42</f>
-        <v>19668.561062386794</v>
-      </c>
-      <c r="E49" s="5">
-        <f t="shared" si="0"/>
-        <v>2891.2784761708585</v>
-      </c>
-      <c r="F49" s="17">
-        <f t="shared" si="1"/>
-        <v>16777.282586215937</v>
-      </c>
-    </row>
-    <row r="50" spans="2:6" ht="17" customHeight="1">
-      <c r="C50" s="1">
-        <f>Summary_Removals!H43</f>
-        <v>18724.163039163599</v>
-      </c>
-      <c r="E50" s="5">
-        <f t="shared" si="0"/>
-        <v>2752.4519667570489</v>
-      </c>
-      <c r="F50" s="17">
-        <f t="shared" si="1"/>
-        <v>15971.71107240655</v>
-      </c>
-    </row>
-    <row r="51" spans="2:6" ht="17" customHeight="1">
-      <c r="C51" s="1">
         <f>Summary_Removals!H44</f>
         <v>17827.342757527626</v>
       </c>
-      <c r="E51" s="5">
+      <c r="E49" s="5">
         <f t="shared" si="0"/>
         <v>2620.619385356561</v>
       </c>
-      <c r="F51" s="17">
+      <c r="F49" s="15">
         <f t="shared" si="1"/>
         <v>15206.723372171065</v>
       </c>
     </row>
+    <row r="50" spans="2:6" ht="17" customHeight="1">
+      <c r="B50" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" s="1">
+        <f>Summary_Removals!H45</f>
+        <v>16975.57539212154</v>
+      </c>
+      <c r="E50" s="5">
+        <f t="shared" si="0"/>
+        <v>2495.4095826418661</v>
+      </c>
+      <c r="F50" s="15">
+        <f t="shared" si="1"/>
+        <v>14480.165809479673</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" ht="17" customHeight="1">
+      <c r="C51" s="1"/>
+      <c r="F51" s="8"/>
+    </row>
     <row r="52" spans="2:6" ht="17" customHeight="1">
       <c r="C52" s="1">
-        <f>Summary_Removals!H45</f>
-        <v>16975.57539212154</v>
-      </c>
-      <c r="E52" s="5">
-        <f t="shared" si="0"/>
-        <v>2495.4095826418661</v>
-      </c>
-      <c r="F52" s="17">
-        <f t="shared" si="1"/>
-        <v>14480.165809479673</v>
-      </c>
-    </row>
-    <row r="53" spans="2:6" ht="17" customHeight="1">
-      <c r="C53" s="1"/>
-      <c r="F53" s="8"/>
-    </row>
-    <row r="54" spans="2:6" ht="17" customHeight="1">
-      <c r="B54" t="s">
-        <v>12</v>
-      </c>
-      <c r="C54" s="1">
         <f>Summary_Removals!H47</f>
         <v>3534761.8700217889</v>
       </c>
-      <c r="F54" s="17">
-        <f>SUM(F13:F52)</f>
+      <c r="F52" s="15">
+        <f>SUM(F11:F50)</f>
         <v>3015151.8751285886</v>
       </c>
     </row>
@@ -11822,7 +11837,7 @@
         <v>202244.78929949357</v>
       </c>
       <c r="H7" s="1">
-        <f t="shared" ref="H7:H45" si="0">SUM(B7:F7)*$G$3</f>
+        <f t="shared" ref="H7:H44" si="0">SUM(B7:F7)*$G$3</f>
         <v>438618.78975034383</v>
       </c>
     </row>
@@ -18964,22 +18979,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="H1" s="16" t="s">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="H1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="9" t="s">
